--- a/Outcome/Publish/figure_data/fig2.xlsx
+++ b/Outcome/Publish/figure_data/fig2.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="454">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="460">
   <si>
     <t xml:space="preserve">Shortname</t>
   </si>
@@ -693,537 +693,564 @@
     <t xml:space="preserve">31. Pertussis</t>
   </si>
   <si>
+    <t xml:space="preserve">Enterovirus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32. Enterovirus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33. Leprosy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35. HEV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37. Brucellosis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38. JE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40. Liver fluke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41. Cholera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42. Trichinosis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43. Leishmaniasis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020-2021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6. Syphilis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7. Gonorrhoea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8. Chikungunya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10. Scrub Typhus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13. Genital herpes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14. Leptospirosis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16. Malaria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17. Chancroid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19. Encephalitis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20. Mumps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22. Measles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23. S. suis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24. Shigellosis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25. Typhoid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26. HCV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27. HAV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28. Zika virus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29. Enterovirus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30. Rubella</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31. Paratyphoid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39. JE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40. Filariasis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41. Diphtheria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42. Cholera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-2023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5. Syphilis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6. Chickenpox</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8. Scrub Typhus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10. Leptospirosis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12. Malaria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14. Genital herpes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15. Liver fluke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17. Chikungunya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18. Chancroid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19. Other meningitis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20. Typhoid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21. HCV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22. Encephalitis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23. Mumps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24. Scarlet fever</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25. Zika virus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26. S. suis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27. Measles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28. Shigellosis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29. HAV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30. Pertussis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31. Enterovirus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32. Paratyphoid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33. Rubella</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36. Filariasis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37. Leprosy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39. Cholera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40. JE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7. HBV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9. CA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11. Genital herpes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13. Measles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15. Malaria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16. Scarlet fever</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17. Liver fluke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18. HCV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19. Chancroid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20. Amebiasis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21. Other meningitis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24. Mumps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25. Chikungunya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27. Pertussis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31. Shigellosis</t>
+  </si>
+  <si>
     <t xml:space="preserve">33. HDV</t>
   </si>
   <si>
-    <t xml:space="preserve">35. Diphtheria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36. Brucellosis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37. JE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39. Liver fluke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40. Cholera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41. Trichinosis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42. Leishmaniasis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2020-2021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6. Syphilis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7. Gonorrhoea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8. Chikungunya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10. Scrub Typhus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13. Genital herpes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14. Leptospirosis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16. Malaria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17. Chancroid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19. Encephalitis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20. Mumps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22. Measles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23. S. suis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24. Shigellosis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25. Typhoid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26. HCV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27. HAV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28. Zika virus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31. Liver fluke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37. Brucellosis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38. JE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40. Diphtheria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41. Cholera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022-2023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5. Syphilis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6. Chickenpox</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8. Scrub Typhus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10. Leptospirosis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12. Malaria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14. Genital herpes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15. Liver fluke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17. Chikungunya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18. Chancroid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19. Other meningitis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20. Typhoid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21. HCV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22. Encephalitis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23. Mumps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24. Scarlet fever</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25. Zika virus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26. S. suis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27. Measles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28. Shigellosis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29. HAV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30. Pertussis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31. Paratyphoid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32. Rubella</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36. Leprosy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38. Cholera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39. JE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7. HBV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9. CA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11. Genital herpes</t>
+    <t xml:space="preserve">34. Leprosy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36. Rubella</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37. Cholera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38. Diphtheria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40. Brucellosis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41. JE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">metric_total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4. Leptospirosis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6. Other meningitis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7. Encephalitis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8. Melioidosis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10. Diphtheria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12. HFMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13. Chickenpox</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14. Cholera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15. HCV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17. Measles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18. HAV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19. HDV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20. Leprosy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22. Pertussis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23. Syphilis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24. Trichinosis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25. Paratyphoid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26. Leishmaniasis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27. Chikungunya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28. Genital herpes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29. Shigellosis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5. Other meningitis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8. Diphtheria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9. Melioidosis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10. Cholera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13. HFMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14. Chickenpox</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15. HDV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16. HCV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17. Amebiasis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18. Leprosy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19. Typhoid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20. Pertussis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21. Syphilis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22. Trichinosis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23. Measles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Leptospirosis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4. Encephalitis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6. Melioidosis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8. Malaria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11. S. suis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13. Influenza</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15. Pertussis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18. Trichinosis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19. Cholera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20. HDV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21. Amebiasis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22. Paratyphoid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23. Leprosy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24. Typhoid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25. Measles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28. Brucellosis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29. Genital herpes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30. Shigellosis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31. HAV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5. S. suis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6. Scrub Typhus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7. Melioidosis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8. Other meningitis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9. Encephalitis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10. Malaria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11. Diphtheria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13. Pertussis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15. HBV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16. Cholera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18. Paratyphoid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19. Measles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20. Syphilis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23. Leishmaniasis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25. Brucellosis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26. Genital herpes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27. Shigellosis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28. HDV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31. Typhoid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. Melioidosis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5. Influenza</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6. S. suis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9. Other meningitis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14. Pertussis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15. Chickenpox</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17. HBV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18. Leishmaniasis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20. Paratyphoid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21. Chikungunya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22. Syphilis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23. HCV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24. Brucellosis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25. Genital herpes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26. Shigellosis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27. HDV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30. Trichinosis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Melioidosis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7. Measles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8. Encephalitis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11. Scrub Typhus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12. Pertussis</t>
   </si>
   <si>
     <t xml:space="preserve">14. Malaria</t>
   </si>
   <si>
-    <t xml:space="preserve">15. Scarlet fever</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17. Liver fluke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18. HCV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19. Chancroid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20. Amebiasis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21. Other meningitis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24. Mumps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25. Chikungunya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27. Pertussis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29. Zika virus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30. Shigellosis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33. Leprosy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35. Rubella</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36. Cholera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37. Diphtheria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40. JE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">metric_total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4. Leptospirosis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6. Other meningitis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7. Encephalitis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8. Melioidosis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10. Diphtheria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12. HFMD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13. Chickenpox</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14. Cholera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15. HCV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17. Measles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18. HAV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19. HDV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20. Leprosy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22. Pertussis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23. Syphilis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24. Trichinosis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25. Paratyphoid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26. Leishmaniasis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27. Chikungunya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28. Genital herpes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29. Shigellosis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5. Other meningitis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8. Diphtheria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9. Melioidosis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10. Cholera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13. HFMD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14. Chickenpox</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15. HDV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16. HCV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17. Amebiasis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18. Leprosy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19. Typhoid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20. Pertussis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21. Syphilis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22. Trichinosis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23. Measles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3. Leptospirosis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4. Encephalitis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6. Melioidosis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8. Malaria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11. S. suis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13. Influenza</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15. Pertussis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18. Trichinosis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19. Cholera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20. HDV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21. Amebiasis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22. Paratyphoid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23. Leprosy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24. Typhoid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25. Measles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28. Brucellosis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29. Genital herpes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31. HAV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5. S. suis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6. Scrub Typhus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7. Melioidosis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8. Other meningitis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9. Encephalitis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10. Malaria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11. Diphtheria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13. Pertussis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15. HBV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16. Cholera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18. Paratyphoid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19. Measles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20. Syphilis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23. Leishmaniasis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25. Brucellosis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26. Genital herpes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27. Shigellosis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28. HDV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31. Typhoid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2. Melioidosis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5. Influenza</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6. S. suis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9. Other meningitis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13. Measles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14. Pertussis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15. Chickenpox</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17. HBV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18. Leishmaniasis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20. Paratyphoid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21. Chikungunya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22. Syphilis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23. HCV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24. Brucellosis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25. Genital herpes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26. Shigellosis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27. HDV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30. Trichinosis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3. Melioidosis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7. Measles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8. Encephalitis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11. Scrub Typhus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12. Pertussis</t>
-  </si>
-  <si>
     <t xml:space="preserve">15. Cholera</t>
   </si>
   <si>
@@ -1317,13 +1344,7 @@
     <t xml:space="preserve">15. JE</t>
   </si>
   <si>
-    <t xml:space="preserve">16. Diphtheria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17. HCV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18. Measles</t>
+    <t xml:space="preserve">17. Diphtheria</t>
   </si>
   <si>
     <t xml:space="preserve">21. Brucellosis</t>
@@ -1344,13 +1365,10 @@
     <t xml:space="preserve">5. Dengue fever</t>
   </si>
   <si>
-    <t xml:space="preserve">12. Diphtheria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14. HCV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15. HFMD</t>
+    <t xml:space="preserve">13. Diphtheria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16. HFMD</t>
   </si>
   <si>
     <t xml:space="preserve">18. Amebiasis</t>
@@ -9001,31 +9019,31 @@
     </row>
     <row r="229">
       <c r="A229" t="s">
-        <v>72</v>
+        <v>226</v>
       </c>
       <c r="B229" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="C229" t="s">
         <v>203</v>
       </c>
       <c r="D229" t="n">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="E229" t="n">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="F229" t="n">
-        <v>93</v>
+        <v>243</v>
       </c>
       <c r="G229" t="n">
-        <v>206</v>
+        <v>243</v>
       </c>
       <c r="H229" t="n">
         <v>32</v>
       </c>
       <c r="I229" t="s">
-        <v>172</v>
+        <v>227</v>
       </c>
       <c r="J229" t="n">
         <v>6</v>
@@ -9033,31 +9051,31 @@
     </row>
     <row r="230">
       <c r="A230" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="B230" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="C230" t="s">
         <v>203</v>
       </c>
       <c r="D230" t="n">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="E230" t="n">
-        <v>38</v>
+        <v>113</v>
       </c>
       <c r="F230" t="n">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="G230" t="n">
-        <v>117</v>
+        <v>206</v>
       </c>
       <c r="H230" t="n">
         <v>33</v>
       </c>
       <c r="I230" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="J230" t="n">
         <v>6</v>
@@ -9065,31 +9083,31 @@
     </row>
     <row r="231">
       <c r="A231" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B231" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C231" t="s">
         <v>203</v>
       </c>
       <c r="D231" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E231" t="n">
-        <v>106</v>
+        <v>38</v>
       </c>
       <c r="F231" t="n">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="G231" t="n">
-        <v>174</v>
+        <v>117</v>
       </c>
       <c r="H231" t="n">
         <v>34</v>
       </c>
       <c r="I231" t="s">
-        <v>123</v>
+        <v>199</v>
       </c>
       <c r="J231" t="n">
         <v>6</v>
@@ -9097,31 +9115,31 @@
     </row>
     <row r="232">
       <c r="A232" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="B232" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="C232" t="s">
         <v>203</v>
       </c>
       <c r="D232" t="n">
-        <v>33</v>
+        <v>85</v>
       </c>
       <c r="E232" t="n">
-        <v>24</v>
+        <v>106</v>
       </c>
       <c r="F232" t="n">
-        <v>8</v>
+        <v>68</v>
       </c>
       <c r="G232" t="n">
-        <v>32</v>
+        <v>174</v>
       </c>
       <c r="H232" t="n">
         <v>35</v>
       </c>
       <c r="I232" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="J232" t="n">
         <v>6</v>
@@ -9129,31 +9147,31 @@
     </row>
     <row r="233">
       <c r="A233" t="s">
-        <v>155</v>
+        <v>86</v>
       </c>
       <c r="B233" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C233" t="s">
         <v>203</v>
       </c>
       <c r="D233" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E233" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="F233" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="G233" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="H233" t="n">
         <v>36</v>
       </c>
       <c r="I233" t="s">
-        <v>228</v>
+        <v>87</v>
       </c>
       <c r="J233" t="n">
         <v>6</v>
@@ -9161,7 +9179,7 @@
     </row>
     <row r="234">
       <c r="A234" t="s">
-        <v>229</v>
+        <v>155</v>
       </c>
       <c r="B234" t="s">
         <v>17</v>
@@ -9170,16 +9188,16 @@
         <v>203</v>
       </c>
       <c r="D234" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="E234" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F234" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G234" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="H234" t="n">
         <v>37</v>
@@ -9193,7 +9211,7 @@
     </row>
     <row r="235">
       <c r="A235" t="s">
-        <v>88</v>
+        <v>231</v>
       </c>
       <c r="B235" t="s">
         <v>17</v>
@@ -9202,22 +9220,22 @@
         <v>203</v>
       </c>
       <c r="D235" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E235" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F235" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="G235" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H235" t="n">
         <v>38</v>
       </c>
       <c r="I235" t="s">
-        <v>175</v>
+        <v>232</v>
       </c>
       <c r="J235" t="n">
         <v>6</v>
@@ -9225,31 +9243,31 @@
     </row>
     <row r="236">
       <c r="A236" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="B236" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C236" t="s">
         <v>203</v>
       </c>
       <c r="D236" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E236" t="n">
-        <v>99</v>
+        <v>8</v>
       </c>
       <c r="F236" t="n">
-        <v>104</v>
+        <v>8</v>
       </c>
       <c r="G236" t="n">
-        <v>203</v>
+        <v>16</v>
       </c>
       <c r="H236" t="n">
         <v>39</v>
       </c>
       <c r="I236" t="s">
-        <v>231</v>
+        <v>202</v>
       </c>
       <c r="J236" t="n">
         <v>6</v>
@@ -9257,7 +9275,7 @@
     </row>
     <row r="237">
       <c r="A237" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B237" t="s">
         <v>28</v>
@@ -9269,19 +9287,19 @@
         <v>18</v>
       </c>
       <c r="E237" t="n">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="F237" t="n">
-        <v>6</v>
+        <v>104</v>
       </c>
       <c r="G237" t="n">
-        <v>65</v>
+        <v>203</v>
       </c>
       <c r="H237" t="n">
         <v>40</v>
       </c>
       <c r="I237" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="J237" t="n">
         <v>6</v>
@@ -9289,31 +9307,31 @@
     </row>
     <row r="238">
       <c r="A238" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="B238" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="C238" t="s">
         <v>203</v>
       </c>
       <c r="D238" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E238" t="n">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="F238" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="G238" t="n">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="H238" t="n">
         <v>41</v>
       </c>
       <c r="I238" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="J238" t="n">
         <v>6</v>
@@ -9321,7 +9339,7 @@
     </row>
     <row r="239">
       <c r="A239" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="B239" t="s">
         <v>17</v>
@@ -9330,22 +9348,22 @@
         <v>203</v>
       </c>
       <c r="D239" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="E239" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="F239" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G239" t="n">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="H239" t="n">
         <v>42</v>
       </c>
       <c r="I239" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="J239" t="n">
         <v>6</v>
@@ -9353,63 +9371,63 @@
     </row>
     <row r="240">
       <c r="A240" t="s">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="B240" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C240" t="s">
-        <v>235</v>
+        <v>203</v>
       </c>
       <c r="D240" t="n">
-        <v>357731</v>
+        <v>1</v>
       </c>
       <c r="E240" t="n">
-        <v>541162</v>
+        <v>1</v>
       </c>
       <c r="F240" t="n">
-        <v>532954</v>
+        <v>5</v>
       </c>
       <c r="G240" t="n">
-        <v>1074116</v>
+        <v>6</v>
       </c>
       <c r="H240" t="n">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="I240" t="s">
-        <v>13</v>
+        <v>236</v>
       </c>
       <c r="J240" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="B241" t="s">
         <v>11</v>
       </c>
       <c r="C241" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D241" t="n">
-        <v>135169</v>
+        <v>357731</v>
       </c>
       <c r="E241" t="n">
-        <v>580298</v>
+        <v>541162</v>
       </c>
       <c r="F241" t="n">
-        <v>568287</v>
+        <v>532954</v>
       </c>
       <c r="G241" t="n">
-        <v>1148585</v>
+        <v>1074116</v>
       </c>
       <c r="H241" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I241" t="s">
-        <v>177</v>
+        <v>13</v>
       </c>
       <c r="J241" t="n">
         <v>7</v>
@@ -9417,31 +9435,31 @@
     </row>
     <row r="242">
       <c r="A242" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B242" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C242" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D242" t="n">
-        <v>83136</v>
+        <v>135169</v>
       </c>
       <c r="E242" t="n">
-        <v>218079</v>
+        <v>580298</v>
       </c>
       <c r="F242" t="n">
-        <v>207520</v>
+        <v>568287</v>
       </c>
       <c r="G242" t="n">
-        <v>425599</v>
+        <v>1148585</v>
       </c>
       <c r="H242" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I242" t="s">
-        <v>18</v>
+        <v>177</v>
       </c>
       <c r="J242" t="n">
         <v>7</v>
@@ -9449,31 +9467,31 @@
     </row>
     <row r="243">
       <c r="A243" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B243" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C243" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D243" t="n">
-        <v>53017</v>
+        <v>83136</v>
       </c>
       <c r="E243" t="n">
-        <v>137129</v>
+        <v>218079</v>
       </c>
       <c r="F243" t="n">
-        <v>165837</v>
+        <v>207520</v>
       </c>
       <c r="G243" t="n">
-        <v>302966</v>
+        <v>425599</v>
       </c>
       <c r="H243" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I243" t="s">
-        <v>206</v>
+        <v>18</v>
       </c>
       <c r="J243" t="n">
         <v>7</v>
@@ -9481,31 +9499,31 @@
     </row>
     <row r="244">
       <c r="A244" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="B244" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="C244" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D244" t="n">
-        <v>45469</v>
+        <v>53017</v>
       </c>
       <c r="E244" t="n">
-        <v>107874</v>
+        <v>137129</v>
       </c>
       <c r="F244" t="n">
-        <v>31253</v>
+        <v>165837</v>
       </c>
       <c r="G244" t="n">
-        <v>139127</v>
+        <v>302966</v>
       </c>
       <c r="H244" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I244" t="s">
-        <v>180</v>
+        <v>206</v>
       </c>
       <c r="J244" t="n">
         <v>7</v>
@@ -9513,31 +9531,31 @@
     </row>
     <row r="245">
       <c r="A245" t="s">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="B245" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="C245" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D245" t="n">
-        <v>21616</v>
+        <v>45469</v>
       </c>
       <c r="E245" t="n">
-        <v>16730</v>
+        <v>107874</v>
       </c>
       <c r="F245" t="n">
-        <v>33988</v>
+        <v>31253</v>
       </c>
       <c r="G245" t="n">
-        <v>50718</v>
+        <v>139127</v>
       </c>
       <c r="H245" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I245" t="s">
-        <v>236</v>
+        <v>180</v>
       </c>
       <c r="J245" t="n">
         <v>7</v>
@@ -9545,31 +9563,31 @@
     </row>
     <row r="246">
       <c r="A246" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="B246" t="s">
         <v>33</v>
       </c>
       <c r="C246" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D246" t="n">
-        <v>13172</v>
+        <v>21616</v>
       </c>
       <c r="E246" t="n">
-        <v>19291</v>
+        <v>16730</v>
       </c>
       <c r="F246" t="n">
-        <v>18997</v>
+        <v>33988</v>
       </c>
       <c r="G246" t="n">
-        <v>38288</v>
+        <v>50718</v>
       </c>
       <c r="H246" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I246" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="J246" t="n">
         <v>7</v>
@@ -9577,31 +9595,31 @@
     </row>
     <row r="247">
       <c r="A247" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="B247" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="C247" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D247" t="n">
-        <v>12002</v>
+        <v>13172</v>
       </c>
       <c r="E247" t="n">
-        <v>16701</v>
+        <v>19291</v>
       </c>
       <c r="F247" t="n">
-        <v>2797</v>
+        <v>18997</v>
       </c>
       <c r="G247" t="n">
-        <v>19498</v>
+        <v>38288</v>
       </c>
       <c r="H247" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I247" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="J247" t="n">
         <v>7</v>
@@ -9609,31 +9627,31 @@
     </row>
     <row r="248">
       <c r="A248" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="B248" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="C248" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D248" t="n">
-        <v>11288</v>
+        <v>12002</v>
       </c>
       <c r="E248" t="n">
-        <v>14106</v>
+        <v>16701</v>
       </c>
       <c r="F248" t="n">
-        <v>13410</v>
+        <v>2797</v>
       </c>
       <c r="G248" t="n">
-        <v>27516</v>
+        <v>19498</v>
       </c>
       <c r="H248" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I248" t="s">
-        <v>159</v>
+        <v>240</v>
       </c>
       <c r="J248" t="n">
         <v>7</v>
@@ -9641,31 +9659,31 @@
     </row>
     <row r="249">
       <c r="A249" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B249" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="C249" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D249" t="n">
-        <v>7965</v>
+        <v>11288</v>
       </c>
       <c r="E249" t="n">
-        <v>17778</v>
+        <v>14106</v>
       </c>
       <c r="F249" t="n">
-        <v>14723</v>
+        <v>13410</v>
       </c>
       <c r="G249" t="n">
-        <v>32501</v>
+        <v>27516</v>
       </c>
       <c r="H249" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I249" t="s">
-        <v>239</v>
+        <v>159</v>
       </c>
       <c r="J249" t="n">
         <v>7</v>
@@ -9673,31 +9691,31 @@
     </row>
     <row r="250">
       <c r="A250" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="B250" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="C250" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D250" t="n">
-        <v>6770</v>
+        <v>7965</v>
       </c>
       <c r="E250" t="n">
-        <v>8267</v>
+        <v>17778</v>
       </c>
       <c r="F250" t="n">
-        <v>8068</v>
+        <v>14723</v>
       </c>
       <c r="G250" t="n">
-        <v>16335</v>
+        <v>32501</v>
       </c>
       <c r="H250" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I250" t="s">
-        <v>161</v>
+        <v>241</v>
       </c>
       <c r="J250" t="n">
         <v>7</v>
@@ -9705,31 +9723,31 @@
     </row>
     <row r="251">
       <c r="A251" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B251" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="C251" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D251" t="n">
-        <v>4999</v>
+        <v>6770</v>
       </c>
       <c r="E251" t="n">
-        <v>5520</v>
+        <v>8267</v>
       </c>
       <c r="F251" t="n">
-        <v>7681</v>
+        <v>8068</v>
       </c>
       <c r="G251" t="n">
-        <v>13201</v>
+        <v>16335</v>
       </c>
       <c r="H251" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I251" t="s">
-        <v>186</v>
+        <v>161</v>
       </c>
       <c r="J251" t="n">
         <v>7</v>
@@ -9737,31 +9755,31 @@
     </row>
     <row r="252">
       <c r="A252" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B252" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="C252" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D252" t="n">
-        <v>3160</v>
+        <v>4999</v>
       </c>
       <c r="E252" t="n">
-        <v>4280</v>
+        <v>5520</v>
       </c>
       <c r="F252" t="n">
-        <v>4590</v>
+        <v>7681</v>
       </c>
       <c r="G252" t="n">
-        <v>8870</v>
+        <v>13201</v>
       </c>
       <c r="H252" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I252" t="s">
-        <v>240</v>
+        <v>186</v>
       </c>
       <c r="J252" t="n">
         <v>7</v>
@@ -9769,31 +9787,31 @@
     </row>
     <row r="253">
       <c r="A253" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="B253" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="C253" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D253" t="n">
-        <v>2878</v>
+        <v>3160</v>
       </c>
       <c r="E253" t="n">
-        <v>5046</v>
+        <v>4280</v>
       </c>
       <c r="F253" t="n">
-        <v>8276</v>
+        <v>4590</v>
       </c>
       <c r="G253" t="n">
-        <v>13322</v>
+        <v>8870</v>
       </c>
       <c r="H253" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I253" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="J253" t="n">
         <v>7</v>
@@ -9801,31 +9819,31 @@
     </row>
     <row r="254">
       <c r="A254" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B254" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C254" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D254" t="n">
-        <v>2575</v>
+        <v>2878</v>
       </c>
       <c r="E254" t="n">
-        <v>4022</v>
+        <v>5046</v>
       </c>
       <c r="F254" t="n">
-        <v>2934</v>
+        <v>8276</v>
       </c>
       <c r="G254" t="n">
-        <v>6956</v>
+        <v>13322</v>
       </c>
       <c r="H254" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I254" t="s">
-        <v>105</v>
+        <v>243</v>
       </c>
       <c r="J254" t="n">
         <v>7</v>
@@ -9833,31 +9851,31 @@
     </row>
     <row r="255">
       <c r="A255" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="B255" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="C255" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D255" t="n">
-        <v>2449</v>
+        <v>2575</v>
       </c>
       <c r="E255" t="n">
-        <v>4130</v>
+        <v>4022</v>
       </c>
       <c r="F255" t="n">
-        <v>7812</v>
+        <v>2934</v>
       </c>
       <c r="G255" t="n">
-        <v>11942</v>
+        <v>6956</v>
       </c>
       <c r="H255" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I255" t="s">
-        <v>242</v>
+        <v>105</v>
       </c>
       <c r="J255" t="n">
         <v>7</v>
@@ -9865,31 +9883,31 @@
     </row>
     <row r="256">
       <c r="A256" t="s">
-        <v>70</v>
+        <v>23</v>
       </c>
       <c r="B256" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="C256" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D256" t="n">
-        <v>2072</v>
+        <v>2449</v>
       </c>
       <c r="E256" t="n">
-        <v>2584</v>
+        <v>4130</v>
       </c>
       <c r="F256" t="n">
-        <v>2686</v>
+        <v>7812</v>
       </c>
       <c r="G256" t="n">
-        <v>5270</v>
+        <v>11942</v>
       </c>
       <c r="H256" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I256" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="J256" t="n">
         <v>7</v>
@@ -9897,31 +9915,31 @@
     </row>
     <row r="257">
       <c r="A257" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="B257" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="C257" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D257" t="n">
-        <v>2051</v>
+        <v>2072</v>
       </c>
       <c r="E257" t="n">
-        <v>3132</v>
+        <v>2584</v>
       </c>
       <c r="F257" t="n">
-        <v>2531</v>
+        <v>2686</v>
       </c>
       <c r="G257" t="n">
-        <v>5663</v>
+        <v>5270</v>
       </c>
       <c r="H257" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I257" t="s">
-        <v>108</v>
+        <v>245</v>
       </c>
       <c r="J257" t="n">
         <v>7</v>
@@ -9929,31 +9947,31 @@
     </row>
     <row r="258">
       <c r="A258" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="B258" t="s">
         <v>48</v>
       </c>
       <c r="C258" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D258" t="n">
-        <v>1590</v>
+        <v>2051</v>
       </c>
       <c r="E258" t="n">
-        <v>1798</v>
+        <v>3132</v>
       </c>
       <c r="F258" t="n">
-        <v>1732</v>
+        <v>2531</v>
       </c>
       <c r="G258" t="n">
-        <v>3530</v>
+        <v>5663</v>
       </c>
       <c r="H258" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I258" t="s">
-        <v>244</v>
+        <v>108</v>
       </c>
       <c r="J258" t="n">
         <v>7</v>
@@ -9961,31 +9979,31 @@
     </row>
     <row r="259">
       <c r="A259" t="s">
-        <v>25</v>
+        <v>68</v>
       </c>
       <c r="B259" t="s">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="C259" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D259" t="n">
-        <v>1576</v>
+        <v>1590</v>
       </c>
       <c r="E259" t="n">
-        <v>4592</v>
+        <v>1798</v>
       </c>
       <c r="F259" t="n">
-        <v>1194</v>
+        <v>1732</v>
       </c>
       <c r="G259" t="n">
-        <v>5786</v>
+        <v>3530</v>
       </c>
       <c r="H259" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I259" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="J259" t="n">
         <v>7</v>
@@ -9993,31 +10011,31 @@
     </row>
     <row r="260">
       <c r="A260" t="s">
-        <v>64</v>
+        <v>25</v>
       </c>
       <c r="B260" t="s">
         <v>11</v>
       </c>
       <c r="C260" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D260" t="n">
-        <v>1516</v>
+        <v>1576</v>
       </c>
       <c r="E260" t="n">
-        <v>5461</v>
+        <v>4592</v>
       </c>
       <c r="F260" t="n">
-        <v>1153</v>
+        <v>1194</v>
       </c>
       <c r="G260" t="n">
-        <v>6614</v>
+        <v>5786</v>
       </c>
       <c r="H260" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I260" t="s">
-        <v>140</v>
+        <v>247</v>
       </c>
       <c r="J260" t="n">
         <v>7</v>
@@ -10025,31 +10043,31 @@
     </row>
     <row r="261">
       <c r="A261" t="s">
-        <v>30</v>
+        <v>64</v>
       </c>
       <c r="B261" t="s">
         <v>11</v>
       </c>
       <c r="C261" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D261" t="n">
-        <v>1456</v>
+        <v>1516</v>
       </c>
       <c r="E261" t="n">
-        <v>13170</v>
+        <v>5461</v>
       </c>
       <c r="F261" t="n">
-        <v>679</v>
+        <v>1153</v>
       </c>
       <c r="G261" t="n">
-        <v>13849</v>
+        <v>6614</v>
       </c>
       <c r="H261" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I261" t="s">
-        <v>246</v>
+        <v>140</v>
       </c>
       <c r="J261" t="n">
         <v>7</v>
@@ -10057,31 +10075,31 @@
     </row>
     <row r="262">
       <c r="A262" t="s">
-        <v>149</v>
+        <v>30</v>
       </c>
       <c r="B262" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C262" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D262" t="n">
-        <v>930</v>
+        <v>1456</v>
       </c>
       <c r="E262" t="n">
-        <v>694</v>
+        <v>13170</v>
       </c>
       <c r="F262" t="n">
-        <v>988</v>
+        <v>679</v>
       </c>
       <c r="G262" t="n">
-        <v>1682</v>
+        <v>13849</v>
       </c>
       <c r="H262" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I262" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="J262" t="n">
         <v>7</v>
@@ -10089,31 +10107,31 @@
     </row>
     <row r="263">
       <c r="A263" t="s">
-        <v>41</v>
+        <v>149</v>
       </c>
       <c r="B263" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C263" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D263" t="n">
-        <v>893</v>
+        <v>930</v>
       </c>
       <c r="E263" t="n">
-        <v>2045</v>
+        <v>694</v>
       </c>
       <c r="F263" t="n">
-        <v>602</v>
+        <v>988</v>
       </c>
       <c r="G263" t="n">
-        <v>2647</v>
+        <v>1682</v>
       </c>
       <c r="H263" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I263" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="J263" t="n">
         <v>7</v>
@@ -10121,31 +10139,31 @@
     </row>
     <row r="264">
       <c r="A264" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B264" t="s">
         <v>28</v>
       </c>
       <c r="C264" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D264" t="n">
-        <v>856</v>
+        <v>893</v>
       </c>
       <c r="E264" t="n">
-        <v>2191</v>
+        <v>2045</v>
       </c>
       <c r="F264" t="n">
-        <v>1971</v>
+        <v>602</v>
       </c>
       <c r="G264" t="n">
-        <v>4162</v>
+        <v>2647</v>
       </c>
       <c r="H264" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I264" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="J264" t="n">
         <v>7</v>
@@ -10153,31 +10171,31 @@
     </row>
     <row r="265">
       <c r="A265" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="B265" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C265" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D265" t="n">
-        <v>736</v>
+        <v>856</v>
       </c>
       <c r="E265" t="n">
-        <v>856</v>
+        <v>2191</v>
       </c>
       <c r="F265" t="n">
-        <v>1933</v>
+        <v>1971</v>
       </c>
       <c r="G265" t="n">
-        <v>2789</v>
+        <v>4162</v>
       </c>
       <c r="H265" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I265" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="J265" t="n">
         <v>7</v>
@@ -10185,31 +10203,31 @@
     </row>
     <row r="266">
       <c r="A266" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="B266" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C266" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D266" t="n">
-        <v>608</v>
+        <v>736</v>
       </c>
       <c r="E266" t="n">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="F266" t="n">
-        <v>598</v>
+        <v>1933</v>
       </c>
       <c r="G266" t="n">
-        <v>1453</v>
+        <v>2789</v>
       </c>
       <c r="H266" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I266" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="J266" t="n">
         <v>7</v>
@@ -10217,31 +10235,31 @@
     </row>
     <row r="267">
       <c r="A267" t="s">
-        <v>223</v>
+        <v>62</v>
       </c>
       <c r="B267" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="C267" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D267" t="n">
-        <v>302</v>
+        <v>608</v>
       </c>
       <c r="E267" t="n">
-        <v>273</v>
+        <v>855</v>
       </c>
       <c r="F267" t="n">
-        <v>1008</v>
+        <v>598</v>
       </c>
       <c r="G267" t="n">
-        <v>1281</v>
+        <v>1453</v>
       </c>
       <c r="H267" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I267" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="J267" t="n">
         <v>7</v>
@@ -10249,31 +10267,31 @@
     </row>
     <row r="268">
       <c r="A268" t="s">
-        <v>60</v>
+        <v>223</v>
       </c>
       <c r="B268" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C268" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D268" t="n">
-        <v>170</v>
+        <v>302</v>
       </c>
       <c r="E268" t="n">
-        <v>745</v>
+        <v>273</v>
       </c>
       <c r="F268" t="n">
-        <v>170</v>
+        <v>1008</v>
       </c>
       <c r="G268" t="n">
-        <v>915</v>
+        <v>1281</v>
       </c>
       <c r="H268" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I268" t="s">
-        <v>119</v>
+        <v>254</v>
       </c>
       <c r="J268" t="n">
         <v>7</v>
@@ -10281,31 +10299,31 @@
     </row>
     <row r="269">
       <c r="A269" t="s">
-        <v>66</v>
+        <v>226</v>
       </c>
       <c r="B269" t="s">
         <v>28</v>
       </c>
       <c r="C269" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D269" t="n">
-        <v>144</v>
+        <v>243</v>
       </c>
       <c r="E269" t="n">
-        <v>517</v>
+        <v>114</v>
       </c>
       <c r="F269" t="n">
-        <v>296</v>
+        <v>389</v>
       </c>
       <c r="G269" t="n">
-        <v>813</v>
+        <v>503</v>
       </c>
       <c r="H269" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I269" t="s">
-        <v>120</v>
+        <v>255</v>
       </c>
       <c r="J269" t="n">
         <v>7</v>
@@ -10313,31 +10331,31 @@
     </row>
     <row r="270">
       <c r="A270" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="B270" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="C270" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D270" t="n">
-        <v>104</v>
+        <v>170</v>
       </c>
       <c r="E270" t="n">
-        <v>18</v>
+        <v>745</v>
       </c>
       <c r="F270" t="n">
-        <v>3083</v>
+        <v>170</v>
       </c>
       <c r="G270" t="n">
-        <v>3101</v>
+        <v>915</v>
       </c>
       <c r="H270" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I270" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="J270" t="n">
         <v>7</v>
@@ -10345,31 +10363,31 @@
     </row>
     <row r="271">
       <c r="A271" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="B271" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="C271" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D271" t="n">
-        <v>93</v>
+        <v>144</v>
       </c>
       <c r="E271" t="n">
-        <v>100</v>
+        <v>517</v>
       </c>
       <c r="F271" t="n">
-        <v>71</v>
+        <v>296</v>
       </c>
       <c r="G271" t="n">
-        <v>171</v>
+        <v>813</v>
       </c>
       <c r="H271" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I271" t="s">
-        <v>172</v>
+        <v>257</v>
       </c>
       <c r="J271" t="n">
         <v>7</v>
@@ -10377,31 +10395,31 @@
     </row>
     <row r="272">
       <c r="A272" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B272" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C272" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D272" t="n">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="E272" t="n">
-        <v>87</v>
+        <v>18</v>
       </c>
       <c r="F272" t="n">
-        <v>105</v>
+        <v>3083</v>
       </c>
       <c r="G272" t="n">
-        <v>192</v>
+        <v>3101</v>
       </c>
       <c r="H272" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I272" t="s">
-        <v>226</v>
+        <v>197</v>
       </c>
       <c r="J272" t="n">
         <v>7</v>
@@ -10409,31 +10427,31 @@
     </row>
     <row r="273">
       <c r="A273" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="B273" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="C273" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D273" t="n">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="E273" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="F273" t="n">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="G273" t="n">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H273" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I273" t="s">
-        <v>123</v>
+        <v>228</v>
       </c>
       <c r="J273" t="n">
         <v>7</v>
@@ -10441,31 +10459,31 @@
     </row>
     <row r="274">
       <c r="A274" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="B274" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="C274" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D274" t="n">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="E274" t="n">
-        <v>257</v>
+        <v>87</v>
       </c>
       <c r="F274" t="n">
-        <v>417</v>
+        <v>105</v>
       </c>
       <c r="G274" t="n">
-        <v>674</v>
+        <v>192</v>
       </c>
       <c r="H274" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I274" t="s">
-        <v>85</v>
+        <v>199</v>
       </c>
       <c r="J274" t="n">
         <v>7</v>
@@ -10473,31 +10491,31 @@
     </row>
     <row r="275">
       <c r="A275" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B275" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="C275" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D275" t="n">
-        <v>20</v>
+        <v>68</v>
       </c>
       <c r="E275" t="n">
-        <v>17</v>
+        <v>85</v>
       </c>
       <c r="F275" t="n">
-        <v>3</v>
+        <v>88</v>
       </c>
       <c r="G275" t="n">
-        <v>20</v>
+        <v>173</v>
       </c>
       <c r="H275" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I275" t="s">
-        <v>153</v>
+        <v>229</v>
       </c>
       <c r="J275" t="n">
         <v>7</v>
@@ -10505,31 +10523,31 @@
     </row>
     <row r="276">
       <c r="A276" t="s">
-        <v>155</v>
+        <v>84</v>
       </c>
       <c r="B276" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C276" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D276" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E276" t="n">
-        <v>31</v>
+        <v>257</v>
       </c>
       <c r="F276" t="n">
-        <v>30</v>
+        <v>417</v>
       </c>
       <c r="G276" t="n">
-        <v>61</v>
+        <v>674</v>
       </c>
       <c r="H276" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I276" t="s">
-        <v>254</v>
+        <v>125</v>
       </c>
       <c r="J276" t="n">
         <v>7</v>
@@ -10537,31 +10555,31 @@
     </row>
     <row r="277">
       <c r="A277" t="s">
-        <v>229</v>
+        <v>82</v>
       </c>
       <c r="B277" t="s">
         <v>17</v>
       </c>
       <c r="C277" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D277" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E277" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="F277" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G277" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="H277" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I277" t="s">
-        <v>255</v>
+        <v>126</v>
       </c>
       <c r="J277" t="n">
         <v>7</v>
@@ -10569,31 +10587,31 @@
     </row>
     <row r="278">
       <c r="A278" t="s">
-        <v>88</v>
+        <v>155</v>
       </c>
       <c r="B278" t="s">
         <v>17</v>
       </c>
       <c r="C278" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D278" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E278" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F278" t="n">
-        <v>85</v>
+        <v>30</v>
       </c>
       <c r="G278" t="n">
-        <v>109</v>
+        <v>61</v>
       </c>
       <c r="H278" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I278" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="J278" t="n">
         <v>7</v>
@@ -10601,31 +10619,31 @@
     </row>
     <row r="279">
       <c r="A279" t="s">
-        <v>86</v>
+        <v>231</v>
       </c>
       <c r="B279" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C279" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D279" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E279" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F279" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G279" t="n">
+        <v>36</v>
+      </c>
+      <c r="H279" t="n">
         <v>39</v>
       </c>
-      <c r="H279" t="n">
-        <v>40</v>
-      </c>
       <c r="I279" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="J279" t="n">
         <v>7</v>
@@ -10633,31 +10651,31 @@
     </row>
     <row r="280">
       <c r="A280" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="B280" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C280" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D280" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E280" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F280" t="n">
-        <v>11</v>
+        <v>85</v>
       </c>
       <c r="G280" t="n">
-        <v>29</v>
+        <v>109</v>
       </c>
       <c r="H280" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I280" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="J280" t="n">
         <v>7</v>
@@ -10665,31 +10683,31 @@
     </row>
     <row r="281">
       <c r="A281" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B281" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C281" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D281" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E281" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="F281" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G281" t="n">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="H281" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I281" t="s">
-        <v>234</v>
+        <v>260</v>
       </c>
       <c r="J281" t="n">
         <v>7</v>
@@ -10697,95 +10715,95 @@
     </row>
     <row r="282">
       <c r="A282" t="s">
-        <v>19</v>
+        <v>76</v>
       </c>
       <c r="B282" t="s">
+        <v>28</v>
+      </c>
+      <c r="C282" t="s">
+        <v>237</v>
+      </c>
+      <c r="D282" t="n">
+        <v>6</v>
+      </c>
+      <c r="E282" t="n">
+        <v>18</v>
+      </c>
+      <c r="F282" t="n">
         <v>11</v>
       </c>
-      <c r="C282" t="s">
-        <v>258</v>
-      </c>
-      <c r="D282" t="n">
-        <v>568287</v>
-      </c>
-      <c r="E282" t="n">
-        <v>135169</v>
-      </c>
-      <c r="F282" t="n">
-        <v>1787304</v>
-      </c>
       <c r="G282" t="n">
-        <v>1922473</v>
+        <v>29</v>
       </c>
       <c r="H282" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="I282" t="s">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="J282" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="s">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="B283" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C283" t="s">
-        <v>258</v>
+        <v>237</v>
       </c>
       <c r="D283" t="n">
-        <v>532954</v>
+        <v>5</v>
       </c>
       <c r="E283" t="n">
-        <v>357731</v>
+        <v>1</v>
       </c>
       <c r="F283" t="n">
-        <v>850543</v>
+        <v>2</v>
       </c>
       <c r="G283" t="n">
-        <v>1208274</v>
+        <v>3</v>
       </c>
       <c r="H283" t="n">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="I283" t="s">
-        <v>205</v>
+        <v>236</v>
       </c>
       <c r="J283" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B284" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C284" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D284" t="n">
-        <v>207520</v>
+        <v>568287</v>
       </c>
       <c r="E284" t="n">
-        <v>83136</v>
+        <v>135169</v>
       </c>
       <c r="F284" t="n">
-        <v>162159</v>
+        <v>1787304</v>
       </c>
       <c r="G284" t="n">
-        <v>245295</v>
+        <v>1922473</v>
       </c>
       <c r="H284" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I284" t="s">
-        <v>18</v>
+        <v>204</v>
       </c>
       <c r="J284" t="n">
         <v>8</v>
@@ -10793,31 +10811,31 @@
     </row>
     <row r="285">
       <c r="A285" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="B285" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="C285" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D285" t="n">
-        <v>165837</v>
+        <v>532954</v>
       </c>
       <c r="E285" t="n">
-        <v>53017</v>
+        <v>357731</v>
       </c>
       <c r="F285" t="n">
-        <v>204390</v>
+        <v>898268</v>
       </c>
       <c r="G285" t="n">
-        <v>257407</v>
+        <v>1255999</v>
       </c>
       <c r="H285" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I285" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="J285" t="n">
         <v>8</v>
@@ -10825,31 +10843,31 @@
     </row>
     <row r="286">
       <c r="A286" t="s">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="B286" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="C286" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D286" t="n">
-        <v>33988</v>
+        <v>207520</v>
       </c>
       <c r="E286" t="n">
-        <v>21616</v>
+        <v>83136</v>
       </c>
       <c r="F286" t="n">
-        <v>59307</v>
+        <v>162159</v>
       </c>
       <c r="G286" t="n">
-        <v>80923</v>
+        <v>245295</v>
       </c>
       <c r="H286" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I286" t="s">
-        <v>259</v>
+        <v>18</v>
       </c>
       <c r="J286" t="n">
         <v>8</v>
@@ -10857,31 +10875,31 @@
     </row>
     <row r="287">
       <c r="A287" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="B287" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="C287" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D287" t="n">
-        <v>31253</v>
+        <v>165837</v>
       </c>
       <c r="E287" t="n">
-        <v>45469</v>
+        <v>53017</v>
       </c>
       <c r="F287" t="n">
-        <v>78449</v>
+        <v>204390</v>
       </c>
       <c r="G287" t="n">
-        <v>123918</v>
+        <v>257407</v>
       </c>
       <c r="H287" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I287" t="s">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="J287" t="n">
         <v>8</v>
@@ -10889,31 +10907,31 @@
     </row>
     <row r="288">
       <c r="A288" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="B288" t="s">
         <v>33</v>
       </c>
       <c r="C288" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D288" t="n">
-        <v>18997</v>
+        <v>33988</v>
       </c>
       <c r="E288" t="n">
-        <v>13172</v>
+        <v>21616</v>
       </c>
       <c r="F288" t="n">
-        <v>32679</v>
+        <v>59307</v>
       </c>
       <c r="G288" t="n">
-        <v>45851</v>
+        <v>80923</v>
       </c>
       <c r="H288" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I288" t="s">
-        <v>237</v>
+        <v>263</v>
       </c>
       <c r="J288" t="n">
         <v>8</v>
@@ -10921,31 +10939,31 @@
     </row>
     <row r="289">
       <c r="A289" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="B289" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C289" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D289" t="n">
-        <v>14723</v>
+        <v>31253</v>
       </c>
       <c r="E289" t="n">
-        <v>7965</v>
+        <v>45469</v>
       </c>
       <c r="F289" t="n">
-        <v>18387</v>
+        <v>78449</v>
       </c>
       <c r="G289" t="n">
-        <v>26352</v>
+        <v>123918</v>
       </c>
       <c r="H289" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I289" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="J289" t="n">
         <v>8</v>
@@ -10953,31 +10971,31 @@
     </row>
     <row r="290">
       <c r="A290" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B290" t="s">
         <v>33</v>
       </c>
       <c r="C290" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D290" t="n">
-        <v>13410</v>
+        <v>18997</v>
       </c>
       <c r="E290" t="n">
-        <v>11288</v>
+        <v>13172</v>
       </c>
       <c r="F290" t="n">
-        <v>33973</v>
+        <v>32679</v>
       </c>
       <c r="G290" t="n">
-        <v>45261</v>
+        <v>45851</v>
       </c>
       <c r="H290" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I290" t="s">
-        <v>159</v>
+        <v>239</v>
       </c>
       <c r="J290" t="n">
         <v>8</v>
@@ -10985,31 +11003,31 @@
     </row>
     <row r="291">
       <c r="A291" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B291" t="s">
         <v>17</v>
       </c>
       <c r="C291" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D291" t="n">
-        <v>8276</v>
+        <v>14723</v>
       </c>
       <c r="E291" t="n">
-        <v>2878</v>
+        <v>7965</v>
       </c>
       <c r="F291" t="n">
-        <v>9558</v>
+        <v>18387</v>
       </c>
       <c r="G291" t="n">
-        <v>12436</v>
+        <v>26352</v>
       </c>
       <c r="H291" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I291" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="J291" t="n">
         <v>8</v>
@@ -11017,31 +11035,31 @@
     </row>
     <row r="292">
       <c r="A292" t="s">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="B292" t="s">
         <v>33</v>
       </c>
       <c r="C292" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D292" t="n">
-        <v>8068</v>
+        <v>13410</v>
       </c>
       <c r="E292" t="n">
-        <v>6770</v>
+        <v>11288</v>
       </c>
       <c r="F292" t="n">
-        <v>21299</v>
+        <v>33973</v>
       </c>
       <c r="G292" t="n">
-        <v>28069</v>
+        <v>45261</v>
       </c>
       <c r="H292" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I292" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="J292" t="n">
         <v>8</v>
@@ -11049,31 +11067,31 @@
     </row>
     <row r="293">
       <c r="A293" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="B293" t="s">
         <v>17</v>
       </c>
       <c r="C293" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D293" t="n">
-        <v>7812</v>
+        <v>8276</v>
       </c>
       <c r="E293" t="n">
-        <v>2449</v>
+        <v>2878</v>
       </c>
       <c r="F293" t="n">
-        <v>8024</v>
+        <v>9558</v>
       </c>
       <c r="G293" t="n">
-        <v>10473</v>
+        <v>12436</v>
       </c>
       <c r="H293" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I293" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="J293" t="n">
         <v>8</v>
@@ -11081,31 +11099,31 @@
     </row>
     <row r="294">
       <c r="A294" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B294" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="C294" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D294" t="n">
-        <v>7681</v>
+        <v>8068</v>
       </c>
       <c r="E294" t="n">
-        <v>4999</v>
+        <v>6770</v>
       </c>
       <c r="F294" t="n">
-        <v>8388</v>
+        <v>21299</v>
       </c>
       <c r="G294" t="n">
-        <v>13387</v>
+        <v>28069</v>
       </c>
       <c r="H294" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I294" t="s">
-        <v>210</v>
+        <v>161</v>
       </c>
       <c r="J294" t="n">
         <v>8</v>
@@ -11113,31 +11131,31 @@
     </row>
     <row r="295">
       <c r="A295" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="B295" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="C295" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D295" t="n">
-        <v>4590</v>
+        <v>7812</v>
       </c>
       <c r="E295" t="n">
-        <v>3160</v>
+        <v>2449</v>
       </c>
       <c r="F295" t="n">
-        <v>11561</v>
+        <v>8024</v>
       </c>
       <c r="G295" t="n">
-        <v>14721</v>
+        <v>10473</v>
       </c>
       <c r="H295" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I295" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="J295" t="n">
         <v>8</v>
@@ -11145,31 +11163,31 @@
     </row>
     <row r="296">
       <c r="A296" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="B296" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C296" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D296" t="n">
-        <v>3083</v>
+        <v>7681</v>
       </c>
       <c r="E296" t="n">
-        <v>104</v>
+        <v>4999</v>
       </c>
       <c r="F296" t="n">
-        <v>7424</v>
+        <v>8388</v>
       </c>
       <c r="G296" t="n">
-        <v>7528</v>
+        <v>13387</v>
       </c>
       <c r="H296" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I296" t="s">
-        <v>265</v>
+        <v>210</v>
       </c>
       <c r="J296" t="n">
         <v>8</v>
@@ -11177,31 +11195,31 @@
     </row>
     <row r="297">
       <c r="A297" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="B297" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C297" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D297" t="n">
-        <v>2934</v>
+        <v>4590</v>
       </c>
       <c r="E297" t="n">
-        <v>2575</v>
+        <v>3160</v>
       </c>
       <c r="F297" t="n">
-        <v>4183</v>
+        <v>11561</v>
       </c>
       <c r="G297" t="n">
-        <v>6758</v>
+        <v>14721</v>
       </c>
       <c r="H297" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I297" t="s">
-        <v>46</v>
+        <v>268</v>
       </c>
       <c r="J297" t="n">
         <v>8</v>
@@ -11209,31 +11227,31 @@
     </row>
     <row r="298">
       <c r="A298" t="s">
-        <v>21</v>
+        <v>74</v>
       </c>
       <c r="B298" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="C298" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D298" t="n">
-        <v>2797</v>
+        <v>3083</v>
       </c>
       <c r="E298" t="n">
-        <v>12002</v>
+        <v>104</v>
       </c>
       <c r="F298" t="n">
-        <v>2112</v>
+        <v>7424</v>
       </c>
       <c r="G298" t="n">
-        <v>14114</v>
+        <v>7528</v>
       </c>
       <c r="H298" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I298" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="J298" t="n">
         <v>8</v>
@@ -11241,31 +11259,31 @@
     </row>
     <row r="299">
       <c r="A299" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="B299" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C299" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D299" t="n">
-        <v>2686</v>
+        <v>2934</v>
       </c>
       <c r="E299" t="n">
-        <v>2072</v>
+        <v>2575</v>
       </c>
       <c r="F299" t="n">
-        <v>4902</v>
+        <v>4183</v>
       </c>
       <c r="G299" t="n">
-        <v>6974</v>
+        <v>6758</v>
       </c>
       <c r="H299" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I299" t="s">
-        <v>267</v>
+        <v>46</v>
       </c>
       <c r="J299" t="n">
         <v>8</v>
@@ -11273,31 +11291,31 @@
     </row>
     <row r="300">
       <c r="A300" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="B300" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="C300" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D300" t="n">
-        <v>2531</v>
+        <v>2797</v>
       </c>
       <c r="E300" t="n">
-        <v>2051</v>
+        <v>12002</v>
       </c>
       <c r="F300" t="n">
-        <v>3933</v>
+        <v>2112</v>
       </c>
       <c r="G300" t="n">
-        <v>5984</v>
+        <v>14114</v>
       </c>
       <c r="H300" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I300" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="J300" t="n">
         <v>8</v>
@@ -11305,31 +11323,31 @@
     </row>
     <row r="301">
       <c r="A301" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="B301" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C301" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D301" t="n">
-        <v>1971</v>
+        <v>2686</v>
       </c>
       <c r="E301" t="n">
-        <v>856</v>
+        <v>2072</v>
       </c>
       <c r="F301" t="n">
-        <v>3210</v>
+        <v>4902</v>
       </c>
       <c r="G301" t="n">
-        <v>4066</v>
+        <v>6974</v>
       </c>
       <c r="H301" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I301" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="J301" t="n">
         <v>8</v>
@@ -11337,31 +11355,31 @@
     </row>
     <row r="302">
       <c r="A302" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B302" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="C302" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D302" t="n">
-        <v>1933</v>
+        <v>2531</v>
       </c>
       <c r="E302" t="n">
-        <v>736</v>
+        <v>2051</v>
       </c>
       <c r="F302" t="n">
-        <v>6186</v>
+        <v>3933</v>
       </c>
       <c r="G302" t="n">
-        <v>6922</v>
+        <v>5984</v>
       </c>
       <c r="H302" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I302" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="J302" t="n">
         <v>8</v>
@@ -11369,31 +11387,31 @@
     </row>
     <row r="303">
       <c r="A303" t="s">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="B303" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="C303" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D303" t="n">
-        <v>1732</v>
+        <v>1971</v>
       </c>
       <c r="E303" t="n">
-        <v>1590</v>
+        <v>856</v>
       </c>
       <c r="F303" t="n">
-        <v>2976</v>
+        <v>3210</v>
       </c>
       <c r="G303" t="n">
-        <v>4566</v>
+        <v>4066</v>
       </c>
       <c r="H303" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="I303" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="J303" t="n">
         <v>8</v>
@@ -11401,31 +11419,31 @@
     </row>
     <row r="304">
       <c r="A304" t="s">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="B304" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="C304" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D304" t="n">
-        <v>1194</v>
+        <v>1933</v>
       </c>
       <c r="E304" t="n">
-        <v>1576</v>
+        <v>736</v>
       </c>
       <c r="F304" t="n">
-        <v>2899</v>
+        <v>6186</v>
       </c>
       <c r="G304" t="n">
-        <v>4475</v>
+        <v>6922</v>
       </c>
       <c r="H304" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I304" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="J304" t="n">
         <v>8</v>
@@ -11433,31 +11451,31 @@
     </row>
     <row r="305">
       <c r="A305" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="B305" t="s">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="C305" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D305" t="n">
-        <v>1153</v>
+        <v>1732</v>
       </c>
       <c r="E305" t="n">
-        <v>1516</v>
+        <v>1590</v>
       </c>
       <c r="F305" t="n">
-        <v>7590</v>
+        <v>2976</v>
       </c>
       <c r="G305" t="n">
-        <v>9106</v>
+        <v>4566</v>
       </c>
       <c r="H305" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I305" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="J305" t="n">
         <v>8</v>
@@ -11465,31 +11483,31 @@
     </row>
     <row r="306">
       <c r="A306" t="s">
-        <v>223</v>
+        <v>25</v>
       </c>
       <c r="B306" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C306" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D306" t="n">
-        <v>1008</v>
+        <v>1194</v>
       </c>
       <c r="E306" t="n">
-        <v>302</v>
+        <v>1576</v>
       </c>
       <c r="F306" t="n">
-        <v>675</v>
+        <v>2899</v>
       </c>
       <c r="G306" t="n">
-        <v>977</v>
+        <v>4475</v>
       </c>
       <c r="H306" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I306" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="J306" t="n">
         <v>8</v>
@@ -11497,31 +11515,31 @@
     </row>
     <row r="307">
       <c r="A307" t="s">
-        <v>149</v>
+        <v>64</v>
       </c>
       <c r="B307" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C307" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D307" t="n">
-        <v>988</v>
+        <v>1153</v>
       </c>
       <c r="E307" t="n">
-        <v>930</v>
+        <v>1516</v>
       </c>
       <c r="F307" t="n">
-        <v>1954</v>
+        <v>7590</v>
       </c>
       <c r="G307" t="n">
-        <v>2884</v>
+        <v>9106</v>
       </c>
       <c r="H307" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I307" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="J307" t="n">
         <v>8</v>
@@ -11529,31 +11547,31 @@
     </row>
     <row r="308">
       <c r="A308" t="s">
-        <v>30</v>
+        <v>223</v>
       </c>
       <c r="B308" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C308" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D308" t="n">
-        <v>679</v>
+        <v>1008</v>
       </c>
       <c r="E308" t="n">
-        <v>1456</v>
+        <v>302</v>
       </c>
       <c r="F308" t="n">
-        <v>7445</v>
+        <v>675</v>
       </c>
       <c r="G308" t="n">
-        <v>8901</v>
+        <v>977</v>
       </c>
       <c r="H308" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="I308" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="J308" t="n">
         <v>8</v>
@@ -11561,31 +11579,31 @@
     </row>
     <row r="309">
       <c r="A309" t="s">
-        <v>41</v>
+        <v>149</v>
       </c>
       <c r="B309" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C309" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D309" t="n">
-        <v>602</v>
+        <v>988</v>
       </c>
       <c r="E309" t="n">
-        <v>893</v>
+        <v>930</v>
       </c>
       <c r="F309" t="n">
-        <v>564</v>
+        <v>1954</v>
       </c>
       <c r="G309" t="n">
-        <v>1457</v>
+        <v>2884</v>
       </c>
       <c r="H309" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I309" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="J309" t="n">
         <v>8</v>
@@ -11593,31 +11611,31 @@
     </row>
     <row r="310">
       <c r="A310" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="B310" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="C310" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D310" t="n">
-        <v>598</v>
+        <v>679</v>
       </c>
       <c r="E310" t="n">
-        <v>608</v>
+        <v>1456</v>
       </c>
       <c r="F310" t="n">
-        <v>1167</v>
+        <v>9274</v>
       </c>
       <c r="G310" t="n">
-        <v>1775</v>
+        <v>10730</v>
       </c>
       <c r="H310" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="I310" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J310" t="n">
         <v>8</v>
@@ -11625,31 +11643,31 @@
     </row>
     <row r="311">
       <c r="A311" t="s">
-        <v>84</v>
+        <v>41</v>
       </c>
       <c r="B311" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="C311" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D311" t="n">
-        <v>417</v>
+        <v>602</v>
       </c>
       <c r="E311" t="n">
-        <v>30</v>
+        <v>893</v>
       </c>
       <c r="F311" t="n">
-        <v>1532</v>
+        <v>564</v>
       </c>
       <c r="G311" t="n">
-        <v>1562</v>
+        <v>1457</v>
       </c>
       <c r="H311" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I311" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="J311" t="n">
         <v>8</v>
@@ -11657,31 +11675,31 @@
     </row>
     <row r="312">
       <c r="A312" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B312" t="s">
         <v>28</v>
       </c>
       <c r="C312" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D312" t="n">
-        <v>296</v>
+        <v>598</v>
       </c>
       <c r="E312" t="n">
-        <v>144</v>
+        <v>608</v>
       </c>
       <c r="F312" t="n">
-        <v>356</v>
+        <v>1167</v>
       </c>
       <c r="G312" t="n">
-        <v>500</v>
+        <v>1775</v>
       </c>
       <c r="H312" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I312" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J312" t="n">
         <v>8</v>
@@ -11689,31 +11707,31 @@
     </row>
     <row r="313">
       <c r="A313" t="s">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="B313" t="s">
         <v>11</v>
       </c>
       <c r="C313" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D313" t="n">
-        <v>170</v>
+        <v>417</v>
       </c>
       <c r="E313" t="n">
-        <v>170</v>
+        <v>30</v>
       </c>
       <c r="F313" t="n">
-        <v>103</v>
+        <v>1532</v>
       </c>
       <c r="G313" t="n">
-        <v>273</v>
+        <v>1562</v>
       </c>
       <c r="H313" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I313" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="J313" t="n">
         <v>8</v>
@@ -11721,31 +11739,31 @@
     </row>
     <row r="314">
       <c r="A314" t="s">
-        <v>78</v>
+        <v>226</v>
       </c>
       <c r="B314" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C314" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D314" t="n">
-        <v>105</v>
+        <v>389</v>
       </c>
       <c r="E314" t="n">
-        <v>79</v>
+        <v>243</v>
       </c>
       <c r="F314" t="n">
-        <v>198</v>
+        <v>977</v>
       </c>
       <c r="G314" t="n">
-        <v>277</v>
+        <v>1220</v>
       </c>
       <c r="H314" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I314" t="s">
-        <v>226</v>
+        <v>284</v>
       </c>
       <c r="J314" t="n">
         <v>8</v>
@@ -11753,31 +11771,31 @@
     </row>
     <row r="315">
       <c r="A315" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="B315" t="s">
         <v>28</v>
       </c>
       <c r="C315" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D315" t="n">
-        <v>88</v>
+        <v>296</v>
       </c>
       <c r="E315" t="n">
-        <v>68</v>
+        <v>144</v>
       </c>
       <c r="F315" t="n">
-        <v>157</v>
+        <v>356</v>
       </c>
       <c r="G315" t="n">
-        <v>225</v>
+        <v>500</v>
       </c>
       <c r="H315" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I315" t="s">
-        <v>123</v>
+        <v>285</v>
       </c>
       <c r="J315" t="n">
         <v>8</v>
@@ -11785,31 +11803,31 @@
     </row>
     <row r="316">
       <c r="A316" t="s">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="B316" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C316" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D316" t="n">
-        <v>85</v>
+        <v>170</v>
       </c>
       <c r="E316" t="n">
-        <v>8</v>
+        <v>170</v>
       </c>
       <c r="F316" t="n">
-        <v>18</v>
+        <v>111</v>
       </c>
       <c r="G316" t="n">
-        <v>26</v>
+        <v>281</v>
       </c>
       <c r="H316" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I316" t="s">
-        <v>124</v>
+        <v>286</v>
       </c>
       <c r="J316" t="n">
         <v>8</v>
@@ -11817,31 +11835,31 @@
     </row>
     <row r="317">
       <c r="A317" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="B317" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="C317" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D317" t="n">
-        <v>71</v>
+        <v>105</v>
       </c>
       <c r="E317" t="n">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="F317" t="n">
-        <v>184</v>
+        <v>198</v>
       </c>
       <c r="G317" t="n">
         <v>277</v>
       </c>
       <c r="H317" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I317" t="s">
-        <v>282</v>
+        <v>199</v>
       </c>
       <c r="J317" t="n">
         <v>8</v>
@@ -11849,31 +11867,31 @@
     </row>
     <row r="318">
       <c r="A318" t="s">
-        <v>155</v>
+        <v>80</v>
       </c>
       <c r="B318" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="C318" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D318" t="n">
-        <v>30</v>
+        <v>88</v>
       </c>
       <c r="E318" t="n">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="F318" t="n">
-        <v>18</v>
+        <v>157</v>
       </c>
       <c r="G318" t="n">
-        <v>36</v>
+        <v>225</v>
       </c>
       <c r="H318" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I318" t="s">
-        <v>254</v>
+        <v>229</v>
       </c>
       <c r="J318" t="n">
         <v>8</v>
@@ -11881,31 +11899,31 @@
     </row>
     <row r="319">
       <c r="A319" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="B319" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C319" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D319" t="n">
-        <v>11</v>
+        <v>85</v>
       </c>
       <c r="E319" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F319" t="n">
-        <v>73</v>
+        <v>18</v>
       </c>
       <c r="G319" t="n">
-        <v>79</v>
+        <v>26</v>
       </c>
       <c r="H319" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I319" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="J319" t="n">
         <v>8</v>
@@ -11913,31 +11931,31 @@
     </row>
     <row r="320">
       <c r="A320" t="s">
-        <v>229</v>
+        <v>72</v>
       </c>
       <c r="B320" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C320" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D320" t="n">
-        <v>10</v>
+        <v>71</v>
       </c>
       <c r="E320" t="n">
-        <v>15</v>
+        <v>93</v>
       </c>
       <c r="F320" t="n">
-        <v>14</v>
+        <v>184</v>
       </c>
       <c r="G320" t="n">
-        <v>29</v>
+        <v>277</v>
       </c>
       <c r="H320" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="I320" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="J320" t="n">
         <v>8</v>
@@ -11945,31 +11963,31 @@
     </row>
     <row r="321">
       <c r="A321" t="s">
-        <v>86</v>
+        <v>155</v>
       </c>
       <c r="B321" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C321" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D321" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="E321" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F321" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="G321" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H321" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I321" t="s">
-        <v>256</v>
+        <v>201</v>
       </c>
       <c r="J321" t="n">
         <v>8</v>
@@ -11977,31 +11995,31 @@
     </row>
     <row r="322">
       <c r="A322" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="B322" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="C322" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D322" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E322" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="F322" t="n">
-        <v>11</v>
+        <v>73</v>
       </c>
       <c r="G322" t="n">
-        <v>31</v>
+        <v>79</v>
       </c>
       <c r="H322" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I322" t="s">
-        <v>233</v>
+        <v>289</v>
       </c>
       <c r="J322" t="n">
         <v>8</v>
@@ -12009,31 +12027,31 @@
     </row>
     <row r="323">
       <c r="A323" t="s">
-        <v>90</v>
+        <v>231</v>
       </c>
       <c r="B323" t="s">
         <v>17</v>
       </c>
       <c r="C323" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D323" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E323" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F323" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G323" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="H323" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I323" t="s">
-        <v>234</v>
+        <v>290</v>
       </c>
       <c r="J323" t="n">
         <v>8</v>
@@ -12041,127 +12059,127 @@
     </row>
     <row r="324">
       <c r="A324" t="s">
-        <v>19</v>
+        <v>86</v>
       </c>
       <c r="B324" t="s">
         <v>11</v>
       </c>
       <c r="C324" t="s">
-        <v>285</v>
+        <v>262</v>
       </c>
       <c r="D324" t="n">
-        <v>1787304</v>
+        <v>6</v>
       </c>
       <c r="E324" t="n">
-        <v>568287</v>
+        <v>8</v>
       </c>
       <c r="F324" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G324" t="n">
-        <v>568287</v>
+        <v>34</v>
       </c>
       <c r="H324" t="n">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="I324" t="s">
-        <v>204</v>
+        <v>260</v>
       </c>
       <c r="J324" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="s">
-        <v>10</v>
+        <v>82</v>
       </c>
       <c r="B325" t="s">
+        <v>17</v>
+      </c>
+      <c r="C325" t="s">
+        <v>262</v>
+      </c>
+      <c r="D325" t="n">
+        <v>3</v>
+      </c>
+      <c r="E325" t="n">
+        <v>20</v>
+      </c>
+      <c r="F325" t="n">
         <v>11</v>
       </c>
-      <c r="C325" t="s">
-        <v>285</v>
-      </c>
-      <c r="D325" t="n">
-        <v>850543</v>
-      </c>
-      <c r="E325" t="n">
-        <v>532954</v>
-      </c>
-      <c r="F325" t="n">
-        <v>0</v>
-      </c>
       <c r="G325" t="n">
-        <v>532954</v>
+        <v>31</v>
       </c>
       <c r="H325" t="n">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="I325" t="s">
-        <v>205</v>
+        <v>235</v>
       </c>
       <c r="J325" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="s">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="B326" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C326" t="s">
-        <v>285</v>
+        <v>262</v>
       </c>
       <c r="D326" t="n">
-        <v>204390</v>
+        <v>2</v>
       </c>
       <c r="E326" t="n">
-        <v>165837</v>
+        <v>5</v>
       </c>
       <c r="F326" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G326" t="n">
-        <v>165837</v>
+        <v>15</v>
       </c>
       <c r="H326" t="n">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="I326" t="s">
-        <v>178</v>
+        <v>236</v>
       </c>
       <c r="J326" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B327" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C327" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="D327" t="n">
-        <v>162159</v>
+        <v>1787304</v>
       </c>
       <c r="E327" t="n">
-        <v>207520</v>
+        <v>568287</v>
       </c>
       <c r="F327" t="n">
         <v>0</v>
       </c>
       <c r="G327" t="n">
-        <v>207520</v>
+        <v>568287</v>
       </c>
       <c r="H327" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I327" t="s">
-        <v>179</v>
+        <v>204</v>
       </c>
       <c r="J327" t="n">
         <v>9</v>
@@ -12169,31 +12187,31 @@
     </row>
     <row r="328">
       <c r="A328" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B328" t="s">
         <v>11</v>
       </c>
       <c r="C328" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="D328" t="n">
-        <v>78449</v>
+        <v>898268</v>
       </c>
       <c r="E328" t="n">
-        <v>31253</v>
+        <v>532954</v>
       </c>
       <c r="F328" t="n">
         <v>0</v>
       </c>
       <c r="G328" t="n">
-        <v>31253</v>
+        <v>532954</v>
       </c>
       <c r="H328" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I328" t="s">
-        <v>180</v>
+        <v>205</v>
       </c>
       <c r="J328" t="n">
         <v>9</v>
@@ -12201,31 +12219,31 @@
     </row>
     <row r="329">
       <c r="A329" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="B329" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C329" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="D329" t="n">
-        <v>59307</v>
+        <v>204390</v>
       </c>
       <c r="E329" t="n">
-        <v>33988</v>
+        <v>165837</v>
       </c>
       <c r="F329" t="n">
         <v>0</v>
       </c>
       <c r="G329" t="n">
-        <v>33988</v>
+        <v>165837</v>
       </c>
       <c r="H329" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I329" t="s">
-        <v>236</v>
+        <v>178</v>
       </c>
       <c r="J329" t="n">
         <v>9</v>
@@ -12233,31 +12251,31 @@
     </row>
     <row r="330">
       <c r="A330" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="B330" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="C330" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="D330" t="n">
-        <v>33973</v>
+        <v>162159</v>
       </c>
       <c r="E330" t="n">
-        <v>13410</v>
+        <v>207520</v>
       </c>
       <c r="F330" t="n">
         <v>0</v>
       </c>
       <c r="G330" t="n">
-        <v>13410</v>
+        <v>207520</v>
       </c>
       <c r="H330" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I330" t="s">
-        <v>286</v>
+        <v>179</v>
       </c>
       <c r="J330" t="n">
         <v>9</v>
@@ -12265,31 +12283,31 @@
     </row>
     <row r="331">
       <c r="A331" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="B331" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="C331" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="D331" t="n">
-        <v>32679</v>
+        <v>78449</v>
       </c>
       <c r="E331" t="n">
-        <v>18997</v>
+        <v>31253</v>
       </c>
       <c r="F331" t="n">
         <v>0</v>
       </c>
       <c r="G331" t="n">
-        <v>18997</v>
+        <v>31253</v>
       </c>
       <c r="H331" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I331" t="s">
-        <v>98</v>
+        <v>180</v>
       </c>
       <c r="J331" t="n">
         <v>9</v>
@@ -12297,31 +12315,31 @@
     </row>
     <row r="332">
       <c r="A332" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="B332" t="s">
         <v>33</v>
       </c>
       <c r="C332" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="D332" t="n">
-        <v>21299</v>
+        <v>59307</v>
       </c>
       <c r="E332" t="n">
-        <v>8068</v>
+        <v>33988</v>
       </c>
       <c r="F332" t="n">
         <v>0</v>
       </c>
       <c r="G332" t="n">
-        <v>8068</v>
+        <v>33988</v>
       </c>
       <c r="H332" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I332" t="s">
-        <v>287</v>
+        <v>238</v>
       </c>
       <c r="J332" t="n">
         <v>9</v>
@@ -12329,31 +12347,31 @@
     </row>
     <row r="333">
       <c r="A333" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B333" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="C333" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="D333" t="n">
-        <v>18387</v>
+        <v>33973</v>
       </c>
       <c r="E333" t="n">
-        <v>14723</v>
+        <v>13410</v>
       </c>
       <c r="F333" t="n">
         <v>0</v>
       </c>
       <c r="G333" t="n">
-        <v>14723</v>
+        <v>13410</v>
       </c>
       <c r="H333" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I333" t="s">
-        <v>239</v>
+        <v>292</v>
       </c>
       <c r="J333" t="n">
         <v>9</v>
@@ -12361,31 +12379,31 @@
     </row>
     <row r="334">
       <c r="A334" t="s">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="B334" t="s">
         <v>33</v>
       </c>
       <c r="C334" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="D334" t="n">
-        <v>11561</v>
+        <v>32679</v>
       </c>
       <c r="E334" t="n">
-        <v>4590</v>
+        <v>18997</v>
       </c>
       <c r="F334" t="n">
         <v>0</v>
       </c>
       <c r="G334" t="n">
-        <v>4590</v>
+        <v>18997</v>
       </c>
       <c r="H334" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I334" t="s">
-        <v>288</v>
+        <v>98</v>
       </c>
       <c r="J334" t="n">
         <v>9</v>
@@ -12393,31 +12411,31 @@
     </row>
     <row r="335">
       <c r="A335" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="B335" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="C335" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="D335" t="n">
-        <v>9558</v>
+        <v>21299</v>
       </c>
       <c r="E335" t="n">
-        <v>8276</v>
+        <v>8068</v>
       </c>
       <c r="F335" t="n">
         <v>0</v>
       </c>
       <c r="G335" t="n">
-        <v>8276</v>
+        <v>8068</v>
       </c>
       <c r="H335" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I335" t="s">
-        <v>132</v>
+        <v>293</v>
       </c>
       <c r="J335" t="n">
         <v>9</v>
@@ -12425,31 +12443,31 @@
     </row>
     <row r="336">
       <c r="A336" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="B336" t="s">
         <v>17</v>
       </c>
       <c r="C336" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="D336" t="n">
-        <v>8388</v>
+        <v>18387</v>
       </c>
       <c r="E336" t="n">
-        <v>7681</v>
+        <v>14723</v>
       </c>
       <c r="F336" t="n">
         <v>0</v>
       </c>
       <c r="G336" t="n">
-        <v>7681</v>
+        <v>14723</v>
       </c>
       <c r="H336" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I336" t="s">
-        <v>210</v>
+        <v>241</v>
       </c>
       <c r="J336" t="n">
         <v>9</v>
@@ -12457,31 +12475,31 @@
     </row>
     <row r="337">
       <c r="A337" t="s">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="B337" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="C337" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="D337" t="n">
-        <v>8024</v>
+        <v>11561</v>
       </c>
       <c r="E337" t="n">
-        <v>7812</v>
+        <v>4590</v>
       </c>
       <c r="F337" t="n">
         <v>0</v>
       </c>
       <c r="G337" t="n">
-        <v>7812</v>
+        <v>4590</v>
       </c>
       <c r="H337" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I337" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="J337" t="n">
         <v>9</v>
@@ -12489,31 +12507,31 @@
     </row>
     <row r="338">
       <c r="A338" t="s">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="B338" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C338" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="D338" t="n">
-        <v>7590</v>
+        <v>9558</v>
       </c>
       <c r="E338" t="n">
-        <v>1153</v>
+        <v>8276</v>
       </c>
       <c r="F338" t="n">
         <v>0</v>
       </c>
       <c r="G338" t="n">
-        <v>1153</v>
+        <v>8276</v>
       </c>
       <c r="H338" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I338" t="s">
-        <v>290</v>
+        <v>132</v>
       </c>
       <c r="J338" t="n">
         <v>9</v>
@@ -12527,10 +12545,10 @@
         <v>11</v>
       </c>
       <c r="C339" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="D339" t="n">
-        <v>7445</v>
+        <v>9274</v>
       </c>
       <c r="E339" t="n">
         <v>679</v>
@@ -12542,10 +12560,10 @@
         <v>679</v>
       </c>
       <c r="H339" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I339" t="s">
-        <v>106</v>
+        <v>295</v>
       </c>
       <c r="J339" t="n">
         <v>9</v>
@@ -12553,31 +12571,31 @@
     </row>
     <row r="340">
       <c r="A340" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="B340" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C340" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="D340" t="n">
-        <v>7424</v>
+        <v>8388</v>
       </c>
       <c r="E340" t="n">
-        <v>3083</v>
+        <v>7681</v>
       </c>
       <c r="F340" t="n">
         <v>0</v>
       </c>
       <c r="G340" t="n">
-        <v>3083</v>
+        <v>7681</v>
       </c>
       <c r="H340" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I340" t="s">
-        <v>291</v>
+        <v>104</v>
       </c>
       <c r="J340" t="n">
         <v>9</v>
@@ -12585,31 +12603,31 @@
     </row>
     <row r="341">
       <c r="A341" t="s">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="B341" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="C341" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="D341" t="n">
-        <v>6186</v>
+        <v>8024</v>
       </c>
       <c r="E341" t="n">
-        <v>1933</v>
+        <v>7812</v>
       </c>
       <c r="F341" t="n">
         <v>0</v>
       </c>
       <c r="G341" t="n">
-        <v>1933</v>
+        <v>7812</v>
       </c>
       <c r="H341" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I341" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="J341" t="n">
         <v>9</v>
@@ -12617,31 +12635,31 @@
     </row>
     <row r="342">
       <c r="A342" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="B342" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="C342" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="D342" t="n">
-        <v>4902</v>
+        <v>7590</v>
       </c>
       <c r="E342" t="n">
-        <v>2686</v>
+        <v>1153</v>
       </c>
       <c r="F342" t="n">
         <v>0</v>
       </c>
       <c r="G342" t="n">
-        <v>2686</v>
+        <v>1153</v>
       </c>
       <c r="H342" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I342" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="J342" t="n">
         <v>9</v>
@@ -12649,31 +12667,31 @@
     </row>
     <row r="343">
       <c r="A343" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="B343" t="s">
         <v>28</v>
       </c>
       <c r="C343" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="D343" t="n">
-        <v>4183</v>
+        <v>7424</v>
       </c>
       <c r="E343" t="n">
-        <v>2934</v>
+        <v>3083</v>
       </c>
       <c r="F343" t="n">
         <v>0</v>
       </c>
       <c r="G343" t="n">
-        <v>2934</v>
+        <v>3083</v>
       </c>
       <c r="H343" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="I343" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="J343" t="n">
         <v>9</v>
@@ -12681,31 +12699,31 @@
     </row>
     <row r="344">
       <c r="A344" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B344" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="C344" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="D344" t="n">
-        <v>3933</v>
+        <v>6186</v>
       </c>
       <c r="E344" t="n">
-        <v>2531</v>
+        <v>1933</v>
       </c>
       <c r="F344" t="n">
         <v>0</v>
       </c>
       <c r="G344" t="n">
-        <v>2531</v>
+        <v>1933</v>
       </c>
       <c r="H344" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="I344" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="J344" t="n">
         <v>9</v>
@@ -12713,31 +12731,31 @@
     </row>
     <row r="345">
       <c r="A345" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="B345" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C345" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="D345" t="n">
-        <v>3210</v>
+        <v>4902</v>
       </c>
       <c r="E345" t="n">
-        <v>1971</v>
+        <v>2686</v>
       </c>
       <c r="F345" t="n">
         <v>0</v>
       </c>
       <c r="G345" t="n">
-        <v>1971</v>
+        <v>2686</v>
       </c>
       <c r="H345" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="I345" t="s">
-        <v>217</v>
+        <v>300</v>
       </c>
       <c r="J345" t="n">
         <v>9</v>
@@ -12745,31 +12763,31 @@
     </row>
     <row r="346">
       <c r="A346" t="s">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="B346" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="C346" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="D346" t="n">
-        <v>2976</v>
+        <v>4183</v>
       </c>
       <c r="E346" t="n">
-        <v>1732</v>
+        <v>2934</v>
       </c>
       <c r="F346" t="n">
         <v>0</v>
       </c>
       <c r="G346" t="n">
-        <v>1732</v>
+        <v>2934</v>
       </c>
       <c r="H346" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="I346" t="s">
-        <v>142</v>
+        <v>301</v>
       </c>
       <c r="J346" t="n">
         <v>9</v>
@@ -12777,31 +12795,31 @@
     </row>
     <row r="347">
       <c r="A347" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="B347" t="s">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="C347" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="D347" t="n">
-        <v>2899</v>
+        <v>3933</v>
       </c>
       <c r="E347" t="n">
-        <v>1194</v>
+        <v>2531</v>
       </c>
       <c r="F347" t="n">
         <v>0</v>
       </c>
       <c r="G347" t="n">
-        <v>1194</v>
+        <v>2531</v>
       </c>
       <c r="H347" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I347" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="J347" t="n">
         <v>9</v>
@@ -12809,31 +12827,31 @@
     </row>
     <row r="348">
       <c r="A348" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="B348" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="C348" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="D348" t="n">
-        <v>2112</v>
+        <v>3210</v>
       </c>
       <c r="E348" t="n">
-        <v>2797</v>
+        <v>1971</v>
       </c>
       <c r="F348" t="n">
         <v>0</v>
       </c>
       <c r="G348" t="n">
-        <v>2797</v>
+        <v>1971</v>
       </c>
       <c r="H348" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="I348" t="s">
-        <v>297</v>
+        <v>217</v>
       </c>
       <c r="J348" t="n">
         <v>9</v>
@@ -12841,31 +12859,31 @@
     </row>
     <row r="349">
       <c r="A349" t="s">
-        <v>149</v>
+        <v>68</v>
       </c>
       <c r="B349" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="C349" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="D349" t="n">
-        <v>1954</v>
+        <v>2976</v>
       </c>
       <c r="E349" t="n">
-        <v>988</v>
+        <v>1732</v>
       </c>
       <c r="F349" t="n">
         <v>0</v>
       </c>
       <c r="G349" t="n">
-        <v>988</v>
+        <v>1732</v>
       </c>
       <c r="H349" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="I349" t="s">
-        <v>275</v>
+        <v>142</v>
       </c>
       <c r="J349" t="n">
         <v>9</v>
@@ -12873,31 +12891,31 @@
     </row>
     <row r="350">
       <c r="A350" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="B350" t="s">
         <v>11</v>
       </c>
       <c r="C350" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="D350" t="n">
-        <v>1532</v>
+        <v>2899</v>
       </c>
       <c r="E350" t="n">
-        <v>417</v>
+        <v>1194</v>
       </c>
       <c r="F350" t="n">
         <v>0</v>
       </c>
       <c r="G350" t="n">
-        <v>417</v>
+        <v>1194</v>
       </c>
       <c r="H350" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I350" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="J350" t="n">
         <v>9</v>
@@ -12905,31 +12923,31 @@
     </row>
     <row r="351">
       <c r="A351" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="B351" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C351" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="D351" t="n">
-        <v>1167</v>
+        <v>2112</v>
       </c>
       <c r="E351" t="n">
-        <v>598</v>
+        <v>2797</v>
       </c>
       <c r="F351" t="n">
         <v>0</v>
       </c>
       <c r="G351" t="n">
-        <v>598</v>
+        <v>2797</v>
       </c>
       <c r="H351" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="I351" t="s">
-        <v>118</v>
+        <v>304</v>
       </c>
       <c r="J351" t="n">
         <v>9</v>
@@ -12937,31 +12955,31 @@
     </row>
     <row r="352">
       <c r="A352" t="s">
-        <v>223</v>
+        <v>149</v>
       </c>
       <c r="B352" t="s">
         <v>17</v>
       </c>
       <c r="C352" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="D352" t="n">
-        <v>675</v>
+        <v>1954</v>
       </c>
       <c r="E352" t="n">
-        <v>1008</v>
+        <v>988</v>
       </c>
       <c r="F352" t="n">
         <v>0</v>
       </c>
       <c r="G352" t="n">
-        <v>1008</v>
+        <v>988</v>
       </c>
       <c r="H352" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="I352" t="s">
-        <v>299</v>
+        <v>279</v>
       </c>
       <c r="J352" t="n">
         <v>9</v>
@@ -12969,31 +12987,31 @@
     </row>
     <row r="353">
       <c r="A353" t="s">
-        <v>41</v>
+        <v>84</v>
       </c>
       <c r="B353" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="C353" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="D353" t="n">
-        <v>564</v>
+        <v>1532</v>
       </c>
       <c r="E353" t="n">
-        <v>602</v>
+        <v>417</v>
       </c>
       <c r="F353" t="n">
         <v>0</v>
       </c>
       <c r="G353" t="n">
-        <v>602</v>
+        <v>417</v>
       </c>
       <c r="H353" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="I353" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="J353" t="n">
         <v>9</v>
@@ -13001,31 +13019,31 @@
     </row>
     <row r="354">
       <c r="A354" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B354" t="s">
         <v>28</v>
       </c>
       <c r="C354" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="D354" t="n">
-        <v>356</v>
+        <v>1167</v>
       </c>
       <c r="E354" t="n">
-        <v>296</v>
+        <v>598</v>
       </c>
       <c r="F354" t="n">
         <v>0</v>
       </c>
       <c r="G354" t="n">
-        <v>296</v>
+        <v>598</v>
       </c>
       <c r="H354" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I354" t="s">
-        <v>280</v>
+        <v>118</v>
       </c>
       <c r="J354" t="n">
         <v>9</v>
@@ -13033,31 +13051,31 @@
     </row>
     <row r="355">
       <c r="A355" t="s">
-        <v>78</v>
+        <v>226</v>
       </c>
       <c r="B355" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C355" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="D355" t="n">
-        <v>198</v>
+        <v>977</v>
       </c>
       <c r="E355" t="n">
-        <v>105</v>
+        <v>389</v>
       </c>
       <c r="F355" t="n">
         <v>0</v>
       </c>
       <c r="G355" t="n">
-        <v>105</v>
+        <v>389</v>
       </c>
       <c r="H355" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I355" t="s">
-        <v>79</v>
+        <v>255</v>
       </c>
       <c r="J355" t="n">
         <v>9</v>
@@ -13065,31 +13083,31 @@
     </row>
     <row r="356">
       <c r="A356" t="s">
-        <v>72</v>
+        <v>223</v>
       </c>
       <c r="B356" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C356" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="D356" t="n">
-        <v>184</v>
+        <v>675</v>
       </c>
       <c r="E356" t="n">
-        <v>71</v>
+        <v>1008</v>
       </c>
       <c r="F356" t="n">
         <v>0</v>
       </c>
       <c r="G356" t="n">
-        <v>71</v>
+        <v>1008</v>
       </c>
       <c r="H356" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="I356" t="s">
-        <v>301</v>
+        <v>224</v>
       </c>
       <c r="J356" t="n">
         <v>9</v>
@@ -13097,31 +13115,31 @@
     </row>
     <row r="357">
       <c r="A357" t="s">
-        <v>80</v>
+        <v>41</v>
       </c>
       <c r="B357" t="s">
         <v>28</v>
       </c>
       <c r="C357" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="D357" t="n">
-        <v>157</v>
+        <v>564</v>
       </c>
       <c r="E357" t="n">
-        <v>88</v>
+        <v>602</v>
       </c>
       <c r="F357" t="n">
         <v>0</v>
       </c>
       <c r="G357" t="n">
-        <v>88</v>
+        <v>602</v>
       </c>
       <c r="H357" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I357" t="s">
-        <v>123</v>
+        <v>306</v>
       </c>
       <c r="J357" t="n">
         <v>9</v>
@@ -13129,31 +13147,31 @@
     </row>
     <row r="358">
       <c r="A358" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="B358" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="C358" t="s">
+        <v>291</v>
+      </c>
+      <c r="D358" t="n">
+        <v>356</v>
+      </c>
+      <c r="E358" t="n">
+        <v>296</v>
+      </c>
+      <c r="F358" t="n">
+        <v>0</v>
+      </c>
+      <c r="G358" t="n">
+        <v>296</v>
+      </c>
+      <c r="H358" t="n">
+        <v>32</v>
+      </c>
+      <c r="I358" t="s">
         <v>285</v>
-      </c>
-      <c r="D358" t="n">
-        <v>103</v>
-      </c>
-      <c r="E358" t="n">
-        <v>170</v>
-      </c>
-      <c r="F358" t="n">
-        <v>0</v>
-      </c>
-      <c r="G358" t="n">
-        <v>170</v>
-      </c>
-      <c r="H358" t="n">
-        <v>35</v>
-      </c>
-      <c r="I358" t="s">
-        <v>302</v>
       </c>
       <c r="J358" t="n">
         <v>9</v>
@@ -13161,31 +13179,31 @@
     </row>
     <row r="359">
       <c r="A359" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B359" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C359" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="D359" t="n">
-        <v>73</v>
+        <v>198</v>
       </c>
       <c r="E359" t="n">
-        <v>11</v>
+        <v>105</v>
       </c>
       <c r="F359" t="n">
         <v>0</v>
       </c>
       <c r="G359" t="n">
-        <v>11</v>
+        <v>105</v>
       </c>
       <c r="H359" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="I359" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="J359" t="n">
         <v>9</v>
@@ -13193,31 +13211,31 @@
     </row>
     <row r="360">
       <c r="A360" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="B360" t="s">
         <v>11</v>
       </c>
       <c r="C360" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="D360" t="n">
-        <v>26</v>
+        <v>184</v>
       </c>
       <c r="E360" t="n">
-        <v>6</v>
+        <v>71</v>
       </c>
       <c r="F360" t="n">
         <v>0</v>
       </c>
       <c r="G360" t="n">
-        <v>6</v>
+        <v>71</v>
       </c>
       <c r="H360" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="I360" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="J360" t="n">
         <v>9</v>
@@ -13225,31 +13243,31 @@
     </row>
     <row r="361">
       <c r="A361" t="s">
+        <v>80</v>
+      </c>
+      <c r="B361" t="s">
+        <v>28</v>
+      </c>
+      <c r="C361" t="s">
+        <v>291</v>
+      </c>
+      <c r="D361" t="n">
+        <v>157</v>
+      </c>
+      <c r="E361" t="n">
         <v>88</v>
       </c>
-      <c r="B361" t="s">
-        <v>17</v>
-      </c>
-      <c r="C361" t="s">
-        <v>285</v>
-      </c>
-      <c r="D361" t="n">
-        <v>18</v>
-      </c>
-      <c r="E361" t="n">
-        <v>85</v>
-      </c>
       <c r="F361" t="n">
         <v>0</v>
       </c>
       <c r="G361" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="H361" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I361" t="s">
-        <v>175</v>
+        <v>229</v>
       </c>
       <c r="J361" t="n">
         <v>9</v>
@@ -13257,31 +13275,31 @@
     </row>
     <row r="362">
       <c r="A362" t="s">
-        <v>155</v>
+        <v>60</v>
       </c>
       <c r="B362" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C362" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="D362" t="n">
-        <v>18</v>
+        <v>111</v>
       </c>
       <c r="E362" t="n">
-        <v>30</v>
+        <v>170</v>
       </c>
       <c r="F362" t="n">
         <v>0</v>
       </c>
       <c r="G362" t="n">
-        <v>30</v>
+        <v>170</v>
       </c>
       <c r="H362" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="I362" t="s">
-        <v>156</v>
+        <v>309</v>
       </c>
       <c r="J362" t="n">
         <v>9</v>
@@ -13289,31 +13307,31 @@
     </row>
     <row r="363">
       <c r="A363" t="s">
-        <v>229</v>
+        <v>76</v>
       </c>
       <c r="B363" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="C363" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="D363" t="n">
-        <v>14</v>
+        <v>73</v>
       </c>
       <c r="E363" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F363" t="n">
         <v>0</v>
       </c>
       <c r="G363" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H363" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="I363" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="J363" t="n">
         <v>9</v>
@@ -13321,31 +13339,31 @@
     </row>
     <row r="364">
       <c r="A364" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="B364" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C364" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="D364" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="E364" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F364" t="n">
         <v>0</v>
       </c>
       <c r="G364" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H364" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="I364" t="s">
-        <v>233</v>
+        <v>311</v>
       </c>
       <c r="J364" t="n">
         <v>9</v>
@@ -13353,33 +13371,161 @@
     </row>
     <row r="365">
       <c r="A365" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B365" t="s">
         <v>17</v>
       </c>
       <c r="C365" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="D365" t="n">
+        <v>18</v>
+      </c>
+      <c r="E365" t="n">
+        <v>85</v>
+      </c>
+      <c r="F365" t="n">
+        <v>0</v>
+      </c>
+      <c r="G365" t="n">
+        <v>85</v>
+      </c>
+      <c r="H365" t="n">
+        <v>39</v>
+      </c>
+      <c r="I365" t="s">
+        <v>202</v>
+      </c>
+      <c r="J365" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="s">
+        <v>155</v>
+      </c>
+      <c r="B366" t="s">
+        <v>17</v>
+      </c>
+      <c r="C366" t="s">
+        <v>291</v>
+      </c>
+      <c r="D366" t="n">
+        <v>18</v>
+      </c>
+      <c r="E366" t="n">
+        <v>30</v>
+      </c>
+      <c r="F366" t="n">
+        <v>0</v>
+      </c>
+      <c r="G366" t="n">
+        <v>30</v>
+      </c>
+      <c r="H366" t="n">
+        <v>40</v>
+      </c>
+      <c r="I366" t="s">
+        <v>312</v>
+      </c>
+      <c r="J366" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="s">
+        <v>231</v>
+      </c>
+      <c r="B367" t="s">
+        <v>17</v>
+      </c>
+      <c r="C367" t="s">
+        <v>291</v>
+      </c>
+      <c r="D367" t="n">
+        <v>14</v>
+      </c>
+      <c r="E367" t="n">
         <v>10</v>
       </c>
-      <c r="E365" t="n">
+      <c r="F367" t="n">
+        <v>0</v>
+      </c>
+      <c r="G367" t="n">
+        <v>10</v>
+      </c>
+      <c r="H367" t="n">
+        <v>41</v>
+      </c>
+      <c r="I367" t="s">
+        <v>313</v>
+      </c>
+      <c r="J367" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="s">
+        <v>82</v>
+      </c>
+      <c r="B368" t="s">
+        <v>17</v>
+      </c>
+      <c r="C368" t="s">
+        <v>291</v>
+      </c>
+      <c r="D368" t="n">
+        <v>11</v>
+      </c>
+      <c r="E368" t="n">
+        <v>3</v>
+      </c>
+      <c r="F368" t="n">
+        <v>0</v>
+      </c>
+      <c r="G368" t="n">
+        <v>3</v>
+      </c>
+      <c r="H368" t="n">
+        <v>42</v>
+      </c>
+      <c r="I368" t="s">
+        <v>235</v>
+      </c>
+      <c r="J368" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="s">
+        <v>90</v>
+      </c>
+      <c r="B369" t="s">
+        <v>17</v>
+      </c>
+      <c r="C369" t="s">
+        <v>291</v>
+      </c>
+      <c r="D369" t="n">
+        <v>10</v>
+      </c>
+      <c r="E369" t="n">
         <v>2</v>
       </c>
-      <c r="F365" t="n">
-        <v>0</v>
-      </c>
-      <c r="G365" t="n">
+      <c r="F369" t="n">
+        <v>0</v>
+      </c>
+      <c r="G369" t="n">
         <v>2</v>
       </c>
-      <c r="H365" t="n">
-        <v>42</v>
-      </c>
-      <c r="I365" t="s">
-        <v>234</v>
-      </c>
-      <c r="J365" t="n">
+      <c r="H369" t="n">
+        <v>43</v>
+      </c>
+      <c r="I369" t="s">
+        <v>236</v>
+      </c>
+      <c r="J369" t="n">
         <v>9</v>
       </c>
     </row>
@@ -13420,7 +13566,7 @@
         <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="J1" t="s">
         <v>8</v>
@@ -13555,7 +13701,7 @@
       </c>
       <c r="I5"/>
       <c r="J5" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="K5" t="n">
         <v>1</v>
@@ -13621,7 +13767,7 @@
       </c>
       <c r="I7"/>
       <c r="J7" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="K7" t="n">
         <v>1</v>
@@ -13654,7 +13800,7 @@
       </c>
       <c r="I8"/>
       <c r="J8" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="K8" t="n">
         <v>1</v>
@@ -13687,7 +13833,7 @@
       </c>
       <c r="I9"/>
       <c r="J9" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="K9" t="n">
         <v>1</v>
@@ -13753,7 +13899,7 @@
       </c>
       <c r="I11"/>
       <c r="J11" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="K11" t="n">
         <v>1</v>
@@ -13819,7 +13965,7 @@
       </c>
       <c r="I13"/>
       <c r="J13" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
@@ -13852,7 +13998,7 @@
       </c>
       <c r="I14"/>
       <c r="J14" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
@@ -13885,7 +14031,7 @@
       </c>
       <c r="I15"/>
       <c r="J15" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
@@ -13918,7 +14064,7 @@
       </c>
       <c r="I16"/>
       <c r="J16" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
@@ -13984,7 +14130,7 @@
       </c>
       <c r="I18"/>
       <c r="J18" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="K18" t="n">
         <v>1</v>
@@ -14017,7 +14163,7 @@
       </c>
       <c r="I19"/>
       <c r="J19" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="K19" t="n">
         <v>1</v>
@@ -14050,7 +14196,7 @@
       </c>
       <c r="I20"/>
       <c r="J20" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="K20" t="n">
         <v>1</v>
@@ -14083,7 +14229,7 @@
       </c>
       <c r="I21"/>
       <c r="J21" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="K21" t="n">
         <v>1</v>
@@ -14149,7 +14295,7 @@
       </c>
       <c r="I23"/>
       <c r="J23" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="K23" t="n">
         <v>1</v>
@@ -14182,7 +14328,7 @@
       </c>
       <c r="I24"/>
       <c r="J24" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="K24" t="n">
         <v>1</v>
@@ -14215,7 +14361,7 @@
       </c>
       <c r="I25"/>
       <c r="J25" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="K25" t="n">
         <v>1</v>
@@ -14248,7 +14394,7 @@
       </c>
       <c r="I26"/>
       <c r="J26" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="K26" t="n">
         <v>1</v>
@@ -14281,7 +14427,7 @@
       </c>
       <c r="I27"/>
       <c r="J27" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="K27" t="n">
         <v>1</v>
@@ -14314,7 +14460,7 @@
       </c>
       <c r="I28"/>
       <c r="J28" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="K28" t="n">
         <v>1</v>
@@ -14347,7 +14493,7 @@
       </c>
       <c r="I29"/>
       <c r="J29" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="K29" t="n">
         <v>1</v>
@@ -14380,7 +14526,7 @@
       </c>
       <c r="I30"/>
       <c r="J30" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="K30" t="n">
         <v>1</v>
@@ -14512,7 +14658,7 @@
       </c>
       <c r="I34"/>
       <c r="J34" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="K34" t="n">
         <v>2</v>
@@ -14545,7 +14691,7 @@
       </c>
       <c r="I35"/>
       <c r="J35" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="K35" t="n">
         <v>2</v>
@@ -14611,7 +14757,7 @@
       </c>
       <c r="I37"/>
       <c r="J37" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="K37" t="n">
         <v>2</v>
@@ -14644,7 +14790,7 @@
       </c>
       <c r="I38"/>
       <c r="J38" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="K38" t="n">
         <v>2</v>
@@ -14677,7 +14823,7 @@
       </c>
       <c r="I39"/>
       <c r="J39" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="K39" t="n">
         <v>2</v>
@@ -14710,7 +14856,7 @@
       </c>
       <c r="I40"/>
       <c r="J40" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="K40" t="n">
         <v>2</v>
@@ -14809,7 +14955,7 @@
       </c>
       <c r="I43"/>
       <c r="J43" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="K43" t="n">
         <v>2</v>
@@ -14842,7 +14988,7 @@
       </c>
       <c r="I44"/>
       <c r="J44" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="K44" t="n">
         <v>2</v>
@@ -14875,7 +15021,7 @@
       </c>
       <c r="I45"/>
       <c r="J45" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="K45" t="n">
         <v>2</v>
@@ -14908,7 +15054,7 @@
       </c>
       <c r="I46"/>
       <c r="J46" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="K46" t="n">
         <v>2</v>
@@ -14941,7 +15087,7 @@
       </c>
       <c r="I47"/>
       <c r="J47" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="K47" t="n">
         <v>2</v>
@@ -14974,7 +15120,7 @@
       </c>
       <c r="I48"/>
       <c r="J48" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="K48" t="n">
         <v>2</v>
@@ -15007,7 +15153,7 @@
       </c>
       <c r="I49"/>
       <c r="J49" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="K49" t="n">
         <v>2</v>
@@ -15040,7 +15186,7 @@
       </c>
       <c r="I50"/>
       <c r="J50" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="K50" t="n">
         <v>2</v>
@@ -15073,7 +15219,7 @@
       </c>
       <c r="I51"/>
       <c r="J51" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="K51" t="n">
         <v>2</v>
@@ -15106,7 +15252,7 @@
       </c>
       <c r="I52"/>
       <c r="J52" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="K52" t="n">
         <v>2</v>
@@ -15139,7 +15285,7 @@
       </c>
       <c r="I53"/>
       <c r="J53" t="s">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="K53" t="n">
         <v>2</v>
@@ -15205,7 +15351,7 @@
       </c>
       <c r="I55"/>
       <c r="J55" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="K55" t="n">
         <v>2</v>
@@ -15238,7 +15384,7 @@
       </c>
       <c r="I56"/>
       <c r="J56" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="K56" t="n">
         <v>2</v>
@@ -15271,7 +15417,7 @@
       </c>
       <c r="I57"/>
       <c r="J57" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="K57" t="n">
         <v>2</v>
@@ -15304,7 +15450,7 @@
       </c>
       <c r="I58"/>
       <c r="J58" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="K58" t="n">
         <v>2</v>
@@ -15337,7 +15483,7 @@
       </c>
       <c r="I59"/>
       <c r="J59" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="K59" t="n">
         <v>2</v>
@@ -15436,7 +15582,7 @@
       </c>
       <c r="I62"/>
       <c r="J62" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="K62" t="n">
         <v>3</v>
@@ -15469,7 +15615,7 @@
       </c>
       <c r="I63"/>
       <c r="J63" t="s">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="K63" t="n">
         <v>3</v>
@@ -15502,7 +15648,7 @@
       </c>
       <c r="I64"/>
       <c r="J64" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="K64" t="n">
         <v>3</v>
@@ -15535,7 +15681,7 @@
       </c>
       <c r="I65"/>
       <c r="J65" t="s">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="K65" t="n">
         <v>3</v>
@@ -15568,7 +15714,7 @@
       </c>
       <c r="I66"/>
       <c r="J66" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="K66" t="n">
         <v>3</v>
@@ -15601,7 +15747,7 @@
       </c>
       <c r="I67"/>
       <c r="J67" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="K67" t="n">
         <v>3</v>
@@ -15667,7 +15813,7 @@
       </c>
       <c r="I69"/>
       <c r="J69" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="K69" t="n">
         <v>3</v>
@@ -15700,7 +15846,7 @@
       </c>
       <c r="I70"/>
       <c r="J70" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="K70" t="n">
         <v>3</v>
@@ -15733,7 +15879,7 @@
       </c>
       <c r="I71"/>
       <c r="J71" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="K71" t="n">
         <v>3</v>
@@ -15766,7 +15912,7 @@
       </c>
       <c r="I72"/>
       <c r="J72" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="K72" t="n">
         <v>3</v>
@@ -15799,7 +15945,7 @@
       </c>
       <c r="I73"/>
       <c r="J73" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="K73" t="n">
         <v>3</v>
@@ -15832,7 +15978,7 @@
       </c>
       <c r="I74"/>
       <c r="J74" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="K74" t="n">
         <v>3</v>
@@ -15865,7 +16011,7 @@
       </c>
       <c r="I75"/>
       <c r="J75" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="K75" t="n">
         <v>3</v>
@@ -15931,7 +16077,7 @@
       </c>
       <c r="I77"/>
       <c r="J77" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="K77" t="n">
         <v>3</v>
@@ -15964,7 +16110,7 @@
       </c>
       <c r="I78"/>
       <c r="J78" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="K78" t="n">
         <v>3</v>
@@ -15997,7 +16143,7 @@
       </c>
       <c r="I79"/>
       <c r="J79" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="K79" t="n">
         <v>3</v>
@@ -16030,7 +16176,7 @@
       </c>
       <c r="I80"/>
       <c r="J80" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="K80" t="n">
         <v>3</v>
@@ -16063,7 +16209,7 @@
       </c>
       <c r="I81"/>
       <c r="J81" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="K81" t="n">
         <v>3</v>
@@ -16096,7 +16242,7 @@
       </c>
       <c r="I82"/>
       <c r="J82" t="s">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="K82" t="n">
         <v>3</v>
@@ -16129,7 +16275,7 @@
       </c>
       <c r="I83"/>
       <c r="J83" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="K83" t="n">
         <v>3</v>
@@ -16162,7 +16308,7 @@
       </c>
       <c r="I84"/>
       <c r="J84" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="K84" t="n">
         <v>3</v>
@@ -16195,7 +16341,7 @@
       </c>
       <c r="I85"/>
       <c r="J85" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="K85" t="n">
         <v>3</v>
@@ -16228,7 +16374,7 @@
       </c>
       <c r="I86"/>
       <c r="J86" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="K86" t="n">
         <v>3</v>
@@ -16261,7 +16407,7 @@
       </c>
       <c r="I87"/>
       <c r="J87" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="K87" t="n">
         <v>3</v>
@@ -16294,7 +16440,7 @@
       </c>
       <c r="I88"/>
       <c r="J88" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="K88" t="n">
         <v>3</v>
@@ -16327,7 +16473,7 @@
       </c>
       <c r="I89"/>
       <c r="J89" t="s">
-        <v>300</v>
+        <v>368</v>
       </c>
       <c r="K89" t="n">
         <v>3</v>
@@ -16360,7 +16506,7 @@
       </c>
       <c r="I90"/>
       <c r="J90" t="s">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="K90" t="n">
         <v>3</v>
@@ -16492,7 +16638,7 @@
       </c>
       <c r="I94"/>
       <c r="J94" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="K94" t="n">
         <v>4</v>
@@ -16525,7 +16671,7 @@
       </c>
       <c r="I95"/>
       <c r="J95" t="s">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="K95" t="n">
         <v>4</v>
@@ -16558,7 +16704,7 @@
       </c>
       <c r="I96"/>
       <c r="J96" t="s">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="K96" t="n">
         <v>4</v>
@@ -16591,7 +16737,7 @@
       </c>
       <c r="I97"/>
       <c r="J97" t="s">
-        <v>363</v>
+        <v>372</v>
       </c>
       <c r="K97" t="n">
         <v>4</v>
@@ -16624,7 +16770,7 @@
       </c>
       <c r="I98"/>
       <c r="J98" t="s">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="K98" t="n">
         <v>4</v>
@@ -16657,7 +16803,7 @@
       </c>
       <c r="I99"/>
       <c r="J99" t="s">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="K99" t="n">
         <v>4</v>
@@ -16690,7 +16836,7 @@
       </c>
       <c r="I100"/>
       <c r="J100" t="s">
-        <v>366</v>
+        <v>375</v>
       </c>
       <c r="K100" t="n">
         <v>4</v>
@@ -16723,7 +16869,7 @@
       </c>
       <c r="I101"/>
       <c r="J101" t="s">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="K101" t="n">
         <v>4</v>
@@ -16756,7 +16902,7 @@
       </c>
       <c r="I102"/>
       <c r="J102" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="K102" t="n">
         <v>4</v>
@@ -16789,7 +16935,7 @@
       </c>
       <c r="I103"/>
       <c r="J103" t="s">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="K103" t="n">
         <v>4</v>
@@ -16822,7 +16968,7 @@
       </c>
       <c r="I104"/>
       <c r="J104" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="K104" t="n">
         <v>4</v>
@@ -16855,7 +17001,7 @@
       </c>
       <c r="I105"/>
       <c r="J105" t="s">
-        <v>369</v>
+        <v>378</v>
       </c>
       <c r="K105" t="n">
         <v>4</v>
@@ -16888,7 +17034,7 @@
       </c>
       <c r="I106"/>
       <c r="J106" t="s">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="K106" t="n">
         <v>4</v>
@@ -16921,7 +17067,7 @@
       </c>
       <c r="I107"/>
       <c r="J107" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="K107" t="n">
         <v>4</v>
@@ -16954,7 +17100,7 @@
       </c>
       <c r="I108"/>
       <c r="J108" t="s">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="K108" t="n">
         <v>4</v>
@@ -16987,7 +17133,7 @@
       </c>
       <c r="I109"/>
       <c r="J109" t="s">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="K109" t="n">
         <v>4</v>
@@ -17020,7 +17166,7 @@
       </c>
       <c r="I110"/>
       <c r="J110" t="s">
-        <v>373</v>
+        <v>382</v>
       </c>
       <c r="K110" t="n">
         <v>4</v>
@@ -17053,7 +17199,7 @@
       </c>
       <c r="I111"/>
       <c r="J111" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K111" t="n">
         <v>4</v>
@@ -17086,7 +17232,7 @@
       </c>
       <c r="I112"/>
       <c r="J112" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="K112" t="n">
         <v>4</v>
@@ -17119,7 +17265,7 @@
       </c>
       <c r="I113"/>
       <c r="J113" t="s">
-        <v>374</v>
+        <v>383</v>
       </c>
       <c r="K113" t="n">
         <v>4</v>
@@ -17185,7 +17331,7 @@
       </c>
       <c r="I115"/>
       <c r="J115" t="s">
-        <v>375</v>
+        <v>384</v>
       </c>
       <c r="K115" t="n">
         <v>4</v>
@@ -17218,7 +17364,7 @@
       </c>
       <c r="I116"/>
       <c r="J116" t="s">
-        <v>376</v>
+        <v>385</v>
       </c>
       <c r="K116" t="n">
         <v>4</v>
@@ -17251,7 +17397,7 @@
       </c>
       <c r="I117"/>
       <c r="J117" t="s">
-        <v>377</v>
+        <v>386</v>
       </c>
       <c r="K117" t="n">
         <v>4</v>
@@ -17284,7 +17430,7 @@
       </c>
       <c r="I118"/>
       <c r="J118" t="s">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="K118" t="n">
         <v>4</v>
@@ -17317,7 +17463,7 @@
       </c>
       <c r="I119"/>
       <c r="J119" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="K119" t="n">
         <v>4</v>
@@ -17383,7 +17529,7 @@
       </c>
       <c r="I121"/>
       <c r="J121" t="s">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="K121" t="n">
         <v>4</v>
@@ -17449,7 +17595,7 @@
       </c>
       <c r="I123"/>
       <c r="J123" t="s">
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="K123" t="n">
         <v>5</v>
@@ -17515,7 +17661,7 @@
       </c>
       <c r="I125"/>
       <c r="J125" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="K125" t="n">
         <v>5</v>
@@ -17548,7 +17694,7 @@
       </c>
       <c r="I126"/>
       <c r="J126" t="s">
-        <v>381</v>
+        <v>390</v>
       </c>
       <c r="K126" t="n">
         <v>5</v>
@@ -17581,7 +17727,7 @@
       </c>
       <c r="I127"/>
       <c r="J127" t="s">
-        <v>382</v>
+        <v>391</v>
       </c>
       <c r="K127" t="n">
         <v>5</v>
@@ -17614,7 +17760,7 @@
       </c>
       <c r="I128"/>
       <c r="J128" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="K128" t="n">
         <v>5</v>
@@ -17647,7 +17793,7 @@
       </c>
       <c r="I129"/>
       <c r="J129" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="K129" t="n">
         <v>5</v>
@@ -17680,7 +17826,7 @@
       </c>
       <c r="I130"/>
       <c r="J130" t="s">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="K130" t="n">
         <v>5</v>
@@ -17713,7 +17859,7 @@
       </c>
       <c r="I131"/>
       <c r="J131" t="s">
-        <v>366</v>
+        <v>375</v>
       </c>
       <c r="K131" t="n">
         <v>5</v>
@@ -17746,7 +17892,7 @@
       </c>
       <c r="I132"/>
       <c r="J132" t="s">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="K132" t="n">
         <v>5</v>
@@ -17779,7 +17925,7 @@
       </c>
       <c r="I133"/>
       <c r="J133" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="K133" t="n">
         <v>5</v>
@@ -17812,7 +17958,7 @@
       </c>
       <c r="I134"/>
       <c r="J134" t="s">
-        <v>384</v>
+        <v>295</v>
       </c>
       <c r="K134" t="n">
         <v>5</v>
@@ -17845,7 +17991,7 @@
       </c>
       <c r="I135"/>
       <c r="J135" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="K135" t="n">
         <v>5</v>
@@ -17878,7 +18024,7 @@
       </c>
       <c r="I136"/>
       <c r="J136" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="K136" t="n">
         <v>5</v>
@@ -17911,7 +18057,7 @@
       </c>
       <c r="I137"/>
       <c r="J137" t="s">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="K137" t="n">
         <v>5</v>
@@ -17944,7 +18090,7 @@
       </c>
       <c r="I138"/>
       <c r="J138" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="K138" t="n">
         <v>5</v>
@@ -17977,7 +18123,7 @@
       </c>
       <c r="I139"/>
       <c r="J139" t="s">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="K139" t="n">
         <v>5</v>
@@ -18043,7 +18189,7 @@
       </c>
       <c r="I141"/>
       <c r="J141" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="K141" t="n">
         <v>5</v>
@@ -18076,7 +18222,7 @@
       </c>
       <c r="I142"/>
       <c r="J142" t="s">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="K142" t="n">
         <v>5</v>
@@ -18109,7 +18255,7 @@
       </c>
       <c r="I143"/>
       <c r="J143" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="K143" t="n">
         <v>5</v>
@@ -18142,7 +18288,7 @@
       </c>
       <c r="I144"/>
       <c r="J144" t="s">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="K144" t="n">
         <v>5</v>
@@ -18175,7 +18321,7 @@
       </c>
       <c r="I145"/>
       <c r="J145" t="s">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="K145" t="n">
         <v>5</v>
@@ -18208,7 +18354,7 @@
       </c>
       <c r="I146"/>
       <c r="J146" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="K146" t="n">
         <v>5</v>
@@ -18241,7 +18387,7 @@
       </c>
       <c r="I147"/>
       <c r="J147" t="s">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="K147" t="n">
         <v>5</v>
@@ -18274,7 +18420,7 @@
       </c>
       <c r="I148"/>
       <c r="J148" t="s">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="K148" t="n">
         <v>5</v>
@@ -18373,7 +18519,7 @@
       </c>
       <c r="I151"/>
       <c r="J151" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="K151" t="n">
         <v>5</v>
@@ -18406,7 +18552,7 @@
       </c>
       <c r="I152"/>
       <c r="J152" t="s">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="K152" t="n">
         <v>5</v>
@@ -18505,7 +18651,7 @@
       </c>
       <c r="I155"/>
       <c r="J155" t="s">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="K155" t="n">
         <v>6</v>
@@ -18538,7 +18684,7 @@
       </c>
       <c r="I156"/>
       <c r="J156" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="K156" t="n">
         <v>6</v>
@@ -18571,7 +18717,7 @@
       </c>
       <c r="I157"/>
       <c r="J157" t="s">
-        <v>381</v>
+        <v>390</v>
       </c>
       <c r="K157" t="n">
         <v>6</v>
@@ -18604,7 +18750,7 @@
       </c>
       <c r="I158"/>
       <c r="J158" t="s">
-        <v>382</v>
+        <v>391</v>
       </c>
       <c r="K158" t="n">
         <v>6</v>
@@ -18637,7 +18783,7 @@
       </c>
       <c r="I159"/>
       <c r="J159" t="s">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="K159" t="n">
         <v>6</v>
@@ -18670,7 +18816,7 @@
       </c>
       <c r="I160"/>
       <c r="J160" t="s">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="K160" t="n">
         <v>6</v>
@@ -18703,7 +18849,7 @@
       </c>
       <c r="I161"/>
       <c r="J161" t="s">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="K161" t="n">
         <v>6</v>
@@ -18736,7 +18882,7 @@
       </c>
       <c r="I162"/>
       <c r="J162" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="K162" t="n">
         <v>6</v>
@@ -18769,7 +18915,7 @@
       </c>
       <c r="I163"/>
       <c r="J163" t="s">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="K163" t="n">
         <v>6</v>
@@ -18802,7 +18948,7 @@
       </c>
       <c r="I164"/>
       <c r="J164" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="K164" t="n">
         <v>6</v>
@@ -18835,7 +18981,7 @@
       </c>
       <c r="I165"/>
       <c r="J165" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="K165" t="n">
         <v>6</v>
@@ -18868,7 +19014,7 @@
       </c>
       <c r="I166"/>
       <c r="J166" t="s">
-        <v>289</v>
+        <v>411</v>
       </c>
       <c r="K166" t="n">
         <v>6</v>
@@ -18901,7 +19047,7 @@
       </c>
       <c r="I167"/>
       <c r="J167" t="s">
-        <v>403</v>
+        <v>412</v>
       </c>
       <c r="K167" t="n">
         <v>6</v>
@@ -18934,7 +19080,7 @@
       </c>
       <c r="I168"/>
       <c r="J168" t="s">
-        <v>404</v>
+        <v>413</v>
       </c>
       <c r="K168" t="n">
         <v>6</v>
@@ -18967,7 +19113,7 @@
       </c>
       <c r="I169"/>
       <c r="J169" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="K169" t="n">
         <v>6</v>
@@ -19000,7 +19146,7 @@
       </c>
       <c r="I170"/>
       <c r="J170" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="K170" t="n">
         <v>6</v>
@@ -19033,7 +19179,7 @@
       </c>
       <c r="I171"/>
       <c r="J171" t="s">
-        <v>407</v>
+        <v>416</v>
       </c>
       <c r="K171" t="n">
         <v>6</v>
@@ -19066,7 +19212,7 @@
       </c>
       <c r="I172"/>
       <c r="J172" t="s">
-        <v>373</v>
+        <v>382</v>
       </c>
       <c r="K172" t="n">
         <v>6</v>
@@ -19074,7 +19220,7 @@
     </row>
     <row r="173">
       <c r="A173" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B173" t="s">
         <v>17</v>
@@ -19099,7 +19245,7 @@
       </c>
       <c r="I173"/>
       <c r="J173" t="s">
-        <v>408</v>
+        <v>417</v>
       </c>
       <c r="K173" t="n">
         <v>6</v>
@@ -19165,7 +19311,7 @@
       </c>
       <c r="I175"/>
       <c r="J175" t="s">
-        <v>409</v>
+        <v>418</v>
       </c>
       <c r="K175" t="n">
         <v>6</v>
@@ -19198,7 +19344,7 @@
       </c>
       <c r="I176"/>
       <c r="J176" t="s">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="K176" t="n">
         <v>6</v>
@@ -19231,7 +19377,7 @@
       </c>
       <c r="I177"/>
       <c r="J177" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="K177" t="n">
         <v>6</v>
@@ -19264,7 +19410,7 @@
       </c>
       <c r="I178"/>
       <c r="J178" t="s">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="K178" t="n">
         <v>6</v>
@@ -19297,7 +19443,7 @@
       </c>
       <c r="I179"/>
       <c r="J179" t="s">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="K179" t="n">
         <v>6</v>
@@ -19429,7 +19575,7 @@
       </c>
       <c r="I183"/>
       <c r="J183" t="s">
-        <v>410</v>
+        <v>419</v>
       </c>
       <c r="K183" t="n">
         <v>6</v>
@@ -19462,7 +19608,7 @@
       </c>
       <c r="I184"/>
       <c r="J184" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="K184" t="n">
         <v>6</v>
@@ -19476,7 +19622,7 @@
         <v>11</v>
       </c>
       <c r="C185" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D185" t="n">
         <v>429</v>
@@ -19509,7 +19655,7 @@
         <v>17</v>
       </c>
       <c r="C186" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D186" t="n">
         <v>56</v>
@@ -19542,7 +19688,7 @@
         <v>17</v>
       </c>
       <c r="C187" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D187" t="n">
         <v>35</v>
@@ -19561,7 +19707,7 @@
       </c>
       <c r="I187"/>
       <c r="J187" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="K187" t="n">
         <v>7</v>
@@ -19575,7 +19721,7 @@
         <v>17</v>
       </c>
       <c r="C188" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D188" t="n">
         <v>34</v>
@@ -19594,7 +19740,7 @@
       </c>
       <c r="I188"/>
       <c r="J188" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="K188" t="n">
         <v>7</v>
@@ -19608,7 +19754,7 @@
         <v>17</v>
       </c>
       <c r="C189" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D189" t="n">
         <v>20</v>
@@ -19627,7 +19773,7 @@
       </c>
       <c r="I189"/>
       <c r="J189" t="s">
-        <v>413</v>
+        <v>422</v>
       </c>
       <c r="K189" t="n">
         <v>7</v>
@@ -19641,7 +19787,7 @@
         <v>48</v>
       </c>
       <c r="C190" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D190" t="n">
         <v>12</v>
@@ -19660,7 +19806,7 @@
       </c>
       <c r="I190"/>
       <c r="J190" t="s">
-        <v>414</v>
+        <v>423</v>
       </c>
       <c r="K190" t="n">
         <v>7</v>
@@ -19674,7 +19820,7 @@
         <v>48</v>
       </c>
       <c r="C191" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D191" t="n">
         <v>5</v>
@@ -19693,7 +19839,7 @@
       </c>
       <c r="I191"/>
       <c r="J191" t="s">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="K191" t="n">
         <v>7</v>
@@ -19707,7 +19853,7 @@
         <v>11</v>
       </c>
       <c r="C192" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D192" t="n">
         <v>4</v>
@@ -19726,7 +19872,7 @@
       </c>
       <c r="I192"/>
       <c r="J192" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="K192" t="n">
         <v>7</v>
@@ -19740,7 +19886,7 @@
         <v>11</v>
       </c>
       <c r="C193" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D193" t="n">
         <v>3</v>
@@ -19759,7 +19905,7 @@
       </c>
       <c r="I193"/>
       <c r="J193" t="s">
-        <v>416</v>
+        <v>425</v>
       </c>
       <c r="K193" t="n">
         <v>7</v>
@@ -19773,7 +19919,7 @@
         <v>17</v>
       </c>
       <c r="C194" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D194" t="n">
         <v>3</v>
@@ -19792,7 +19938,7 @@
       </c>
       <c r="I194"/>
       <c r="J194" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="K194" t="n">
         <v>7</v>
@@ -19806,7 +19952,7 @@
         <v>17</v>
       </c>
       <c r="C195" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D195" t="n">
         <v>2</v>
@@ -19839,7 +19985,7 @@
         <v>28</v>
       </c>
       <c r="C196" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D196" t="n">
         <v>1</v>
@@ -19858,7 +20004,7 @@
       </c>
       <c r="I196"/>
       <c r="J196" t="s">
-        <v>417</v>
+        <v>426</v>
       </c>
       <c r="K196" t="n">
         <v>7</v>
@@ -19872,7 +20018,7 @@
         <v>17</v>
       </c>
       <c r="C197" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D197" t="n">
         <v>1</v>
@@ -19891,7 +20037,7 @@
       </c>
       <c r="I197"/>
       <c r="J197" t="s">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="K197" t="n">
         <v>7</v>
@@ -19905,7 +20051,7 @@
         <v>11</v>
       </c>
       <c r="C198" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D198" t="n">
         <v>0</v>
@@ -19924,7 +20070,7 @@
       </c>
       <c r="I198"/>
       <c r="J198" t="s">
-        <v>419</v>
+        <v>428</v>
       </c>
       <c r="K198" t="n">
         <v>7</v>
@@ -19938,7 +20084,7 @@
         <v>11</v>
       </c>
       <c r="C199" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D199" t="n">
         <v>0</v>
@@ -19957,7 +20103,7 @@
       </c>
       <c r="I199"/>
       <c r="J199" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="K199" t="n">
         <v>7</v>
@@ -19971,7 +20117,7 @@
         <v>33</v>
       </c>
       <c r="C200" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D200" t="n">
         <v>0</v>
@@ -19990,7 +20136,7 @@
       </c>
       <c r="I200"/>
       <c r="J200" t="s">
-        <v>420</v>
+        <v>429</v>
       </c>
       <c r="K200" t="n">
         <v>7</v>
@@ -20004,7 +20150,7 @@
         <v>28</v>
       </c>
       <c r="C201" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D201" t="n">
         <v>0</v>
@@ -20023,7 +20169,7 @@
       </c>
       <c r="I201"/>
       <c r="J201" t="s">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="K201" t="n">
         <v>7</v>
@@ -20031,13 +20177,13 @@
     </row>
     <row r="202">
       <c r="A202" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B202" t="s">
         <v>17</v>
       </c>
       <c r="C202" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D202" t="n">
         <v>0</v>
@@ -20056,7 +20202,7 @@
       </c>
       <c r="I202"/>
       <c r="J202" t="s">
-        <v>422</v>
+        <v>431</v>
       </c>
       <c r="K202" t="n">
         <v>7</v>
@@ -20070,7 +20216,7 @@
         <v>17</v>
       </c>
       <c r="C203" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D203" t="n">
         <v>0</v>
@@ -20089,7 +20235,7 @@
       </c>
       <c r="I203"/>
       <c r="J203" t="s">
-        <v>423</v>
+        <v>432</v>
       </c>
       <c r="K203" t="n">
         <v>7</v>
@@ -20103,7 +20249,7 @@
         <v>33</v>
       </c>
       <c r="C204" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D204" t="n">
         <v>0</v>
@@ -20122,7 +20268,7 @@
       </c>
       <c r="I204"/>
       <c r="J204" t="s">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="K204" t="n">
         <v>7</v>
@@ -20136,7 +20282,7 @@
         <v>33</v>
       </c>
       <c r="C205" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D205" t="n">
         <v>0</v>
@@ -20155,7 +20301,7 @@
       </c>
       <c r="I205"/>
       <c r="J205" t="s">
-        <v>425</v>
+        <v>434</v>
       </c>
       <c r="K205" t="n">
         <v>7</v>
@@ -20169,7 +20315,7 @@
         <v>28</v>
       </c>
       <c r="C206" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D206" t="n">
         <v>0</v>
@@ -20188,7 +20334,7 @@
       </c>
       <c r="I206"/>
       <c r="J206" t="s">
-        <v>426</v>
+        <v>435</v>
       </c>
       <c r="K206" t="n">
         <v>7</v>
@@ -20202,7 +20348,7 @@
         <v>17</v>
       </c>
       <c r="C207" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D207" t="n">
         <v>0</v>
@@ -20221,7 +20367,7 @@
       </c>
       <c r="I207"/>
       <c r="J207" t="s">
-        <v>427</v>
+        <v>436</v>
       </c>
       <c r="K207" t="n">
         <v>7</v>
@@ -20235,7 +20381,7 @@
         <v>33</v>
       </c>
       <c r="C208" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D208" t="n">
         <v>0</v>
@@ -20254,7 +20400,7 @@
       </c>
       <c r="I208"/>
       <c r="J208" t="s">
-        <v>428</v>
+        <v>437</v>
       </c>
       <c r="K208" t="n">
         <v>7</v>
@@ -20268,7 +20414,7 @@
         <v>28</v>
       </c>
       <c r="C209" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D209" t="n">
         <v>0</v>
@@ -20287,7 +20433,7 @@
       </c>
       <c r="I209"/>
       <c r="J209" t="s">
-        <v>429</v>
+        <v>438</v>
       </c>
       <c r="K209" t="n">
         <v>7</v>
@@ -20301,7 +20447,7 @@
         <v>11</v>
       </c>
       <c r="C210" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D210" t="n">
         <v>0</v>
@@ -20320,7 +20466,7 @@
       </c>
       <c r="I210"/>
       <c r="J210" t="s">
-        <v>430</v>
+        <v>439</v>
       </c>
       <c r="K210" t="n">
         <v>7</v>
@@ -20334,7 +20480,7 @@
         <v>33</v>
       </c>
       <c r="C211" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D211" t="n">
         <v>0</v>
@@ -20353,7 +20499,7 @@
       </c>
       <c r="I211"/>
       <c r="J211" t="s">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="K211" t="n">
         <v>7</v>
@@ -20367,7 +20513,7 @@
         <v>28</v>
       </c>
       <c r="C212" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D212" t="n">
         <v>0</v>
@@ -20400,7 +20546,7 @@
         <v>11</v>
       </c>
       <c r="C213" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D213" t="n">
         <v>0</v>
@@ -20433,7 +20579,7 @@
         <v>28</v>
       </c>
       <c r="C214" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D214" t="n">
         <v>0</v>
@@ -20466,7 +20612,7 @@
         <v>17</v>
       </c>
       <c r="C215" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D215" t="n">
         <v>0</v>
@@ -20485,7 +20631,7 @@
       </c>
       <c r="I215"/>
       <c r="J215" t="s">
-        <v>410</v>
+        <v>419</v>
       </c>
       <c r="K215" t="n">
         <v>7</v>
@@ -20499,7 +20645,7 @@
         <v>28</v>
       </c>
       <c r="C216" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D216" t="n">
         <v>0</v>
@@ -20518,7 +20664,7 @@
       </c>
       <c r="I216"/>
       <c r="J216" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="K216" t="n">
         <v>7</v>
@@ -20532,7 +20678,7 @@
         <v>11</v>
       </c>
       <c r="C217" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D217" t="n">
         <v>651</v>
@@ -20541,10 +20687,10 @@
         <v>429</v>
       </c>
       <c r="F217" t="n">
-        <v>1560</v>
+        <v>1569</v>
       </c>
       <c r="G217" t="n">
-        <v>1989</v>
+        <v>1998</v>
       </c>
       <c r="H217" t="n">
         <v>1</v>
@@ -20565,7 +20711,7 @@
         <v>17</v>
       </c>
       <c r="C218" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D218" t="n">
         <v>258</v>
@@ -20584,7 +20730,7 @@
       </c>
       <c r="I218"/>
       <c r="J218" t="s">
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="K218" t="n">
         <v>8</v>
@@ -20598,7 +20744,7 @@
         <v>17</v>
       </c>
       <c r="C219" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D219" t="n">
         <v>212</v>
@@ -20631,7 +20777,7 @@
         <v>17</v>
       </c>
       <c r="C220" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D220" t="n">
         <v>92</v>
@@ -20650,7 +20796,7 @@
       </c>
       <c r="I220"/>
       <c r="J220" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="K220" t="n">
         <v>8</v>
@@ -20664,7 +20810,7 @@
         <v>17</v>
       </c>
       <c r="C221" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D221" t="n">
         <v>44</v>
@@ -20683,7 +20829,7 @@
       </c>
       <c r="I221"/>
       <c r="J221" t="s">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="K221" t="n">
         <v>8</v>
@@ -20697,7 +20843,7 @@
         <v>48</v>
       </c>
       <c r="C222" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D222" t="n">
         <v>17</v>
@@ -20716,7 +20862,7 @@
       </c>
       <c r="I222"/>
       <c r="J222" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="K222" t="n">
         <v>8</v>
@@ -20730,7 +20876,7 @@
         <v>11</v>
       </c>
       <c r="C223" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D223" t="n">
         <v>14</v>
@@ -20749,7 +20895,7 @@
       </c>
       <c r="I223"/>
       <c r="J223" t="s">
-        <v>431</v>
+        <v>440</v>
       </c>
       <c r="K223" t="n">
         <v>8</v>
@@ -20763,7 +20909,7 @@
         <v>48</v>
       </c>
       <c r="C224" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D224" t="n">
         <v>14</v>
@@ -20782,7 +20928,7 @@
       </c>
       <c r="I224"/>
       <c r="J224" t="s">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="K224" t="n">
         <v>8</v>
@@ -20796,7 +20942,7 @@
         <v>17</v>
       </c>
       <c r="C225" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D225" t="n">
         <v>10</v>
@@ -20829,7 +20975,7 @@
         <v>33</v>
       </c>
       <c r="C226" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D226" t="n">
         <v>7</v>
@@ -20848,7 +20994,7 @@
       </c>
       <c r="I226"/>
       <c r="J226" t="s">
-        <v>432</v>
+        <v>441</v>
       </c>
       <c r="K226" t="n">
         <v>8</v>
@@ -20862,7 +21008,7 @@
         <v>17</v>
       </c>
       <c r="C227" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D227" t="n">
         <v>7</v>
@@ -20895,7 +21041,7 @@
         <v>11</v>
       </c>
       <c r="C228" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D228" t="n">
         <v>4</v>
@@ -20914,7 +21060,7 @@
       </c>
       <c r="I228"/>
       <c r="J228" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="K228" t="n">
         <v>8</v>
@@ -20928,7 +21074,7 @@
         <v>28</v>
       </c>
       <c r="C229" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D229" t="n">
         <v>1</v>
@@ -20947,7 +21093,7 @@
       </c>
       <c r="I229"/>
       <c r="J229" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="K229" t="n">
         <v>8</v>
@@ -20961,7 +21107,7 @@
         <v>28</v>
       </c>
       <c r="C230" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D230" t="n">
         <v>1</v>
@@ -20980,7 +21126,7 @@
       </c>
       <c r="I230"/>
       <c r="J230" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="K230" t="n">
         <v>8</v>
@@ -20988,13 +21134,13 @@
     </row>
     <row r="231">
       <c r="A231" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B231" t="s">
         <v>17</v>
       </c>
       <c r="C231" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D231" t="n">
         <v>1</v>
@@ -21013,7 +21159,7 @@
       </c>
       <c r="I231"/>
       <c r="J231" t="s">
-        <v>433</v>
+        <v>442</v>
       </c>
       <c r="K231" t="n">
         <v>8</v>
@@ -21021,32 +21167,32 @@
     </row>
     <row r="232">
       <c r="A232" t="s">
-        <v>86</v>
+        <v>30</v>
       </c>
       <c r="B232" t="s">
         <v>11</v>
       </c>
       <c r="C232" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D232" t="n">
         <v>0</v>
       </c>
       <c r="E232" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F232" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G232" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H232" t="n">
         <v>16</v>
       </c>
       <c r="I232"/>
       <c r="J232" t="s">
-        <v>434</v>
+        <v>106</v>
       </c>
       <c r="K232" t="n">
         <v>8</v>
@@ -21054,32 +21200,32 @@
     </row>
     <row r="233">
       <c r="A233" t="s">
-        <v>52</v>
+        <v>86</v>
       </c>
       <c r="B233" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="C233" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D233" t="n">
         <v>0</v>
       </c>
       <c r="E233" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F233" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G233" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H233" t="n">
         <v>17</v>
       </c>
       <c r="I233"/>
       <c r="J233" t="s">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="K233" t="n">
         <v>8</v>
@@ -21087,13 +21233,13 @@
     </row>
     <row r="234">
       <c r="A234" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="B234" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="C234" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D234" t="n">
         <v>0</v>
@@ -21102,17 +21248,17 @@
         <v>0</v>
       </c>
       <c r="F234" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G234" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H234" t="n">
         <v>18</v>
       </c>
       <c r="I234"/>
       <c r="J234" t="s">
-        <v>436</v>
+        <v>299</v>
       </c>
       <c r="K234" t="n">
         <v>8</v>
@@ -21126,7 +21272,7 @@
         <v>33</v>
       </c>
       <c r="C235" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D235" t="n">
         <v>0</v>
@@ -21145,7 +21291,7 @@
       </c>
       <c r="I235"/>
       <c r="J235" t="s">
-        <v>407</v>
+        <v>416</v>
       </c>
       <c r="K235" t="n">
         <v>8</v>
@@ -21159,7 +21305,7 @@
         <v>28</v>
       </c>
       <c r="C236" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D236" t="n">
         <v>0</v>
@@ -21178,7 +21324,7 @@
       </c>
       <c r="I236"/>
       <c r="J236" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="K236" t="n">
         <v>8</v>
@@ -21192,7 +21338,7 @@
         <v>17</v>
       </c>
       <c r="C237" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D237" t="n">
         <v>0</v>
@@ -21211,7 +21357,7 @@
       </c>
       <c r="I237"/>
       <c r="J237" t="s">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="K237" t="n">
         <v>8</v>
@@ -21225,7 +21371,7 @@
         <v>33</v>
       </c>
       <c r="C238" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D238" t="n">
         <v>0</v>
@@ -21244,7 +21390,7 @@
       </c>
       <c r="I238"/>
       <c r="J238" t="s">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="K238" t="n">
         <v>8</v>
@@ -21258,7 +21404,7 @@
         <v>28</v>
       </c>
       <c r="C239" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D239" t="n">
         <v>0</v>
@@ -21291,7 +21437,7 @@
         <v>17</v>
       </c>
       <c r="C240" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D240" t="n">
         <v>0</v>
@@ -21324,7 +21470,7 @@
         <v>11</v>
       </c>
       <c r="C241" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D241" t="n">
         <v>0</v>
@@ -21343,7 +21489,7 @@
       </c>
       <c r="I241"/>
       <c r="J241" t="s">
-        <v>439</v>
+        <v>446</v>
       </c>
       <c r="K241" t="n">
         <v>8</v>
@@ -21357,7 +21503,7 @@
         <v>33</v>
       </c>
       <c r="C242" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D242" t="n">
         <v>0</v>
@@ -21376,7 +21522,7 @@
       </c>
       <c r="I242"/>
       <c r="J242" t="s">
-        <v>440</v>
+        <v>447</v>
       </c>
       <c r="K242" t="n">
         <v>8</v>
@@ -21390,7 +21536,7 @@
         <v>28</v>
       </c>
       <c r="C243" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D243" t="n">
         <v>0</v>
@@ -21409,7 +21555,7 @@
       </c>
       <c r="I243"/>
       <c r="J243" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K243" t="n">
         <v>8</v>
@@ -21423,7 +21569,7 @@
         <v>17</v>
       </c>
       <c r="C244" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D244" t="n">
         <v>0</v>
@@ -21442,7 +21588,7 @@
       </c>
       <c r="I244"/>
       <c r="J244" t="s">
-        <v>441</v>
+        <v>448</v>
       </c>
       <c r="K244" t="n">
         <v>8</v>
@@ -21456,7 +21602,7 @@
         <v>11</v>
       </c>
       <c r="C245" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D245" t="n">
         <v>0</v>
@@ -21489,7 +21635,7 @@
         <v>28</v>
       </c>
       <c r="C246" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D246" t="n">
         <v>0</v>
@@ -21522,7 +21668,7 @@
         <v>17</v>
       </c>
       <c r="C247" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D247" t="n">
         <v>0</v>
@@ -21541,7 +21687,7 @@
       </c>
       <c r="I247"/>
       <c r="J247" t="s">
-        <v>410</v>
+        <v>419</v>
       </c>
       <c r="K247" t="n">
         <v>8</v>
@@ -21555,7 +21701,7 @@
         <v>28</v>
       </c>
       <c r="C248" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D248" t="n">
         <v>0</v>
@@ -21574,7 +21720,7 @@
       </c>
       <c r="I248"/>
       <c r="J248" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="K248" t="n">
         <v>8</v>
@@ -21588,10 +21734,10 @@
         <v>11</v>
       </c>
       <c r="C249" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="D249" t="n">
-        <v>1560</v>
+        <v>1569</v>
       </c>
       <c r="E249" t="n">
         <v>651</v>
@@ -21606,7 +21752,7 @@
         <v>1</v>
       </c>
       <c r="I249" t="n">
-        <v>12306</v>
+        <v>12315</v>
       </c>
       <c r="J249" t="s">
         <v>13</v>
@@ -21623,7 +21769,7 @@
         <v>17</v>
       </c>
       <c r="C250" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="D250" t="n">
         <v>330</v>
@@ -21644,7 +21790,7 @@
         <v>1091</v>
       </c>
       <c r="J250" t="s">
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="K250" t="n">
         <v>9</v>
@@ -21658,7 +21804,7 @@
         <v>17</v>
       </c>
       <c r="C251" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="D251" t="n">
         <v>168</v>
@@ -21679,7 +21825,7 @@
         <v>875</v>
       </c>
       <c r="J251" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="K251" t="n">
         <v>9</v>
@@ -21693,7 +21839,7 @@
         <v>11</v>
       </c>
       <c r="C252" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="D252" t="n">
         <v>156</v>
@@ -21728,7 +21874,7 @@
         <v>17</v>
       </c>
       <c r="C253" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="D253" t="n">
         <v>144</v>
@@ -21749,7 +21895,7 @@
         <v>1571</v>
       </c>
       <c r="J253" t="s">
-        <v>442</v>
+        <v>449</v>
       </c>
       <c r="K253" t="n">
         <v>9</v>
@@ -21763,7 +21909,7 @@
         <v>17</v>
       </c>
       <c r="C254" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="D254" t="n">
         <v>110</v>
@@ -21784,7 +21930,7 @@
         <v>324</v>
       </c>
       <c r="J254" t="s">
-        <v>382</v>
+        <v>391</v>
       </c>
       <c r="K254" t="n">
         <v>9</v>
@@ -21798,7 +21944,7 @@
         <v>48</v>
       </c>
       <c r="C255" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="D255" t="n">
         <v>18</v>
@@ -21819,7 +21965,7 @@
         <v>210</v>
       </c>
       <c r="J255" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="K255" t="n">
         <v>9</v>
@@ -21833,7 +21979,7 @@
         <v>48</v>
       </c>
       <c r="C256" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="D256" t="n">
         <v>16</v>
@@ -21854,7 +22000,7 @@
         <v>199</v>
       </c>
       <c r="J256" t="s">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="K256" t="n">
         <v>9</v>
@@ -21868,7 +22014,7 @@
         <v>17</v>
       </c>
       <c r="C257" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="D257" t="n">
         <v>15</v>
@@ -21903,7 +22049,7 @@
         <v>33</v>
       </c>
       <c r="C258" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="D258" t="n">
         <v>11</v>
@@ -21924,7 +22070,7 @@
         <v>19</v>
       </c>
       <c r="J258" t="s">
-        <v>432</v>
+        <v>441</v>
       </c>
       <c r="K258" t="n">
         <v>9</v>
@@ -21932,34 +22078,34 @@
     </row>
     <row r="259">
       <c r="A259" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="B259" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C259" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="D259" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E259" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F259" t="n">
         <v>0</v>
       </c>
       <c r="G259" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H259" t="n">
         <v>11</v>
       </c>
       <c r="I259" t="n">
-        <v>155</v>
+        <v>56</v>
       </c>
       <c r="J259" t="s">
-        <v>185</v>
+        <v>131</v>
       </c>
       <c r="K259" t="n">
         <v>9</v>
@@ -21967,34 +22113,34 @@
     </row>
     <row r="260">
       <c r="A260" t="s">
-        <v>86</v>
+        <v>23</v>
       </c>
       <c r="B260" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C260" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="D260" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E260" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F260" t="n">
         <v>0</v>
       </c>
       <c r="G260" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H260" t="n">
         <v>12</v>
       </c>
       <c r="I260" t="n">
-        <v>78</v>
+        <v>155</v>
       </c>
       <c r="J260" t="s">
-        <v>443</v>
+        <v>267</v>
       </c>
       <c r="K260" t="n">
         <v>9</v>
@@ -22002,34 +22148,34 @@
     </row>
     <row r="261">
       <c r="A261" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B261" t="s">
         <v>11</v>
       </c>
       <c r="C261" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="D261" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E261" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F261" t="n">
         <v>0</v>
       </c>
       <c r="G261" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H261" t="n">
         <v>13</v>
       </c>
       <c r="I261" t="n">
-        <v>15</v>
+        <v>78</v>
       </c>
       <c r="J261" t="s">
-        <v>368</v>
+        <v>450</v>
       </c>
       <c r="K261" t="n">
         <v>9</v>
@@ -22037,34 +22183,34 @@
     </row>
     <row r="262">
       <c r="A262" t="s">
-        <v>52</v>
+        <v>84</v>
       </c>
       <c r="B262" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="C262" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="D262" t="n">
         <v>2</v>
       </c>
       <c r="E262" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F262" t="n">
         <v>0</v>
       </c>
       <c r="G262" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H262" t="n">
         <v>14</v>
       </c>
       <c r="I262" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="J262" t="s">
-        <v>444</v>
+        <v>393</v>
       </c>
       <c r="K262" t="n">
         <v>9</v>
@@ -22072,34 +22218,34 @@
     </row>
     <row r="263">
       <c r="A263" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="B263" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C263" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="D263" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E263" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F263" t="n">
         <v>0</v>
       </c>
       <c r="G263" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H263" t="n">
         <v>15</v>
       </c>
       <c r="I263" t="n">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="J263" t="s">
-        <v>445</v>
+        <v>323</v>
       </c>
       <c r="K263" t="n">
         <v>9</v>
@@ -22107,34 +22253,34 @@
     </row>
     <row r="264">
       <c r="A264" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B264" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="C264" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="D264" t="n">
         <v>1</v>
       </c>
       <c r="E264" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F264" t="n">
         <v>0</v>
       </c>
       <c r="G264" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H264" t="n">
         <v>16</v>
       </c>
       <c r="I264" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="J264" t="s">
-        <v>106</v>
+        <v>451</v>
       </c>
       <c r="K264" t="n">
         <v>9</v>
@@ -22148,7 +22294,7 @@
         <v>33</v>
       </c>
       <c r="C265" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="D265" t="n">
         <v>1</v>
@@ -22169,7 +22315,7 @@
         <v>40</v>
       </c>
       <c r="J265" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="K265" t="n">
         <v>9</v>
@@ -22183,7 +22329,7 @@
         <v>28</v>
       </c>
       <c r="C266" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="D266" t="n">
         <v>1</v>
@@ -22204,7 +22350,7 @@
         <v>4</v>
       </c>
       <c r="J266" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="K266" t="n">
         <v>9</v>
@@ -22218,7 +22364,7 @@
         <v>17</v>
       </c>
       <c r="C267" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="D267" t="n">
         <v>1</v>
@@ -22239,7 +22385,7 @@
         <v>1</v>
       </c>
       <c r="J267" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="K267" t="n">
         <v>9</v>
@@ -22253,7 +22399,7 @@
         <v>33</v>
       </c>
       <c r="C268" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="D268" t="n">
         <v>1</v>
@@ -22288,7 +22434,7 @@
         <v>28</v>
       </c>
       <c r="C269" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="D269" t="n">
         <v>1</v>
@@ -22309,7 +22455,7 @@
         <v>1</v>
       </c>
       <c r="J269" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="K269" t="n">
         <v>9</v>
@@ -22323,7 +22469,7 @@
         <v>28</v>
       </c>
       <c r="C270" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="D270" t="n">
         <v>0</v>
@@ -22344,7 +22490,7 @@
         <v>28</v>
       </c>
       <c r="J270" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="K270" t="n">
         <v>9</v>
@@ -22352,13 +22498,13 @@
     </row>
     <row r="271">
       <c r="A271" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B271" t="s">
         <v>17</v>
       </c>
       <c r="C271" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="D271" t="n">
         <v>0</v>
@@ -22379,7 +22525,7 @@
         <v>1</v>
       </c>
       <c r="J271" t="s">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="K271" t="n">
         <v>9</v>
@@ -22393,7 +22539,7 @@
         <v>11</v>
       </c>
       <c r="C272" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="D272" t="n">
         <v>0</v>
@@ -22414,7 +22560,7 @@
         <v>17</v>
       </c>
       <c r="J272" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="K272" t="n">
         <v>9</v>
@@ -22428,7 +22574,7 @@
         <v>33</v>
       </c>
       <c r="C273" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="D273" t="n">
         <v>0</v>
@@ -22449,7 +22595,7 @@
         <v>3</v>
       </c>
       <c r="J273" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="K273" t="n">
         <v>9</v>
@@ -22463,7 +22609,7 @@
         <v>17</v>
       </c>
       <c r="C274" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="D274" t="n">
         <v>0</v>
@@ -22484,7 +22630,7 @@
         <v>1</v>
       </c>
       <c r="J274" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="K274" t="n">
         <v>9</v>
@@ -22498,7 +22644,7 @@
         <v>28</v>
       </c>
       <c r="C275" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="D275" t="n">
         <v>0</v>
@@ -22519,7 +22665,7 @@
         <v>1</v>
       </c>
       <c r="J275" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K275" t="n">
         <v>9</v>
@@ -22533,7 +22679,7 @@
         <v>17</v>
       </c>
       <c r="C276" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="D276" t="n">
         <v>0</v>
@@ -22554,7 +22700,7 @@
         <v>1</v>
       </c>
       <c r="J276" t="s">
-        <v>441</v>
+        <v>448</v>
       </c>
       <c r="K276" t="n">
         <v>9</v>
@@ -22568,7 +22714,7 @@
         <v>11</v>
       </c>
       <c r="C277" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="D277" t="n">
         <v>0</v>
@@ -22603,7 +22749,7 @@
         <v>28</v>
       </c>
       <c r="C278" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="D278" t="n">
         <v>0</v>
@@ -22638,7 +22784,7 @@
         <v>17</v>
       </c>
       <c r="C279" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="D279" t="n">
         <v>0</v>
@@ -22659,7 +22805,7 @@
         <v>1</v>
       </c>
       <c r="J279" t="s">
-        <v>410</v>
+        <v>419</v>
       </c>
       <c r="K279" t="n">
         <v>9</v>
@@ -22673,7 +22819,7 @@
         <v>28</v>
       </c>
       <c r="C280" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="D280" t="n">
         <v>0</v>
@@ -22694,7 +22840,7 @@
         <v>1</v>
       </c>
       <c r="J280" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="K280" t="n">
         <v>9</v>

--- a/Outcome/Publish/figure_data/fig2.xlsx
+++ b/Outcome/Publish/figure_data/fig2.xlsx
@@ -189,10 +189,10 @@
     <t xml:space="preserve">21. Genital herpes</t>
   </si>
   <si>
-    <t xml:space="preserve">CA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22. CA</t>
+    <t xml:space="preserve">CA (HPV)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22. CA (HPV)</t>
   </si>
   <si>
     <t xml:space="preserve">Rubella</t>
@@ -348,7 +348,7 @@
     <t xml:space="preserve">20. Genital herpes</t>
   </si>
   <si>
-    <t xml:space="preserve">21. CA</t>
+    <t xml:space="preserve">21. CA (HPV)</t>
   </si>
   <si>
     <t xml:space="preserve">22. HCV</t>
@@ -423,7 +423,7 @@
     <t xml:space="preserve">16. Typhoid</t>
   </si>
   <si>
-    <t xml:space="preserve">17. CA</t>
+    <t xml:space="preserve">17. CA (HPV)</t>
   </si>
   <si>
     <t xml:space="preserve">18. Genital herpes</t>
@@ -498,7 +498,7 @@
     <t xml:space="preserve">10. Mumps</t>
   </si>
   <si>
-    <t xml:space="preserve">11. CA</t>
+    <t xml:space="preserve">11. CA (HPV)</t>
   </si>
   <si>
     <t xml:space="preserve">12. Syphilis</t>
@@ -567,7 +567,7 @@
     <t xml:space="preserve">9. Syphilis</t>
   </si>
   <si>
-    <t xml:space="preserve">10. CA</t>
+    <t xml:space="preserve">10. CA (HPV)</t>
   </si>
   <si>
     <t xml:space="preserve">11. Malaria</t>
@@ -642,7 +642,7 @@
     <t xml:space="preserve">9. Chikungunya</t>
   </si>
   <si>
-    <t xml:space="preserve">12. CA</t>
+    <t xml:space="preserve">12. CA (HPV)</t>
   </si>
   <si>
     <t xml:space="preserve">13. Melioidosis</t>
@@ -894,7 +894,7 @@
     <t xml:space="preserve">7. HBV</t>
   </si>
   <si>
-    <t xml:space="preserve">9. CA</t>
+    <t xml:space="preserve">9. CA (HPV)</t>
   </si>
   <si>
     <t xml:space="preserve">11. Genital herpes</t>

--- a/Outcome/Publish/figure_data/fig2.xlsx
+++ b/Outcome/Publish/figure_data/fig2.xlsx
@@ -6,14 +6,18 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="A" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="B" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="panel A" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="panel C" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="panelB" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="panelC" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="panelE" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="panelF" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="460">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="474">
   <si>
     <t xml:space="preserve">Shortname</t>
   </si>
@@ -1393,6 +1397,48 @@
   </si>
   <si>
     <t xml:space="preserve">26. Chikungunya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AgeGroup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AgeGroupID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max_tag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Outcome</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0-4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Others</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5-9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20-39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40-59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Outcome_Fill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total</t>
   </si>
 </sst>
 </file>
@@ -22850,4 +22896,4218 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>460</v>
+      </c>
+      <c r="B1" t="s">
+        <v>461</v>
+      </c>
+      <c r="C1" t="s">
+        <v>462</v>
+      </c>
+      <c r="D1" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>464</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1257443.09356982</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>464</v>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" t="n">
+        <v>653657.716757474</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>464</v>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" t="n">
+        <v>778335.599275723</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>464</v>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>465</v>
+      </c>
+      <c r="D5" t="n">
+        <v>410123.920688537</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>466</v>
+      </c>
+      <c r="B6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" t="n">
+        <v>207210.406276195</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>466</v>
+      </c>
+      <c r="B7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" t="n">
+        <v>673512.419055442</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>466</v>
+      </c>
+      <c r="B8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" t="n">
+        <v>195085.354133745</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>466</v>
+      </c>
+      <c r="B9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" t="s">
+        <v>465</v>
+      </c>
+      <c r="D9" t="n">
+        <v>410266.63549073</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>467</v>
+      </c>
+      <c r="B10" t="n">
+        <v>3</v>
+      </c>
+      <c r="C10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" t="n">
+        <v>506614.23767102</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>467</v>
+      </c>
+      <c r="B11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" t="n">
+        <v>316456.043334976</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>467</v>
+      </c>
+      <c r="B12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C12" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" t="n">
+        <v>150953.40760811</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>467</v>
+      </c>
+      <c r="B13" t="n">
+        <v>3</v>
+      </c>
+      <c r="C13" t="s">
+        <v>465</v>
+      </c>
+      <c r="D13" t="n">
+        <v>179593.807880794</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>468</v>
+      </c>
+      <c r="B14" t="n">
+        <v>4</v>
+      </c>
+      <c r="C14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" t="n">
+        <v>247009.701346544</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>468</v>
+      </c>
+      <c r="B15" t="n">
+        <v>4</v>
+      </c>
+      <c r="C15" t="s">
+        <v>16</v>
+      </c>
+      <c r="D15" t="n">
+        <v>228775.52818226</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>468</v>
+      </c>
+      <c r="B16" t="n">
+        <v>4</v>
+      </c>
+      <c r="C16" t="s">
+        <v>14</v>
+      </c>
+      <c r="D16" t="n">
+        <v>80702.3493339277</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>468</v>
+      </c>
+      <c r="B17" t="n">
+        <v>4</v>
+      </c>
+      <c r="C17" t="s">
+        <v>465</v>
+      </c>
+      <c r="D17" t="n">
+        <v>183659.029471305</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>469</v>
+      </c>
+      <c r="B18" t="n">
+        <v>5</v>
+      </c>
+      <c r="C18" t="s">
+        <v>10</v>
+      </c>
+      <c r="D18" t="n">
+        <v>291134.379172665</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>469</v>
+      </c>
+      <c r="B19" t="n">
+        <v>5</v>
+      </c>
+      <c r="C19" t="s">
+        <v>19</v>
+      </c>
+      <c r="D19" t="n">
+        <v>929183.598146722</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>469</v>
+      </c>
+      <c r="B20" t="n">
+        <v>5</v>
+      </c>
+      <c r="C20" t="s">
+        <v>16</v>
+      </c>
+      <c r="D20" t="n">
+        <v>441897.75352447</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>469</v>
+      </c>
+      <c r="B21" t="n">
+        <v>5</v>
+      </c>
+      <c r="C21" t="s">
+        <v>465</v>
+      </c>
+      <c r="D21" t="n">
+        <v>736636.991080393</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>470</v>
+      </c>
+      <c r="B22" t="n">
+        <v>6</v>
+      </c>
+      <c r="C22" t="s">
+        <v>10</v>
+      </c>
+      <c r="D22" t="n">
+        <v>627996.515626952</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>470</v>
+      </c>
+      <c r="B23" t="n">
+        <v>6</v>
+      </c>
+      <c r="C23" t="s">
+        <v>19</v>
+      </c>
+      <c r="D23" t="n">
+        <v>574225.006020735</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>470</v>
+      </c>
+      <c r="B24" t="n">
+        <v>6</v>
+      </c>
+      <c r="C24" t="s">
+        <v>16</v>
+      </c>
+      <c r="D24" t="n">
+        <v>153375.300212957</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>470</v>
+      </c>
+      <c r="B25" t="n">
+        <v>6</v>
+      </c>
+      <c r="C25" t="s">
+        <v>465</v>
+      </c>
+      <c r="D25" t="n">
+        <v>401809.73923787</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>471</v>
+      </c>
+      <c r="B26" t="n">
+        <v>7</v>
+      </c>
+      <c r="C26" t="s">
+        <v>10</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1610710.70529812</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>471</v>
+      </c>
+      <c r="B27" t="n">
+        <v>7</v>
+      </c>
+      <c r="C27" t="s">
+        <v>19</v>
+      </c>
+      <c r="D27" t="n">
+        <v>282733.321002064</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>471</v>
+      </c>
+      <c r="B28" t="n">
+        <v>7</v>
+      </c>
+      <c r="C28" t="s">
+        <v>16</v>
+      </c>
+      <c r="D28" t="n">
+        <v>48021.1745600166</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>471</v>
+      </c>
+      <c r="B29" t="n">
+        <v>7</v>
+      </c>
+      <c r="C29" t="s">
+        <v>465</v>
+      </c>
+      <c r="D29" t="n">
+        <v>182634.26604043</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>460</v>
+      </c>
+      <c r="B1" t="s">
+        <v>461</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" t="s">
+        <v>463</v>
+      </c>
+      <c r="F1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>464</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>464</v>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>464</v>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>127</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>464</v>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>158</v>
+      </c>
+      <c r="D5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>464</v>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="s">
+        <v>176</v>
+      </c>
+      <c r="D6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>464</v>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="s">
+        <v>203</v>
+      </c>
+      <c r="D7" t="n">
+        <v>6</v>
+      </c>
+      <c r="E7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>464</v>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="s">
+        <v>237</v>
+      </c>
+      <c r="D8" t="n">
+        <v>7</v>
+      </c>
+      <c r="E8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>464</v>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="s">
+        <v>262</v>
+      </c>
+      <c r="D9" t="n">
+        <v>8</v>
+      </c>
+      <c r="E9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>464</v>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="s">
+        <v>291</v>
+      </c>
+      <c r="D10" t="n">
+        <v>9</v>
+      </c>
+      <c r="E10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F10" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>467</v>
+      </c>
+      <c r="B11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="s">
+        <v>16</v>
+      </c>
+      <c r="F11" t="s">
+        <v>17</v>
+      </c>
+      <c r="G11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>467</v>
+      </c>
+      <c r="B12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C12" t="s">
+        <v>92</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" t="s">
+        <v>16</v>
+      </c>
+      <c r="F12" t="s">
+        <v>17</v>
+      </c>
+      <c r="G12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>467</v>
+      </c>
+      <c r="B13" t="n">
+        <v>3</v>
+      </c>
+      <c r="C13" t="s">
+        <v>127</v>
+      </c>
+      <c r="D13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" t="s">
+        <v>16</v>
+      </c>
+      <c r="F13" t="s">
+        <v>17</v>
+      </c>
+      <c r="G13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>467</v>
+      </c>
+      <c r="B14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C14" t="s">
+        <v>158</v>
+      </c>
+      <c r="D14" t="n">
+        <v>4</v>
+      </c>
+      <c r="E14" t="s">
+        <v>16</v>
+      </c>
+      <c r="F14" t="s">
+        <v>17</v>
+      </c>
+      <c r="G14" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>467</v>
+      </c>
+      <c r="B15" t="n">
+        <v>3</v>
+      </c>
+      <c r="C15" t="s">
+        <v>176</v>
+      </c>
+      <c r="D15" t="n">
+        <v>5</v>
+      </c>
+      <c r="E15" t="s">
+        <v>19</v>
+      </c>
+      <c r="F15" t="s">
+        <v>11</v>
+      </c>
+      <c r="G15" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>467</v>
+      </c>
+      <c r="B16" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" t="s">
+        <v>203</v>
+      </c>
+      <c r="D16" t="n">
+        <v>6</v>
+      </c>
+      <c r="E16" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" t="s">
+        <v>11</v>
+      </c>
+      <c r="G16" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>467</v>
+      </c>
+      <c r="B17" t="n">
+        <v>3</v>
+      </c>
+      <c r="C17" t="s">
+        <v>237</v>
+      </c>
+      <c r="D17" t="n">
+        <v>7</v>
+      </c>
+      <c r="E17" t="s">
+        <v>16</v>
+      </c>
+      <c r="F17" t="s">
+        <v>17</v>
+      </c>
+      <c r="G17" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>467</v>
+      </c>
+      <c r="B18" t="n">
+        <v>3</v>
+      </c>
+      <c r="C18" t="s">
+        <v>262</v>
+      </c>
+      <c r="D18" t="n">
+        <v>8</v>
+      </c>
+      <c r="E18" t="s">
+        <v>19</v>
+      </c>
+      <c r="F18" t="s">
+        <v>11</v>
+      </c>
+      <c r="G18" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>467</v>
+      </c>
+      <c r="B19" t="n">
+        <v>3</v>
+      </c>
+      <c r="C19" t="s">
+        <v>291</v>
+      </c>
+      <c r="D19" t="n">
+        <v>9</v>
+      </c>
+      <c r="E19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F19" t="s">
+        <v>11</v>
+      </c>
+      <c r="G19" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>468</v>
+      </c>
+      <c r="B20" t="n">
+        <v>4</v>
+      </c>
+      <c r="C20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="s">
+        <v>16</v>
+      </c>
+      <c r="F20" t="s">
+        <v>17</v>
+      </c>
+      <c r="G20" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>468</v>
+      </c>
+      <c r="B21" t="n">
+        <v>4</v>
+      </c>
+      <c r="C21" t="s">
+        <v>92</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" t="s">
+        <v>16</v>
+      </c>
+      <c r="F21" t="s">
+        <v>17</v>
+      </c>
+      <c r="G21" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>468</v>
+      </c>
+      <c r="B22" t="n">
+        <v>4</v>
+      </c>
+      <c r="C22" t="s">
+        <v>127</v>
+      </c>
+      <c r="D22" t="n">
+        <v>3</v>
+      </c>
+      <c r="E22" t="s">
+        <v>16</v>
+      </c>
+      <c r="F22" t="s">
+        <v>17</v>
+      </c>
+      <c r="G22" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>468</v>
+      </c>
+      <c r="B23" t="n">
+        <v>4</v>
+      </c>
+      <c r="C23" t="s">
+        <v>158</v>
+      </c>
+      <c r="D23" t="n">
+        <v>4</v>
+      </c>
+      <c r="E23" t="s">
+        <v>16</v>
+      </c>
+      <c r="F23" t="s">
+        <v>17</v>
+      </c>
+      <c r="G23" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>468</v>
+      </c>
+      <c r="B24" t="n">
+        <v>4</v>
+      </c>
+      <c r="C24" t="s">
+        <v>176</v>
+      </c>
+      <c r="D24" t="n">
+        <v>5</v>
+      </c>
+      <c r="E24" t="s">
+        <v>19</v>
+      </c>
+      <c r="F24" t="s">
+        <v>11</v>
+      </c>
+      <c r="G24" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>468</v>
+      </c>
+      <c r="B25" t="n">
+        <v>4</v>
+      </c>
+      <c r="C25" t="s">
+        <v>203</v>
+      </c>
+      <c r="D25" t="n">
+        <v>6</v>
+      </c>
+      <c r="E25" t="s">
+        <v>16</v>
+      </c>
+      <c r="F25" t="s">
+        <v>17</v>
+      </c>
+      <c r="G25" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>468</v>
+      </c>
+      <c r="B26" t="n">
+        <v>4</v>
+      </c>
+      <c r="C26" t="s">
+        <v>237</v>
+      </c>
+      <c r="D26" t="n">
+        <v>7</v>
+      </c>
+      <c r="E26" t="s">
+        <v>16</v>
+      </c>
+      <c r="F26" t="s">
+        <v>17</v>
+      </c>
+      <c r="G26" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>468</v>
+      </c>
+      <c r="B27" t="n">
+        <v>4</v>
+      </c>
+      <c r="C27" t="s">
+        <v>262</v>
+      </c>
+      <c r="D27" t="n">
+        <v>8</v>
+      </c>
+      <c r="E27" t="s">
+        <v>19</v>
+      </c>
+      <c r="F27" t="s">
+        <v>11</v>
+      </c>
+      <c r="G27" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>468</v>
+      </c>
+      <c r="B28" t="n">
+        <v>4</v>
+      </c>
+      <c r="C28" t="s">
+        <v>291</v>
+      </c>
+      <c r="D28" t="n">
+        <v>9</v>
+      </c>
+      <c r="E28" t="s">
+        <v>19</v>
+      </c>
+      <c r="F28" t="s">
+        <v>11</v>
+      </c>
+      <c r="G28" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>469</v>
+      </c>
+      <c r="B29" t="n">
+        <v>5</v>
+      </c>
+      <c r="C29" t="s">
+        <v>12</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" t="s">
+        <v>16</v>
+      </c>
+      <c r="F29" t="s">
+        <v>17</v>
+      </c>
+      <c r="G29" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>469</v>
+      </c>
+      <c r="B30" t="n">
+        <v>5</v>
+      </c>
+      <c r="C30" t="s">
+        <v>92</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2</v>
+      </c>
+      <c r="E30" t="s">
+        <v>16</v>
+      </c>
+      <c r="F30" t="s">
+        <v>17</v>
+      </c>
+      <c r="G30" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>469</v>
+      </c>
+      <c r="B31" t="n">
+        <v>5</v>
+      </c>
+      <c r="C31" t="s">
+        <v>127</v>
+      </c>
+      <c r="D31" t="n">
+        <v>3</v>
+      </c>
+      <c r="E31" t="s">
+        <v>16</v>
+      </c>
+      <c r="F31" t="s">
+        <v>17</v>
+      </c>
+      <c r="G31" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>469</v>
+      </c>
+      <c r="B32" t="n">
+        <v>5</v>
+      </c>
+      <c r="C32" t="s">
+        <v>158</v>
+      </c>
+      <c r="D32" t="n">
+        <v>4</v>
+      </c>
+      <c r="E32" t="s">
+        <v>16</v>
+      </c>
+      <c r="F32" t="s">
+        <v>17</v>
+      </c>
+      <c r="G32" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>469</v>
+      </c>
+      <c r="B33" t="n">
+        <v>5</v>
+      </c>
+      <c r="C33" t="s">
+        <v>176</v>
+      </c>
+      <c r="D33" t="n">
+        <v>5</v>
+      </c>
+      <c r="E33" t="s">
+        <v>19</v>
+      </c>
+      <c r="F33" t="s">
+        <v>11</v>
+      </c>
+      <c r="G33" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>469</v>
+      </c>
+      <c r="B34" t="n">
+        <v>5</v>
+      </c>
+      <c r="C34" t="s">
+        <v>203</v>
+      </c>
+      <c r="D34" t="n">
+        <v>6</v>
+      </c>
+      <c r="E34" t="s">
+        <v>19</v>
+      </c>
+      <c r="F34" t="s">
+        <v>11</v>
+      </c>
+      <c r="G34" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>469</v>
+      </c>
+      <c r="B35" t="n">
+        <v>5</v>
+      </c>
+      <c r="C35" t="s">
+        <v>237</v>
+      </c>
+      <c r="D35" t="n">
+        <v>7</v>
+      </c>
+      <c r="E35" t="s">
+        <v>10</v>
+      </c>
+      <c r="F35" t="s">
+        <v>11</v>
+      </c>
+      <c r="G35" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>469</v>
+      </c>
+      <c r="B36" t="n">
+        <v>5</v>
+      </c>
+      <c r="C36" t="s">
+        <v>262</v>
+      </c>
+      <c r="D36" t="n">
+        <v>8</v>
+      </c>
+      <c r="E36" t="s">
+        <v>19</v>
+      </c>
+      <c r="F36" t="s">
+        <v>11</v>
+      </c>
+      <c r="G36" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>469</v>
+      </c>
+      <c r="B37" t="n">
+        <v>5</v>
+      </c>
+      <c r="C37" t="s">
+        <v>291</v>
+      </c>
+      <c r="D37" t="n">
+        <v>9</v>
+      </c>
+      <c r="E37" t="s">
+        <v>19</v>
+      </c>
+      <c r="F37" t="s">
+        <v>11</v>
+      </c>
+      <c r="G37" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>470</v>
+      </c>
+      <c r="B38" t="n">
+        <v>6</v>
+      </c>
+      <c r="C38" t="s">
+        <v>12</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" t="s">
+        <v>10</v>
+      </c>
+      <c r="F38" t="s">
+        <v>11</v>
+      </c>
+      <c r="G38" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>470</v>
+      </c>
+      <c r="B39" t="n">
+        <v>6</v>
+      </c>
+      <c r="C39" t="s">
+        <v>92</v>
+      </c>
+      <c r="D39" t="n">
+        <v>2</v>
+      </c>
+      <c r="E39" t="s">
+        <v>10</v>
+      </c>
+      <c r="F39" t="s">
+        <v>11</v>
+      </c>
+      <c r="G39" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>470</v>
+      </c>
+      <c r="B40" t="n">
+        <v>6</v>
+      </c>
+      <c r="C40" t="s">
+        <v>127</v>
+      </c>
+      <c r="D40" t="n">
+        <v>3</v>
+      </c>
+      <c r="E40" t="s">
+        <v>10</v>
+      </c>
+      <c r="F40" t="s">
+        <v>11</v>
+      </c>
+      <c r="G40" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>470</v>
+      </c>
+      <c r="B41" t="n">
+        <v>6</v>
+      </c>
+      <c r="C41" t="s">
+        <v>158</v>
+      </c>
+      <c r="D41" t="n">
+        <v>4</v>
+      </c>
+      <c r="E41" t="s">
+        <v>10</v>
+      </c>
+      <c r="F41" t="s">
+        <v>11</v>
+      </c>
+      <c r="G41" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>470</v>
+      </c>
+      <c r="B42" t="n">
+        <v>6</v>
+      </c>
+      <c r="C42" t="s">
+        <v>176</v>
+      </c>
+      <c r="D42" t="n">
+        <v>5</v>
+      </c>
+      <c r="E42" t="s">
+        <v>10</v>
+      </c>
+      <c r="F42" t="s">
+        <v>11</v>
+      </c>
+      <c r="G42" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>470</v>
+      </c>
+      <c r="B43" t="n">
+        <v>6</v>
+      </c>
+      <c r="C43" t="s">
+        <v>203</v>
+      </c>
+      <c r="D43" t="n">
+        <v>6</v>
+      </c>
+      <c r="E43" t="s">
+        <v>10</v>
+      </c>
+      <c r="F43" t="s">
+        <v>11</v>
+      </c>
+      <c r="G43" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>470</v>
+      </c>
+      <c r="B44" t="n">
+        <v>6</v>
+      </c>
+      <c r="C44" t="s">
+        <v>237</v>
+      </c>
+      <c r="D44" t="n">
+        <v>7</v>
+      </c>
+      <c r="E44" t="s">
+        <v>10</v>
+      </c>
+      <c r="F44" t="s">
+        <v>11</v>
+      </c>
+      <c r="G44" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>470</v>
+      </c>
+      <c r="B45" t="n">
+        <v>6</v>
+      </c>
+      <c r="C45" t="s">
+        <v>262</v>
+      </c>
+      <c r="D45" t="n">
+        <v>8</v>
+      </c>
+      <c r="E45" t="s">
+        <v>10</v>
+      </c>
+      <c r="F45" t="s">
+        <v>11</v>
+      </c>
+      <c r="G45" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>470</v>
+      </c>
+      <c r="B46" t="n">
+        <v>6</v>
+      </c>
+      <c r="C46" t="s">
+        <v>291</v>
+      </c>
+      <c r="D46" t="n">
+        <v>9</v>
+      </c>
+      <c r="E46" t="s">
+        <v>19</v>
+      </c>
+      <c r="F46" t="s">
+        <v>11</v>
+      </c>
+      <c r="G46" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>466</v>
+      </c>
+      <c r="B47" t="n">
+        <v>2</v>
+      </c>
+      <c r="C47" t="s">
+        <v>12</v>
+      </c>
+      <c r="D47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" t="s">
+        <v>14</v>
+      </c>
+      <c r="F47" t="s">
+        <v>11</v>
+      </c>
+      <c r="G47" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>466</v>
+      </c>
+      <c r="B48" t="n">
+        <v>2</v>
+      </c>
+      <c r="C48" t="s">
+        <v>92</v>
+      </c>
+      <c r="D48" t="n">
+        <v>2</v>
+      </c>
+      <c r="E48" t="s">
+        <v>14</v>
+      </c>
+      <c r="F48" t="s">
+        <v>11</v>
+      </c>
+      <c r="G48" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>466</v>
+      </c>
+      <c r="B49" t="n">
+        <v>2</v>
+      </c>
+      <c r="C49" t="s">
+        <v>127</v>
+      </c>
+      <c r="D49" t="n">
+        <v>3</v>
+      </c>
+      <c r="E49" t="s">
+        <v>16</v>
+      </c>
+      <c r="F49" t="s">
+        <v>17</v>
+      </c>
+      <c r="G49" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>466</v>
+      </c>
+      <c r="B50" t="n">
+        <v>2</v>
+      </c>
+      <c r="C50" t="s">
+        <v>158</v>
+      </c>
+      <c r="D50" t="n">
+        <v>4</v>
+      </c>
+      <c r="E50" t="s">
+        <v>14</v>
+      </c>
+      <c r="F50" t="s">
+        <v>11</v>
+      </c>
+      <c r="G50" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>466</v>
+      </c>
+      <c r="B51" t="n">
+        <v>2</v>
+      </c>
+      <c r="C51" t="s">
+        <v>176</v>
+      </c>
+      <c r="D51" t="n">
+        <v>5</v>
+      </c>
+      <c r="E51" t="s">
+        <v>19</v>
+      </c>
+      <c r="F51" t="s">
+        <v>11</v>
+      </c>
+      <c r="G51" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>466</v>
+      </c>
+      <c r="B52" t="n">
+        <v>2</v>
+      </c>
+      <c r="C52" t="s">
+        <v>203</v>
+      </c>
+      <c r="D52" t="n">
+        <v>6</v>
+      </c>
+      <c r="E52" t="s">
+        <v>19</v>
+      </c>
+      <c r="F52" t="s">
+        <v>11</v>
+      </c>
+      <c r="G52" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>466</v>
+      </c>
+      <c r="B53" t="n">
+        <v>2</v>
+      </c>
+      <c r="C53" t="s">
+        <v>237</v>
+      </c>
+      <c r="D53" t="n">
+        <v>7</v>
+      </c>
+      <c r="E53" t="s">
+        <v>19</v>
+      </c>
+      <c r="F53" t="s">
+        <v>11</v>
+      </c>
+      <c r="G53" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>466</v>
+      </c>
+      <c r="B54" t="n">
+        <v>2</v>
+      </c>
+      <c r="C54" t="s">
+        <v>262</v>
+      </c>
+      <c r="D54" t="n">
+        <v>8</v>
+      </c>
+      <c r="E54" t="s">
+        <v>19</v>
+      </c>
+      <c r="F54" t="s">
+        <v>11</v>
+      </c>
+      <c r="G54" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>466</v>
+      </c>
+      <c r="B55" t="n">
+        <v>2</v>
+      </c>
+      <c r="C55" t="s">
+        <v>291</v>
+      </c>
+      <c r="D55" t="n">
+        <v>9</v>
+      </c>
+      <c r="E55" t="s">
+        <v>19</v>
+      </c>
+      <c r="F55" t="s">
+        <v>11</v>
+      </c>
+      <c r="G55" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>471</v>
+      </c>
+      <c r="B56" t="n">
+        <v>7</v>
+      </c>
+      <c r="C56" t="s">
+        <v>12</v>
+      </c>
+      <c r="D56" t="n">
+        <v>1</v>
+      </c>
+      <c r="E56" t="s">
+        <v>10</v>
+      </c>
+      <c r="F56" t="s">
+        <v>11</v>
+      </c>
+      <c r="G56" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>471</v>
+      </c>
+      <c r="B57" t="n">
+        <v>7</v>
+      </c>
+      <c r="C57" t="s">
+        <v>92</v>
+      </c>
+      <c r="D57" t="n">
+        <v>2</v>
+      </c>
+      <c r="E57" t="s">
+        <v>10</v>
+      </c>
+      <c r="F57" t="s">
+        <v>11</v>
+      </c>
+      <c r="G57" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>471</v>
+      </c>
+      <c r="B58" t="n">
+        <v>7</v>
+      </c>
+      <c r="C58" t="s">
+        <v>127</v>
+      </c>
+      <c r="D58" t="n">
+        <v>3</v>
+      </c>
+      <c r="E58" t="s">
+        <v>10</v>
+      </c>
+      <c r="F58" t="s">
+        <v>11</v>
+      </c>
+      <c r="G58" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>471</v>
+      </c>
+      <c r="B59" t="n">
+        <v>7</v>
+      </c>
+      <c r="C59" t="s">
+        <v>158</v>
+      </c>
+      <c r="D59" t="n">
+        <v>4</v>
+      </c>
+      <c r="E59" t="s">
+        <v>10</v>
+      </c>
+      <c r="F59" t="s">
+        <v>11</v>
+      </c>
+      <c r="G59" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>471</v>
+      </c>
+      <c r="B60" t="n">
+        <v>7</v>
+      </c>
+      <c r="C60" t="s">
+        <v>176</v>
+      </c>
+      <c r="D60" t="n">
+        <v>5</v>
+      </c>
+      <c r="E60" t="s">
+        <v>10</v>
+      </c>
+      <c r="F60" t="s">
+        <v>11</v>
+      </c>
+      <c r="G60" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>471</v>
+      </c>
+      <c r="B61" t="n">
+        <v>7</v>
+      </c>
+      <c r="C61" t="s">
+        <v>203</v>
+      </c>
+      <c r="D61" t="n">
+        <v>6</v>
+      </c>
+      <c r="E61" t="s">
+        <v>10</v>
+      </c>
+      <c r="F61" t="s">
+        <v>11</v>
+      </c>
+      <c r="G61" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>471</v>
+      </c>
+      <c r="B62" t="n">
+        <v>7</v>
+      </c>
+      <c r="C62" t="s">
+        <v>237</v>
+      </c>
+      <c r="D62" t="n">
+        <v>7</v>
+      </c>
+      <c r="E62" t="s">
+        <v>10</v>
+      </c>
+      <c r="F62" t="s">
+        <v>11</v>
+      </c>
+      <c r="G62" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>471</v>
+      </c>
+      <c r="B63" t="n">
+        <v>7</v>
+      </c>
+      <c r="C63" t="s">
+        <v>262</v>
+      </c>
+      <c r="D63" t="n">
+        <v>8</v>
+      </c>
+      <c r="E63" t="s">
+        <v>10</v>
+      </c>
+      <c r="F63" t="s">
+        <v>11</v>
+      </c>
+      <c r="G63" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>471</v>
+      </c>
+      <c r="B64" t="n">
+        <v>7</v>
+      </c>
+      <c r="C64" t="s">
+        <v>291</v>
+      </c>
+      <c r="D64" t="n">
+        <v>9</v>
+      </c>
+      <c r="E64" t="s">
+        <v>10</v>
+      </c>
+      <c r="F64" t="s">
+        <v>11</v>
+      </c>
+      <c r="G64" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>473</v>
+      </c>
+      <c r="B65" t="n">
+        <v>8.2</v>
+      </c>
+      <c r="C65" t="s">
+        <v>12</v>
+      </c>
+      <c r="D65" t="n">
+        <v>1</v>
+      </c>
+      <c r="E65" t="s">
+        <v>10</v>
+      </c>
+      <c r="F65" t="s">
+        <v>11</v>
+      </c>
+      <c r="G65" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>473</v>
+      </c>
+      <c r="B66" t="n">
+        <v>8.2</v>
+      </c>
+      <c r="C66" t="s">
+        <v>92</v>
+      </c>
+      <c r="D66" t="n">
+        <v>2</v>
+      </c>
+      <c r="E66" t="s">
+        <v>10</v>
+      </c>
+      <c r="F66" t="s">
+        <v>11</v>
+      </c>
+      <c r="G66" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>473</v>
+      </c>
+      <c r="B67" t="n">
+        <v>8.2</v>
+      </c>
+      <c r="C67" t="s">
+        <v>127</v>
+      </c>
+      <c r="D67" t="n">
+        <v>3</v>
+      </c>
+      <c r="E67" t="s">
+        <v>10</v>
+      </c>
+      <c r="F67" t="s">
+        <v>11</v>
+      </c>
+      <c r="G67" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>473</v>
+      </c>
+      <c r="B68" t="n">
+        <v>8.2</v>
+      </c>
+      <c r="C68" t="s">
+        <v>158</v>
+      </c>
+      <c r="D68" t="n">
+        <v>4</v>
+      </c>
+      <c r="E68" t="s">
+        <v>10</v>
+      </c>
+      <c r="F68" t="s">
+        <v>11</v>
+      </c>
+      <c r="G68" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>473</v>
+      </c>
+      <c r="B69" t="n">
+        <v>8.2</v>
+      </c>
+      <c r="C69" t="s">
+        <v>176</v>
+      </c>
+      <c r="D69" t="n">
+        <v>5</v>
+      </c>
+      <c r="E69" t="s">
+        <v>10</v>
+      </c>
+      <c r="F69" t="s">
+        <v>11</v>
+      </c>
+      <c r="G69" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>473</v>
+      </c>
+      <c r="B70" t="n">
+        <v>8.2</v>
+      </c>
+      <c r="C70" t="s">
+        <v>203</v>
+      </c>
+      <c r="D70" t="n">
+        <v>6</v>
+      </c>
+      <c r="E70" t="s">
+        <v>19</v>
+      </c>
+      <c r="F70" t="s">
+        <v>11</v>
+      </c>
+      <c r="G70" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>473</v>
+      </c>
+      <c r="B71" t="n">
+        <v>8.2</v>
+      </c>
+      <c r="C71" t="s">
+        <v>237</v>
+      </c>
+      <c r="D71" t="n">
+        <v>7</v>
+      </c>
+      <c r="E71" t="s">
+        <v>10</v>
+      </c>
+      <c r="F71" t="s">
+        <v>11</v>
+      </c>
+      <c r="G71" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>473</v>
+      </c>
+      <c r="B72" t="n">
+        <v>8.2</v>
+      </c>
+      <c r="C72" t="s">
+        <v>262</v>
+      </c>
+      <c r="D72" t="n">
+        <v>8</v>
+      </c>
+      <c r="E72" t="s">
+        <v>19</v>
+      </c>
+      <c r="F72" t="s">
+        <v>11</v>
+      </c>
+      <c r="G72" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>473</v>
+      </c>
+      <c r="B73" t="n">
+        <v>8.2</v>
+      </c>
+      <c r="C73" t="s">
+        <v>291</v>
+      </c>
+      <c r="D73" t="n">
+        <v>9</v>
+      </c>
+      <c r="E73" t="s">
+        <v>19</v>
+      </c>
+      <c r="F73" t="s">
+        <v>11</v>
+      </c>
+      <c r="G73" t="s">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>460</v>
+      </c>
+      <c r="B1" t="s">
+        <v>461</v>
+      </c>
+      <c r="C1" t="s">
+        <v>462</v>
+      </c>
+      <c r="D1" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>464</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="n">
+        <v>336.080851276617</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>464</v>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" t="n">
+        <v>40.4357357286305</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>464</v>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" t="n">
+        <v>169.699817591538</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>464</v>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>465</v>
+      </c>
+      <c r="D5" t="n">
+        <v>191.654561429724</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>466</v>
+      </c>
+      <c r="B6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" t="n">
+        <v>123.433050356455</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>466</v>
+      </c>
+      <c r="B7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" t="n">
+        <v>35.5613447848116</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>466</v>
+      </c>
+      <c r="B8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" t="n">
+        <v>202.728745098835</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>466</v>
+      </c>
+      <c r="B9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" t="s">
+        <v>465</v>
+      </c>
+      <c r="D9" t="n">
+        <v>75.0283032288795</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>467</v>
+      </c>
+      <c r="B10" t="n">
+        <v>3</v>
+      </c>
+      <c r="C10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" t="n">
+        <v>80.9761478966684</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>467</v>
+      </c>
+      <c r="B11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" t="n">
+        <v>28.3782590097662</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>467</v>
+      </c>
+      <c r="B12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C12" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12" t="n">
+        <v>205.745763807094</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>467</v>
+      </c>
+      <c r="B13" t="n">
+        <v>3</v>
+      </c>
+      <c r="C13" t="s">
+        <v>465</v>
+      </c>
+      <c r="D13" t="n">
+        <v>70.03391855809</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>468</v>
+      </c>
+      <c r="B14" t="n">
+        <v>4</v>
+      </c>
+      <c r="C14" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" t="n">
+        <v>66.3469031230314</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>468</v>
+      </c>
+      <c r="B15" t="n">
+        <v>4</v>
+      </c>
+      <c r="C15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" t="n">
+        <v>27.5016333122411</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>468</v>
+      </c>
+      <c r="B16" t="n">
+        <v>4</v>
+      </c>
+      <c r="C16" t="s">
+        <v>16</v>
+      </c>
+      <c r="D16" t="n">
+        <v>181.560075908497</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>468</v>
+      </c>
+      <c r="B17" t="n">
+        <v>4</v>
+      </c>
+      <c r="C17" t="s">
+        <v>465</v>
+      </c>
+      <c r="D17" t="n">
+        <v>67.4717672663374</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>469</v>
+      </c>
+      <c r="B18" t="n">
+        <v>5</v>
+      </c>
+      <c r="C18" t="s">
+        <v>10</v>
+      </c>
+      <c r="D18" t="n">
+        <v>638.968665995045</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>469</v>
+      </c>
+      <c r="B19" t="n">
+        <v>5</v>
+      </c>
+      <c r="C19" t="s">
+        <v>16</v>
+      </c>
+      <c r="D19" t="n">
+        <v>463.168177197315</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>469</v>
+      </c>
+      <c r="B20" t="n">
+        <v>5</v>
+      </c>
+      <c r="C20" t="s">
+        <v>39</v>
+      </c>
+      <c r="D20" t="n">
+        <v>211.095224336815</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>469</v>
+      </c>
+      <c r="B21" t="n">
+        <v>5</v>
+      </c>
+      <c r="C21" t="s">
+        <v>465</v>
+      </c>
+      <c r="D21" t="n">
+        <v>519.652686835759</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>470</v>
+      </c>
+      <c r="B22" t="n">
+        <v>6</v>
+      </c>
+      <c r="C22" t="s">
+        <v>10</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2446.43752319239</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>470</v>
+      </c>
+      <c r="B23" t="n">
+        <v>6</v>
+      </c>
+      <c r="C23" t="s">
+        <v>39</v>
+      </c>
+      <c r="D23" t="n">
+        <v>384.713255981969</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>470</v>
+      </c>
+      <c r="B24" t="n">
+        <v>6</v>
+      </c>
+      <c r="C24" t="s">
+        <v>54</v>
+      </c>
+      <c r="D24" t="n">
+        <v>505.262578811219</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>470</v>
+      </c>
+      <c r="B25" t="n">
+        <v>6</v>
+      </c>
+      <c r="C25" t="s">
+        <v>465</v>
+      </c>
+      <c r="D25" t="n">
+        <v>729.342289003483</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>471</v>
+      </c>
+      <c r="B26" t="n">
+        <v>7</v>
+      </c>
+      <c r="C26" t="s">
+        <v>10</v>
+      </c>
+      <c r="D26" t="n">
+        <v>8580.75685815979</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>471</v>
+      </c>
+      <c r="B27" t="n">
+        <v>7</v>
+      </c>
+      <c r="C27" t="s">
+        <v>19</v>
+      </c>
+      <c r="D27" t="n">
+        <v>269.151549583756</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>471</v>
+      </c>
+      <c r="B28" t="n">
+        <v>7</v>
+      </c>
+      <c r="C28" t="s">
+        <v>54</v>
+      </c>
+      <c r="D28" t="n">
+        <v>391.243936788619</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>471</v>
+      </c>
+      <c r="B29" t="n">
+        <v>7</v>
+      </c>
+      <c r="C29" t="s">
+        <v>465</v>
+      </c>
+      <c r="D29" t="n">
+        <v>629.570375736621</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>460</v>
+      </c>
+      <c r="B1" t="s">
+        <v>461</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" t="s">
+        <v>463</v>
+      </c>
+      <c r="F1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>464</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>464</v>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>464</v>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>127</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>464</v>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>158</v>
+      </c>
+      <c r="D5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>464</v>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="s">
+        <v>176</v>
+      </c>
+      <c r="D6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>464</v>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="s">
+        <v>203</v>
+      </c>
+      <c r="D7" t="n">
+        <v>6</v>
+      </c>
+      <c r="E7" t="s">
+        <v>30</v>
+      </c>
+      <c r="F7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>464</v>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="s">
+        <v>237</v>
+      </c>
+      <c r="D8" t="n">
+        <v>7</v>
+      </c>
+      <c r="E8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>464</v>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="s">
+        <v>262</v>
+      </c>
+      <c r="D9" t="n">
+        <v>8</v>
+      </c>
+      <c r="E9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>464</v>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="s">
+        <v>291</v>
+      </c>
+      <c r="D10" t="n">
+        <v>9</v>
+      </c>
+      <c r="E10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>467</v>
+      </c>
+      <c r="B11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="s">
+        <v>16</v>
+      </c>
+      <c r="F11" t="s">
+        <v>17</v>
+      </c>
+      <c r="G11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>467</v>
+      </c>
+      <c r="B12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C12" t="s">
+        <v>92</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" t="s">
+        <v>16</v>
+      </c>
+      <c r="F12" t="s">
+        <v>17</v>
+      </c>
+      <c r="G12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>467</v>
+      </c>
+      <c r="B13" t="n">
+        <v>3</v>
+      </c>
+      <c r="C13" t="s">
+        <v>127</v>
+      </c>
+      <c r="D13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" t="s">
+        <v>16</v>
+      </c>
+      <c r="F13" t="s">
+        <v>17</v>
+      </c>
+      <c r="G13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>467</v>
+      </c>
+      <c r="B14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C14" t="s">
+        <v>158</v>
+      </c>
+      <c r="D14" t="n">
+        <v>4</v>
+      </c>
+      <c r="E14" t="s">
+        <v>16</v>
+      </c>
+      <c r="F14" t="s">
+        <v>17</v>
+      </c>
+      <c r="G14" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>467</v>
+      </c>
+      <c r="B15" t="n">
+        <v>3</v>
+      </c>
+      <c r="C15" t="s">
+        <v>176</v>
+      </c>
+      <c r="D15" t="n">
+        <v>5</v>
+      </c>
+      <c r="E15" t="s">
+        <v>16</v>
+      </c>
+      <c r="F15" t="s">
+        <v>17</v>
+      </c>
+      <c r="G15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>467</v>
+      </c>
+      <c r="B16" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" t="s">
+        <v>203</v>
+      </c>
+      <c r="D16" t="n">
+        <v>6</v>
+      </c>
+      <c r="E16" t="s">
+        <v>16</v>
+      </c>
+      <c r="F16" t="s">
+        <v>17</v>
+      </c>
+      <c r="G16" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>467</v>
+      </c>
+      <c r="B17" t="n">
+        <v>3</v>
+      </c>
+      <c r="C17" t="s">
+        <v>237</v>
+      </c>
+      <c r="D17" t="n">
+        <v>7</v>
+      </c>
+      <c r="E17" t="s">
+        <v>16</v>
+      </c>
+      <c r="F17" t="s">
+        <v>17</v>
+      </c>
+      <c r="G17" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>467</v>
+      </c>
+      <c r="B18" t="n">
+        <v>3</v>
+      </c>
+      <c r="C18" t="s">
+        <v>262</v>
+      </c>
+      <c r="D18" t="n">
+        <v>8</v>
+      </c>
+      <c r="E18" t="s">
+        <v>16</v>
+      </c>
+      <c r="F18" t="s">
+        <v>17</v>
+      </c>
+      <c r="G18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>467</v>
+      </c>
+      <c r="B19" t="n">
+        <v>3</v>
+      </c>
+      <c r="C19" t="s">
+        <v>291</v>
+      </c>
+      <c r="D19" t="n">
+        <v>9</v>
+      </c>
+      <c r="E19" t="s">
+        <v>16</v>
+      </c>
+      <c r="F19" t="s">
+        <v>17</v>
+      </c>
+      <c r="G19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>468</v>
+      </c>
+      <c r="B20" t="n">
+        <v>4</v>
+      </c>
+      <c r="C20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="s">
+        <v>16</v>
+      </c>
+      <c r="F20" t="s">
+        <v>17</v>
+      </c>
+      <c r="G20" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>468</v>
+      </c>
+      <c r="B21" t="n">
+        <v>4</v>
+      </c>
+      <c r="C21" t="s">
+        <v>92</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" t="s">
+        <v>16</v>
+      </c>
+      <c r="F21" t="s">
+        <v>17</v>
+      </c>
+      <c r="G21" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>468</v>
+      </c>
+      <c r="B22" t="n">
+        <v>4</v>
+      </c>
+      <c r="C22" t="s">
+        <v>127</v>
+      </c>
+      <c r="D22" t="n">
+        <v>3</v>
+      </c>
+      <c r="E22" t="s">
+        <v>16</v>
+      </c>
+      <c r="F22" t="s">
+        <v>17</v>
+      </c>
+      <c r="G22" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>468</v>
+      </c>
+      <c r="B23" t="n">
+        <v>4</v>
+      </c>
+      <c r="C23" t="s">
+        <v>158</v>
+      </c>
+      <c r="D23" t="n">
+        <v>4</v>
+      </c>
+      <c r="E23" t="s">
+        <v>16</v>
+      </c>
+      <c r="F23" t="s">
+        <v>17</v>
+      </c>
+      <c r="G23" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>468</v>
+      </c>
+      <c r="B24" t="n">
+        <v>4</v>
+      </c>
+      <c r="C24" t="s">
+        <v>176</v>
+      </c>
+      <c r="D24" t="n">
+        <v>5</v>
+      </c>
+      <c r="E24" t="s">
+        <v>16</v>
+      </c>
+      <c r="F24" t="s">
+        <v>17</v>
+      </c>
+      <c r="G24" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>468</v>
+      </c>
+      <c r="B25" t="n">
+        <v>4</v>
+      </c>
+      <c r="C25" t="s">
+        <v>203</v>
+      </c>
+      <c r="D25" t="n">
+        <v>6</v>
+      </c>
+      <c r="E25" t="s">
+        <v>16</v>
+      </c>
+      <c r="F25" t="s">
+        <v>17</v>
+      </c>
+      <c r="G25" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>468</v>
+      </c>
+      <c r="B26" t="n">
+        <v>4</v>
+      </c>
+      <c r="C26" t="s">
+        <v>237</v>
+      </c>
+      <c r="D26" t="n">
+        <v>7</v>
+      </c>
+      <c r="E26" t="s">
+        <v>16</v>
+      </c>
+      <c r="F26" t="s">
+        <v>17</v>
+      </c>
+      <c r="G26" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>468</v>
+      </c>
+      <c r="B27" t="n">
+        <v>4</v>
+      </c>
+      <c r="C27" t="s">
+        <v>262</v>
+      </c>
+      <c r="D27" t="n">
+        <v>8</v>
+      </c>
+      <c r="E27" t="s">
+        <v>16</v>
+      </c>
+      <c r="F27" t="s">
+        <v>17</v>
+      </c>
+      <c r="G27" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>468</v>
+      </c>
+      <c r="B28" t="n">
+        <v>4</v>
+      </c>
+      <c r="C28" t="s">
+        <v>291</v>
+      </c>
+      <c r="D28" t="n">
+        <v>9</v>
+      </c>
+      <c r="E28" t="s">
+        <v>16</v>
+      </c>
+      <c r="F28" t="s">
+        <v>17</v>
+      </c>
+      <c r="G28" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>469</v>
+      </c>
+      <c r="B29" t="n">
+        <v>5</v>
+      </c>
+      <c r="C29" t="s">
+        <v>12</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" t="s">
+        <v>10</v>
+      </c>
+      <c r="F29" t="s">
+        <v>11</v>
+      </c>
+      <c r="G29" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>469</v>
+      </c>
+      <c r="B30" t="n">
+        <v>5</v>
+      </c>
+      <c r="C30" t="s">
+        <v>92</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2</v>
+      </c>
+      <c r="E30" t="s">
+        <v>10</v>
+      </c>
+      <c r="F30" t="s">
+        <v>11</v>
+      </c>
+      <c r="G30" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>469</v>
+      </c>
+      <c r="B31" t="n">
+        <v>5</v>
+      </c>
+      <c r="C31" t="s">
+        <v>127</v>
+      </c>
+      <c r="D31" t="n">
+        <v>3</v>
+      </c>
+      <c r="E31" t="s">
+        <v>10</v>
+      </c>
+      <c r="F31" t="s">
+        <v>11</v>
+      </c>
+      <c r="G31" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>469</v>
+      </c>
+      <c r="B32" t="n">
+        <v>5</v>
+      </c>
+      <c r="C32" t="s">
+        <v>158</v>
+      </c>
+      <c r="D32" t="n">
+        <v>4</v>
+      </c>
+      <c r="E32" t="s">
+        <v>10</v>
+      </c>
+      <c r="F32" t="s">
+        <v>11</v>
+      </c>
+      <c r="G32" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>469</v>
+      </c>
+      <c r="B33" t="n">
+        <v>5</v>
+      </c>
+      <c r="C33" t="s">
+        <v>176</v>
+      </c>
+      <c r="D33" t="n">
+        <v>5</v>
+      </c>
+      <c r="E33" t="s">
+        <v>16</v>
+      </c>
+      <c r="F33" t="s">
+        <v>17</v>
+      </c>
+      <c r="G33" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>469</v>
+      </c>
+      <c r="B34" t="n">
+        <v>5</v>
+      </c>
+      <c r="C34" t="s">
+        <v>203</v>
+      </c>
+      <c r="D34" t="n">
+        <v>6</v>
+      </c>
+      <c r="E34" t="s">
+        <v>16</v>
+      </c>
+      <c r="F34" t="s">
+        <v>17</v>
+      </c>
+      <c r="G34" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>469</v>
+      </c>
+      <c r="B35" t="n">
+        <v>5</v>
+      </c>
+      <c r="C35" t="s">
+        <v>237</v>
+      </c>
+      <c r="D35" t="n">
+        <v>7</v>
+      </c>
+      <c r="E35" t="s">
+        <v>10</v>
+      </c>
+      <c r="F35" t="s">
+        <v>11</v>
+      </c>
+      <c r="G35" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>469</v>
+      </c>
+      <c r="B36" t="n">
+        <v>5</v>
+      </c>
+      <c r="C36" t="s">
+        <v>262</v>
+      </c>
+      <c r="D36" t="n">
+        <v>8</v>
+      </c>
+      <c r="E36" t="s">
+        <v>16</v>
+      </c>
+      <c r="F36" t="s">
+        <v>17</v>
+      </c>
+      <c r="G36" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>469</v>
+      </c>
+      <c r="B37" t="n">
+        <v>5</v>
+      </c>
+      <c r="C37" t="s">
+        <v>291</v>
+      </c>
+      <c r="D37" t="n">
+        <v>9</v>
+      </c>
+      <c r="E37" t="s">
+        <v>10</v>
+      </c>
+      <c r="F37" t="s">
+        <v>11</v>
+      </c>
+      <c r="G37" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>470</v>
+      </c>
+      <c r="B38" t="n">
+        <v>6</v>
+      </c>
+      <c r="C38" t="s">
+        <v>12</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" t="s">
+        <v>10</v>
+      </c>
+      <c r="F38" t="s">
+        <v>11</v>
+      </c>
+      <c r="G38" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>470</v>
+      </c>
+      <c r="B39" t="n">
+        <v>6</v>
+      </c>
+      <c r="C39" t="s">
+        <v>92</v>
+      </c>
+      <c r="D39" t="n">
+        <v>2</v>
+      </c>
+      <c r="E39" t="s">
+        <v>10</v>
+      </c>
+      <c r="F39" t="s">
+        <v>11</v>
+      </c>
+      <c r="G39" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>470</v>
+      </c>
+      <c r="B40" t="n">
+        <v>6</v>
+      </c>
+      <c r="C40" t="s">
+        <v>127</v>
+      </c>
+      <c r="D40" t="n">
+        <v>3</v>
+      </c>
+      <c r="E40" t="s">
+        <v>10</v>
+      </c>
+      <c r="F40" t="s">
+        <v>11</v>
+      </c>
+      <c r="G40" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>470</v>
+      </c>
+      <c r="B41" t="n">
+        <v>6</v>
+      </c>
+      <c r="C41" t="s">
+        <v>158</v>
+      </c>
+      <c r="D41" t="n">
+        <v>4</v>
+      </c>
+      <c r="E41" t="s">
+        <v>10</v>
+      </c>
+      <c r="F41" t="s">
+        <v>11</v>
+      </c>
+      <c r="G41" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>470</v>
+      </c>
+      <c r="B42" t="n">
+        <v>6</v>
+      </c>
+      <c r="C42" t="s">
+        <v>176</v>
+      </c>
+      <c r="D42" t="n">
+        <v>5</v>
+      </c>
+      <c r="E42" t="s">
+        <v>10</v>
+      </c>
+      <c r="F42" t="s">
+        <v>11</v>
+      </c>
+      <c r="G42" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>470</v>
+      </c>
+      <c r="B43" t="n">
+        <v>6</v>
+      </c>
+      <c r="C43" t="s">
+        <v>203</v>
+      </c>
+      <c r="D43" t="n">
+        <v>6</v>
+      </c>
+      <c r="E43" t="s">
+        <v>10</v>
+      </c>
+      <c r="F43" t="s">
+        <v>11</v>
+      </c>
+      <c r="G43" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>470</v>
+      </c>
+      <c r="B44" t="n">
+        <v>6</v>
+      </c>
+      <c r="C44" t="s">
+        <v>237</v>
+      </c>
+      <c r="D44" t="n">
+        <v>7</v>
+      </c>
+      <c r="E44" t="s">
+        <v>10</v>
+      </c>
+      <c r="F44" t="s">
+        <v>11</v>
+      </c>
+      <c r="G44" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>470</v>
+      </c>
+      <c r="B45" t="n">
+        <v>6</v>
+      </c>
+      <c r="C45" t="s">
+        <v>262</v>
+      </c>
+      <c r="D45" t="n">
+        <v>8</v>
+      </c>
+      <c r="E45" t="s">
+        <v>10</v>
+      </c>
+      <c r="F45" t="s">
+        <v>11</v>
+      </c>
+      <c r="G45" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>470</v>
+      </c>
+      <c r="B46" t="n">
+        <v>6</v>
+      </c>
+      <c r="C46" t="s">
+        <v>291</v>
+      </c>
+      <c r="D46" t="n">
+        <v>9</v>
+      </c>
+      <c r="E46" t="s">
+        <v>10</v>
+      </c>
+      <c r="F46" t="s">
+        <v>11</v>
+      </c>
+      <c r="G46" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>466</v>
+      </c>
+      <c r="B47" t="n">
+        <v>2</v>
+      </c>
+      <c r="C47" t="s">
+        <v>12</v>
+      </c>
+      <c r="D47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" t="s">
+        <v>10</v>
+      </c>
+      <c r="F47" t="s">
+        <v>11</v>
+      </c>
+      <c r="G47" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>466</v>
+      </c>
+      <c r="B48" t="n">
+        <v>2</v>
+      </c>
+      <c r="C48" t="s">
+        <v>92</v>
+      </c>
+      <c r="D48" t="n">
+        <v>2</v>
+      </c>
+      <c r="E48" t="s">
+        <v>16</v>
+      </c>
+      <c r="F48" t="s">
+        <v>17</v>
+      </c>
+      <c r="G48" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>466</v>
+      </c>
+      <c r="B49" t="n">
+        <v>2</v>
+      </c>
+      <c r="C49" t="s">
+        <v>127</v>
+      </c>
+      <c r="D49" t="n">
+        <v>3</v>
+      </c>
+      <c r="E49" t="s">
+        <v>16</v>
+      </c>
+      <c r="F49" t="s">
+        <v>17</v>
+      </c>
+      <c r="G49" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>466</v>
+      </c>
+      <c r="B50" t="n">
+        <v>2</v>
+      </c>
+      <c r="C50" t="s">
+        <v>158</v>
+      </c>
+      <c r="D50" t="n">
+        <v>4</v>
+      </c>
+      <c r="E50" t="s">
+        <v>16</v>
+      </c>
+      <c r="F50" t="s">
+        <v>17</v>
+      </c>
+      <c r="G50" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>466</v>
+      </c>
+      <c r="B51" t="n">
+        <v>2</v>
+      </c>
+      <c r="C51" t="s">
+        <v>176</v>
+      </c>
+      <c r="D51" t="n">
+        <v>5</v>
+      </c>
+      <c r="E51" t="s">
+        <v>16</v>
+      </c>
+      <c r="F51" t="s">
+        <v>17</v>
+      </c>
+      <c r="G51" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>466</v>
+      </c>
+      <c r="B52" t="n">
+        <v>2</v>
+      </c>
+      <c r="C52" t="s">
+        <v>203</v>
+      </c>
+      <c r="D52" t="n">
+        <v>6</v>
+      </c>
+      <c r="E52" t="s">
+        <v>16</v>
+      </c>
+      <c r="F52" t="s">
+        <v>17</v>
+      </c>
+      <c r="G52" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>466</v>
+      </c>
+      <c r="B53" t="n">
+        <v>2</v>
+      </c>
+      <c r="C53" t="s">
+        <v>237</v>
+      </c>
+      <c r="D53" t="n">
+        <v>7</v>
+      </c>
+      <c r="E53" t="s">
+        <v>16</v>
+      </c>
+      <c r="F53" t="s">
+        <v>17</v>
+      </c>
+      <c r="G53" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>466</v>
+      </c>
+      <c r="B54" t="n">
+        <v>2</v>
+      </c>
+      <c r="C54" t="s">
+        <v>262</v>
+      </c>
+      <c r="D54" t="n">
+        <v>8</v>
+      </c>
+      <c r="E54" t="s">
+        <v>16</v>
+      </c>
+      <c r="F54" t="s">
+        <v>17</v>
+      </c>
+      <c r="G54" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>466</v>
+      </c>
+      <c r="B55" t="n">
+        <v>2</v>
+      </c>
+      <c r="C55" t="s">
+        <v>291</v>
+      </c>
+      <c r="D55" t="n">
+        <v>9</v>
+      </c>
+      <c r="E55" t="s">
+        <v>16</v>
+      </c>
+      <c r="F55" t="s">
+        <v>17</v>
+      </c>
+      <c r="G55" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>471</v>
+      </c>
+      <c r="B56" t="n">
+        <v>7</v>
+      </c>
+      <c r="C56" t="s">
+        <v>12</v>
+      </c>
+      <c r="D56" t="n">
+        <v>1</v>
+      </c>
+      <c r="E56" t="s">
+        <v>10</v>
+      </c>
+      <c r="F56" t="s">
+        <v>11</v>
+      </c>
+      <c r="G56" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>471</v>
+      </c>
+      <c r="B57" t="n">
+        <v>7</v>
+      </c>
+      <c r="C57" t="s">
+        <v>92</v>
+      </c>
+      <c r="D57" t="n">
+        <v>2</v>
+      </c>
+      <c r="E57" t="s">
+        <v>10</v>
+      </c>
+      <c r="F57" t="s">
+        <v>11</v>
+      </c>
+      <c r="G57" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>471</v>
+      </c>
+      <c r="B58" t="n">
+        <v>7</v>
+      </c>
+      <c r="C58" t="s">
+        <v>127</v>
+      </c>
+      <c r="D58" t="n">
+        <v>3</v>
+      </c>
+      <c r="E58" t="s">
+        <v>10</v>
+      </c>
+      <c r="F58" t="s">
+        <v>11</v>
+      </c>
+      <c r="G58" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>471</v>
+      </c>
+      <c r="B59" t="n">
+        <v>7</v>
+      </c>
+      <c r="C59" t="s">
+        <v>158</v>
+      </c>
+      <c r="D59" t="n">
+        <v>4</v>
+      </c>
+      <c r="E59" t="s">
+        <v>10</v>
+      </c>
+      <c r="F59" t="s">
+        <v>11</v>
+      </c>
+      <c r="G59" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>471</v>
+      </c>
+      <c r="B60" t="n">
+        <v>7</v>
+      </c>
+      <c r="C60" t="s">
+        <v>176</v>
+      </c>
+      <c r="D60" t="n">
+        <v>5</v>
+      </c>
+      <c r="E60" t="s">
+        <v>10</v>
+      </c>
+      <c r="F60" t="s">
+        <v>11</v>
+      </c>
+      <c r="G60" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>471</v>
+      </c>
+      <c r="B61" t="n">
+        <v>7</v>
+      </c>
+      <c r="C61" t="s">
+        <v>203</v>
+      </c>
+      <c r="D61" t="n">
+        <v>6</v>
+      </c>
+      <c r="E61" t="s">
+        <v>10</v>
+      </c>
+      <c r="F61" t="s">
+        <v>11</v>
+      </c>
+      <c r="G61" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>471</v>
+      </c>
+      <c r="B62" t="n">
+        <v>7</v>
+      </c>
+      <c r="C62" t="s">
+        <v>237</v>
+      </c>
+      <c r="D62" t="n">
+        <v>7</v>
+      </c>
+      <c r="E62" t="s">
+        <v>10</v>
+      </c>
+      <c r="F62" t="s">
+        <v>11</v>
+      </c>
+      <c r="G62" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>471</v>
+      </c>
+      <c r="B63" t="n">
+        <v>7</v>
+      </c>
+      <c r="C63" t="s">
+        <v>262</v>
+      </c>
+      <c r="D63" t="n">
+        <v>8</v>
+      </c>
+      <c r="E63" t="s">
+        <v>10</v>
+      </c>
+      <c r="F63" t="s">
+        <v>11</v>
+      </c>
+      <c r="G63" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>471</v>
+      </c>
+      <c r="B64" t="n">
+        <v>7</v>
+      </c>
+      <c r="C64" t="s">
+        <v>291</v>
+      </c>
+      <c r="D64" t="n">
+        <v>9</v>
+      </c>
+      <c r="E64" t="s">
+        <v>10</v>
+      </c>
+      <c r="F64" t="s">
+        <v>11</v>
+      </c>
+      <c r="G64" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>473</v>
+      </c>
+      <c r="B65" t="n">
+        <v>8.2</v>
+      </c>
+      <c r="C65" t="s">
+        <v>12</v>
+      </c>
+      <c r="D65" t="n">
+        <v>1</v>
+      </c>
+      <c r="E65" t="s">
+        <v>10</v>
+      </c>
+      <c r="F65" t="s">
+        <v>11</v>
+      </c>
+      <c r="G65" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>473</v>
+      </c>
+      <c r="B66" t="n">
+        <v>8.2</v>
+      </c>
+      <c r="C66" t="s">
+        <v>92</v>
+      </c>
+      <c r="D66" t="n">
+        <v>2</v>
+      </c>
+      <c r="E66" t="s">
+        <v>10</v>
+      </c>
+      <c r="F66" t="s">
+        <v>11</v>
+      </c>
+      <c r="G66" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>473</v>
+      </c>
+      <c r="B67" t="n">
+        <v>8.2</v>
+      </c>
+      <c r="C67" t="s">
+        <v>127</v>
+      </c>
+      <c r="D67" t="n">
+        <v>3</v>
+      </c>
+      <c r="E67" t="s">
+        <v>10</v>
+      </c>
+      <c r="F67" t="s">
+        <v>11</v>
+      </c>
+      <c r="G67" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>473</v>
+      </c>
+      <c r="B68" t="n">
+        <v>8.2</v>
+      </c>
+      <c r="C68" t="s">
+        <v>158</v>
+      </c>
+      <c r="D68" t="n">
+        <v>4</v>
+      </c>
+      <c r="E68" t="s">
+        <v>10</v>
+      </c>
+      <c r="F68" t="s">
+        <v>11</v>
+      </c>
+      <c r="G68" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>473</v>
+      </c>
+      <c r="B69" t="n">
+        <v>8.2</v>
+      </c>
+      <c r="C69" t="s">
+        <v>176</v>
+      </c>
+      <c r="D69" t="n">
+        <v>5</v>
+      </c>
+      <c r="E69" t="s">
+        <v>10</v>
+      </c>
+      <c r="F69" t="s">
+        <v>11</v>
+      </c>
+      <c r="G69" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>473</v>
+      </c>
+      <c r="B70" t="n">
+        <v>8.2</v>
+      </c>
+      <c r="C70" t="s">
+        <v>203</v>
+      </c>
+      <c r="D70" t="n">
+        <v>6</v>
+      </c>
+      <c r="E70" t="s">
+        <v>10</v>
+      </c>
+      <c r="F70" t="s">
+        <v>11</v>
+      </c>
+      <c r="G70" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>473</v>
+      </c>
+      <c r="B71" t="n">
+        <v>8.2</v>
+      </c>
+      <c r="C71" t="s">
+        <v>237</v>
+      </c>
+      <c r="D71" t="n">
+        <v>7</v>
+      </c>
+      <c r="E71" t="s">
+        <v>10</v>
+      </c>
+      <c r="F71" t="s">
+        <v>11</v>
+      </c>
+      <c r="G71" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>473</v>
+      </c>
+      <c r="B72" t="n">
+        <v>8.2</v>
+      </c>
+      <c r="C72" t="s">
+        <v>262</v>
+      </c>
+      <c r="D72" t="n">
+        <v>8</v>
+      </c>
+      <c r="E72" t="s">
+        <v>10</v>
+      </c>
+      <c r="F72" t="s">
+        <v>11</v>
+      </c>
+      <c r="G72" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>473</v>
+      </c>
+      <c r="B73" t="n">
+        <v>8.2</v>
+      </c>
+      <c r="C73" t="s">
+        <v>291</v>
+      </c>
+      <c r="D73" t="n">
+        <v>9</v>
+      </c>
+      <c r="E73" t="s">
+        <v>10</v>
+      </c>
+      <c r="F73" t="s">
+        <v>11</v>
+      </c>
+      <c r="G73" t="s">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
 </file>
--- a/Outcome/Publish/figure_data/fig2.xlsx
+++ b/Outcome/Publish/figure_data/fig2.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="474">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="468">
   <si>
     <t xml:space="preserve">Shortname</t>
   </si>
@@ -1324,19 +1324,7 @@
     <t xml:space="preserve">21. HBV</t>
   </si>
   <si>
-    <t xml:space="preserve">22. Amebiasis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23. Brucellosis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24. Genital herpes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25. Shigellosis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26. Chickenpox</t>
+    <t xml:space="preserve">22. Chickenpox</t>
   </si>
   <si>
     <t xml:space="preserve">7. Influenza</t>
@@ -1351,13 +1339,13 @@
     <t xml:space="preserve">17. Diphtheria</t>
   </si>
   <si>
-    <t xml:space="preserve">21. Brucellosis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22. Genital herpes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25. Chickenpox</t>
+    <t xml:space="preserve">20. Chickenpox</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22. Brucellosis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23. Genital herpes</t>
   </si>
   <si>
     <t xml:space="preserve">26. HDV</t>
@@ -1375,22 +1363,16 @@
     <t xml:space="preserve">16. HFMD</t>
   </si>
   <si>
-    <t xml:space="preserve">18. Amebiasis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19. Brucellosis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21. Shigellosis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22. Cholera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23. JE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24. Chickenpox</t>
+    <t xml:space="preserve">18. Chickenpox</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20. Brucellosis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22. Shigellosis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24. JE</t>
   </si>
   <si>
     <t xml:space="preserve">25. HDV</t>
@@ -10840,10 +10822,10 @@
         <v>135169</v>
       </c>
       <c r="F284" t="n">
-        <v>1787304</v>
+        <v>1847330</v>
       </c>
       <c r="G284" t="n">
-        <v>1922473</v>
+        <v>1982499</v>
       </c>
       <c r="H284" t="n">
         <v>1</v>
@@ -10872,10 +10854,10 @@
         <v>357731</v>
       </c>
       <c r="F285" t="n">
-        <v>898268</v>
+        <v>916372</v>
       </c>
       <c r="G285" t="n">
-        <v>1255999</v>
+        <v>1274103</v>
       </c>
       <c r="H285" t="n">
         <v>2</v>
@@ -10904,10 +10886,10 @@
         <v>83136</v>
       </c>
       <c r="F286" t="n">
-        <v>162159</v>
+        <v>163644</v>
       </c>
       <c r="G286" t="n">
-        <v>245295</v>
+        <v>246780</v>
       </c>
       <c r="H286" t="n">
         <v>3</v>
@@ -10936,10 +10918,10 @@
         <v>53017</v>
       </c>
       <c r="F287" t="n">
-        <v>204390</v>
+        <v>206180</v>
       </c>
       <c r="G287" t="n">
-        <v>257407</v>
+        <v>259197</v>
       </c>
       <c r="H287" t="n">
         <v>4</v>
@@ -10968,10 +10950,10 @@
         <v>21616</v>
       </c>
       <c r="F288" t="n">
-        <v>59307</v>
+        <v>60343</v>
       </c>
       <c r="G288" t="n">
-        <v>80923</v>
+        <v>81959</v>
       </c>
       <c r="H288" t="n">
         <v>5</v>
@@ -11000,10 +10982,10 @@
         <v>45469</v>
       </c>
       <c r="F289" t="n">
-        <v>78449</v>
+        <v>79882</v>
       </c>
       <c r="G289" t="n">
-        <v>123918</v>
+        <v>125351</v>
       </c>
       <c r="H289" t="n">
         <v>6</v>
@@ -11032,10 +11014,10 @@
         <v>13172</v>
       </c>
       <c r="F290" t="n">
-        <v>32679</v>
+        <v>33287</v>
       </c>
       <c r="G290" t="n">
-        <v>45851</v>
+        <v>46459</v>
       </c>
       <c r="H290" t="n">
         <v>7</v>
@@ -11064,10 +11046,10 @@
         <v>7965</v>
       </c>
       <c r="F291" t="n">
-        <v>18387</v>
+        <v>18693</v>
       </c>
       <c r="G291" t="n">
-        <v>26352</v>
+        <v>26658</v>
       </c>
       <c r="H291" t="n">
         <v>8</v>
@@ -11096,10 +11078,10 @@
         <v>11288</v>
       </c>
       <c r="F292" t="n">
-        <v>33973</v>
+        <v>34468</v>
       </c>
       <c r="G292" t="n">
-        <v>45261</v>
+        <v>45756</v>
       </c>
       <c r="H292" t="n">
         <v>9</v>
@@ -11128,10 +11110,10 @@
         <v>2878</v>
       </c>
       <c r="F293" t="n">
-        <v>9558</v>
+        <v>9852</v>
       </c>
       <c r="G293" t="n">
-        <v>12436</v>
+        <v>12730</v>
       </c>
       <c r="H293" t="n">
         <v>10</v>
@@ -11160,10 +11142,10 @@
         <v>6770</v>
       </c>
       <c r="F294" t="n">
-        <v>21299</v>
+        <v>21755</v>
       </c>
       <c r="G294" t="n">
-        <v>28069</v>
+        <v>28525</v>
       </c>
       <c r="H294" t="n">
         <v>11</v>
@@ -11192,10 +11174,10 @@
         <v>2449</v>
       </c>
       <c r="F295" t="n">
-        <v>8024</v>
+        <v>8125</v>
       </c>
       <c r="G295" t="n">
-        <v>10473</v>
+        <v>10574</v>
       </c>
       <c r="H295" t="n">
         <v>12</v>
@@ -11224,10 +11206,10 @@
         <v>4999</v>
       </c>
       <c r="F296" t="n">
-        <v>8388</v>
+        <v>8569</v>
       </c>
       <c r="G296" t="n">
-        <v>13387</v>
+        <v>13568</v>
       </c>
       <c r="H296" t="n">
         <v>13</v>
@@ -11256,10 +11238,10 @@
         <v>3160</v>
       </c>
       <c r="F297" t="n">
-        <v>11561</v>
+        <v>11891</v>
       </c>
       <c r="G297" t="n">
-        <v>14721</v>
+        <v>15051</v>
       </c>
       <c r="H297" t="n">
         <v>14</v>
@@ -11288,10 +11270,10 @@
         <v>104</v>
       </c>
       <c r="F298" t="n">
-        <v>7424</v>
+        <v>7422</v>
       </c>
       <c r="G298" t="n">
-        <v>7528</v>
+        <v>7526</v>
       </c>
       <c r="H298" t="n">
         <v>15</v>
@@ -11320,10 +11302,10 @@
         <v>2575</v>
       </c>
       <c r="F299" t="n">
-        <v>4183</v>
+        <v>4245</v>
       </c>
       <c r="G299" t="n">
-        <v>6758</v>
+        <v>6820</v>
       </c>
       <c r="H299" t="n">
         <v>16</v>
@@ -11352,10 +11334,10 @@
         <v>12002</v>
       </c>
       <c r="F300" t="n">
-        <v>2112</v>
+        <v>2132</v>
       </c>
       <c r="G300" t="n">
-        <v>14114</v>
+        <v>14134</v>
       </c>
       <c r="H300" t="n">
         <v>17</v>
@@ -11384,10 +11366,10 @@
         <v>2072</v>
       </c>
       <c r="F301" t="n">
-        <v>4902</v>
+        <v>5019</v>
       </c>
       <c r="G301" t="n">
-        <v>6974</v>
+        <v>7091</v>
       </c>
       <c r="H301" t="n">
         <v>18</v>
@@ -11416,10 +11398,10 @@
         <v>2051</v>
       </c>
       <c r="F302" t="n">
-        <v>3933</v>
+        <v>4047</v>
       </c>
       <c r="G302" t="n">
-        <v>5984</v>
+        <v>6098</v>
       </c>
       <c r="H302" t="n">
         <v>19</v>
@@ -11448,10 +11430,10 @@
         <v>856</v>
       </c>
       <c r="F303" t="n">
-        <v>3210</v>
+        <v>3279</v>
       </c>
       <c r="G303" t="n">
-        <v>4066</v>
+        <v>4135</v>
       </c>
       <c r="H303" t="n">
         <v>20</v>
@@ -11480,10 +11462,10 @@
         <v>736</v>
       </c>
       <c r="F304" t="n">
-        <v>6186</v>
+        <v>6310</v>
       </c>
       <c r="G304" t="n">
-        <v>6922</v>
+        <v>7046</v>
       </c>
       <c r="H304" t="n">
         <v>21</v>
@@ -11512,10 +11494,10 @@
         <v>1590</v>
       </c>
       <c r="F305" t="n">
-        <v>2976</v>
+        <v>3129</v>
       </c>
       <c r="G305" t="n">
-        <v>4566</v>
+        <v>4719</v>
       </c>
       <c r="H305" t="n">
         <v>22</v>
@@ -11544,10 +11526,10 @@
         <v>1576</v>
       </c>
       <c r="F306" t="n">
-        <v>2899</v>
+        <v>3009</v>
       </c>
       <c r="G306" t="n">
-        <v>4475</v>
+        <v>4585</v>
       </c>
       <c r="H306" t="n">
         <v>23</v>
@@ -11576,10 +11558,10 @@
         <v>1516</v>
       </c>
       <c r="F307" t="n">
-        <v>7590</v>
+        <v>7840</v>
       </c>
       <c r="G307" t="n">
-        <v>9106</v>
+        <v>9356</v>
       </c>
       <c r="H307" t="n">
         <v>24</v>
@@ -11608,10 +11590,10 @@
         <v>302</v>
       </c>
       <c r="F308" t="n">
-        <v>675</v>
+        <v>689</v>
       </c>
       <c r="G308" t="n">
-        <v>977</v>
+        <v>991</v>
       </c>
       <c r="H308" t="n">
         <v>25</v>
@@ -11640,10 +11622,10 @@
         <v>930</v>
       </c>
       <c r="F309" t="n">
-        <v>1954</v>
+        <v>1977</v>
       </c>
       <c r="G309" t="n">
-        <v>2884</v>
+        <v>2907</v>
       </c>
       <c r="H309" t="n">
         <v>26</v>
@@ -11672,10 +11654,10 @@
         <v>1456</v>
       </c>
       <c r="F310" t="n">
-        <v>9274</v>
+        <v>9319</v>
       </c>
       <c r="G310" t="n">
-        <v>10730</v>
+        <v>10775</v>
       </c>
       <c r="H310" t="n">
         <v>27</v>
@@ -11704,10 +11686,10 @@
         <v>893</v>
       </c>
       <c r="F311" t="n">
-        <v>564</v>
+        <v>578</v>
       </c>
       <c r="G311" t="n">
-        <v>1457</v>
+        <v>1471</v>
       </c>
       <c r="H311" t="n">
         <v>28</v>
@@ -11736,10 +11718,10 @@
         <v>608</v>
       </c>
       <c r="F312" t="n">
-        <v>1167</v>
+        <v>1185</v>
       </c>
       <c r="G312" t="n">
-        <v>1775</v>
+        <v>1793</v>
       </c>
       <c r="H312" t="n">
         <v>29</v>
@@ -11768,10 +11750,10 @@
         <v>30</v>
       </c>
       <c r="F313" t="n">
-        <v>1532</v>
+        <v>1535</v>
       </c>
       <c r="G313" t="n">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="H313" t="n">
         <v>30</v>
@@ -11800,10 +11782,10 @@
         <v>243</v>
       </c>
       <c r="F314" t="n">
-        <v>977</v>
+        <v>993</v>
       </c>
       <c r="G314" t="n">
-        <v>1220</v>
+        <v>1236</v>
       </c>
       <c r="H314" t="n">
         <v>31</v>
@@ -11832,10 +11814,10 @@
         <v>144</v>
       </c>
       <c r="F315" t="n">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="G315" t="n">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H315" t="n">
         <v>32</v>
@@ -11864,10 +11846,10 @@
         <v>170</v>
       </c>
       <c r="F316" t="n">
-        <v>111</v>
+        <v>87</v>
       </c>
       <c r="G316" t="n">
-        <v>281</v>
+        <v>257</v>
       </c>
       <c r="H316" t="n">
         <v>33</v>
@@ -11896,10 +11878,10 @@
         <v>79</v>
       </c>
       <c r="F317" t="n">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="G317" t="n">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="H317" t="n">
         <v>34</v>
@@ -11928,10 +11910,10 @@
         <v>68</v>
       </c>
       <c r="F318" t="n">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="G318" t="n">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="H318" t="n">
         <v>35</v>
@@ -11992,10 +11974,10 @@
         <v>93</v>
       </c>
       <c r="F320" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G320" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H320" t="n">
         <v>37</v>
@@ -12056,10 +12038,10 @@
         <v>6</v>
       </c>
       <c r="F322" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G322" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H322" t="n">
         <v>39</v>
@@ -12120,10 +12102,10 @@
         <v>8</v>
       </c>
       <c r="F324" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G324" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H324" t="n">
         <v>41</v>
@@ -12152,10 +12134,10 @@
         <v>20</v>
       </c>
       <c r="F325" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G325" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H325" t="n">
         <v>42</v>
@@ -12210,7 +12192,7 @@
         <v>291</v>
       </c>
       <c r="D327" t="n">
-        <v>1787304</v>
+        <v>1847330</v>
       </c>
       <c r="E327" t="n">
         <v>568287</v>
@@ -12242,7 +12224,7 @@
         <v>291</v>
       </c>
       <c r="D328" t="n">
-        <v>898268</v>
+        <v>916372</v>
       </c>
       <c r="E328" t="n">
         <v>532954</v>
@@ -12274,7 +12256,7 @@
         <v>291</v>
       </c>
       <c r="D329" t="n">
-        <v>204390</v>
+        <v>206180</v>
       </c>
       <c r="E329" t="n">
         <v>165837</v>
@@ -12306,7 +12288,7 @@
         <v>291</v>
       </c>
       <c r="D330" t="n">
-        <v>162159</v>
+        <v>163644</v>
       </c>
       <c r="E330" t="n">
         <v>207520</v>
@@ -12338,7 +12320,7 @@
         <v>291</v>
       </c>
       <c r="D331" t="n">
-        <v>78449</v>
+        <v>79882</v>
       </c>
       <c r="E331" t="n">
         <v>31253</v>
@@ -12370,7 +12352,7 @@
         <v>291</v>
       </c>
       <c r="D332" t="n">
-        <v>59307</v>
+        <v>60343</v>
       </c>
       <c r="E332" t="n">
         <v>33988</v>
@@ -12402,7 +12384,7 @@
         <v>291</v>
       </c>
       <c r="D333" t="n">
-        <v>33973</v>
+        <v>34468</v>
       </c>
       <c r="E333" t="n">
         <v>13410</v>
@@ -12434,7 +12416,7 @@
         <v>291</v>
       </c>
       <c r="D334" t="n">
-        <v>32679</v>
+        <v>33287</v>
       </c>
       <c r="E334" t="n">
         <v>18997</v>
@@ -12466,7 +12448,7 @@
         <v>291</v>
       </c>
       <c r="D335" t="n">
-        <v>21299</v>
+        <v>21755</v>
       </c>
       <c r="E335" t="n">
         <v>8068</v>
@@ -12498,7 +12480,7 @@
         <v>291</v>
       </c>
       <c r="D336" t="n">
-        <v>18387</v>
+        <v>18693</v>
       </c>
       <c r="E336" t="n">
         <v>14723</v>
@@ -12530,7 +12512,7 @@
         <v>291</v>
       </c>
       <c r="D337" t="n">
-        <v>11561</v>
+        <v>11891</v>
       </c>
       <c r="E337" t="n">
         <v>4590</v>
@@ -12562,7 +12544,7 @@
         <v>291</v>
       </c>
       <c r="D338" t="n">
-        <v>9558</v>
+        <v>9852</v>
       </c>
       <c r="E338" t="n">
         <v>8276</v>
@@ -12594,7 +12576,7 @@
         <v>291</v>
       </c>
       <c r="D339" t="n">
-        <v>9274</v>
+        <v>9319</v>
       </c>
       <c r="E339" t="n">
         <v>679</v>
@@ -12626,7 +12608,7 @@
         <v>291</v>
       </c>
       <c r="D340" t="n">
-        <v>8388</v>
+        <v>8569</v>
       </c>
       <c r="E340" t="n">
         <v>7681</v>
@@ -12658,7 +12640,7 @@
         <v>291</v>
       </c>
       <c r="D341" t="n">
-        <v>8024</v>
+        <v>8125</v>
       </c>
       <c r="E341" t="n">
         <v>7812</v>
@@ -12690,7 +12672,7 @@
         <v>291</v>
       </c>
       <c r="D342" t="n">
-        <v>7590</v>
+        <v>7840</v>
       </c>
       <c r="E342" t="n">
         <v>1153</v>
@@ -12722,7 +12704,7 @@
         <v>291</v>
       </c>
       <c r="D343" t="n">
-        <v>7424</v>
+        <v>7422</v>
       </c>
       <c r="E343" t="n">
         <v>3083</v>
@@ -12754,7 +12736,7 @@
         <v>291</v>
       </c>
       <c r="D344" t="n">
-        <v>6186</v>
+        <v>6310</v>
       </c>
       <c r="E344" t="n">
         <v>1933</v>
@@ -12786,7 +12768,7 @@
         <v>291</v>
       </c>
       <c r="D345" t="n">
-        <v>4902</v>
+        <v>5019</v>
       </c>
       <c r="E345" t="n">
         <v>2686</v>
@@ -12818,7 +12800,7 @@
         <v>291</v>
       </c>
       <c r="D346" t="n">
-        <v>4183</v>
+        <v>4245</v>
       </c>
       <c r="E346" t="n">
         <v>2934</v>
@@ -12850,7 +12832,7 @@
         <v>291</v>
       </c>
       <c r="D347" t="n">
-        <v>3933</v>
+        <v>4047</v>
       </c>
       <c r="E347" t="n">
         <v>2531</v>
@@ -12882,7 +12864,7 @@
         <v>291</v>
       </c>
       <c r="D348" t="n">
-        <v>3210</v>
+        <v>3279</v>
       </c>
       <c r="E348" t="n">
         <v>1971</v>
@@ -12914,7 +12896,7 @@
         <v>291</v>
       </c>
       <c r="D349" t="n">
-        <v>2976</v>
+        <v>3129</v>
       </c>
       <c r="E349" t="n">
         <v>1732</v>
@@ -12946,7 +12928,7 @@
         <v>291</v>
       </c>
       <c r="D350" t="n">
-        <v>2899</v>
+        <v>3009</v>
       </c>
       <c r="E350" t="n">
         <v>1194</v>
@@ -12978,7 +12960,7 @@
         <v>291</v>
       </c>
       <c r="D351" t="n">
-        <v>2112</v>
+        <v>2132</v>
       </c>
       <c r="E351" t="n">
         <v>2797</v>
@@ -13010,7 +12992,7 @@
         <v>291</v>
       </c>
       <c r="D352" t="n">
-        <v>1954</v>
+        <v>1977</v>
       </c>
       <c r="E352" t="n">
         <v>988</v>
@@ -13042,7 +13024,7 @@
         <v>291</v>
       </c>
       <c r="D353" t="n">
-        <v>1532</v>
+        <v>1535</v>
       </c>
       <c r="E353" t="n">
         <v>417</v>
@@ -13074,7 +13056,7 @@
         <v>291</v>
       </c>
       <c r="D354" t="n">
-        <v>1167</v>
+        <v>1185</v>
       </c>
       <c r="E354" t="n">
         <v>598</v>
@@ -13106,7 +13088,7 @@
         <v>291</v>
       </c>
       <c r="D355" t="n">
-        <v>977</v>
+        <v>993</v>
       </c>
       <c r="E355" t="n">
         <v>389</v>
@@ -13138,7 +13120,7 @@
         <v>291</v>
       </c>
       <c r="D356" t="n">
-        <v>675</v>
+        <v>689</v>
       </c>
       <c r="E356" t="n">
         <v>1008</v>
@@ -13170,7 +13152,7 @@
         <v>291</v>
       </c>
       <c r="D357" t="n">
-        <v>564</v>
+        <v>578</v>
       </c>
       <c r="E357" t="n">
         <v>602</v>
@@ -13202,7 +13184,7 @@
         <v>291</v>
       </c>
       <c r="D358" t="n">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E358" t="n">
         <v>296</v>
@@ -13234,7 +13216,7 @@
         <v>291</v>
       </c>
       <c r="D359" t="n">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="E359" t="n">
         <v>105</v>
@@ -13266,7 +13248,7 @@
         <v>291</v>
       </c>
       <c r="D360" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E360" t="n">
         <v>71</v>
@@ -13298,7 +13280,7 @@
         <v>291</v>
       </c>
       <c r="D361" t="n">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="E361" t="n">
         <v>88</v>
@@ -13330,7 +13312,7 @@
         <v>291</v>
       </c>
       <c r="D362" t="n">
-        <v>111</v>
+        <v>87</v>
       </c>
       <c r="E362" t="n">
         <v>170</v>
@@ -13362,7 +13344,7 @@
         <v>291</v>
       </c>
       <c r="D363" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E363" t="n">
         <v>11</v>
@@ -13394,7 +13376,7 @@
         <v>291</v>
       </c>
       <c r="D364" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E364" t="n">
         <v>6</v>
@@ -13522,7 +13504,7 @@
         <v>291</v>
       </c>
       <c r="D368" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E368" t="n">
         <v>3</v>
@@ -20355,10 +20337,10 @@
     </row>
     <row r="206">
       <c r="A206" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="B206" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="C206" t="s">
         <v>237</v>
@@ -20388,10 +20370,10 @@
     </row>
     <row r="207">
       <c r="A207" t="s">
-        <v>155</v>
+        <v>45</v>
       </c>
       <c r="B207" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="C207" t="s">
         <v>237</v>
@@ -20413,7 +20395,7 @@
       </c>
       <c r="I207"/>
       <c r="J207" t="s">
-        <v>436</v>
+        <v>418</v>
       </c>
       <c r="K207" t="n">
         <v>7</v>
@@ -20421,10 +20403,10 @@
     </row>
     <row r="208">
       <c r="A208" t="s">
-        <v>56</v>
+        <v>155</v>
       </c>
       <c r="B208" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="C208" t="s">
         <v>237</v>
@@ -20446,7 +20428,7 @@
       </c>
       <c r="I208"/>
       <c r="J208" t="s">
-        <v>437</v>
+        <v>401</v>
       </c>
       <c r="K208" t="n">
         <v>7</v>
@@ -20454,10 +20436,10 @@
     </row>
     <row r="209">
       <c r="A209" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="B209" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C209" t="s">
         <v>237</v>
@@ -20479,7 +20461,7 @@
       </c>
       <c r="I209"/>
       <c r="J209" t="s">
-        <v>438</v>
+        <v>402</v>
       </c>
       <c r="K209" t="n">
         <v>7</v>
@@ -20487,10 +20469,10 @@
     </row>
     <row r="210">
       <c r="A210" t="s">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="B210" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="C210" t="s">
         <v>237</v>
@@ -20512,7 +20494,7 @@
       </c>
       <c r="I210"/>
       <c r="J210" t="s">
-        <v>439</v>
+        <v>403</v>
       </c>
       <c r="K210" t="n">
         <v>7</v>
@@ -20733,10 +20715,10 @@
         <v>429</v>
       </c>
       <c r="F217" t="n">
-        <v>1569</v>
+        <v>1628</v>
       </c>
       <c r="G217" t="n">
-        <v>1998</v>
+        <v>2057</v>
       </c>
       <c r="H217" t="n">
         <v>1</v>
@@ -20766,10 +20748,10 @@
         <v>20</v>
       </c>
       <c r="F218" t="n">
-        <v>330</v>
+        <v>341</v>
       </c>
       <c r="G218" t="n">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="H218" t="n">
         <v>2</v>
@@ -20832,10 +20814,10 @@
         <v>34</v>
       </c>
       <c r="F220" t="n">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="G220" t="n">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="H220" t="n">
         <v>4</v>
@@ -20931,17 +20913,17 @@
         <v>3</v>
       </c>
       <c r="F223" t="n">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="G223" t="n">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="H223" t="n">
         <v>7</v>
       </c>
       <c r="I223"/>
       <c r="J223" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="K223" t="n">
         <v>8</v>
@@ -20964,10 +20946,10 @@
         <v>12</v>
       </c>
       <c r="F224" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G224" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H224" t="n">
         <v>8</v>
@@ -21040,7 +21022,7 @@
       </c>
       <c r="I226"/>
       <c r="J226" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="K226" t="n">
         <v>8</v>
@@ -21205,7 +21187,7 @@
       </c>
       <c r="I231"/>
       <c r="J231" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="K231" t="n">
         <v>8</v>
@@ -21271,7 +21253,7 @@
       </c>
       <c r="I233"/>
       <c r="J233" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="K233" t="n">
         <v>8</v>
@@ -21345,10 +21327,10 @@
     </row>
     <row r="236">
       <c r="A236" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="B236" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="C236" t="s">
         <v>262</v>
@@ -21370,7 +21352,7 @@
       </c>
       <c r="I236"/>
       <c r="J236" t="s">
-        <v>301</v>
+        <v>440</v>
       </c>
       <c r="K236" t="n">
         <v>8</v>
@@ -21378,10 +21360,10 @@
     </row>
     <row r="237">
       <c r="A237" t="s">
-        <v>155</v>
+        <v>45</v>
       </c>
       <c r="B237" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="C237" t="s">
         <v>262</v>
@@ -21403,7 +21385,7 @@
       </c>
       <c r="I237"/>
       <c r="J237" t="s">
-        <v>444</v>
+        <v>361</v>
       </c>
       <c r="K237" t="n">
         <v>8</v>
@@ -21411,10 +21393,10 @@
     </row>
     <row r="238">
       <c r="A238" t="s">
-        <v>56</v>
+        <v>155</v>
       </c>
       <c r="B238" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="C238" t="s">
         <v>262</v>
@@ -21436,7 +21418,7 @@
       </c>
       <c r="I238"/>
       <c r="J238" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="K238" t="n">
         <v>8</v>
@@ -21444,10 +21426,10 @@
     </row>
     <row r="239">
       <c r="A239" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="B239" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C239" t="s">
         <v>262</v>
@@ -21469,7 +21451,7 @@
       </c>
       <c r="I239"/>
       <c r="J239" t="s">
-        <v>218</v>
+        <v>442</v>
       </c>
       <c r="K239" t="n">
         <v>8</v>
@@ -21477,10 +21459,10 @@
     </row>
     <row r="240">
       <c r="A240" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="B240" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="C240" t="s">
         <v>262</v>
@@ -21489,10 +21471,10 @@
         <v>0</v>
       </c>
       <c r="E240" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F240" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G240" t="n">
         <v>1</v>
@@ -21502,7 +21484,7 @@
       </c>
       <c r="I240"/>
       <c r="J240" t="s">
-        <v>114</v>
+        <v>250</v>
       </c>
       <c r="K240" t="n">
         <v>8</v>
@@ -21510,10 +21492,10 @@
     </row>
     <row r="241">
       <c r="A241" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="B241" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C241" t="s">
         <v>262</v>
@@ -21522,20 +21504,20 @@
         <v>0</v>
       </c>
       <c r="E241" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F241" t="n">
         <v>0</v>
       </c>
       <c r="G241" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H241" t="n">
         <v>25</v>
       </c>
       <c r="I241"/>
       <c r="J241" t="s">
-        <v>446</v>
+        <v>304</v>
       </c>
       <c r="K241" t="n">
         <v>8</v>
@@ -21568,7 +21550,7 @@
       </c>
       <c r="I242"/>
       <c r="J242" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="K242" t="n">
         <v>8</v>
@@ -21634,7 +21616,7 @@
       </c>
       <c r="I244"/>
       <c r="J244" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="K244" t="n">
         <v>8</v>
@@ -21783,7 +21765,7 @@
         <v>291</v>
       </c>
       <c r="D249" t="n">
-        <v>1569</v>
+        <v>1628</v>
       </c>
       <c r="E249" t="n">
         <v>651</v>
@@ -21798,7 +21780,7 @@
         <v>1</v>
       </c>
       <c r="I249" t="n">
-        <v>12315</v>
+        <v>12374</v>
       </c>
       <c r="J249" t="s">
         <v>13</v>
@@ -21818,7 +21800,7 @@
         <v>291</v>
       </c>
       <c r="D250" t="n">
-        <v>330</v>
+        <v>341</v>
       </c>
       <c r="E250" t="n">
         <v>258</v>
@@ -21833,7 +21815,7 @@
         <v>2</v>
       </c>
       <c r="I250" t="n">
-        <v>1091</v>
+        <v>1102</v>
       </c>
       <c r="J250" t="s">
         <v>389</v>
@@ -21853,7 +21835,7 @@
         <v>291</v>
       </c>
       <c r="D251" t="n">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="E251" t="n">
         <v>92</v>
@@ -21868,7 +21850,7 @@
         <v>3</v>
       </c>
       <c r="I251" t="n">
-        <v>875</v>
+        <v>880</v>
       </c>
       <c r="J251" t="s">
         <v>351</v>
@@ -21888,7 +21870,7 @@
         <v>291</v>
       </c>
       <c r="D252" t="n">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="E252" t="n">
         <v>14</v>
@@ -21903,7 +21885,7 @@
         <v>4</v>
       </c>
       <c r="I252" t="n">
-        <v>831</v>
+        <v>842</v>
       </c>
       <c r="J252" t="s">
         <v>20</v>
@@ -21941,7 +21923,7 @@
         <v>1571</v>
       </c>
       <c r="J253" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="K253" t="n">
         <v>9</v>
@@ -21993,7 +21975,7 @@
         <v>291</v>
       </c>
       <c r="D255" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E255" t="n">
         <v>14</v>
@@ -22008,7 +21990,7 @@
         <v>7</v>
       </c>
       <c r="I255" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="J255" t="s">
         <v>317</v>
@@ -22116,7 +22098,7 @@
         <v>19</v>
       </c>
       <c r="J258" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="K258" t="n">
         <v>9</v>
@@ -22221,7 +22203,7 @@
         <v>78</v>
       </c>
       <c r="J261" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="K261" t="n">
         <v>9</v>
@@ -22326,7 +22308,7 @@
         <v>32</v>
       </c>
       <c r="J264" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="K264" t="n">
         <v>9</v>
@@ -22369,10 +22351,10 @@
     </row>
     <row r="266">
       <c r="A266" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="B266" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="C266" t="s">
         <v>291</v>
@@ -22393,10 +22375,10 @@
         <v>18</v>
       </c>
       <c r="I266" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="J266" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="K266" t="n">
         <v>9</v>
@@ -22404,10 +22386,10 @@
     </row>
     <row r="267">
       <c r="A267" t="s">
-        <v>155</v>
+        <v>45</v>
       </c>
       <c r="B267" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="C267" t="s">
         <v>291</v>
@@ -22428,10 +22410,10 @@
         <v>19</v>
       </c>
       <c r="I267" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J267" t="s">
-        <v>453</v>
+        <v>215</v>
       </c>
       <c r="K267" t="n">
         <v>9</v>
@@ -22439,10 +22421,10 @@
     </row>
     <row r="268">
       <c r="A268" t="s">
-        <v>56</v>
+        <v>155</v>
       </c>
       <c r="B268" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="C268" t="s">
         <v>291</v>
@@ -22466,7 +22448,7 @@
         <v>1</v>
       </c>
       <c r="J268" t="s">
-        <v>110</v>
+        <v>449</v>
       </c>
       <c r="K268" t="n">
         <v>9</v>
@@ -22474,10 +22456,10 @@
     </row>
     <row r="269">
       <c r="A269" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="B269" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C269" t="s">
         <v>291</v>
@@ -22501,7 +22483,7 @@
         <v>1</v>
       </c>
       <c r="J269" t="s">
-        <v>454</v>
+        <v>57</v>
       </c>
       <c r="K269" t="n">
         <v>9</v>
@@ -22509,7 +22491,7 @@
     </row>
     <row r="270">
       <c r="A270" t="s">
-        <v>76</v>
+        <v>41</v>
       </c>
       <c r="B270" t="s">
         <v>28</v>
@@ -22518,25 +22500,25 @@
         <v>291</v>
       </c>
       <c r="D270" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E270" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F270" t="n">
         <v>0</v>
       </c>
       <c r="G270" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H270" t="n">
         <v>22</v>
       </c>
       <c r="I270" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="J270" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="K270" t="n">
         <v>9</v>
@@ -22544,10 +22526,10 @@
     </row>
     <row r="271">
       <c r="A271" t="s">
-        <v>231</v>
+        <v>76</v>
       </c>
       <c r="B271" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="C271" t="s">
         <v>291</v>
@@ -22568,10 +22550,10 @@
         <v>23</v>
       </c>
       <c r="I271" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="J271" t="s">
-        <v>456</v>
+        <v>113</v>
       </c>
       <c r="K271" t="n">
         <v>9</v>
@@ -22579,10 +22561,10 @@
     </row>
     <row r="272">
       <c r="A272" t="s">
-        <v>14</v>
+        <v>231</v>
       </c>
       <c r="B272" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C272" t="s">
         <v>291</v>
@@ -22591,22 +22573,22 @@
         <v>0</v>
       </c>
       <c r="E272" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F272" t="n">
         <v>0</v>
       </c>
       <c r="G272" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H272" t="n">
         <v>24</v>
       </c>
       <c r="I272" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="J272" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="K272" t="n">
         <v>9</v>
@@ -22641,7 +22623,7 @@
         <v>3</v>
       </c>
       <c r="J273" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="K273" t="n">
         <v>9</v>
@@ -22676,7 +22658,7 @@
         <v>1</v>
       </c>
       <c r="J274" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="K274" t="n">
         <v>9</v>
@@ -22746,7 +22728,7 @@
         <v>1</v>
       </c>
       <c r="J276" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="K276" t="n">
         <v>9</v>
@@ -22905,21 +22887,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="B1" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="C1" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="D1" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="B2" t="n">
         <v>1</v>
@@ -22928,12 +22910,12 @@
         <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>1257443.09356982</v>
+        <v>1122035.09356982</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="B3" t="n">
         <v>1</v>
@@ -22942,12 +22924,12 @@
         <v>19</v>
       </c>
       <c r="D3" t="n">
-        <v>653657.716757474</v>
+        <v>424390.716757474</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="B4" t="n">
         <v>1</v>
@@ -22956,82 +22938,82 @@
         <v>27</v>
       </c>
       <c r="D4" t="n">
-        <v>778335.599275723</v>
+        <v>635915.599275723</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="D5" t="n">
-        <v>410123.920688537</v>
+        <v>372089.920688537</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="B6" t="n">
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="D6" t="n">
-        <v>207210.406276195</v>
+        <v>342927.419055442</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="B7" t="n">
         <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D7" t="n">
-        <v>673512.419055442</v>
+        <v>177939.354133745</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="B8" t="n">
         <v>2</v>
       </c>
       <c r="C8" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>195085.354133745</v>
+        <v>177032.729009513</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="B9" t="n">
         <v>2</v>
       </c>
       <c r="C9" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="D9" t="n">
-        <v>410266.63549073</v>
+        <v>299117.312757412</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="B10" t="n">
         <v>3</v>
@@ -23040,12 +23022,12 @@
         <v>19</v>
       </c>
       <c r="D10" t="n">
-        <v>506614.23767102</v>
+        <v>274748.23767102</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="B11" t="n">
         <v>3</v>
@@ -23054,12 +23036,12 @@
         <v>16</v>
       </c>
       <c r="D11" t="n">
-        <v>316456.043334976</v>
+        <v>295964.043334976</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="B12" t="n">
         <v>3</v>
@@ -23068,26 +23050,26 @@
         <v>14</v>
       </c>
       <c r="D12" t="n">
-        <v>150953.40760811</v>
+        <v>137663.40760811</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="B13" t="n">
         <v>3</v>
       </c>
       <c r="C13" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="D13" t="n">
-        <v>179593.807880794</v>
+        <v>141464.807880794</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="B14" t="n">
         <v>4</v>
@@ -23096,12 +23078,12 @@
         <v>19</v>
       </c>
       <c r="D14" t="n">
-        <v>247009.701346544</v>
+        <v>134604.701346544</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="B15" t="n">
         <v>4</v>
@@ -23110,12 +23092,12 @@
         <v>16</v>
       </c>
       <c r="D15" t="n">
-        <v>228775.52818226</v>
+        <v>208241.52818226</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="B16" t="n">
         <v>4</v>
@@ -23124,26 +23106,26 @@
         <v>14</v>
       </c>
       <c r="D16" t="n">
-        <v>80702.3493339277</v>
+        <v>73372.3493339277</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="B17" t="n">
         <v>4</v>
       </c>
       <c r="C17" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="D17" t="n">
-        <v>183659.029471305</v>
+        <v>146601.029471305</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="B18" t="n">
         <v>5</v>
@@ -23152,12 +23134,12 @@
         <v>10</v>
       </c>
       <c r="D18" t="n">
-        <v>291134.379172665</v>
+        <v>223030.379172665</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="B19" t="n">
         <v>5</v>
@@ -23166,12 +23148,12 @@
         <v>19</v>
       </c>
       <c r="D19" t="n">
-        <v>929183.598146722</v>
+        <v>500926.598146722</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="B20" t="n">
         <v>5</v>
@@ -23180,26 +23162,26 @@
         <v>16</v>
       </c>
       <c r="D20" t="n">
-        <v>441897.75352447</v>
+        <v>390503.75352447</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="B21" t="n">
         <v>5</v>
       </c>
       <c r="C21" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="D21" t="n">
-        <v>736636.991080393</v>
+        <v>612843.991080393</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="B22" t="n">
         <v>6</v>
@@ -23208,12 +23190,12 @@
         <v>10</v>
       </c>
       <c r="D22" t="n">
-        <v>627996.515626952</v>
+        <v>493463.515626952</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="B23" t="n">
         <v>6</v>
@@ -23222,12 +23204,12 @@
         <v>19</v>
       </c>
       <c r="D23" t="n">
-        <v>574225.006020735</v>
+        <v>306849.006020735</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="B24" t="n">
         <v>6</v>
@@ -23236,26 +23218,26 @@
         <v>16</v>
       </c>
       <c r="D24" t="n">
-        <v>153375.300212957</v>
+        <v>133103.300212957</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="B25" t="n">
         <v>6</v>
       </c>
       <c r="C25" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="D25" t="n">
-        <v>401809.73923787</v>
+        <v>335025.73923787</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="B26" t="n">
         <v>7</v>
@@ -23264,12 +23246,12 @@
         <v>10</v>
       </c>
       <c r="D26" t="n">
-        <v>1610710.70529812</v>
+        <v>1256320.70529812</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="B27" t="n">
         <v>7</v>
@@ -23278,12 +23260,12 @@
         <v>19</v>
       </c>
       <c r="D27" t="n">
-        <v>282733.321002064</v>
+        <v>149106.321002064</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="B28" t="n">
         <v>7</v>
@@ -23292,21 +23274,21 @@
         <v>16</v>
       </c>
       <c r="D28" t="n">
-        <v>48021.1745600166</v>
+        <v>39708.1745600166</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="B29" t="n">
         <v>7</v>
       </c>
       <c r="C29" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="D29" t="n">
-        <v>182634.26604043</v>
+        <v>142650.26604043</v>
       </c>
     </row>
   </sheetData>
@@ -23322,10 +23304,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="B1" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
@@ -23334,18 +23316,18 @@
         <v>9</v>
       </c>
       <c r="E1" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="F1" t="s">
         <v>1</v>
       </c>
       <c r="G1" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="B2" t="n">
         <v>1</v>
@@ -23368,7 +23350,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="B3" t="n">
         <v>1</v>
@@ -23391,7 +23373,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="B4" t="n">
         <v>1</v>
@@ -23414,7 +23396,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="B5" t="n">
         <v>1</v>
@@ -23437,7 +23419,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="B6" t="n">
         <v>1</v>
@@ -23460,7 +23442,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="B7" t="n">
         <v>1</v>
@@ -23483,7 +23465,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="B8" t="n">
         <v>1</v>
@@ -23506,7 +23488,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="B9" t="n">
         <v>1</v>
@@ -23529,39 +23511,39 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C10" t="s">
-        <v>291</v>
+        <v>12</v>
       </c>
       <c r="D10" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E10" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F10" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G10" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="B11" t="n">
         <v>3</v>
       </c>
       <c r="C11" t="s">
-        <v>12</v>
+        <v>92</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11" t="s">
         <v>16</v>
@@ -23575,16 +23557,16 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="B12" t="n">
         <v>3</v>
       </c>
       <c r="C12" t="s">
-        <v>92</v>
+        <v>127</v>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E12" t="s">
         <v>16</v>
@@ -23598,16 +23580,16 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="B13" t="n">
         <v>3</v>
       </c>
       <c r="C13" t="s">
-        <v>127</v>
+        <v>158</v>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E13" t="s">
         <v>16</v>
@@ -23621,39 +23603,39 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="B14" t="n">
         <v>3</v>
       </c>
       <c r="C14" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E14" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F14" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G14" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="B15" t="n">
         <v>3</v>
       </c>
       <c r="C15" t="s">
-        <v>176</v>
+        <v>203</v>
       </c>
       <c r="D15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E15" t="s">
         <v>19</v>
@@ -23667,108 +23649,108 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="B16" t="n">
         <v>3</v>
       </c>
       <c r="C16" t="s">
-        <v>203</v>
+        <v>237</v>
       </c>
       <c r="D16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E16" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F16" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G16" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="B17" t="n">
         <v>3</v>
       </c>
       <c r="C17" t="s">
-        <v>237</v>
+        <v>262</v>
       </c>
       <c r="D17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E17" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F17" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G17" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C18" t="s">
-        <v>262</v>
+        <v>12</v>
       </c>
       <c r="D18" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E18" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F18" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G18" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="B19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C19" t="s">
-        <v>291</v>
+        <v>92</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E19" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F19" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G19" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="B20" t="n">
         <v>4</v>
       </c>
       <c r="C20" t="s">
-        <v>12</v>
+        <v>127</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E20" t="s">
         <v>16</v>
@@ -23782,16 +23764,16 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="B21" t="n">
         <v>4</v>
       </c>
       <c r="C21" t="s">
-        <v>92</v>
+        <v>158</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E21" t="s">
         <v>16</v>
@@ -23805,39 +23787,39 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="B22" t="n">
         <v>4</v>
       </c>
       <c r="C22" t="s">
-        <v>127</v>
+        <v>176</v>
       </c>
       <c r="D22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E22" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F22" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G22" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="B23" t="n">
         <v>4</v>
       </c>
       <c r="C23" t="s">
-        <v>158</v>
+        <v>203</v>
       </c>
       <c r="D23" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E23" t="s">
         <v>16</v>
@@ -23851,62 +23833,62 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="B24" t="n">
         <v>4</v>
       </c>
       <c r="C24" t="s">
-        <v>176</v>
+        <v>237</v>
       </c>
       <c r="D24" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E24" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F24" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G24" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="B25" t="n">
         <v>4</v>
       </c>
       <c r="C25" t="s">
-        <v>203</v>
+        <v>262</v>
       </c>
       <c r="D25" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E25" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F25" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G25" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="B26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C26" t="s">
-        <v>237</v>
+        <v>12</v>
       </c>
       <c r="D26" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E26" t="s">
         <v>16</v>
@@ -23920,62 +23902,62 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="B27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C27" t="s">
-        <v>262</v>
+        <v>92</v>
       </c>
       <c r="D27" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E27" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F27" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G27" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="B28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C28" t="s">
-        <v>291</v>
+        <v>127</v>
       </c>
       <c r="D28" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E28" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F28" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G28" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="B29" t="n">
         <v>5</v>
       </c>
       <c r="C29" t="s">
-        <v>12</v>
+        <v>158</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E29" t="s">
         <v>16</v>
@@ -23989,85 +23971,85 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="B30" t="n">
         <v>5</v>
       </c>
       <c r="C30" t="s">
-        <v>92</v>
+        <v>176</v>
       </c>
       <c r="D30" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E30" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F30" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G30" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="B31" t="n">
         <v>5</v>
       </c>
       <c r="C31" t="s">
-        <v>127</v>
+        <v>203</v>
       </c>
       <c r="D31" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E31" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F31" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G31" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="B32" t="n">
         <v>5</v>
       </c>
       <c r="C32" t="s">
-        <v>158</v>
+        <v>237</v>
       </c>
       <c r="D32" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E32" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F32" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G32" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="B33" t="n">
         <v>5</v>
       </c>
       <c r="C33" t="s">
-        <v>176</v>
+        <v>262</v>
       </c>
       <c r="D33" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E33" t="s">
         <v>19</v>
@@ -24081,39 +24063,39 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="B34" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C34" t="s">
-        <v>203</v>
+        <v>12</v>
       </c>
       <c r="D34" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E34" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F34" t="s">
         <v>11</v>
       </c>
       <c r="G34" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="B35" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C35" t="s">
-        <v>237</v>
+        <v>92</v>
       </c>
       <c r="D35" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E35" t="s">
         <v>10</v>
@@ -24127,62 +24109,62 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="B36" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C36" t="s">
-        <v>262</v>
+        <v>127</v>
       </c>
       <c r="D36" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E36" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F36" t="s">
         <v>11</v>
       </c>
       <c r="G36" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="B37" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C37" t="s">
-        <v>291</v>
+        <v>158</v>
       </c>
       <c r="D37" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E37" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F37" t="s">
         <v>11</v>
       </c>
       <c r="G37" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="B38" t="n">
         <v>6</v>
       </c>
       <c r="C38" t="s">
-        <v>12</v>
+        <v>176</v>
       </c>
       <c r="D38" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E38" t="s">
         <v>10</v>
@@ -24196,16 +24178,16 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="B39" t="n">
         <v>6</v>
       </c>
       <c r="C39" t="s">
-        <v>92</v>
+        <v>203</v>
       </c>
       <c r="D39" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E39" t="s">
         <v>10</v>
@@ -24219,16 +24201,16 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="B40" t="n">
         <v>6</v>
       </c>
       <c r="C40" t="s">
-        <v>127</v>
+        <v>237</v>
       </c>
       <c r="D40" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E40" t="s">
         <v>10</v>
@@ -24242,16 +24224,16 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="B41" t="n">
         <v>6</v>
       </c>
       <c r="C41" t="s">
-        <v>158</v>
+        <v>262</v>
       </c>
       <c r="D41" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E41" t="s">
         <v>10</v>
@@ -24265,108 +24247,108 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>470</v>
+        <v>460</v>
       </c>
       <c r="B42" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C42" t="s">
-        <v>176</v>
+        <v>12</v>
       </c>
       <c r="D42" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E42" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F42" t="s">
         <v>11</v>
       </c>
       <c r="G42" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>470</v>
+        <v>460</v>
       </c>
       <c r="B43" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C43" t="s">
-        <v>203</v>
+        <v>92</v>
       </c>
       <c r="D43" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E43" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F43" t="s">
         <v>11</v>
       </c>
       <c r="G43" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>470</v>
+        <v>460</v>
       </c>
       <c r="B44" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C44" t="s">
-        <v>237</v>
+        <v>127</v>
       </c>
       <c r="D44" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E44" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F44" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G44" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>470</v>
+        <v>460</v>
       </c>
       <c r="B45" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C45" t="s">
-        <v>262</v>
+        <v>158</v>
       </c>
       <c r="D45" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E45" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F45" t="s">
         <v>11</v>
       </c>
       <c r="G45" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>470</v>
+        <v>460</v>
       </c>
       <c r="B46" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C46" t="s">
-        <v>291</v>
+        <v>176</v>
       </c>
       <c r="D46" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E46" t="s">
         <v>19</v>
@@ -24380,223 +24362,223 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="B47" t="n">
         <v>2</v>
       </c>
       <c r="C47" t="s">
-        <v>12</v>
+        <v>203</v>
       </c>
       <c r="D47" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E47" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F47" t="s">
         <v>11</v>
       </c>
       <c r="G47" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="B48" t="n">
         <v>2</v>
       </c>
       <c r="C48" t="s">
-        <v>92</v>
+        <v>237</v>
       </c>
       <c r="D48" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E48" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F48" t="s">
         <v>11</v>
       </c>
       <c r="G48" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="B49" t="n">
         <v>2</v>
       </c>
       <c r="C49" t="s">
-        <v>127</v>
+        <v>262</v>
       </c>
       <c r="D49" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E49" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F49" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G49" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B50" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C50" t="s">
-        <v>158</v>
+        <v>12</v>
       </c>
       <c r="D50" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E50" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F50" t="s">
         <v>11</v>
       </c>
       <c r="G50" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B51" t="n">
+        <v>7</v>
+      </c>
+      <c r="C51" t="s">
+        <v>92</v>
+      </c>
+      <c r="D51" t="n">
         <v>2</v>
       </c>
-      <c r="C51" t="s">
-        <v>176</v>
-      </c>
-      <c r="D51" t="n">
-        <v>5</v>
-      </c>
       <c r="E51" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F51" t="s">
         <v>11</v>
       </c>
       <c r="G51" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B52" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C52" t="s">
-        <v>203</v>
+        <v>127</v>
       </c>
       <c r="D52" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E52" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F52" t="s">
         <v>11</v>
       </c>
       <c r="G52" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B53" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C53" t="s">
-        <v>237</v>
+        <v>158</v>
       </c>
       <c r="D53" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E53" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F53" t="s">
         <v>11</v>
       </c>
       <c r="G53" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B54" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C54" t="s">
-        <v>262</v>
+        <v>176</v>
       </c>
       <c r="D54" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E54" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F54" t="s">
         <v>11</v>
       </c>
       <c r="G54" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B55" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C55" t="s">
-        <v>291</v>
+        <v>203</v>
       </c>
       <c r="D55" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E55" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F55" t="s">
         <v>11</v>
       </c>
       <c r="G55" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="B56" t="n">
         <v>7</v>
       </c>
       <c r="C56" t="s">
-        <v>12</v>
+        <v>237</v>
       </c>
       <c r="D56" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E56" t="s">
         <v>10</v>
@@ -24610,16 +24592,16 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="B57" t="n">
         <v>7</v>
       </c>
       <c r="C57" t="s">
-        <v>92</v>
+        <v>262</v>
       </c>
       <c r="D57" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E57" t="s">
         <v>10</v>
@@ -24633,16 +24615,16 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="B58" t="n">
-        <v>7</v>
+        <v>8.2</v>
       </c>
       <c r="C58" t="s">
-        <v>127</v>
+        <v>12</v>
       </c>
       <c r="D58" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E58" t="s">
         <v>10</v>
@@ -24656,16 +24638,16 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="B59" t="n">
-        <v>7</v>
+        <v>8.2</v>
       </c>
       <c r="C59" t="s">
-        <v>158</v>
+        <v>92</v>
       </c>
       <c r="D59" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E59" t="s">
         <v>10</v>
@@ -24679,16 +24661,16 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="B60" t="n">
-        <v>7</v>
+        <v>8.2</v>
       </c>
       <c r="C60" t="s">
-        <v>176</v>
+        <v>127</v>
       </c>
       <c r="D60" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E60" t="s">
         <v>10</v>
@@ -24702,16 +24684,16 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="B61" t="n">
-        <v>7</v>
+        <v>8.2</v>
       </c>
       <c r="C61" t="s">
-        <v>203</v>
+        <v>158</v>
       </c>
       <c r="D61" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E61" t="s">
         <v>10</v>
@@ -24725,16 +24707,16 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="B62" t="n">
-        <v>7</v>
+        <v>8.2</v>
       </c>
       <c r="C62" t="s">
-        <v>237</v>
+        <v>176</v>
       </c>
       <c r="D62" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E62" t="s">
         <v>10</v>
@@ -24748,39 +24730,39 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="B63" t="n">
-        <v>7</v>
+        <v>8.2</v>
       </c>
       <c r="C63" t="s">
-        <v>262</v>
+        <v>203</v>
       </c>
       <c r="D63" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E63" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F63" t="s">
         <v>11</v>
       </c>
       <c r="G63" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="B64" t="n">
+        <v>8.2</v>
+      </c>
+      <c r="C64" t="s">
+        <v>237</v>
+      </c>
+      <c r="D64" t="n">
         <v>7</v>
-      </c>
-      <c r="C64" t="s">
-        <v>291</v>
-      </c>
-      <c r="D64" t="n">
-        <v>9</v>
       </c>
       <c r="E64" t="s">
         <v>10</v>
@@ -24794,208 +24776,24 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="B65" t="n">
         <v>8.2</v>
       </c>
       <c r="C65" t="s">
-        <v>12</v>
+        <v>262</v>
       </c>
       <c r="D65" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E65" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F65" t="s">
         <v>11</v>
       </c>
       <c r="G65" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="s">
-        <v>473</v>
-      </c>
-      <c r="B66" t="n">
-        <v>8.2</v>
-      </c>
-      <c r="C66" t="s">
-        <v>92</v>
-      </c>
-      <c r="D66" t="n">
-        <v>2</v>
-      </c>
-      <c r="E66" t="s">
-        <v>10</v>
-      </c>
-      <c r="F66" t="s">
-        <v>11</v>
-      </c>
-      <c r="G66" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="s">
-        <v>473</v>
-      </c>
-      <c r="B67" t="n">
-        <v>8.2</v>
-      </c>
-      <c r="C67" t="s">
-        <v>127</v>
-      </c>
-      <c r="D67" t="n">
-        <v>3</v>
-      </c>
-      <c r="E67" t="s">
-        <v>10</v>
-      </c>
-      <c r="F67" t="s">
-        <v>11</v>
-      </c>
-      <c r="G67" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="s">
-        <v>473</v>
-      </c>
-      <c r="B68" t="n">
-        <v>8.2</v>
-      </c>
-      <c r="C68" t="s">
-        <v>158</v>
-      </c>
-      <c r="D68" t="n">
-        <v>4</v>
-      </c>
-      <c r="E68" t="s">
-        <v>10</v>
-      </c>
-      <c r="F68" t="s">
-        <v>11</v>
-      </c>
-      <c r="G68" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="s">
-        <v>473</v>
-      </c>
-      <c r="B69" t="n">
-        <v>8.2</v>
-      </c>
-      <c r="C69" t="s">
-        <v>176</v>
-      </c>
-      <c r="D69" t="n">
-        <v>5</v>
-      </c>
-      <c r="E69" t="s">
-        <v>10</v>
-      </c>
-      <c r="F69" t="s">
-        <v>11</v>
-      </c>
-      <c r="G69" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="s">
-        <v>473</v>
-      </c>
-      <c r="B70" t="n">
-        <v>8.2</v>
-      </c>
-      <c r="C70" t="s">
-        <v>203</v>
-      </c>
-      <c r="D70" t="n">
-        <v>6</v>
-      </c>
-      <c r="E70" t="s">
-        <v>19</v>
-      </c>
-      <c r="F70" t="s">
-        <v>11</v>
-      </c>
-      <c r="G70" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="s">
-        <v>473</v>
-      </c>
-      <c r="B71" t="n">
-        <v>8.2</v>
-      </c>
-      <c r="C71" t="s">
-        <v>237</v>
-      </c>
-      <c r="D71" t="n">
-        <v>7</v>
-      </c>
-      <c r="E71" t="s">
-        <v>10</v>
-      </c>
-      <c r="F71" t="s">
-        <v>11</v>
-      </c>
-      <c r="G71" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="s">
-        <v>473</v>
-      </c>
-      <c r="B72" t="n">
-        <v>8.2</v>
-      </c>
-      <c r="C72" t="s">
-        <v>262</v>
-      </c>
-      <c r="D72" t="n">
-        <v>8</v>
-      </c>
-      <c r="E72" t="s">
-        <v>19</v>
-      </c>
-      <c r="F72" t="s">
-        <v>11</v>
-      </c>
-      <c r="G72" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="s">
-        <v>473</v>
-      </c>
-      <c r="B73" t="n">
-        <v>8.2</v>
-      </c>
-      <c r="C73" t="s">
-        <v>291</v>
-      </c>
-      <c r="D73" t="n">
-        <v>9</v>
-      </c>
-      <c r="E73" t="s">
-        <v>19</v>
-      </c>
-      <c r="F73" t="s">
-        <v>11</v>
-      </c>
-      <c r="G73" t="s">
         <v>19</v>
       </c>
     </row>
@@ -25012,21 +24810,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="B1" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="C1" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="D1" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="B2" t="n">
         <v>1</v>
@@ -25035,54 +24833,54 @@
         <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>336.080851276617</v>
+        <v>318.080851276617</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D3" t="n">
-        <v>40.4357357286305</v>
+        <v>161.699817591538</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>16</v>
+        <v>86</v>
       </c>
       <c r="D4" t="n">
-        <v>169.699817591538</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="D5" t="n">
-        <v>191.654561429724</v>
+        <v>158.090297158354</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="B6" t="n">
         <v>2</v>
@@ -25091,12 +24889,12 @@
         <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>123.433050356455</v>
+        <v>117.433050356455</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="B7" t="n">
         <v>2</v>
@@ -25105,12 +24903,12 @@
         <v>19</v>
       </c>
       <c r="D7" t="n">
-        <v>35.5613447848116</v>
+        <v>25.5613447848116</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="B8" t="n">
         <v>2</v>
@@ -25119,26 +24917,26 @@
         <v>16</v>
       </c>
       <c r="D8" t="n">
-        <v>202.728745098835</v>
+        <v>187.728745098835</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="B9" t="n">
         <v>2</v>
       </c>
       <c r="C9" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="D9" t="n">
-        <v>75.0283032288795</v>
+        <v>68.0283032288795</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="B10" t="n">
         <v>3</v>
@@ -25147,12 +24945,12 @@
         <v>10</v>
       </c>
       <c r="D10" t="n">
-        <v>80.9761478966684</v>
+        <v>69.9761478966684</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="B11" t="n">
         <v>3</v>
@@ -25161,12 +24959,12 @@
         <v>19</v>
       </c>
       <c r="D11" t="n">
-        <v>28.3782590097662</v>
+        <v>23.3782590097662</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="B12" t="n">
         <v>3</v>
@@ -25175,26 +24973,26 @@
         <v>16</v>
       </c>
       <c r="D12" t="n">
-        <v>205.745763807094</v>
+        <v>192.745763807094</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="B13" t="n">
         <v>3</v>
       </c>
       <c r="C13" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="D13" t="n">
-        <v>70.03391855809</v>
+        <v>65.03391855809</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="B14" t="n">
         <v>4</v>
@@ -25203,12 +25001,12 @@
         <v>10</v>
       </c>
       <c r="D14" t="n">
-        <v>66.3469031230314</v>
+        <v>63.3469031230314</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="B15" t="n">
         <v>4</v>
@@ -25217,12 +25015,12 @@
         <v>19</v>
       </c>
       <c r="D15" t="n">
-        <v>27.5016333122411</v>
+        <v>25.5016333122411</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="B16" t="n">
         <v>4</v>
@@ -25231,26 +25029,26 @@
         <v>16</v>
       </c>
       <c r="D16" t="n">
-        <v>181.560075908497</v>
+        <v>172.560075908497</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="B17" t="n">
         <v>4</v>
       </c>
       <c r="C17" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="D17" t="n">
-        <v>67.4717672663374</v>
+        <v>64.4717672663374</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="B18" t="n">
         <v>5</v>
@@ -25259,12 +25057,12 @@
         <v>10</v>
       </c>
       <c r="D18" t="n">
-        <v>638.968665995045</v>
+        <v>584.968665995045</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="B19" t="n">
         <v>5</v>
@@ -25273,12 +25071,12 @@
         <v>16</v>
       </c>
       <c r="D19" t="n">
-        <v>463.168177197315</v>
+        <v>423.168177197315</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="B20" t="n">
         <v>5</v>
@@ -25287,26 +25085,26 @@
         <v>39</v>
       </c>
       <c r="D20" t="n">
-        <v>211.095224336815</v>
+        <v>191.095224336815</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="B21" t="n">
         <v>5</v>
       </c>
       <c r="C21" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="D21" t="n">
-        <v>519.652686835759</v>
+        <v>450.652686835759</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="B22" t="n">
         <v>6</v>
@@ -25315,12 +25113,12 @@
         <v>10</v>
       </c>
       <c r="D22" t="n">
-        <v>2446.43752319239</v>
+        <v>2154.43752319239</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="B23" t="n">
         <v>6</v>
@@ -25329,12 +25127,12 @@
         <v>39</v>
       </c>
       <c r="D23" t="n">
-        <v>384.713255981969</v>
+        <v>304.713255981969</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="B24" t="n">
         <v>6</v>
@@ -25343,26 +25141,26 @@
         <v>54</v>
       </c>
       <c r="D24" t="n">
-        <v>505.262578811219</v>
+        <v>358.262578811219</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="B25" t="n">
         <v>6</v>
       </c>
       <c r="C25" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="D25" t="n">
-        <v>729.342289003483</v>
+        <v>611.342289003483</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="B26" t="n">
         <v>7</v>
@@ -25371,12 +25169,12 @@
         <v>10</v>
       </c>
       <c r="D26" t="n">
-        <v>8580.75685815979</v>
+        <v>7406.75685815979</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="B27" t="n">
         <v>7</v>
@@ -25385,12 +25183,12 @@
         <v>19</v>
       </c>
       <c r="D27" t="n">
-        <v>269.151549583756</v>
+        <v>191.151549583756</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="B28" t="n">
         <v>7</v>
@@ -25399,21 +25197,21 @@
         <v>54</v>
       </c>
       <c r="D28" t="n">
-        <v>391.243936788619</v>
+        <v>258.243936788619</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="B29" t="n">
         <v>7</v>
       </c>
       <c r="C29" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="D29" t="n">
-        <v>629.570375736621</v>
+        <v>509.570375736621</v>
       </c>
     </row>
   </sheetData>
@@ -25429,10 +25227,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="B1" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
@@ -25441,18 +25239,18 @@
         <v>9</v>
       </c>
       <c r="E1" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="F1" t="s">
         <v>1</v>
       </c>
       <c r="G1" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="B2" t="n">
         <v>1</v>
@@ -25475,7 +25273,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="B3" t="n">
         <v>1</v>
@@ -25498,7 +25296,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="B4" t="n">
         <v>1</v>
@@ -25521,7 +25319,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="B5" t="n">
         <v>1</v>
@@ -25544,7 +25342,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="B6" t="n">
         <v>1</v>
@@ -25567,7 +25365,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="B7" t="n">
         <v>1</v>
@@ -25585,12 +25383,12 @@
         <v>11</v>
       </c>
       <c r="G7" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="B8" t="n">
         <v>1</v>
@@ -25613,7 +25411,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="B9" t="n">
         <v>1</v>
@@ -25636,39 +25434,39 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C10" t="s">
-        <v>291</v>
+        <v>12</v>
       </c>
       <c r="D10" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F10" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G10" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="B11" t="n">
         <v>3</v>
       </c>
       <c r="C11" t="s">
-        <v>12</v>
+        <v>92</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11" t="s">
         <v>16</v>
@@ -25682,16 +25480,16 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="B12" t="n">
         <v>3</v>
       </c>
       <c r="C12" t="s">
-        <v>92</v>
+        <v>127</v>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E12" t="s">
         <v>16</v>
@@ -25705,16 +25503,16 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="B13" t="n">
         <v>3</v>
       </c>
       <c r="C13" t="s">
-        <v>127</v>
+        <v>158</v>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E13" t="s">
         <v>16</v>
@@ -25728,16 +25526,16 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="B14" t="n">
         <v>3</v>
       </c>
       <c r="C14" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E14" t="s">
         <v>16</v>
@@ -25751,16 +25549,16 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="B15" t="n">
         <v>3</v>
       </c>
       <c r="C15" t="s">
-        <v>176</v>
+        <v>203</v>
       </c>
       <c r="D15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E15" t="s">
         <v>16</v>
@@ -25774,16 +25572,16 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="B16" t="n">
         <v>3</v>
       </c>
       <c r="C16" t="s">
-        <v>203</v>
+        <v>237</v>
       </c>
       <c r="D16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E16" t="s">
         <v>16</v>
@@ -25797,16 +25595,16 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="B17" t="n">
         <v>3</v>
       </c>
       <c r="C17" t="s">
-        <v>237</v>
+        <v>262</v>
       </c>
       <c r="D17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E17" t="s">
         <v>16</v>
@@ -25820,16 +25618,16 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C18" t="s">
-        <v>262</v>
+        <v>12</v>
       </c>
       <c r="D18" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E18" t="s">
         <v>16</v>
@@ -25843,16 +25641,16 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="B19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C19" t="s">
-        <v>291</v>
+        <v>92</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E19" t="s">
         <v>16</v>
@@ -25866,16 +25664,16 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="B20" t="n">
         <v>4</v>
       </c>
       <c r="C20" t="s">
-        <v>12</v>
+        <v>127</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E20" t="s">
         <v>16</v>
@@ -25889,16 +25687,16 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="B21" t="n">
         <v>4</v>
       </c>
       <c r="C21" t="s">
-        <v>92</v>
+        <v>158</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E21" t="s">
         <v>16</v>
@@ -25912,16 +25710,16 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="B22" t="n">
         <v>4</v>
       </c>
       <c r="C22" t="s">
-        <v>127</v>
+        <v>176</v>
       </c>
       <c r="D22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E22" t="s">
         <v>16</v>
@@ -25935,16 +25733,16 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="B23" t="n">
         <v>4</v>
       </c>
       <c r="C23" t="s">
-        <v>158</v>
+        <v>203</v>
       </c>
       <c r="D23" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E23" t="s">
         <v>16</v>
@@ -25958,16 +25756,16 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="B24" t="n">
         <v>4</v>
       </c>
       <c r="C24" t="s">
-        <v>176</v>
+        <v>237</v>
       </c>
       <c r="D24" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E24" t="s">
         <v>16</v>
@@ -25981,16 +25779,16 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="B25" t="n">
         <v>4</v>
       </c>
       <c r="C25" t="s">
-        <v>203</v>
+        <v>262</v>
       </c>
       <c r="D25" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E25" t="s">
         <v>16</v>
@@ -26004,85 +25802,85 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="B26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C26" t="s">
-        <v>237</v>
+        <v>12</v>
       </c>
       <c r="D26" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E26" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F26" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G26" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="B27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C27" t="s">
-        <v>262</v>
+        <v>92</v>
       </c>
       <c r="D27" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E27" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F27" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G27" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="B28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C28" t="s">
-        <v>291</v>
+        <v>127</v>
       </c>
       <c r="D28" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E28" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F28" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G28" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="B29" t="n">
         <v>5</v>
       </c>
       <c r="C29" t="s">
-        <v>12</v>
+        <v>158</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E29" t="s">
         <v>10</v>
@@ -26096,62 +25894,62 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="B30" t="n">
         <v>5</v>
       </c>
       <c r="C30" t="s">
-        <v>92</v>
+        <v>176</v>
       </c>
       <c r="D30" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E30" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F30" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G30" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="B31" t="n">
         <v>5</v>
       </c>
       <c r="C31" t="s">
-        <v>127</v>
+        <v>203</v>
       </c>
       <c r="D31" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E31" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F31" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G31" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="B32" t="n">
         <v>5</v>
       </c>
       <c r="C32" t="s">
-        <v>158</v>
+        <v>237</v>
       </c>
       <c r="D32" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E32" t="s">
         <v>10</v>
@@ -26165,16 +25963,16 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="B33" t="n">
         <v>5</v>
       </c>
       <c r="C33" t="s">
-        <v>176</v>
+        <v>262</v>
       </c>
       <c r="D33" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E33" t="s">
         <v>16</v>
@@ -26188,39 +25986,39 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="B34" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C34" t="s">
-        <v>203</v>
+        <v>12</v>
       </c>
       <c r="D34" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E34" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F34" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G34" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="B35" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C35" t="s">
-        <v>237</v>
+        <v>92</v>
       </c>
       <c r="D35" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E35" t="s">
         <v>10</v>
@@ -26234,39 +26032,39 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="B36" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C36" t="s">
-        <v>262</v>
+        <v>127</v>
       </c>
       <c r="D36" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E36" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F36" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G36" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="B37" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C37" t="s">
-        <v>291</v>
+        <v>158</v>
       </c>
       <c r="D37" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E37" t="s">
         <v>10</v>
@@ -26280,16 +26078,16 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="B38" t="n">
         <v>6</v>
       </c>
       <c r="C38" t="s">
-        <v>12</v>
+        <v>176</v>
       </c>
       <c r="D38" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E38" t="s">
         <v>10</v>
@@ -26303,16 +26101,16 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="B39" t="n">
         <v>6</v>
       </c>
       <c r="C39" t="s">
-        <v>92</v>
+        <v>203</v>
       </c>
       <c r="D39" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E39" t="s">
         <v>10</v>
@@ -26326,16 +26124,16 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="B40" t="n">
         <v>6</v>
       </c>
       <c r="C40" t="s">
-        <v>127</v>
+        <v>237</v>
       </c>
       <c r="D40" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E40" t="s">
         <v>10</v>
@@ -26349,16 +26147,16 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="B41" t="n">
         <v>6</v>
       </c>
       <c r="C41" t="s">
-        <v>158</v>
+        <v>262</v>
       </c>
       <c r="D41" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E41" t="s">
         <v>10</v>
@@ -26372,16 +26170,16 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>470</v>
+        <v>460</v>
       </c>
       <c r="B42" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C42" t="s">
-        <v>176</v>
+        <v>12</v>
       </c>
       <c r="D42" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E42" t="s">
         <v>10</v>
@@ -26395,131 +26193,131 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>470</v>
+        <v>460</v>
       </c>
       <c r="B43" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C43" t="s">
-        <v>203</v>
+        <v>92</v>
       </c>
       <c r="D43" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E43" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F43" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G43" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>470</v>
+        <v>460</v>
       </c>
       <c r="B44" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C44" t="s">
-        <v>237</v>
+        <v>127</v>
       </c>
       <c r="D44" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E44" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F44" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G44" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>470</v>
+        <v>460</v>
       </c>
       <c r="B45" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C45" t="s">
-        <v>262</v>
+        <v>158</v>
       </c>
       <c r="D45" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E45" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F45" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G45" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>470</v>
+        <v>460</v>
       </c>
       <c r="B46" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C46" t="s">
-        <v>291</v>
+        <v>176</v>
       </c>
       <c r="D46" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E46" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F46" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G46" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="B47" t="n">
         <v>2</v>
       </c>
       <c r="C47" t="s">
-        <v>12</v>
+        <v>203</v>
       </c>
       <c r="D47" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E47" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F47" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G47" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="B48" t="n">
         <v>2</v>
       </c>
       <c r="C48" t="s">
-        <v>92</v>
+        <v>237</v>
       </c>
       <c r="D48" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E48" t="s">
         <v>16</v>
@@ -26533,16 +26331,16 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="B49" t="n">
         <v>2</v>
       </c>
       <c r="C49" t="s">
-        <v>127</v>
+        <v>262</v>
       </c>
       <c r="D49" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E49" t="s">
         <v>16</v>
@@ -26556,154 +26354,154 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B50" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C50" t="s">
-        <v>158</v>
+        <v>12</v>
       </c>
       <c r="D50" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E50" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F50" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G50" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B51" t="n">
+        <v>7</v>
+      </c>
+      <c r="C51" t="s">
+        <v>92</v>
+      </c>
+      <c r="D51" t="n">
         <v>2</v>
       </c>
-      <c r="C51" t="s">
-        <v>176</v>
-      </c>
-      <c r="D51" t="n">
-        <v>5</v>
-      </c>
       <c r="E51" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F51" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G51" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B52" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C52" t="s">
-        <v>203</v>
+        <v>127</v>
       </c>
       <c r="D52" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E52" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F52" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G52" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B53" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C53" t="s">
-        <v>237</v>
+        <v>158</v>
       </c>
       <c r="D53" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E53" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F53" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G53" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B54" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C54" t="s">
-        <v>262</v>
+        <v>176</v>
       </c>
       <c r="D54" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E54" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F54" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G54" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B55" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C55" t="s">
-        <v>291</v>
+        <v>203</v>
       </c>
       <c r="D55" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E55" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F55" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G55" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="B56" t="n">
         <v>7</v>
       </c>
       <c r="C56" t="s">
-        <v>12</v>
+        <v>237</v>
       </c>
       <c r="D56" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E56" t="s">
         <v>10</v>
@@ -26717,16 +26515,16 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="B57" t="n">
         <v>7</v>
       </c>
       <c r="C57" t="s">
-        <v>92</v>
+        <v>262</v>
       </c>
       <c r="D57" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E57" t="s">
         <v>10</v>
@@ -26740,16 +26538,16 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="B58" t="n">
-        <v>7</v>
+        <v>8.2</v>
       </c>
       <c r="C58" t="s">
-        <v>127</v>
+        <v>12</v>
       </c>
       <c r="D58" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E58" t="s">
         <v>10</v>
@@ -26763,16 +26561,16 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="B59" t="n">
-        <v>7</v>
+        <v>8.2</v>
       </c>
       <c r="C59" t="s">
-        <v>158</v>
+        <v>92</v>
       </c>
       <c r="D59" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E59" t="s">
         <v>10</v>
@@ -26786,16 +26584,16 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="B60" t="n">
-        <v>7</v>
+        <v>8.2</v>
       </c>
       <c r="C60" t="s">
-        <v>176</v>
+        <v>127</v>
       </c>
       <c r="D60" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E60" t="s">
         <v>10</v>
@@ -26809,16 +26607,16 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="B61" t="n">
-        <v>7</v>
+        <v>8.2</v>
       </c>
       <c r="C61" t="s">
-        <v>203</v>
+        <v>158</v>
       </c>
       <c r="D61" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E61" t="s">
         <v>10</v>
@@ -26832,16 +26630,16 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="B62" t="n">
-        <v>7</v>
+        <v>8.2</v>
       </c>
       <c r="C62" t="s">
-        <v>237</v>
+        <v>176</v>
       </c>
       <c r="D62" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E62" t="s">
         <v>10</v>
@@ -26855,16 +26653,16 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="B63" t="n">
-        <v>7</v>
+        <v>8.2</v>
       </c>
       <c r="C63" t="s">
-        <v>262</v>
+        <v>203</v>
       </c>
       <c r="D63" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E63" t="s">
         <v>10</v>
@@ -26878,16 +26676,16 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="B64" t="n">
+        <v>8.2</v>
+      </c>
+      <c r="C64" t="s">
+        <v>237</v>
+      </c>
+      <c r="D64" t="n">
         <v>7</v>
-      </c>
-      <c r="C64" t="s">
-        <v>291</v>
-      </c>
-      <c r="D64" t="n">
-        <v>9</v>
       </c>
       <c r="E64" t="s">
         <v>10</v>
@@ -26901,16 +26699,16 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="B65" t="n">
         <v>8.2</v>
       </c>
       <c r="C65" t="s">
-        <v>12</v>
+        <v>262</v>
       </c>
       <c r="D65" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E65" t="s">
         <v>10</v>
@@ -26919,190 +26717,6 @@
         <v>11</v>
       </c>
       <c r="G65" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="s">
-        <v>473</v>
-      </c>
-      <c r="B66" t="n">
-        <v>8.2</v>
-      </c>
-      <c r="C66" t="s">
-        <v>92</v>
-      </c>
-      <c r="D66" t="n">
-        <v>2</v>
-      </c>
-      <c r="E66" t="s">
-        <v>10</v>
-      </c>
-      <c r="F66" t="s">
-        <v>11</v>
-      </c>
-      <c r="G66" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="s">
-        <v>473</v>
-      </c>
-      <c r="B67" t="n">
-        <v>8.2</v>
-      </c>
-      <c r="C67" t="s">
-        <v>127</v>
-      </c>
-      <c r="D67" t="n">
-        <v>3</v>
-      </c>
-      <c r="E67" t="s">
-        <v>10</v>
-      </c>
-      <c r="F67" t="s">
-        <v>11</v>
-      </c>
-      <c r="G67" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="s">
-        <v>473</v>
-      </c>
-      <c r="B68" t="n">
-        <v>8.2</v>
-      </c>
-      <c r="C68" t="s">
-        <v>158</v>
-      </c>
-      <c r="D68" t="n">
-        <v>4</v>
-      </c>
-      <c r="E68" t="s">
-        <v>10</v>
-      </c>
-      <c r="F68" t="s">
-        <v>11</v>
-      </c>
-      <c r="G68" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="s">
-        <v>473</v>
-      </c>
-      <c r="B69" t="n">
-        <v>8.2</v>
-      </c>
-      <c r="C69" t="s">
-        <v>176</v>
-      </c>
-      <c r="D69" t="n">
-        <v>5</v>
-      </c>
-      <c r="E69" t="s">
-        <v>10</v>
-      </c>
-      <c r="F69" t="s">
-        <v>11</v>
-      </c>
-      <c r="G69" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="s">
-        <v>473</v>
-      </c>
-      <c r="B70" t="n">
-        <v>8.2</v>
-      </c>
-      <c r="C70" t="s">
-        <v>203</v>
-      </c>
-      <c r="D70" t="n">
-        <v>6</v>
-      </c>
-      <c r="E70" t="s">
-        <v>10</v>
-      </c>
-      <c r="F70" t="s">
-        <v>11</v>
-      </c>
-      <c r="G70" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="s">
-        <v>473</v>
-      </c>
-      <c r="B71" t="n">
-        <v>8.2</v>
-      </c>
-      <c r="C71" t="s">
-        <v>237</v>
-      </c>
-      <c r="D71" t="n">
-        <v>7</v>
-      </c>
-      <c r="E71" t="s">
-        <v>10</v>
-      </c>
-      <c r="F71" t="s">
-        <v>11</v>
-      </c>
-      <c r="G71" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="s">
-        <v>473</v>
-      </c>
-      <c r="B72" t="n">
-        <v>8.2</v>
-      </c>
-      <c r="C72" t="s">
-        <v>262</v>
-      </c>
-      <c r="D72" t="n">
-        <v>8</v>
-      </c>
-      <c r="E72" t="s">
-        <v>10</v>
-      </c>
-      <c r="F72" t="s">
-        <v>11</v>
-      </c>
-      <c r="G72" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="s">
-        <v>473</v>
-      </c>
-      <c r="B73" t="n">
-        <v>8.2</v>
-      </c>
-      <c r="C73" t="s">
-        <v>291</v>
-      </c>
-      <c r="D73" t="n">
-        <v>9</v>
-      </c>
-      <c r="E73" t="s">
-        <v>10</v>
-      </c>
-      <c r="F73" t="s">
-        <v>11</v>
-      </c>
-      <c r="G73" t="s">
         <v>10</v>
       </c>
     </row>

--- a/Outcome/Publish/figure_data/fig2.xlsx
+++ b/Outcome/Publish/figure_data/fig2.xlsx
@@ -22910,7 +22910,7 @@
         <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>1122035.09356982</v>
+        <v>1352767.09356982</v>
       </c>
     </row>
     <row r="3">
@@ -22924,7 +22924,7 @@
         <v>19</v>
       </c>
       <c r="D3" t="n">
-        <v>424390.716757474</v>
+        <v>668844.716757474</v>
       </c>
     </row>
     <row r="4">
@@ -22938,7 +22938,7 @@
         <v>27</v>
       </c>
       <c r="D4" t="n">
-        <v>635915.599275723</v>
+        <v>780643.599275723</v>
       </c>
     </row>
     <row r="5">
@@ -22952,7 +22952,7 @@
         <v>459</v>
       </c>
       <c r="D5" t="n">
-        <v>372089.920688537</v>
+        <v>410364.920688537</v>
       </c>
     </row>
     <row r="6">
@@ -22963,10 +22963,10 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>342927.419055442</v>
+        <v>209882.406276195</v>
       </c>
     </row>
     <row r="7">
@@ -22977,10 +22977,10 @@
         <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D7" t="n">
-        <v>177939.354133745</v>
+        <v>698234.419055442</v>
       </c>
     </row>
     <row r="8">
@@ -22991,10 +22991,10 @@
         <v>2</v>
       </c>
       <c r="C8" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D8" t="n">
-        <v>177032.729009513</v>
+        <v>196487.354133745</v>
       </c>
     </row>
     <row r="9">
@@ -23008,7 +23008,7 @@
         <v>459</v>
       </c>
       <c r="D9" t="n">
-        <v>299117.312757412</v>
+        <v>411701.63549073</v>
       </c>
     </row>
     <row r="10">
@@ -23022,7 +23022,7 @@
         <v>19</v>
       </c>
       <c r="D10" t="n">
-        <v>274748.23767102</v>
+        <v>526505.23767102</v>
       </c>
     </row>
     <row r="11">
@@ -23036,7 +23036,7 @@
         <v>16</v>
       </c>
       <c r="D11" t="n">
-        <v>295964.043334976</v>
+        <v>324080.043334976</v>
       </c>
     </row>
     <row r="12">
@@ -23050,7 +23050,7 @@
         <v>14</v>
       </c>
       <c r="D12" t="n">
-        <v>137663.40760811</v>
+        <v>151456.40760811</v>
       </c>
     </row>
     <row r="13">
@@ -23064,7 +23064,7 @@
         <v>459</v>
       </c>
       <c r="D13" t="n">
-        <v>141464.807880794</v>
+        <v>181103.807880794</v>
       </c>
     </row>
     <row r="14">
@@ -23078,7 +23078,7 @@
         <v>19</v>
       </c>
       <c r="D14" t="n">
-        <v>134604.701346544</v>
+        <v>256606.701346544</v>
       </c>
     </row>
     <row r="15">
@@ -23092,7 +23092,7 @@
         <v>16</v>
       </c>
       <c r="D15" t="n">
-        <v>208241.52818226</v>
+        <v>229081.52818226</v>
       </c>
     </row>
     <row r="16">
@@ -23106,7 +23106,7 @@
         <v>14</v>
       </c>
       <c r="D16" t="n">
-        <v>73372.3493339277</v>
+        <v>81020.3493339277</v>
       </c>
     </row>
     <row r="17">
@@ -23120,7 +23120,7 @@
         <v>459</v>
       </c>
       <c r="D17" t="n">
-        <v>146601.029471305</v>
+        <v>184956.029471305</v>
       </c>
     </row>
     <row r="18">
@@ -23134,7 +23134,7 @@
         <v>10</v>
       </c>
       <c r="D18" t="n">
-        <v>223030.379172665</v>
+        <v>292727.379172665</v>
       </c>
     </row>
     <row r="19">
@@ -23148,7 +23148,7 @@
         <v>19</v>
       </c>
       <c r="D19" t="n">
-        <v>500926.598146722</v>
+        <v>960694.598146722</v>
       </c>
     </row>
     <row r="20">
@@ -23162,7 +23162,7 @@
         <v>16</v>
       </c>
       <c r="D20" t="n">
-        <v>390503.75352447</v>
+        <v>443001.75352447</v>
       </c>
     </row>
     <row r="21">
@@ -23176,7 +23176,7 @@
         <v>459</v>
       </c>
       <c r="D21" t="n">
-        <v>612843.991080393</v>
+        <v>740759.991080393</v>
       </c>
     </row>
     <row r="22">
@@ -23190,7 +23190,7 @@
         <v>10</v>
       </c>
       <c r="D22" t="n">
-        <v>493463.515626952</v>
+        <v>632294.515626952</v>
       </c>
     </row>
     <row r="23">
@@ -23204,7 +23204,7 @@
         <v>19</v>
       </c>
       <c r="D23" t="n">
-        <v>306849.006020735</v>
+        <v>589344.006020735</v>
       </c>
     </row>
     <row r="24">
@@ -23218,7 +23218,7 @@
         <v>16</v>
       </c>
       <c r="D24" t="n">
-        <v>133103.300212957</v>
+        <v>157078.300212957</v>
       </c>
     </row>
     <row r="25">
@@ -23232,7 +23232,7 @@
         <v>459</v>
       </c>
       <c r="D25" t="n">
-        <v>335025.73923787</v>
+        <v>402068.73923787</v>
       </c>
     </row>
     <row r="26">
@@ -23246,7 +23246,7 @@
         <v>10</v>
       </c>
       <c r="D26" t="n">
-        <v>1256320.70529812</v>
+        <v>1624393.70529812</v>
       </c>
     </row>
     <row r="27">
@@ -23260,7 +23260,7 @@
         <v>19</v>
       </c>
       <c r="D27" t="n">
-        <v>149106.321002064</v>
+        <v>290810.321002064</v>
       </c>
     </row>
     <row r="28">
@@ -23274,7 +23274,7 @@
         <v>16</v>
       </c>
       <c r="D28" t="n">
-        <v>39708.1745600166</v>
+        <v>50650.1745600166</v>
       </c>
     </row>
     <row r="29">
@@ -23288,7 +23288,7 @@
         <v>459</v>
       </c>
       <c r="D29" t="n">
-        <v>142650.26604043</v>
+        <v>182005.26604043</v>
       </c>
     </row>
   </sheetData>
@@ -23511,25 +23511,25 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>12</v>
+        <v>291</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E10" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F10" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G10" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
@@ -23540,10 +23540,10 @@
         <v>3</v>
       </c>
       <c r="C11" t="s">
-        <v>92</v>
+        <v>12</v>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E11" t="s">
         <v>16</v>
@@ -23563,10 +23563,10 @@
         <v>3</v>
       </c>
       <c r="C12" t="s">
-        <v>127</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E12" t="s">
         <v>16</v>
@@ -23586,10 +23586,10 @@
         <v>3</v>
       </c>
       <c r="C13" t="s">
-        <v>158</v>
+        <v>127</v>
       </c>
       <c r="D13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E13" t="s">
         <v>16</v>
@@ -23609,19 +23609,19 @@
         <v>3</v>
       </c>
       <c r="C14" t="s">
-        <v>176</v>
+        <v>158</v>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E14" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F14" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G14" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15">
@@ -23632,10 +23632,10 @@
         <v>3</v>
       </c>
       <c r="C15" t="s">
-        <v>203</v>
+        <v>176</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E15" t="s">
         <v>19</v>
@@ -23655,19 +23655,19 @@
         <v>3</v>
       </c>
       <c r="C16" t="s">
-        <v>237</v>
+        <v>203</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E16" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F16" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G16" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17">
@@ -23678,65 +23678,65 @@
         <v>3</v>
       </c>
       <c r="C17" t="s">
-        <v>262</v>
+        <v>237</v>
       </c>
       <c r="D17" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E17" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F17" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G17" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C18" t="s">
-        <v>12</v>
+        <v>262</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E18" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F18" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G18" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C19" t="s">
-        <v>92</v>
+        <v>291</v>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E19" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F19" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G19" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20">
@@ -23747,10 +23747,10 @@
         <v>4</v>
       </c>
       <c r="C20" t="s">
-        <v>127</v>
+        <v>12</v>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E20" t="s">
         <v>16</v>
@@ -23770,10 +23770,10 @@
         <v>4</v>
       </c>
       <c r="C21" t="s">
-        <v>158</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E21" t="s">
         <v>16</v>
@@ -23793,19 +23793,19 @@
         <v>4</v>
       </c>
       <c r="C22" t="s">
-        <v>176</v>
+        <v>127</v>
       </c>
       <c r="D22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E22" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F22" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G22" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23">
@@ -23816,10 +23816,10 @@
         <v>4</v>
       </c>
       <c r="C23" t="s">
-        <v>203</v>
+        <v>158</v>
       </c>
       <c r="D23" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E23" t="s">
         <v>16</v>
@@ -23839,19 +23839,19 @@
         <v>4</v>
       </c>
       <c r="C24" t="s">
-        <v>237</v>
+        <v>176</v>
       </c>
       <c r="D24" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E24" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F24" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G24" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25">
@@ -23862,33 +23862,33 @@
         <v>4</v>
       </c>
       <c r="C25" t="s">
-        <v>262</v>
+        <v>203</v>
       </c>
       <c r="D25" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E25" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F25" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G25" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C26" t="s">
-        <v>12</v>
+        <v>237</v>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E26" t="s">
         <v>16</v>
@@ -23902,48 +23902,48 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C27" t="s">
-        <v>92</v>
+        <v>262</v>
       </c>
       <c r="D27" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E27" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F27" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G27" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C28" t="s">
-        <v>127</v>
+        <v>291</v>
       </c>
       <c r="D28" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E28" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F28" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G28" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="29">
@@ -23954,10 +23954,10 @@
         <v>5</v>
       </c>
       <c r="C29" t="s">
-        <v>158</v>
+        <v>12</v>
       </c>
       <c r="D29" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E29" t="s">
         <v>16</v>
@@ -23977,19 +23977,19 @@
         <v>5</v>
       </c>
       <c r="C30" t="s">
-        <v>176</v>
+        <v>92</v>
       </c>
       <c r="D30" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E30" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F30" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G30" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="31">
@@ -24000,19 +24000,19 @@
         <v>5</v>
       </c>
       <c r="C31" t="s">
-        <v>203</v>
+        <v>127</v>
       </c>
       <c r="D31" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E31" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F31" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G31" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="32">
@@ -24023,19 +24023,19 @@
         <v>5</v>
       </c>
       <c r="C32" t="s">
-        <v>237</v>
+        <v>158</v>
       </c>
       <c r="D32" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E32" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F32" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G32" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="33">
@@ -24046,10 +24046,10 @@
         <v>5</v>
       </c>
       <c r="C33" t="s">
-        <v>262</v>
+        <v>176</v>
       </c>
       <c r="D33" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E33" t="s">
         <v>19</v>
@@ -24063,39 +24063,39 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B34" t="n">
+        <v>5</v>
+      </c>
+      <c r="C34" t="s">
+        <v>203</v>
+      </c>
+      <c r="D34" t="n">
         <v>6</v>
       </c>
-      <c r="C34" t="s">
-        <v>12</v>
-      </c>
-      <c r="D34" t="n">
-        <v>1</v>
-      </c>
       <c r="E34" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F34" t="s">
         <v>11</v>
       </c>
       <c r="G34" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B35" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C35" t="s">
-        <v>92</v>
+        <v>237</v>
       </c>
       <c r="D35" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E35" t="s">
         <v>10</v>
@@ -24109,48 +24109,48 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B36" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C36" t="s">
-        <v>127</v>
+        <v>262</v>
       </c>
       <c r="D36" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E36" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F36" t="s">
         <v>11</v>
       </c>
       <c r="G36" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C37" t="s">
-        <v>158</v>
+        <v>291</v>
       </c>
       <c r="D37" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E37" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F37" t="s">
         <v>11</v>
       </c>
       <c r="G37" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="38">
@@ -24161,10 +24161,10 @@
         <v>6</v>
       </c>
       <c r="C38" t="s">
-        <v>176</v>
+        <v>12</v>
       </c>
       <c r="D38" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E38" t="s">
         <v>10</v>
@@ -24184,10 +24184,10 @@
         <v>6</v>
       </c>
       <c r="C39" t="s">
-        <v>203</v>
+        <v>92</v>
       </c>
       <c r="D39" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E39" t="s">
         <v>10</v>
@@ -24207,10 +24207,10 @@
         <v>6</v>
       </c>
       <c r="C40" t="s">
-        <v>237</v>
+        <v>127</v>
       </c>
       <c r="D40" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E40" t="s">
         <v>10</v>
@@ -24230,10 +24230,10 @@
         <v>6</v>
       </c>
       <c r="C41" t="s">
-        <v>262</v>
+        <v>158</v>
       </c>
       <c r="D41" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E41" t="s">
         <v>10</v>
@@ -24247,108 +24247,108 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="B42" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C42" t="s">
-        <v>12</v>
+        <v>176</v>
       </c>
       <c r="D42" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E42" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F42" t="s">
         <v>11</v>
       </c>
       <c r="G42" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="B43" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C43" t="s">
-        <v>92</v>
+        <v>203</v>
       </c>
       <c r="D43" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E43" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F43" t="s">
         <v>11</v>
       </c>
       <c r="G43" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="B44" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C44" t="s">
-        <v>127</v>
+        <v>237</v>
       </c>
       <c r="D44" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E44" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F44" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G44" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="B45" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C45" t="s">
-        <v>158</v>
+        <v>262</v>
       </c>
       <c r="D45" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E45" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F45" t="s">
         <v>11</v>
       </c>
       <c r="G45" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="B46" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C46" t="s">
-        <v>176</v>
+        <v>291</v>
       </c>
       <c r="D46" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E46" t="s">
         <v>19</v>
@@ -24368,19 +24368,19 @@
         <v>2</v>
       </c>
       <c r="C47" t="s">
-        <v>203</v>
+        <v>12</v>
       </c>
       <c r="D47" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E47" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F47" t="s">
         <v>11</v>
       </c>
       <c r="G47" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="48">
@@ -24391,19 +24391,19 @@
         <v>2</v>
       </c>
       <c r="C48" t="s">
-        <v>237</v>
+        <v>92</v>
       </c>
       <c r="D48" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E48" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F48" t="s">
         <v>11</v>
       </c>
       <c r="G48" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="49">
@@ -24414,157 +24414,157 @@
         <v>2</v>
       </c>
       <c r="C49" t="s">
-        <v>262</v>
+        <v>127</v>
       </c>
       <c r="D49" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E49" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F49" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G49" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="B50" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C50" t="s">
-        <v>12</v>
+        <v>158</v>
       </c>
       <c r="D50" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E50" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F50" t="s">
         <v>11</v>
       </c>
       <c r="G50" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="B51" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C51" t="s">
-        <v>92</v>
+        <v>176</v>
       </c>
       <c r="D51" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E51" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F51" t="s">
         <v>11</v>
       </c>
       <c r="G51" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="B52" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C52" t="s">
-        <v>127</v>
+        <v>203</v>
       </c>
       <c r="D52" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E52" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F52" t="s">
         <v>11</v>
       </c>
       <c r="G52" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="B53" t="n">
+        <v>2</v>
+      </c>
+      <c r="C53" t="s">
+        <v>237</v>
+      </c>
+      <c r="D53" t="n">
         <v>7</v>
       </c>
-      <c r="C53" t="s">
-        <v>158</v>
-      </c>
-      <c r="D53" t="n">
-        <v>4</v>
-      </c>
       <c r="E53" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F53" t="s">
         <v>11</v>
       </c>
       <c r="G53" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="B54" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C54" t="s">
-        <v>176</v>
+        <v>262</v>
       </c>
       <c r="D54" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E54" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F54" t="s">
         <v>11</v>
       </c>
       <c r="G54" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="B55" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C55" t="s">
-        <v>203</v>
+        <v>291</v>
       </c>
       <c r="D55" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E55" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F55" t="s">
         <v>11</v>
       </c>
       <c r="G55" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="56">
@@ -24575,10 +24575,10 @@
         <v>7</v>
       </c>
       <c r="C56" t="s">
-        <v>237</v>
+        <v>12</v>
       </c>
       <c r="D56" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E56" t="s">
         <v>10</v>
@@ -24598,10 +24598,10 @@
         <v>7</v>
       </c>
       <c r="C57" t="s">
-        <v>262</v>
+        <v>92</v>
       </c>
       <c r="D57" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E57" t="s">
         <v>10</v>
@@ -24615,16 +24615,16 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="B58" t="n">
-        <v>8.2</v>
+        <v>7</v>
       </c>
       <c r="C58" t="s">
-        <v>12</v>
+        <v>127</v>
       </c>
       <c r="D58" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E58" t="s">
         <v>10</v>
@@ -24638,16 +24638,16 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="B59" t="n">
-        <v>8.2</v>
+        <v>7</v>
       </c>
       <c r="C59" t="s">
-        <v>92</v>
+        <v>158</v>
       </c>
       <c r="D59" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E59" t="s">
         <v>10</v>
@@ -24661,16 +24661,16 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="B60" t="n">
-        <v>8.2</v>
+        <v>7</v>
       </c>
       <c r="C60" t="s">
-        <v>127</v>
+        <v>176</v>
       </c>
       <c r="D60" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E60" t="s">
         <v>10</v>
@@ -24684,16 +24684,16 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="B61" t="n">
-        <v>8.2</v>
+        <v>7</v>
       </c>
       <c r="C61" t="s">
-        <v>158</v>
+        <v>203</v>
       </c>
       <c r="D61" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E61" t="s">
         <v>10</v>
@@ -24707,16 +24707,16 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="B62" t="n">
-        <v>8.2</v>
+        <v>7</v>
       </c>
       <c r="C62" t="s">
-        <v>176</v>
+        <v>237</v>
       </c>
       <c r="D62" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E62" t="s">
         <v>10</v>
@@ -24730,39 +24730,39 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="B63" t="n">
-        <v>8.2</v>
+        <v>7</v>
       </c>
       <c r="C63" t="s">
-        <v>203</v>
+        <v>262</v>
       </c>
       <c r="D63" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E63" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F63" t="s">
         <v>11</v>
       </c>
       <c r="G63" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="B64" t="n">
-        <v>8.2</v>
+        <v>7</v>
       </c>
       <c r="C64" t="s">
-        <v>237</v>
+        <v>291</v>
       </c>
       <c r="D64" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E64" t="s">
         <v>10</v>
@@ -24782,18 +24782,202 @@
         <v>8.2</v>
       </c>
       <c r="C65" t="s">
+        <v>12</v>
+      </c>
+      <c r="D65" t="n">
+        <v>1</v>
+      </c>
+      <c r="E65" t="s">
+        <v>10</v>
+      </c>
+      <c r="F65" t="s">
+        <v>11</v>
+      </c>
+      <c r="G65" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>467</v>
+      </c>
+      <c r="B66" t="n">
+        <v>8.2</v>
+      </c>
+      <c r="C66" t="s">
+        <v>92</v>
+      </c>
+      <c r="D66" t="n">
+        <v>2</v>
+      </c>
+      <c r="E66" t="s">
+        <v>10</v>
+      </c>
+      <c r="F66" t="s">
+        <v>11</v>
+      </c>
+      <c r="G66" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>467</v>
+      </c>
+      <c r="B67" t="n">
+        <v>8.2</v>
+      </c>
+      <c r="C67" t="s">
+        <v>127</v>
+      </c>
+      <c r="D67" t="n">
+        <v>3</v>
+      </c>
+      <c r="E67" t="s">
+        <v>10</v>
+      </c>
+      <c r="F67" t="s">
+        <v>11</v>
+      </c>
+      <c r="G67" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>467</v>
+      </c>
+      <c r="B68" t="n">
+        <v>8.2</v>
+      </c>
+      <c r="C68" t="s">
+        <v>158</v>
+      </c>
+      <c r="D68" t="n">
+        <v>4</v>
+      </c>
+      <c r="E68" t="s">
+        <v>10</v>
+      </c>
+      <c r="F68" t="s">
+        <v>11</v>
+      </c>
+      <c r="G68" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>467</v>
+      </c>
+      <c r="B69" t="n">
+        <v>8.2</v>
+      </c>
+      <c r="C69" t="s">
+        <v>176</v>
+      </c>
+      <c r="D69" t="n">
+        <v>5</v>
+      </c>
+      <c r="E69" t="s">
+        <v>10</v>
+      </c>
+      <c r="F69" t="s">
+        <v>11</v>
+      </c>
+      <c r="G69" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>467</v>
+      </c>
+      <c r="B70" t="n">
+        <v>8.2</v>
+      </c>
+      <c r="C70" t="s">
+        <v>203</v>
+      </c>
+      <c r="D70" t="n">
+        <v>6</v>
+      </c>
+      <c r="E70" t="s">
+        <v>19</v>
+      </c>
+      <c r="F70" t="s">
+        <v>11</v>
+      </c>
+      <c r="G70" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>467</v>
+      </c>
+      <c r="B71" t="n">
+        <v>8.2</v>
+      </c>
+      <c r="C71" t="s">
+        <v>237</v>
+      </c>
+      <c r="D71" t="n">
+        <v>7</v>
+      </c>
+      <c r="E71" t="s">
+        <v>10</v>
+      </c>
+      <c r="F71" t="s">
+        <v>11</v>
+      </c>
+      <c r="G71" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>467</v>
+      </c>
+      <c r="B72" t="n">
+        <v>8.2</v>
+      </c>
+      <c r="C72" t="s">
         <v>262</v>
       </c>
-      <c r="D65" t="n">
+      <c r="D72" t="n">
         <v>8</v>
       </c>
-      <c r="E65" t="s">
+      <c r="E72" t="s">
         <v>19</v>
       </c>
-      <c r="F65" t="s">
-        <v>11</v>
-      </c>
-      <c r="G65" t="s">
+      <c r="F72" t="s">
+        <v>11</v>
+      </c>
+      <c r="G72" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>467</v>
+      </c>
+      <c r="B73" t="n">
+        <v>8.2</v>
+      </c>
+      <c r="C73" t="s">
+        <v>291</v>
+      </c>
+      <c r="D73" t="n">
+        <v>9</v>
+      </c>
+      <c r="E73" t="s">
+        <v>19</v>
+      </c>
+      <c r="F73" t="s">
+        <v>11</v>
+      </c>
+      <c r="G73" t="s">
         <v>19</v>
       </c>
     </row>
@@ -24833,7 +25017,7 @@
         <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>318.080851276617</v>
+        <v>336.080851276617</v>
       </c>
     </row>
     <row r="3">
@@ -24844,10 +25028,10 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D3" t="n">
-        <v>161.699817591538</v>
+        <v>40.4357357286305</v>
       </c>
     </row>
     <row r="4">
@@ -24858,10 +25042,10 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>86</v>
+        <v>16</v>
       </c>
       <c r="D4" t="n">
-        <v>38</v>
+        <v>169.699817591538</v>
       </c>
     </row>
     <row r="5">
@@ -24875,7 +25059,7 @@
         <v>459</v>
       </c>
       <c r="D5" t="n">
-        <v>158.090297158354</v>
+        <v>191.654561429724</v>
       </c>
     </row>
     <row r="6">
@@ -24889,7 +25073,7 @@
         <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>117.433050356455</v>
+        <v>123.433050356455</v>
       </c>
     </row>
     <row r="7">
@@ -24903,7 +25087,7 @@
         <v>19</v>
       </c>
       <c r="D7" t="n">
-        <v>25.5613447848116</v>
+        <v>35.5613447848116</v>
       </c>
     </row>
     <row r="8">
@@ -24917,7 +25101,7 @@
         <v>16</v>
       </c>
       <c r="D8" t="n">
-        <v>187.728745098835</v>
+        <v>202.728745098835</v>
       </c>
     </row>
     <row r="9">
@@ -24931,7 +25115,7 @@
         <v>459</v>
       </c>
       <c r="D9" t="n">
-        <v>68.0283032288795</v>
+        <v>75.0283032288795</v>
       </c>
     </row>
     <row r="10">
@@ -24945,7 +25129,7 @@
         <v>10</v>
       </c>
       <c r="D10" t="n">
-        <v>69.9761478966684</v>
+        <v>81.9761478966684</v>
       </c>
     </row>
     <row r="11">
@@ -24959,7 +25143,7 @@
         <v>19</v>
       </c>
       <c r="D11" t="n">
-        <v>23.3782590097662</v>
+        <v>28.3782590097662</v>
       </c>
     </row>
     <row r="12">
@@ -24973,7 +25157,7 @@
         <v>16</v>
       </c>
       <c r="D12" t="n">
-        <v>192.745763807094</v>
+        <v>206.745763807094</v>
       </c>
     </row>
     <row r="13">
@@ -24987,7 +25171,7 @@
         <v>459</v>
       </c>
       <c r="D13" t="n">
-        <v>65.03391855809</v>
+        <v>71.03391855809</v>
       </c>
     </row>
     <row r="14">
@@ -25001,7 +25185,7 @@
         <v>10</v>
       </c>
       <c r="D14" t="n">
-        <v>63.3469031230314</v>
+        <v>66.3469031230314</v>
       </c>
     </row>
     <row r="15">
@@ -25015,7 +25199,7 @@
         <v>19</v>
       </c>
       <c r="D15" t="n">
-        <v>25.5016333122411</v>
+        <v>27.5016333122411</v>
       </c>
     </row>
     <row r="16">
@@ -25029,7 +25213,7 @@
         <v>16</v>
       </c>
       <c r="D16" t="n">
-        <v>172.560075908497</v>
+        <v>181.560075908497</v>
       </c>
     </row>
     <row r="17">
@@ -25043,7 +25227,7 @@
         <v>459</v>
       </c>
       <c r="D17" t="n">
-        <v>64.4717672663374</v>
+        <v>67.4717672663374</v>
       </c>
     </row>
     <row r="18">
@@ -25057,7 +25241,7 @@
         <v>10</v>
       </c>
       <c r="D18" t="n">
-        <v>584.968665995045</v>
+        <v>642.968665995045</v>
       </c>
     </row>
     <row r="19">
@@ -25071,7 +25255,7 @@
         <v>16</v>
       </c>
       <c r="D19" t="n">
-        <v>423.168177197315</v>
+        <v>463.168177197315</v>
       </c>
     </row>
     <row r="20">
@@ -25085,7 +25269,7 @@
         <v>39</v>
       </c>
       <c r="D20" t="n">
-        <v>191.095224336815</v>
+        <v>212.095224336815</v>
       </c>
     </row>
     <row r="21">
@@ -25099,7 +25283,7 @@
         <v>459</v>
       </c>
       <c r="D21" t="n">
-        <v>450.652686835759</v>
+        <v>519.652686835759</v>
       </c>
     </row>
     <row r="22">
@@ -25113,7 +25297,7 @@
         <v>10</v>
       </c>
       <c r="D22" t="n">
-        <v>2154.43752319239</v>
+        <v>2457.43752319239</v>
       </c>
     </row>
     <row r="23">
@@ -25127,7 +25311,7 @@
         <v>39</v>
       </c>
       <c r="D23" t="n">
-        <v>304.713255981969</v>
+        <v>386.713255981969</v>
       </c>
     </row>
     <row r="24">
@@ -25141,7 +25325,7 @@
         <v>54</v>
       </c>
       <c r="D24" t="n">
-        <v>358.262578811219</v>
+        <v>512.262578811219</v>
       </c>
     </row>
     <row r="25">
@@ -25155,7 +25339,7 @@
         <v>459</v>
       </c>
       <c r="D25" t="n">
-        <v>611.342289003483</v>
+        <v>733.342289003483</v>
       </c>
     </row>
     <row r="26">
@@ -25169,7 +25353,7 @@
         <v>10</v>
       </c>
       <c r="D26" t="n">
-        <v>7406.75685815979</v>
+        <v>8634.75685815979</v>
       </c>
     </row>
     <row r="27">
@@ -25183,7 +25367,7 @@
         <v>19</v>
       </c>
       <c r="D27" t="n">
-        <v>191.151549583756</v>
+        <v>279.151549583756</v>
       </c>
     </row>
     <row r="28">
@@ -25197,7 +25381,7 @@
         <v>54</v>
       </c>
       <c r="D28" t="n">
-        <v>258.243936788619</v>
+        <v>396.243936788619</v>
       </c>
     </row>
     <row r="29">
@@ -25211,7 +25395,7 @@
         <v>459</v>
       </c>
       <c r="D29" t="n">
-        <v>509.570375736621</v>
+        <v>633.570375736621</v>
       </c>
     </row>
   </sheetData>
@@ -25434,25 +25618,25 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>12</v>
+        <v>291</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E10" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G10" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
@@ -25463,10 +25647,10 @@
         <v>3</v>
       </c>
       <c r="C11" t="s">
-        <v>92</v>
+        <v>12</v>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E11" t="s">
         <v>16</v>
@@ -25486,10 +25670,10 @@
         <v>3</v>
       </c>
       <c r="C12" t="s">
-        <v>127</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E12" t="s">
         <v>16</v>
@@ -25509,10 +25693,10 @@
         <v>3</v>
       </c>
       <c r="C13" t="s">
-        <v>158</v>
+        <v>127</v>
       </c>
       <c r="D13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E13" t="s">
         <v>16</v>
@@ -25532,10 +25716,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="s">
-        <v>176</v>
+        <v>158</v>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E14" t="s">
         <v>16</v>
@@ -25555,10 +25739,10 @@
         <v>3</v>
       </c>
       <c r="C15" t="s">
-        <v>203</v>
+        <v>176</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E15" t="s">
         <v>16</v>
@@ -25578,10 +25762,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="s">
-        <v>237</v>
+        <v>203</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E16" t="s">
         <v>16</v>
@@ -25601,10 +25785,10 @@
         <v>3</v>
       </c>
       <c r="C17" t="s">
-        <v>262</v>
+        <v>237</v>
       </c>
       <c r="D17" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E17" t="s">
         <v>16</v>
@@ -25618,16 +25802,16 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C18" t="s">
-        <v>12</v>
+        <v>262</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E18" t="s">
         <v>16</v>
@@ -25641,16 +25825,16 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C19" t="s">
-        <v>92</v>
+        <v>291</v>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E19" t="s">
         <v>16</v>
@@ -25670,10 +25854,10 @@
         <v>4</v>
       </c>
       <c r="C20" t="s">
-        <v>127</v>
+        <v>12</v>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E20" t="s">
         <v>16</v>
@@ -25693,10 +25877,10 @@
         <v>4</v>
       </c>
       <c r="C21" t="s">
-        <v>158</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E21" t="s">
         <v>16</v>
@@ -25716,10 +25900,10 @@
         <v>4</v>
       </c>
       <c r="C22" t="s">
-        <v>176</v>
+        <v>127</v>
       </c>
       <c r="D22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E22" t="s">
         <v>16</v>
@@ -25739,10 +25923,10 @@
         <v>4</v>
       </c>
       <c r="C23" t="s">
-        <v>203</v>
+        <v>158</v>
       </c>
       <c r="D23" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E23" t="s">
         <v>16</v>
@@ -25762,10 +25946,10 @@
         <v>4</v>
       </c>
       <c r="C24" t="s">
-        <v>237</v>
+        <v>176</v>
       </c>
       <c r="D24" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E24" t="s">
         <v>16</v>
@@ -25785,10 +25969,10 @@
         <v>4</v>
       </c>
       <c r="C25" t="s">
-        <v>262</v>
+        <v>203</v>
       </c>
       <c r="D25" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E25" t="s">
         <v>16</v>
@@ -25802,71 +25986,71 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C26" t="s">
-        <v>12</v>
+        <v>237</v>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E26" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F26" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G26" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C27" t="s">
-        <v>92</v>
+        <v>262</v>
       </c>
       <c r="D27" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E27" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F27" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G27" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C28" t="s">
-        <v>127</v>
+        <v>291</v>
       </c>
       <c r="D28" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E28" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F28" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G28" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="29">
@@ -25877,10 +26061,10 @@
         <v>5</v>
       </c>
       <c r="C29" t="s">
-        <v>158</v>
+        <v>12</v>
       </c>
       <c r="D29" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E29" t="s">
         <v>10</v>
@@ -25900,19 +26084,19 @@
         <v>5</v>
       </c>
       <c r="C30" t="s">
-        <v>176</v>
+        <v>92</v>
       </c>
       <c r="D30" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E30" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F30" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G30" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31">
@@ -25923,19 +26107,19 @@
         <v>5</v>
       </c>
       <c r="C31" t="s">
-        <v>203</v>
+        <v>127</v>
       </c>
       <c r="D31" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E31" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F31" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G31" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32">
@@ -25946,10 +26130,10 @@
         <v>5</v>
       </c>
       <c r="C32" t="s">
-        <v>237</v>
+        <v>158</v>
       </c>
       <c r="D32" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E32" t="s">
         <v>10</v>
@@ -25969,10 +26153,10 @@
         <v>5</v>
       </c>
       <c r="C33" t="s">
-        <v>262</v>
+        <v>176</v>
       </c>
       <c r="D33" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E33" t="s">
         <v>16</v>
@@ -25986,39 +26170,39 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B34" t="n">
+        <v>5</v>
+      </c>
+      <c r="C34" t="s">
+        <v>203</v>
+      </c>
+      <c r="D34" t="n">
         <v>6</v>
       </c>
-      <c r="C34" t="s">
-        <v>12</v>
-      </c>
-      <c r="D34" t="n">
-        <v>1</v>
-      </c>
       <c r="E34" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F34" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G34" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B35" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C35" t="s">
-        <v>92</v>
+        <v>237</v>
       </c>
       <c r="D35" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E35" t="s">
         <v>10</v>
@@ -26032,39 +26216,39 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B36" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C36" t="s">
-        <v>127</v>
+        <v>262</v>
       </c>
       <c r="D36" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E36" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F36" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G36" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C37" t="s">
-        <v>158</v>
+        <v>291</v>
       </c>
       <c r="D37" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E37" t="s">
         <v>10</v>
@@ -26084,10 +26268,10 @@
         <v>6</v>
       </c>
       <c r="C38" t="s">
-        <v>176</v>
+        <v>12</v>
       </c>
       <c r="D38" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E38" t="s">
         <v>10</v>
@@ -26107,10 +26291,10 @@
         <v>6</v>
       </c>
       <c r="C39" t="s">
-        <v>203</v>
+        <v>92</v>
       </c>
       <c r="D39" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E39" t="s">
         <v>10</v>
@@ -26130,10 +26314,10 @@
         <v>6</v>
       </c>
       <c r="C40" t="s">
-        <v>237</v>
+        <v>127</v>
       </c>
       <c r="D40" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E40" t="s">
         <v>10</v>
@@ -26153,10 +26337,10 @@
         <v>6</v>
       </c>
       <c r="C41" t="s">
-        <v>262</v>
+        <v>158</v>
       </c>
       <c r="D41" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E41" t="s">
         <v>10</v>
@@ -26170,16 +26354,16 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="B42" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C42" t="s">
-        <v>12</v>
+        <v>176</v>
       </c>
       <c r="D42" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E42" t="s">
         <v>10</v>
@@ -26193,94 +26377,94 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="B43" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C43" t="s">
-        <v>92</v>
+        <v>203</v>
       </c>
       <c r="D43" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E43" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F43" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G43" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="B44" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C44" t="s">
-        <v>127</v>
+        <v>237</v>
       </c>
       <c r="D44" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E44" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F44" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G44" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="B45" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C45" t="s">
-        <v>158</v>
+        <v>262</v>
       </c>
       <c r="D45" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E45" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F45" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G45" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="B46" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C46" t="s">
-        <v>176</v>
+        <v>291</v>
       </c>
       <c r="D46" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E46" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F46" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G46" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="47">
@@ -26291,19 +26475,19 @@
         <v>2</v>
       </c>
       <c r="C47" t="s">
-        <v>203</v>
+        <v>12</v>
       </c>
       <c r="D47" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E47" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F47" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G47" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="48">
@@ -26314,10 +26498,10 @@
         <v>2</v>
       </c>
       <c r="C48" t="s">
-        <v>237</v>
+        <v>92</v>
       </c>
       <c r="D48" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E48" t="s">
         <v>16</v>
@@ -26337,10 +26521,10 @@
         <v>2</v>
       </c>
       <c r="C49" t="s">
-        <v>262</v>
+        <v>127</v>
       </c>
       <c r="D49" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E49" t="s">
         <v>16</v>
@@ -26354,140 +26538,140 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="B50" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C50" t="s">
-        <v>12</v>
+        <v>158</v>
       </c>
       <c r="D50" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E50" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F50" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G50" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="B51" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C51" t="s">
-        <v>92</v>
+        <v>176</v>
       </c>
       <c r="D51" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E51" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F51" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G51" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="B52" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C52" t="s">
-        <v>127</v>
+        <v>203</v>
       </c>
       <c r="D52" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E52" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F52" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G52" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="B53" t="n">
+        <v>2</v>
+      </c>
+      <c r="C53" t="s">
+        <v>237</v>
+      </c>
+      <c r="D53" t="n">
         <v>7</v>
       </c>
-      <c r="C53" t="s">
-        <v>158</v>
-      </c>
-      <c r="D53" t="n">
-        <v>4</v>
-      </c>
       <c r="E53" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F53" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G53" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="B54" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C54" t="s">
-        <v>176</v>
+        <v>262</v>
       </c>
       <c r="D54" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E54" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F54" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G54" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="B55" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C55" t="s">
-        <v>203</v>
+        <v>291</v>
       </c>
       <c r="D55" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E55" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F55" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G55" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="56">
@@ -26498,10 +26682,10 @@
         <v>7</v>
       </c>
       <c r="C56" t="s">
-        <v>237</v>
+        <v>12</v>
       </c>
       <c r="D56" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E56" t="s">
         <v>10</v>
@@ -26521,10 +26705,10 @@
         <v>7</v>
       </c>
       <c r="C57" t="s">
-        <v>262</v>
+        <v>92</v>
       </c>
       <c r="D57" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E57" t="s">
         <v>10</v>
@@ -26538,16 +26722,16 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="B58" t="n">
-        <v>8.2</v>
+        <v>7</v>
       </c>
       <c r="C58" t="s">
-        <v>12</v>
+        <v>127</v>
       </c>
       <c r="D58" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E58" t="s">
         <v>10</v>
@@ -26561,16 +26745,16 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="B59" t="n">
-        <v>8.2</v>
+        <v>7</v>
       </c>
       <c r="C59" t="s">
-        <v>92</v>
+        <v>158</v>
       </c>
       <c r="D59" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E59" t="s">
         <v>10</v>
@@ -26584,16 +26768,16 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="B60" t="n">
-        <v>8.2</v>
+        <v>7</v>
       </c>
       <c r="C60" t="s">
-        <v>127</v>
+        <v>176</v>
       </c>
       <c r="D60" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E60" t="s">
         <v>10</v>
@@ -26607,16 +26791,16 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="B61" t="n">
-        <v>8.2</v>
+        <v>7</v>
       </c>
       <c r="C61" t="s">
-        <v>158</v>
+        <v>203</v>
       </c>
       <c r="D61" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E61" t="s">
         <v>10</v>
@@ -26630,16 +26814,16 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="B62" t="n">
-        <v>8.2</v>
+        <v>7</v>
       </c>
       <c r="C62" t="s">
-        <v>176</v>
+        <v>237</v>
       </c>
       <c r="D62" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E62" t="s">
         <v>10</v>
@@ -26653,16 +26837,16 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="B63" t="n">
-        <v>8.2</v>
+        <v>7</v>
       </c>
       <c r="C63" t="s">
-        <v>203</v>
+        <v>262</v>
       </c>
       <c r="D63" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E63" t="s">
         <v>10</v>
@@ -26676,16 +26860,16 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="B64" t="n">
-        <v>8.2</v>
+        <v>7</v>
       </c>
       <c r="C64" t="s">
-        <v>237</v>
+        <v>291</v>
       </c>
       <c r="D64" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E64" t="s">
         <v>10</v>
@@ -26705,10 +26889,10 @@
         <v>8.2</v>
       </c>
       <c r="C65" t="s">
-        <v>262</v>
+        <v>12</v>
       </c>
       <c r="D65" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E65" t="s">
         <v>10</v>
@@ -26717,6 +26901,190 @@
         <v>11</v>
       </c>
       <c r="G65" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>467</v>
+      </c>
+      <c r="B66" t="n">
+        <v>8.2</v>
+      </c>
+      <c r="C66" t="s">
+        <v>92</v>
+      </c>
+      <c r="D66" t="n">
+        <v>2</v>
+      </c>
+      <c r="E66" t="s">
+        <v>10</v>
+      </c>
+      <c r="F66" t="s">
+        <v>11</v>
+      </c>
+      <c r="G66" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>467</v>
+      </c>
+      <c r="B67" t="n">
+        <v>8.2</v>
+      </c>
+      <c r="C67" t="s">
+        <v>127</v>
+      </c>
+      <c r="D67" t="n">
+        <v>3</v>
+      </c>
+      <c r="E67" t="s">
+        <v>10</v>
+      </c>
+      <c r="F67" t="s">
+        <v>11</v>
+      </c>
+      <c r="G67" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>467</v>
+      </c>
+      <c r="B68" t="n">
+        <v>8.2</v>
+      </c>
+      <c r="C68" t="s">
+        <v>158</v>
+      </c>
+      <c r="D68" t="n">
+        <v>4</v>
+      </c>
+      <c r="E68" t="s">
+        <v>10</v>
+      </c>
+      <c r="F68" t="s">
+        <v>11</v>
+      </c>
+      <c r="G68" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>467</v>
+      </c>
+      <c r="B69" t="n">
+        <v>8.2</v>
+      </c>
+      <c r="C69" t="s">
+        <v>176</v>
+      </c>
+      <c r="D69" t="n">
+        <v>5</v>
+      </c>
+      <c r="E69" t="s">
+        <v>10</v>
+      </c>
+      <c r="F69" t="s">
+        <v>11</v>
+      </c>
+      <c r="G69" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>467</v>
+      </c>
+      <c r="B70" t="n">
+        <v>8.2</v>
+      </c>
+      <c r="C70" t="s">
+        <v>203</v>
+      </c>
+      <c r="D70" t="n">
+        <v>6</v>
+      </c>
+      <c r="E70" t="s">
+        <v>10</v>
+      </c>
+      <c r="F70" t="s">
+        <v>11</v>
+      </c>
+      <c r="G70" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>467</v>
+      </c>
+      <c r="B71" t="n">
+        <v>8.2</v>
+      </c>
+      <c r="C71" t="s">
+        <v>237</v>
+      </c>
+      <c r="D71" t="n">
+        <v>7</v>
+      </c>
+      <c r="E71" t="s">
+        <v>10</v>
+      </c>
+      <c r="F71" t="s">
+        <v>11</v>
+      </c>
+      <c r="G71" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>467</v>
+      </c>
+      <c r="B72" t="n">
+        <v>8.2</v>
+      </c>
+      <c r="C72" t="s">
+        <v>262</v>
+      </c>
+      <c r="D72" t="n">
+        <v>8</v>
+      </c>
+      <c r="E72" t="s">
+        <v>10</v>
+      </c>
+      <c r="F72" t="s">
+        <v>11</v>
+      </c>
+      <c r="G72" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>467</v>
+      </c>
+      <c r="B73" t="n">
+        <v>8.2</v>
+      </c>
+      <c r="C73" t="s">
+        <v>291</v>
+      </c>
+      <c r="D73" t="n">
+        <v>9</v>
+      </c>
+      <c r="E73" t="s">
+        <v>10</v>
+      </c>
+      <c r="F73" t="s">
+        <v>11</v>
+      </c>
+      <c r="G73" t="s">
         <v>10</v>
       </c>
     </row>

--- a/Outcome/Publish/figure_data/fig2.xlsx
+++ b/Outcome/Publish/figure_data/fig2.xlsx
@@ -696,7 +696,7 @@
         <v>9</v>
       </c>
       <c r="E2" t="n">
-        <v>6.93</v>
+        <v>7.01</v>
       </c>
       <c r="F2" t="s">
         <v>10</v>
@@ -719,7 +719,7 @@
         <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>-2.75</v>
+        <v>-2.91</v>
       </c>
       <c r="F3" t="s">
         <v>12</v>
@@ -742,7 +742,7 @@
         <v>13</v>
       </c>
       <c r="E4" t="n">
-        <v>6.58</v>
+        <v>6.66</v>
       </c>
       <c r="F4" t="s">
         <v>12</v>
@@ -788,7 +788,7 @@
         <v>15</v>
       </c>
       <c r="E6" t="n">
-        <v>-12.81</v>
+        <v>-12.84</v>
       </c>
       <c r="F6" t="s">
         <v>12</v>
@@ -811,7 +811,7 @@
         <v>16</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.65</v>
+        <v>-3.66</v>
       </c>
       <c r="F7" t="s">
         <v>12</v>
@@ -834,7 +834,7 @@
         <v>17</v>
       </c>
       <c r="E8" t="n">
-        <v>4.48</v>
+        <v>4.53</v>
       </c>
       <c r="F8" t="s">
         <v>12</v>
@@ -880,7 +880,7 @@
         <v>11</v>
       </c>
       <c r="E10" t="n">
-        <v>0.41</v>
+        <v>0.44</v>
       </c>
       <c r="F10" t="s">
         <v>12</v>
@@ -926,7 +926,7 @@
         <v>14</v>
       </c>
       <c r="E12" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="F12" t="s">
         <v>12</v>
@@ -972,7 +972,7 @@
         <v>16</v>
       </c>
       <c r="E14" t="n">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="F14" t="s">
         <v>12</v>
@@ -995,7 +995,7 @@
         <v>17</v>
       </c>
       <c r="E15" t="n">
-        <v>-2.14</v>
+        <v>-2.16</v>
       </c>
       <c r="F15" t="s">
         <v>12</v>
@@ -1018,7 +1018,7 @@
         <v>9</v>
       </c>
       <c r="E16" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="F16" t="s">
         <v>12</v>
@@ -1041,7 +1041,7 @@
         <v>11</v>
       </c>
       <c r="E17" t="n">
-        <v>-4.76</v>
+        <v>-4.58</v>
       </c>
       <c r="F17" t="s">
         <v>12</v>
@@ -1064,7 +1064,7 @@
         <v>13</v>
       </c>
       <c r="E18" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="F18" t="s">
         <v>12</v>
@@ -1087,7 +1087,7 @@
         <v>14</v>
       </c>
       <c r="E19" t="n">
-        <v>3.47</v>
+        <v>3.41</v>
       </c>
       <c r="F19" t="s">
         <v>10</v>
@@ -1110,7 +1110,7 @@
         <v>15</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.73</v>
+        <v>-3.75</v>
       </c>
       <c r="F20" t="s">
         <v>12</v>
@@ -1133,7 +1133,7 @@
         <v>16</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.39</v>
+        <v>-0.41</v>
       </c>
       <c r="F21" t="s">
         <v>12</v>
@@ -1156,7 +1156,7 @@
         <v>17</v>
       </c>
       <c r="E22" t="n">
-        <v>0.59</v>
+        <v>0.56</v>
       </c>
       <c r="F22" t="s">
         <v>12</v>
@@ -1179,7 +1179,7 @@
         <v>9</v>
       </c>
       <c r="E23" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="F23" t="s">
         <v>12</v>
@@ -1202,7 +1202,7 @@
         <v>11</v>
       </c>
       <c r="E24" t="n">
-        <v>6.66</v>
+        <v>6.53</v>
       </c>
       <c r="F24" t="s">
         <v>10</v>
@@ -1225,7 +1225,7 @@
         <v>13</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.99</v>
+        <v>-4.97</v>
       </c>
       <c r="F25" t="s">
         <v>12</v>
@@ -1248,7 +1248,7 @@
         <v>14</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.15</v>
+        <v>-1.07</v>
       </c>
       <c r="F26" t="s">
         <v>12</v>
@@ -1271,7 +1271,7 @@
         <v>15</v>
       </c>
       <c r="E27" t="n">
-        <v>0.33</v>
+        <v>0.36</v>
       </c>
       <c r="F27" t="s">
         <v>12</v>
@@ -1294,7 +1294,7 @@
         <v>16</v>
       </c>
       <c r="E28" t="n">
-        <v>-2.61</v>
+        <v>-2.66</v>
       </c>
       <c r="F28" t="s">
         <v>12</v>
@@ -1317,7 +1317,7 @@
         <v>17</v>
       </c>
       <c r="E29" t="n">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="F29" t="s">
         <v>12</v>
@@ -1340,7 +1340,7 @@
         <v>9</v>
       </c>
       <c r="E30" t="n">
-        <v>0.99</v>
+        <v>0.94</v>
       </c>
       <c r="F30" t="s">
         <v>12</v>
@@ -1363,7 +1363,7 @@
         <v>11</v>
       </c>
       <c r="E31" t="n">
-        <v>2.65</v>
+        <v>2.84</v>
       </c>
       <c r="F31" t="s">
         <v>12</v>
@@ -1409,7 +1409,7 @@
         <v>14</v>
       </c>
       <c r="E33" t="n">
-        <v>3.62</v>
+        <v>3.73</v>
       </c>
       <c r="F33" t="s">
         <v>12</v>
@@ -1432,7 +1432,7 @@
         <v>15</v>
       </c>
       <c r="E34" t="n">
-        <v>-11.7</v>
+        <v>-11.8</v>
       </c>
       <c r="F34" t="s">
         <v>12</v>
@@ -1455,7 +1455,7 @@
         <v>16</v>
       </c>
       <c r="E35" t="n">
-        <v>2.93</v>
+        <v>2.86</v>
       </c>
       <c r="F35" t="s">
         <v>12</v>
@@ -1478,7 +1478,7 @@
         <v>17</v>
       </c>
       <c r="E36" t="n">
-        <v>-4.57</v>
+        <v>-4.65</v>
       </c>
       <c r="F36" t="s">
         <v>12</v>
@@ -1501,7 +1501,7 @@
         <v>9</v>
       </c>
       <c r="E37" t="n">
-        <v>0.71</v>
+        <v>0.77</v>
       </c>
       <c r="F37" t="s">
         <v>12</v>
@@ -1524,7 +1524,7 @@
         <v>11</v>
       </c>
       <c r="E38" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="F38" t="s">
         <v>12</v>
@@ -1547,7 +1547,7 @@
         <v>13</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.31</v>
+        <v>-1.15</v>
       </c>
       <c r="F39" t="s">
         <v>12</v>
@@ -1570,7 +1570,7 @@
         <v>14</v>
       </c>
       <c r="E40" t="n">
-        <v>2.54</v>
+        <v>2.34</v>
       </c>
       <c r="F40" t="s">
         <v>12</v>
@@ -1593,7 +1593,7 @@
         <v>15</v>
       </c>
       <c r="E41" t="n">
-        <v>-9.5</v>
+        <v>-9.38</v>
       </c>
       <c r="F41" t="s">
         <v>12</v>
@@ -1616,7 +1616,7 @@
         <v>16</v>
       </c>
       <c r="E42" t="n">
-        <v>7.6</v>
+        <v>7.27</v>
       </c>
       <c r="F42" t="s">
         <v>10</v>
@@ -1639,7 +1639,7 @@
         <v>17</v>
       </c>
       <c r="E43" t="n">
-        <v>-1.39</v>
+        <v>-1.24</v>
       </c>
       <c r="F43" t="s">
         <v>12</v>
@@ -1662,7 +1662,7 @@
         <v>9</v>
       </c>
       <c r="E44" t="n">
-        <v>1.82</v>
+        <v>1.69</v>
       </c>
       <c r="F44" t="s">
         <v>12</v>
@@ -1685,7 +1685,7 @@
         <v>11</v>
       </c>
       <c r="E45" t="n">
-        <v>-7.94</v>
+        <v>-7.73</v>
       </c>
       <c r="F45" t="s">
         <v>12</v>
@@ -1731,7 +1731,7 @@
         <v>14</v>
       </c>
       <c r="E47" t="n">
-        <v>3.16</v>
+        <v>3.19</v>
       </c>
       <c r="F47" t="s">
         <v>12</v>
@@ -1754,7 +1754,7 @@
         <v>15</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.52</v>
+        <v>-0.49</v>
       </c>
       <c r="F48" t="s">
         <v>12</v>
@@ -1777,7 +1777,7 @@
         <v>16</v>
       </c>
       <c r="E49" t="n">
-        <v>-7.31</v>
+        <v>-7.49</v>
       </c>
       <c r="F49" t="s">
         <v>12</v>
@@ -1800,7 +1800,7 @@
         <v>17</v>
       </c>
       <c r="E50" t="n">
-        <v>5.46</v>
+        <v>5.5</v>
       </c>
       <c r="F50" t="s">
         <v>10</v>
@@ -1823,7 +1823,7 @@
         <v>9</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.49</v>
+        <v>-0.59</v>
       </c>
       <c r="F51" t="s">
         <v>12</v>
@@ -1846,7 +1846,7 @@
         <v>11</v>
       </c>
       <c r="E52" t="n">
-        <v>-5.2</v>
+        <v>-4.72</v>
       </c>
       <c r="F52" t="s">
         <v>12</v>
@@ -1869,7 +1869,7 @@
         <v>13</v>
       </c>
       <c r="E53" t="n">
-        <v>-3.94</v>
+        <v>-4.41</v>
       </c>
       <c r="F53" t="s">
         <v>12</v>
@@ -1892,7 +1892,7 @@
         <v>14</v>
       </c>
       <c r="E54" t="n">
-        <v>7.32</v>
+        <v>7.24</v>
       </c>
       <c r="F54" t="s">
         <v>10</v>
@@ -1915,7 +1915,7 @@
         <v>15</v>
       </c>
       <c r="E55" t="n">
-        <v>4.42</v>
+        <v>4.52</v>
       </c>
       <c r="F55" t="s">
         <v>12</v>
@@ -1938,7 +1938,7 @@
         <v>16</v>
       </c>
       <c r="E56" t="n">
-        <v>-4.32</v>
+        <v>-4.29</v>
       </c>
       <c r="F56" t="s">
         <v>12</v>
@@ -1961,7 +1961,7 @@
         <v>17</v>
       </c>
       <c r="E57" t="n">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="F57" t="s">
         <v>12</v>
@@ -1984,7 +1984,7 @@
         <v>9</v>
       </c>
       <c r="E58" t="n">
-        <v>3.31</v>
+        <v>3.33</v>
       </c>
       <c r="F58" t="s">
         <v>12</v>
@@ -2007,7 +2007,7 @@
         <v>11</v>
       </c>
       <c r="E59" t="n">
-        <v>-1.55</v>
+        <v>-1.62</v>
       </c>
       <c r="F59" t="s">
         <v>12</v>
@@ -2030,7 +2030,7 @@
         <v>13</v>
       </c>
       <c r="E60" t="n">
-        <v>-4.97</v>
+        <v>-4.96</v>
       </c>
       <c r="F60" t="s">
         <v>12</v>
@@ -2076,7 +2076,7 @@
         <v>15</v>
       </c>
       <c r="E62" t="n">
-        <v>-3.5</v>
+        <v>-3.49</v>
       </c>
       <c r="F62" t="s">
         <v>12</v>
@@ -2099,7 +2099,7 @@
         <v>16</v>
       </c>
       <c r="E63" t="n">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="F63" t="s">
         <v>12</v>
@@ -2122,7 +2122,7 @@
         <v>17</v>
       </c>
       <c r="E64" t="n">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="F64" t="s">
         <v>12</v>
@@ -2145,7 +2145,7 @@
         <v>9</v>
       </c>
       <c r="E65" t="n">
-        <v>-1.06</v>
+        <v>-0.92</v>
       </c>
       <c r="F65" t="s">
         <v>12</v>
@@ -2168,7 +2168,7 @@
         <v>11</v>
       </c>
       <c r="E66" t="n">
-        <v>6.61</v>
+        <v>6.24</v>
       </c>
       <c r="F66" t="s">
         <v>10</v>
@@ -2191,7 +2191,7 @@
         <v>13</v>
       </c>
       <c r="E67" t="n">
-        <v>-6.48</v>
+        <v>-6.33</v>
       </c>
       <c r="F67" t="s">
         <v>12</v>
@@ -2214,7 +2214,7 @@
         <v>14</v>
       </c>
       <c r="E68" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="F68" t="s">
         <v>12</v>
@@ -2237,7 +2237,7 @@
         <v>15</v>
       </c>
       <c r="E69" t="n">
-        <v>0.36</v>
+        <v>0.31</v>
       </c>
       <c r="F69" t="s">
         <v>12</v>
@@ -2260,7 +2260,7 @@
         <v>16</v>
       </c>
       <c r="E70" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="F70" t="s">
         <v>12</v>
@@ -2283,7 +2283,7 @@
         <v>17</v>
       </c>
       <c r="E71" t="n">
-        <v>-1.62</v>
+        <v>-1.54</v>
       </c>
       <c r="F71" t="s">
         <v>12</v>
@@ -2306,7 +2306,7 @@
         <v>9</v>
       </c>
       <c r="E72" t="n">
-        <v>1.18</v>
+        <v>1.02</v>
       </c>
       <c r="F72" t="s">
         <v>12</v>
@@ -2329,7 +2329,7 @@
         <v>11</v>
       </c>
       <c r="E73" t="n">
-        <v>5.98</v>
+        <v>6.45</v>
       </c>
       <c r="F73" t="s">
         <v>10</v>
@@ -2352,7 +2352,7 @@
         <v>13</v>
       </c>
       <c r="E74" t="n">
-        <v>-2.04</v>
+        <v>-2.38</v>
       </c>
       <c r="F74" t="s">
         <v>12</v>
@@ -2375,7 +2375,7 @@
         <v>14</v>
       </c>
       <c r="E75" t="n">
-        <v>-0.14</v>
+        <v>-0.2</v>
       </c>
       <c r="F75" t="s">
         <v>12</v>
@@ -2398,7 +2398,7 @@
         <v>15</v>
       </c>
       <c r="E76" t="n">
-        <v>-11.23</v>
+        <v>-11.1</v>
       </c>
       <c r="F76" t="s">
         <v>12</v>
@@ -2421,7 +2421,7 @@
         <v>16</v>
       </c>
       <c r="E77" t="n">
-        <v>1.51</v>
+        <v>1.61</v>
       </c>
       <c r="F77" t="s">
         <v>12</v>
@@ -2444,7 +2444,7 @@
         <v>17</v>
       </c>
       <c r="E78" t="n">
-        <v>4.75</v>
+        <v>4.61</v>
       </c>
       <c r="F78" t="s">
         <v>12</v>
@@ -2467,7 +2467,7 @@
         <v>9</v>
       </c>
       <c r="E79" t="n">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="F79" t="s">
         <v>12</v>
@@ -2490,7 +2490,7 @@
         <v>11</v>
       </c>
       <c r="E80" t="n">
-        <v>-15.74</v>
+        <v>-14.29</v>
       </c>
       <c r="F80" t="s">
         <v>12</v>
@@ -2513,7 +2513,7 @@
         <v>13</v>
       </c>
       <c r="E81" t="n">
-        <v>-0.79</v>
+        <v>-1.21</v>
       </c>
       <c r="F81" t="s">
         <v>12</v>
@@ -2536,7 +2536,7 @@
         <v>14</v>
       </c>
       <c r="E82" t="n">
-        <v>6.66</v>
+        <v>6.59</v>
       </c>
       <c r="F82" t="s">
         <v>10</v>
@@ -2559,7 +2559,7 @@
         <v>15</v>
       </c>
       <c r="E83" t="n">
-        <v>-0.2</v>
+        <v>-0.62</v>
       </c>
       <c r="F83" t="s">
         <v>12</v>
@@ -2582,7 +2582,7 @@
         <v>16</v>
       </c>
       <c r="E84" t="n">
-        <v>4.97</v>
+        <v>4.87</v>
       </c>
       <c r="F84" t="s">
         <v>12</v>
@@ -2605,7 +2605,7 @@
         <v>17</v>
       </c>
       <c r="E85" t="n">
-        <v>1.6</v>
+        <v>1.32</v>
       </c>
       <c r="F85" t="s">
         <v>12</v>
@@ -2628,7 +2628,7 @@
         <v>9</v>
       </c>
       <c r="E86" t="n">
-        <v>1.36</v>
+        <v>1.61</v>
       </c>
       <c r="F86" t="s">
         <v>12</v>
@@ -2651,7 +2651,7 @@
         <v>11</v>
       </c>
       <c r="E87" t="n">
-        <v>-6.1</v>
+        <v>-7.04</v>
       </c>
       <c r="F87" t="s">
         <v>12</v>
@@ -2674,7 +2674,7 @@
         <v>13</v>
       </c>
       <c r="E88" t="n">
-        <v>6.91</v>
+        <v>6.98</v>
       </c>
       <c r="F88" t="s">
         <v>10</v>
@@ -2697,7 +2697,7 @@
         <v>14</v>
       </c>
       <c r="E89" t="n">
-        <v>5.65</v>
+        <v>5.57</v>
       </c>
       <c r="F89" t="s">
         <v>12</v>
@@ -2720,7 +2720,7 @@
         <v>15</v>
       </c>
       <c r="E90" t="n">
-        <v>-8.15</v>
+        <v>-7.86</v>
       </c>
       <c r="F90" t="s">
         <v>12</v>
@@ -2743,7 +2743,7 @@
         <v>16</v>
       </c>
       <c r="E91" t="n">
-        <v>-1.58</v>
+        <v>-1.39</v>
       </c>
       <c r="F91" t="s">
         <v>12</v>
@@ -2766,7 +2766,7 @@
         <v>17</v>
       </c>
       <c r="E92" t="n">
-        <v>1.91</v>
+        <v>2.14</v>
       </c>
       <c r="F92" t="s">
         <v>12</v>
@@ -2789,7 +2789,7 @@
         <v>9</v>
       </c>
       <c r="E93" t="n">
-        <v>2.99</v>
+        <v>2.77</v>
       </c>
       <c r="F93" t="s">
         <v>12</v>
@@ -2812,7 +2812,7 @@
         <v>11</v>
       </c>
       <c r="E94" t="n">
-        <v>-7.66</v>
+        <v>-5.31</v>
       </c>
       <c r="F94" t="s">
         <v>12</v>
@@ -2835,7 +2835,7 @@
         <v>13</v>
       </c>
       <c r="E95" t="n">
-        <v>3.24</v>
+        <v>3.02</v>
       </c>
       <c r="F95" t="s">
         <v>12</v>
@@ -2858,7 +2858,7 @@
         <v>14</v>
       </c>
       <c r="E96" t="n">
-        <v>4.86</v>
+        <v>4.39</v>
       </c>
       <c r="F96" t="s">
         <v>10</v>
@@ -2881,7 +2881,7 @@
         <v>15</v>
       </c>
       <c r="E97" t="n">
-        <v>-10.26</v>
+        <v>-11.07</v>
       </c>
       <c r="F97" t="s">
         <v>12</v>
@@ -2904,7 +2904,7 @@
         <v>16</v>
       </c>
       <c r="E98" t="n">
-        <v>3.98</v>
+        <v>3.63</v>
       </c>
       <c r="F98" t="s">
         <v>12</v>
@@ -2927,7 +2927,7 @@
         <v>17</v>
       </c>
       <c r="E99" t="n">
-        <v>2.85</v>
+        <v>2.57</v>
       </c>
       <c r="F99" t="s">
         <v>12</v>
@@ -2973,7 +2973,7 @@
         <v>11</v>
       </c>
       <c r="E101" t="n">
-        <v>-7.99</v>
+        <v>-8.42</v>
       </c>
       <c r="F101" t="s">
         <v>12</v>
@@ -2996,7 +2996,7 @@
         <v>13</v>
       </c>
       <c r="E102" t="n">
-        <v>-3.07</v>
+        <v>-2.71</v>
       </c>
       <c r="F102" t="s">
         <v>12</v>
@@ -3019,7 +3019,7 @@
         <v>14</v>
       </c>
       <c r="E103" t="n">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="F103" t="s">
         <v>12</v>
@@ -3042,7 +3042,7 @@
         <v>15</v>
       </c>
       <c r="E104" t="n">
-        <v>-3.15</v>
+        <v>-3.09</v>
       </c>
       <c r="F104" t="s">
         <v>12</v>
@@ -3065,7 +3065,7 @@
         <v>16</v>
       </c>
       <c r="E105" t="n">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="F105" t="s">
         <v>12</v>
@@ -3088,7 +3088,7 @@
         <v>17</v>
       </c>
       <c r="E106" t="n">
-        <v>3.58</v>
+        <v>3.48</v>
       </c>
       <c r="F106" t="s">
         <v>12</v>
@@ -3111,7 +3111,7 @@
         <v>9</v>
       </c>
       <c r="E107" t="n">
-        <v>-0.59</v>
+        <v>-0.48</v>
       </c>
       <c r="F107" t="s">
         <v>12</v>
@@ -3134,7 +3134,7 @@
         <v>11</v>
       </c>
       <c r="E108" t="n">
-        <v>-0.83</v>
+        <v>-0.93</v>
       </c>
       <c r="F108" t="s">
         <v>12</v>
@@ -3157,7 +3157,7 @@
         <v>13</v>
       </c>
       <c r="E109" t="n">
-        <v>5.98</v>
+        <v>6.26</v>
       </c>
       <c r="F109" t="s">
         <v>10</v>
@@ -3180,7 +3180,7 @@
         <v>14</v>
       </c>
       <c r="E110" t="n">
-        <v>3.02</v>
+        <v>3.13</v>
       </c>
       <c r="F110" t="s">
         <v>12</v>
@@ -3203,7 +3203,7 @@
         <v>15</v>
       </c>
       <c r="E111" t="n">
-        <v>-15.4</v>
+        <v>-15.89</v>
       </c>
       <c r="F111" t="s">
         <v>12</v>
@@ -3226,7 +3226,7 @@
         <v>16</v>
       </c>
       <c r="E112" t="n">
-        <v>5.24</v>
+        <v>5.28</v>
       </c>
       <c r="F112" t="s">
         <v>12</v>
@@ -3249,7 +3249,7 @@
         <v>17</v>
       </c>
       <c r="E113" t="n">
-        <v>2.59</v>
+        <v>2.64</v>
       </c>
       <c r="F113" t="s">
         <v>12</v>
@@ -3272,7 +3272,7 @@
         <v>9</v>
       </c>
       <c r="E114" t="n">
-        <v>-9.73</v>
+        <v>-9.56</v>
       </c>
       <c r="F114" t="s">
         <v>12</v>
@@ -3295,7 +3295,7 @@
         <v>11</v>
       </c>
       <c r="E115" t="n">
-        <v>-0.51</v>
+        <v>-1.04</v>
       </c>
       <c r="F115" t="s">
         <v>12</v>
@@ -3318,7 +3318,7 @@
         <v>13</v>
       </c>
       <c r="E116" t="n">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="F116" t="s">
         <v>12</v>
@@ -3341,7 +3341,7 @@
         <v>14</v>
       </c>
       <c r="E117" t="n">
-        <v>5.14</v>
+        <v>5.22</v>
       </c>
       <c r="F117" t="s">
         <v>10</v>
@@ -3364,7 +3364,7 @@
         <v>15</v>
       </c>
       <c r="E118" t="n">
-        <v>-0.95</v>
+        <v>-0.9</v>
       </c>
       <c r="F118" t="s">
         <v>12</v>
@@ -3387,7 +3387,7 @@
         <v>16</v>
       </c>
       <c r="E119" t="n">
-        <v>2.19</v>
+        <v>2.32</v>
       </c>
       <c r="F119" t="s">
         <v>12</v>
@@ -3410,7 +3410,7 @@
         <v>17</v>
       </c>
       <c r="E120" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="F120" t="s">
         <v>12</v>
@@ -3433,7 +3433,7 @@
         <v>9</v>
       </c>
       <c r="E121" t="n">
-        <v>4.45</v>
+        <v>4.48</v>
       </c>
       <c r="F121" t="s">
         <v>12</v>
@@ -3456,7 +3456,7 @@
         <v>11</v>
       </c>
       <c r="E122" t="n">
-        <v>-13.67</v>
+        <v>-13.31</v>
       </c>
       <c r="F122" t="s">
         <v>12</v>
@@ -3479,7 +3479,7 @@
         <v>13</v>
       </c>
       <c r="E123" t="n">
-        <v>3.85</v>
+        <v>3.53</v>
       </c>
       <c r="F123" t="s">
         <v>12</v>
@@ -3502,7 +3502,7 @@
         <v>14</v>
       </c>
       <c r="E124" t="n">
-        <v>3.01</v>
+        <v>2.97</v>
       </c>
       <c r="F124" t="s">
         <v>12</v>
@@ -3525,7 +3525,7 @@
         <v>15</v>
       </c>
       <c r="E125" t="n">
-        <v>-5.64</v>
+        <v>-5.79</v>
       </c>
       <c r="F125" t="s">
         <v>12</v>
@@ -3548,7 +3548,7 @@
         <v>16</v>
       </c>
       <c r="E126" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="F126" t="s">
         <v>12</v>
@@ -3571,7 +3571,7 @@
         <v>17</v>
       </c>
       <c r="E127" t="n">
-        <v>6.28</v>
+        <v>6.39</v>
       </c>
       <c r="F127" t="s">
         <v>10</v>
@@ -3594,7 +3594,7 @@
         <v>9</v>
       </c>
       <c r="E128" t="n">
-        <v>4.63</v>
+        <v>4.92</v>
       </c>
       <c r="F128" t="s">
         <v>12</v>
@@ -3617,7 +3617,7 @@
         <v>11</v>
       </c>
       <c r="E129" t="n">
-        <v>-4.97</v>
+        <v>-5.87</v>
       </c>
       <c r="F129" t="s">
         <v>12</v>
@@ -3640,7 +3640,7 @@
         <v>13</v>
       </c>
       <c r="E130" t="n">
-        <v>5.35</v>
+        <v>5.72</v>
       </c>
       <c r="F130" t="s">
         <v>10</v>
@@ -3663,7 +3663,7 @@
         <v>14</v>
       </c>
       <c r="E131" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="F131" t="s">
         <v>12</v>
@@ -3686,7 +3686,7 @@
         <v>15</v>
       </c>
       <c r="E132" t="n">
-        <v>-6.81</v>
+        <v>-6.87</v>
       </c>
       <c r="F132" t="s">
         <v>12</v>
@@ -3709,7 +3709,7 @@
         <v>16</v>
       </c>
       <c r="E133" t="n">
-        <v>-3.72</v>
+        <v>-3.64</v>
       </c>
       <c r="F133" t="s">
         <v>12</v>
@@ -3732,7 +3732,7 @@
         <v>17</v>
       </c>
       <c r="E134" t="n">
-        <v>3.99</v>
+        <v>4.15</v>
       </c>
       <c r="F134" t="s">
         <v>12</v>
@@ -3755,7 +3755,7 @@
         <v>9</v>
       </c>
       <c r="E135" t="n">
-        <v>3.93</v>
+        <v>3.98</v>
       </c>
       <c r="F135" t="s">
         <v>12</v>
@@ -3778,7 +3778,7 @@
         <v>11</v>
       </c>
       <c r="E136" t="n">
-        <v>-1.27</v>
+        <v>-1.98</v>
       </c>
       <c r="F136" t="s">
         <v>12</v>
@@ -3801,7 +3801,7 @@
         <v>13</v>
       </c>
       <c r="E137" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="F137" t="s">
         <v>12</v>
@@ -3847,7 +3847,7 @@
         <v>15</v>
       </c>
       <c r="E139" t="n">
-        <v>-15.17</v>
+        <v>-14.62</v>
       </c>
       <c r="F139" t="s">
         <v>12</v>
@@ -3870,7 +3870,7 @@
         <v>16</v>
       </c>
       <c r="E140" t="n">
-        <v>3.57</v>
+        <v>3.69</v>
       </c>
       <c r="F140" t="s">
         <v>12</v>
@@ -3893,7 +3893,7 @@
         <v>17</v>
       </c>
       <c r="E141" t="n">
-        <v>5.58</v>
+        <v>5.61</v>
       </c>
       <c r="F141" t="s">
         <v>10</v>
@@ -3910,13 +3910,13 @@
         <v>40</v>
       </c>
       <c r="C142" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D142" t="s">
         <v>9</v>
       </c>
       <c r="E142" t="n">
-        <v>-6.91</v>
+        <v>-6.87</v>
       </c>
       <c r="F142" t="s">
         <v>12</v>
@@ -3933,13 +3933,13 @@
         <v>40</v>
       </c>
       <c r="C143" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D143" t="s">
         <v>11</v>
       </c>
       <c r="E143" t="n">
-        <v>-6.06</v>
+        <v>-6.94</v>
       </c>
       <c r="F143" t="s">
         <v>12</v>
@@ -3956,16 +3956,16 @@
         <v>40</v>
       </c>
       <c r="C144" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D144" t="s">
         <v>13</v>
       </c>
       <c r="E144" t="n">
-        <v>4.66</v>
+        <v>4.93</v>
       </c>
       <c r="F144" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G144" t="n">
         <v>1</v>
@@ -3979,13 +3979,13 @@
         <v>40</v>
       </c>
       <c r="C145" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D145" t="s">
         <v>14</v>
       </c>
       <c r="E145" t="n">
-        <v>3.92</v>
+        <v>4.09</v>
       </c>
       <c r="F145" t="s">
         <v>12</v>
@@ -4002,13 +4002,13 @@
         <v>40</v>
       </c>
       <c r="C146" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D146" t="s">
         <v>15</v>
       </c>
       <c r="E146" t="n">
-        <v>-4.2</v>
+        <v>-4.11</v>
       </c>
       <c r="F146" t="s">
         <v>12</v>
@@ -4025,16 +4025,16 @@
         <v>40</v>
       </c>
       <c r="C147" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D147" t="s">
         <v>16</v>
       </c>
       <c r="E147" t="n">
-        <v>4.82</v>
+        <v>4.91</v>
       </c>
       <c r="F147" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G147" t="n">
         <v>1</v>
@@ -4048,13 +4048,13 @@
         <v>40</v>
       </c>
       <c r="C148" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D148" t="s">
         <v>17</v>
       </c>
       <c r="E148" t="n">
-        <v>3.76</v>
+        <v>3.99</v>
       </c>
       <c r="F148" t="s">
         <v>12</v>
@@ -4077,7 +4077,7 @@
         <v>9</v>
       </c>
       <c r="E149" t="n">
-        <v>3.34</v>
+        <v>3.55</v>
       </c>
       <c r="F149" t="s">
         <v>12</v>
@@ -4100,7 +4100,7 @@
         <v>11</v>
       </c>
       <c r="E150" t="n">
-        <v>-3.93</v>
+        <v>-5.31</v>
       </c>
       <c r="F150" t="s">
         <v>12</v>
@@ -4123,7 +4123,7 @@
         <v>13</v>
       </c>
       <c r="E151" t="n">
-        <v>-6.61</v>
+        <v>-6.22</v>
       </c>
       <c r="F151" t="s">
         <v>12</v>
@@ -4146,7 +4146,7 @@
         <v>14</v>
       </c>
       <c r="E152" t="n">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="F152" t="s">
         <v>12</v>
@@ -4169,7 +4169,7 @@
         <v>15</v>
       </c>
       <c r="E153" t="n">
-        <v>-3.98</v>
+        <v>-3.15</v>
       </c>
       <c r="F153" t="s">
         <v>12</v>
@@ -4192,7 +4192,7 @@
         <v>16</v>
       </c>
       <c r="E154" t="n">
-        <v>8.01</v>
+        <v>7.93</v>
       </c>
       <c r="F154" t="s">
         <v>10</v>
@@ -4215,7 +4215,7 @@
         <v>17</v>
       </c>
       <c r="E155" t="n">
-        <v>0.21</v>
+        <v>0.3</v>
       </c>
       <c r="F155" t="s">
         <v>12</v>
@@ -4238,7 +4238,7 @@
         <v>9</v>
       </c>
       <c r="E156" t="n">
-        <v>4.47</v>
+        <v>4.54</v>
       </c>
       <c r="F156" t="s">
         <v>12</v>
@@ -4261,7 +4261,7 @@
         <v>11</v>
       </c>
       <c r="E157" t="n">
-        <v>-6.63</v>
+        <v>-6.95</v>
       </c>
       <c r="F157" t="s">
         <v>12</v>
@@ -4284,7 +4284,7 @@
         <v>13</v>
       </c>
       <c r="E158" t="n">
-        <v>8.12</v>
+        <v>8.2</v>
       </c>
       <c r="F158" t="s">
         <v>10</v>
@@ -4307,7 +4307,7 @@
         <v>14</v>
       </c>
       <c r="E159" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="F159" t="s">
         <v>12</v>
@@ -4353,7 +4353,7 @@
         <v>16</v>
       </c>
       <c r="E161" t="n">
-        <v>-0.04</v>
+        <v>0.01</v>
       </c>
       <c r="F161" t="s">
         <v>12</v>
@@ -4376,7 +4376,7 @@
         <v>17</v>
       </c>
       <c r="E162" t="n">
-        <v>3.32</v>
+        <v>3.38</v>
       </c>
       <c r="F162" t="s">
         <v>12</v>
@@ -4399,7 +4399,7 @@
         <v>9</v>
       </c>
       <c r="E163" t="n">
-        <v>3.16</v>
+        <v>3.18</v>
       </c>
       <c r="F163" t="s">
         <v>12</v>
@@ -4422,7 +4422,7 @@
         <v>11</v>
       </c>
       <c r="E164" t="n">
-        <v>-2.4</v>
+        <v>-2.46</v>
       </c>
       <c r="F164" t="s">
         <v>12</v>
@@ -4445,7 +4445,7 @@
         <v>13</v>
       </c>
       <c r="E165" t="n">
-        <v>0.19</v>
+        <v>0.12</v>
       </c>
       <c r="F165" t="s">
         <v>12</v>
@@ -4468,7 +4468,7 @@
         <v>14</v>
       </c>
       <c r="E166" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="F166" t="s">
         <v>12</v>
@@ -4491,7 +4491,7 @@
         <v>15</v>
       </c>
       <c r="E167" t="n">
-        <v>-9.34</v>
+        <v>-9.24</v>
       </c>
       <c r="F167" t="s">
         <v>12</v>
@@ -4514,7 +4514,7 @@
         <v>16</v>
       </c>
       <c r="E168" t="n">
-        <v>-0.28</v>
+        <v>-0.21</v>
       </c>
       <c r="F168" t="s">
         <v>12</v>
@@ -4537,7 +4537,7 @@
         <v>17</v>
       </c>
       <c r="E169" t="n">
-        <v>6.37</v>
+        <v>6.29</v>
       </c>
       <c r="F169" t="s">
         <v>10</v>
@@ -19993,31 +19993,31 @@
         <v>43831</v>
       </c>
       <c r="B2" t="n">
-        <v>103.142008007965</v>
+        <v>100.666598923567</v>
       </c>
       <c r="C2" t="n">
-        <v>101.597513185194</v>
+        <v>100.289069523661</v>
       </c>
       <c r="D2" t="s">
         <v>27</v>
       </c>
       <c r="E2" t="n">
-        <v>71.9242464014197</v>
+        <v>69.4874426342305</v>
       </c>
       <c r="F2" t="n">
-        <v>54.0845662216064</v>
+        <v>55.2812886872976</v>
       </c>
       <c r="G2" t="n">
-        <v>135.830383176162</v>
+        <v>130.847239683661</v>
       </c>
       <c r="H2" t="n">
-        <v>155.629519536699</v>
+        <v>151.824300510126</v>
       </c>
       <c r="I2" t="n">
         <v>82</v>
       </c>
       <c r="J2" t="n">
-        <v>19.5975131851943</v>
+        <v>18.2890695236613</v>
       </c>
       <c r="K2" t="s">
         <v>55</v>
@@ -20028,31 +20028,31 @@
         <v>43862</v>
       </c>
       <c r="B3" t="n">
-        <v>94.0257394054479</v>
+        <v>96.7418762135356</v>
       </c>
       <c r="C3" t="n">
-        <v>91.8742709084118</v>
+        <v>94.5146919289456</v>
       </c>
       <c r="D3" t="s">
         <v>27</v>
       </c>
       <c r="E3" t="n">
-        <v>58.9273751908996</v>
+        <v>59.6370736296586</v>
       </c>
       <c r="F3" t="n">
-        <v>47.1678401081767</v>
+        <v>48.4416352539779</v>
       </c>
       <c r="G3" t="n">
-        <v>129.270657653326</v>
+        <v>135.406121737482</v>
       </c>
       <c r="H3" t="n">
-        <v>152.712052388469</v>
+        <v>166.409517440532</v>
       </c>
       <c r="I3" t="n">
         <v>59</v>
       </c>
       <c r="J3" t="n">
-        <v>32.8742709084118</v>
+        <v>35.5146919289456</v>
       </c>
       <c r="K3" t="s">
         <v>55</v>
@@ -20063,31 +20063,31 @@
         <v>43891</v>
       </c>
       <c r="B4" t="n">
-        <v>86.5425435946124</v>
+        <v>86.1095837617557</v>
       </c>
       <c r="C4" t="n">
-        <v>84.3153618483463</v>
+        <v>80.3086393427535</v>
       </c>
       <c r="D4" t="s">
         <v>27</v>
       </c>
       <c r="E4" t="n">
-        <v>50.0382941547041</v>
+        <v>51.0776646112217</v>
       </c>
       <c r="F4" t="n">
-        <v>42.5917722676132</v>
+        <v>37.6725800615182</v>
       </c>
       <c r="G4" t="n">
-        <v>128.853790807822</v>
+        <v>126.779741521836</v>
       </c>
       <c r="H4" t="n">
-        <v>153.258673429339</v>
+        <v>157.602681574389</v>
       </c>
       <c r="I4" t="n">
         <v>37</v>
       </c>
       <c r="J4" t="n">
-        <v>47.3153618483463</v>
+        <v>43.3086393427535</v>
       </c>
       <c r="K4" t="s">
         <v>55</v>
@@ -20098,31 +20098,31 @@
         <v>43922</v>
       </c>
       <c r="B5" t="n">
-        <v>66.2898993953181</v>
+        <v>66.8314536108904</v>
       </c>
       <c r="C5" t="n">
-        <v>61.9609772027194</v>
+        <v>63.1137280628198</v>
       </c>
       <c r="D5" t="s">
         <v>27</v>
       </c>
       <c r="E5" t="n">
-        <v>30.866781538629</v>
+        <v>34.6212165354159</v>
       </c>
       <c r="F5" t="n">
-        <v>16.4181346036355</v>
+        <v>23.1429648057822</v>
       </c>
       <c r="G5" t="n">
-        <v>107.076356436504</v>
+        <v>99.9337748924992</v>
       </c>
       <c r="H5" t="n">
-        <v>133.034409397257</v>
+        <v>145.170297496694</v>
       </c>
       <c r="I5" t="n">
         <v>33</v>
       </c>
       <c r="J5" t="n">
-        <v>28.9609772027194</v>
+        <v>30.1137280628198</v>
       </c>
       <c r="K5" t="s">
         <v>55</v>
@@ -20133,31 +20133,31 @@
         <v>43952</v>
       </c>
       <c r="B6" t="n">
-        <v>88.7569055514601</v>
+        <v>89.7473917890047</v>
       </c>
       <c r="C6" t="n">
-        <v>83.7124355416431</v>
+        <v>84.1441904867504</v>
       </c>
       <c r="D6" t="s">
         <v>27</v>
       </c>
       <c r="E6" t="n">
-        <v>44.3085015210776</v>
+        <v>47.5927067322497</v>
       </c>
       <c r="F6" t="n">
-        <v>28.1100397710468</v>
+        <v>33.4644983835991</v>
       </c>
       <c r="G6" t="n">
-        <v>138.354572229435</v>
+        <v>134.328798480269</v>
       </c>
       <c r="H6" t="n">
-        <v>166.738624565679</v>
+        <v>181.300971786804</v>
       </c>
       <c r="I6" t="n">
         <v>41</v>
       </c>
       <c r="J6" t="n">
-        <v>42.7124355416431</v>
+        <v>43.1441904867504</v>
       </c>
       <c r="K6" t="s">
         <v>55</v>
@@ -20168,31 +20168,31 @@
         <v>43983</v>
       </c>
       <c r="B7" t="n">
-        <v>100.891841189895</v>
+        <v>101.73894715845</v>
       </c>
       <c r="C7" t="n">
-        <v>99.0632945312107</v>
+        <v>93.7539860581792</v>
       </c>
       <c r="D7" t="s">
         <v>27</v>
       </c>
       <c r="E7" t="n">
-        <v>53.621561194501</v>
+        <v>55.8087445417226</v>
       </c>
       <c r="F7" t="n">
-        <v>31.202633797248</v>
+        <v>37.5636707437152</v>
       </c>
       <c r="G7" t="n">
-        <v>151.571214156687</v>
+        <v>161.634727621708</v>
       </c>
       <c r="H7" t="n">
-        <v>201.21182233766</v>
+        <v>194.074924373364</v>
       </c>
       <c r="I7" t="n">
         <v>51</v>
       </c>
       <c r="J7" t="n">
-        <v>48.0632945312107</v>
+        <v>42.7539860581792</v>
       </c>
       <c r="K7" t="s">
         <v>55</v>
@@ -20203,31 +20203,31 @@
         <v>44013</v>
       </c>
       <c r="B8" t="n">
-        <v>74.4819248672666</v>
+        <v>76.3862010568517</v>
       </c>
       <c r="C8" t="n">
-        <v>68.6595201335142</v>
+        <v>72.1815933722544</v>
       </c>
       <c r="D8" t="s">
         <v>27</v>
       </c>
       <c r="E8" t="n">
-        <v>28.1135612049713</v>
+        <v>35.0657954104114</v>
       </c>
       <c r="F8" t="n">
-        <v>14.5349739761833</v>
+        <v>19.2924089499052</v>
       </c>
       <c r="G8" t="n">
-        <v>123.198765157506</v>
+        <v>123.563214608897</v>
       </c>
       <c r="H8" t="n">
-        <v>156.567780607732</v>
+        <v>157.568730593736</v>
       </c>
       <c r="I8" t="n">
         <v>50</v>
       </c>
       <c r="J8" t="n">
-        <v>18.6595201335142</v>
+        <v>22.1815933722544</v>
       </c>
       <c r="K8" t="s">
         <v>55</v>
@@ -20238,31 +20238,31 @@
         <v>44044</v>
       </c>
       <c r="B9" t="n">
-        <v>62.4021516413587</v>
+        <v>63.3352134636723</v>
       </c>
       <c r="C9" t="n">
-        <v>56.6969860911199</v>
+        <v>55.2391736487043</v>
       </c>
       <c r="D9" t="s">
         <v>27</v>
       </c>
       <c r="E9" t="n">
-        <v>19.9955963486962</v>
+        <v>22.4951479988973</v>
       </c>
       <c r="F9" t="n">
-        <v>4.62935227972286</v>
+        <v>8.29649061533934</v>
       </c>
       <c r="G9" t="n">
-        <v>107.1918948958</v>
+        <v>111.744960818904</v>
       </c>
       <c r="H9" t="n">
-        <v>140.149319295739</v>
+        <v>152.06377450755</v>
       </c>
       <c r="I9" t="n">
         <v>66</v>
       </c>
       <c r="J9" t="n">
-        <v>-9.3030139088801</v>
+        <v>-10.7608263512957</v>
       </c>
       <c r="K9" t="s">
         <v>54</v>
@@ -20273,34 +20273,34 @@
         <v>44075</v>
       </c>
       <c r="B10" t="n">
-        <v>51.6009058516841</v>
+        <v>52.3800967217096</v>
       </c>
       <c r="C10" t="n">
-        <v>47.6077475431201</v>
+        <v>44.0583713890754</v>
       </c>
       <c r="D10" t="s">
         <v>27</v>
       </c>
       <c r="E10" t="n">
-        <v>10.316903232499</v>
+        <v>15.6183534863695</v>
       </c>
       <c r="F10" t="n">
-        <v>2.83806859850208</v>
+        <v>6.71116730335453</v>
       </c>
       <c r="G10" t="n">
-        <v>96.9371781173669</v>
+        <v>99.5907667189208</v>
       </c>
       <c r="H10" t="n">
-        <v>130.629828528473</v>
+        <v>134.208682162575</v>
       </c>
       <c r="I10" t="n">
         <v>45</v>
       </c>
       <c r="J10" t="n">
-        <v>2.60774754312012</v>
+        <v>-0.941628610924639</v>
       </c>
       <c r="K10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11">
@@ -20308,31 +20308,31 @@
         <v>44105</v>
       </c>
       <c r="B11" t="n">
-        <v>43.8016229921512</v>
+        <v>43.8558166004629</v>
       </c>
       <c r="C11" t="n">
-        <v>38.5193278795987</v>
+        <v>37.2572942581037</v>
       </c>
       <c r="D11" t="s">
         <v>27</v>
       </c>
       <c r="E11" t="n">
-        <v>6.72531727400113</v>
+        <v>9.9607490448456</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0921136833208134</v>
+        <v>1.33443318599007</v>
       </c>
       <c r="G11" t="n">
-        <v>85.3384065834918</v>
+        <v>82.8451360882952</v>
       </c>
       <c r="H11" t="n">
-        <v>127.848971376049</v>
+        <v>124.860123778509</v>
       </c>
       <c r="I11" t="n">
         <v>34</v>
       </c>
       <c r="J11" t="n">
-        <v>4.51932787959869</v>
+        <v>3.25729425810366</v>
       </c>
       <c r="K11" t="s">
         <v>55</v>
@@ -20343,31 +20343,31 @@
         <v>44136</v>
       </c>
       <c r="B12" t="n">
-        <v>45.1115650845244</v>
+        <v>45.8896959612355</v>
       </c>
       <c r="C12" t="n">
-        <v>39.1519271497735</v>
+        <v>39.5120483215681</v>
       </c>
       <c r="D12" t="s">
         <v>27</v>
       </c>
       <c r="E12" t="n">
-        <v>6.3592277737366</v>
+        <v>8.78616073441127</v>
       </c>
       <c r="F12" t="n">
-        <v>0.149860247650734</v>
+        <v>0.323708739676595</v>
       </c>
       <c r="G12" t="n">
-        <v>89.7542000340665</v>
+        <v>86.5256598813251</v>
       </c>
       <c r="H12" t="n">
-        <v>137.934178216876</v>
+        <v>128.451884462198</v>
       </c>
       <c r="I12" t="n">
         <v>28</v>
       </c>
       <c r="J12" t="n">
-        <v>11.1519271497735</v>
+        <v>11.5120483215681</v>
       </c>
       <c r="K12" t="s">
         <v>55</v>
@@ -20378,31 +20378,31 @@
         <v>44166</v>
       </c>
       <c r="B13" t="n">
-        <v>43.5466976623482</v>
+        <v>43.3771513742983</v>
       </c>
       <c r="C13" t="n">
-        <v>35.0243813158426</v>
+        <v>38.5077556169106</v>
       </c>
       <c r="D13" t="s">
         <v>27</v>
       </c>
       <c r="E13" t="n">
-        <v>4.57995071092579</v>
+        <v>7.56217754690498</v>
       </c>
       <c r="F13" t="n">
-        <v>0.230111163303546</v>
+        <v>0.0412446460005103</v>
       </c>
       <c r="G13" t="n">
-        <v>87.7768719356632</v>
+        <v>90.0694398366629</v>
       </c>
       <c r="H13" t="n">
-        <v>152.016293678052</v>
+        <v>114.49627077559</v>
       </c>
       <c r="I13" t="n">
         <v>34</v>
       </c>
       <c r="J13" t="n">
-        <v>1.02438131584255</v>
+        <v>4.50775561691064</v>
       </c>
       <c r="K13" t="s">
         <v>55</v>
@@ -20413,31 +20413,31 @@
         <v>44197</v>
       </c>
       <c r="B14" t="n">
-        <v>94.7370331536177</v>
+        <v>94.7213826296309</v>
       </c>
       <c r="C14" t="n">
-        <v>83.7941169174908</v>
+        <v>84.887589086856</v>
       </c>
       <c r="D14" t="s">
         <v>27</v>
       </c>
       <c r="E14" t="n">
-        <v>26.0961587762575</v>
+        <v>31.8935968947676</v>
       </c>
       <c r="F14" t="n">
-        <v>8.22630633507329</v>
+        <v>17.3364496181972</v>
       </c>
       <c r="G14" t="n">
-        <v>174.653572163901</v>
+        <v>162.243555256515</v>
       </c>
       <c r="H14" t="n">
-        <v>263.462031951206</v>
+        <v>221.077062108814</v>
       </c>
       <c r="I14" t="n">
         <v>34</v>
       </c>
       <c r="J14" t="n">
-        <v>49.7941169174908</v>
+        <v>50.887589086856</v>
       </c>
       <c r="K14" t="s">
         <v>55</v>
@@ -20448,31 +20448,31 @@
         <v>44228</v>
       </c>
       <c r="B15" t="n">
-        <v>87.0130509589936</v>
+        <v>87.3373074842749</v>
       </c>
       <c r="C15" t="n">
-        <v>77.7522941967705</v>
+        <v>79.4679370514014</v>
       </c>
       <c r="D15" t="s">
         <v>27</v>
       </c>
       <c r="E15" t="n">
-        <v>23.0676279192944</v>
+        <v>29.4578807666057</v>
       </c>
       <c r="F15" t="n">
-        <v>3.44990950472972</v>
+        <v>9.8805144635104</v>
       </c>
       <c r="G15" t="n">
-        <v>166.052183053413</v>
+        <v>148.612054405791</v>
       </c>
       <c r="H15" t="n">
-        <v>253.069082515684</v>
+        <v>230.218546215372</v>
       </c>
       <c r="I15" t="n">
         <v>35</v>
       </c>
       <c r="J15" t="n">
-        <v>42.7522941967705</v>
+        <v>44.4679370514014</v>
       </c>
       <c r="K15" t="s">
         <v>55</v>
@@ -20483,31 +20483,31 @@
         <v>44256</v>
       </c>
       <c r="B16" t="n">
-        <v>79.5080079865908</v>
+        <v>80.2328983518101</v>
       </c>
       <c r="C16" t="n">
-        <v>69.421624546242</v>
+        <v>70.6977998704573</v>
       </c>
       <c r="D16" t="s">
         <v>27</v>
       </c>
       <c r="E16" t="n">
-        <v>13.8764583458678</v>
+        <v>21.0571342747125</v>
       </c>
       <c r="F16" t="n">
-        <v>1.70482458399181</v>
+        <v>4.76368753352174</v>
       </c>
       <c r="G16" t="n">
-        <v>157.707683451857</v>
+        <v>158.12618678346</v>
       </c>
       <c r="H16" t="n">
-        <v>221.419474864786</v>
+        <v>208.861312801999</v>
       </c>
       <c r="I16" t="n">
         <v>50</v>
       </c>
       <c r="J16" t="n">
-        <v>19.421624546242</v>
+        <v>20.6977998704573</v>
       </c>
       <c r="K16" t="s">
         <v>55</v>
@@ -20518,31 +20518,31 @@
         <v>44287</v>
       </c>
       <c r="B17" t="n">
-        <v>61.8503770702369</v>
+        <v>62.8477444104797</v>
       </c>
       <c r="C17" t="n">
-        <v>52.1197945455125</v>
+        <v>52.3467627488013</v>
       </c>
       <c r="D17" t="s">
         <v>27</v>
       </c>
       <c r="E17" t="n">
-        <v>7.23565819796883</v>
+        <v>12.7041465426686</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0220410354686744</v>
+        <v>2.60020172373513</v>
       </c>
       <c r="G17" t="n">
-        <v>127.884275811524</v>
+        <v>129.542033593943</v>
       </c>
       <c r="H17" t="n">
-        <v>192.982727879725</v>
+        <v>168.20217189723</v>
       </c>
       <c r="I17" t="n">
         <v>34</v>
       </c>
       <c r="J17" t="n">
-        <v>18.1197945455125</v>
+        <v>18.3467627488013</v>
       </c>
       <c r="K17" t="s">
         <v>55</v>
@@ -20553,31 +20553,31 @@
         <v>44317</v>
       </c>
       <c r="B18" t="n">
-        <v>83.1358002434085</v>
+        <v>84.8980094714249</v>
       </c>
       <c r="C18" t="n">
-        <v>69.5624220497271</v>
+        <v>72.7308875540084</v>
       </c>
       <c r="D18" t="s">
         <v>27</v>
       </c>
       <c r="E18" t="n">
-        <v>13.7570082513373</v>
+        <v>17.1312561325979</v>
       </c>
       <c r="F18" t="n">
-        <v>1.75679509762897</v>
+        <v>5.97026602582112</v>
       </c>
       <c r="G18" t="n">
-        <v>171.151349787637</v>
+        <v>167.893225890588</v>
       </c>
       <c r="H18" t="n">
-        <v>265.180800996923</v>
+        <v>237.256645915028</v>
       </c>
       <c r="I18" t="n">
         <v>24</v>
       </c>
       <c r="J18" t="n">
-        <v>45.5624220497271</v>
+        <v>48.7308875540084</v>
       </c>
       <c r="K18" t="s">
         <v>55</v>
@@ -20588,31 +20588,31 @@
         <v>44348</v>
       </c>
       <c r="B19" t="n">
-        <v>88.8655347576364</v>
+        <v>93.2223475120822</v>
       </c>
       <c r="C19" t="n">
-        <v>75.5903295315997</v>
+        <v>79.8312120541057</v>
       </c>
       <c r="D19" t="s">
         <v>27</v>
       </c>
       <c r="E19" t="n">
-        <v>19.1402523989489</v>
+        <v>24.4946527915237</v>
       </c>
       <c r="F19" t="n">
-        <v>1.43123155192356</v>
+        <v>5.02703469335316</v>
       </c>
       <c r="G19" t="n">
-        <v>177.844850149436</v>
+        <v>183.526381521328</v>
       </c>
       <c r="H19" t="n">
-        <v>238.938262125025</v>
+        <v>246.048183582551</v>
       </c>
       <c r="I19" t="n">
         <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>49.5903295315997</v>
+        <v>53.8312120541057</v>
       </c>
       <c r="K19" t="s">
         <v>55</v>
@@ -20623,31 +20623,31 @@
         <v>44378</v>
       </c>
       <c r="B20" t="n">
-        <v>69.3173467232553</v>
+        <v>72.4502740408591</v>
       </c>
       <c r="C20" t="n">
-        <v>54.2824527016389</v>
+        <v>60.4147028683735</v>
       </c>
       <c r="D20" t="s">
         <v>27</v>
       </c>
       <c r="E20" t="n">
-        <v>9.81863851224515</v>
+        <v>12.1253149415341</v>
       </c>
       <c r="F20" t="n">
-        <v>0.01</v>
+        <v>0.415400516144465</v>
       </c>
       <c r="G20" t="n">
-        <v>158.117686548118</v>
+        <v>144.095908445958</v>
       </c>
       <c r="H20" t="n">
-        <v>208.211869285798</v>
+        <v>220.289503921844</v>
       </c>
       <c r="I20" t="n">
         <v>22</v>
       </c>
       <c r="J20" t="n">
-        <v>32.2824527016389</v>
+        <v>38.4147028683735</v>
       </c>
       <c r="K20" t="s">
         <v>55</v>
@@ -20658,31 +20658,31 @@
         <v>44409</v>
       </c>
       <c r="B21" t="n">
-        <v>59.2690661524549</v>
+        <v>61.4424104364035</v>
       </c>
       <c r="C21" t="n">
-        <v>42.9843233684724</v>
+        <v>44.8171625197965</v>
       </c>
       <c r="D21" t="s">
         <v>27</v>
       </c>
       <c r="E21" t="n">
-        <v>2.18936938760982</v>
+        <v>8.46245116959994</v>
       </c>
       <c r="F21" t="n">
-        <v>0.01</v>
+        <v>0.0164650063529436</v>
       </c>
       <c r="G21" t="n">
-        <v>134.184253712006</v>
+        <v>139.767522486499</v>
       </c>
       <c r="H21" t="n">
-        <v>220.124859668217</v>
+        <v>205.457424602727</v>
       </c>
       <c r="I21" t="n">
         <v>15</v>
       </c>
       <c r="J21" t="n">
-        <v>27.9843233684724</v>
+        <v>29.8171625197965</v>
       </c>
       <c r="K21" t="s">
         <v>55</v>
@@ -20693,31 +20693,31 @@
         <v>44440</v>
       </c>
       <c r="B22" t="n">
-        <v>49.5548252979612</v>
+        <v>51.5260958308507</v>
       </c>
       <c r="C22" t="n">
-        <v>34.4081731420249</v>
+        <v>38.4625187828818</v>
       </c>
       <c r="D22" t="s">
         <v>27</v>
       </c>
       <c r="E22" t="n">
-        <v>0.358154346425045</v>
+        <v>0.819626930785189</v>
       </c>
       <c r="F22" t="n">
         <v>0.01</v>
       </c>
       <c r="G22" t="n">
-        <v>114.572012359576</v>
+        <v>115.845503438084</v>
       </c>
       <c r="H22" t="n">
-        <v>188.668800962201</v>
+        <v>175.658684053434</v>
       </c>
       <c r="I22" t="n">
         <v>18</v>
       </c>
       <c r="J22" t="n">
-        <v>16.4081731420249</v>
+        <v>20.4625187828818</v>
       </c>
       <c r="K22" t="s">
         <v>55</v>
@@ -20728,31 +20728,31 @@
         <v>44470</v>
       </c>
       <c r="B23" t="n">
-        <v>41.509867906575</v>
+        <v>45.0821225192802</v>
       </c>
       <c r="C23" t="n">
-        <v>24.7650391633173</v>
+        <v>32.1665849171207</v>
       </c>
       <c r="D23" t="s">
         <v>27</v>
       </c>
       <c r="E23" t="n">
-        <v>0.01</v>
+        <v>0.290943743376903</v>
       </c>
       <c r="F23" t="n">
         <v>0.01</v>
       </c>
       <c r="G23" t="n">
-        <v>100.917119290509</v>
+        <v>114.129736923523</v>
       </c>
       <c r="H23" t="n">
-        <v>179.551895672748</v>
+        <v>164.085309906739</v>
       </c>
       <c r="I23" t="n">
         <v>17</v>
       </c>
       <c r="J23" t="n">
-        <v>7.76503916331729</v>
+        <v>15.1665849171207</v>
       </c>
       <c r="K23" t="s">
         <v>55</v>
@@ -20763,31 +20763,31 @@
         <v>44501</v>
       </c>
       <c r="B24" t="n">
-        <v>42.9994511412661</v>
+        <v>45.7407037512889</v>
       </c>
       <c r="C24" t="n">
-        <v>24.1139539216896</v>
+        <v>31.4396051222677</v>
       </c>
       <c r="D24" t="s">
         <v>27</v>
       </c>
       <c r="E24" t="n">
-        <v>0.01</v>
+        <v>0.499403302863925</v>
       </c>
       <c r="F24" t="n">
         <v>0.01</v>
       </c>
       <c r="G24" t="n">
-        <v>111.090110197049</v>
+        <v>107.730605360966</v>
       </c>
       <c r="H24" t="n">
-        <v>181.065354394703</v>
+        <v>201.822046893442</v>
       </c>
       <c r="I24" t="n">
         <v>14</v>
       </c>
       <c r="J24" t="n">
-        <v>10.1139539216896</v>
+        <v>17.4396051222677</v>
       </c>
       <c r="K24" t="s">
         <v>55</v>
@@ -20798,31 +20798,31 @@
         <v>44531</v>
       </c>
       <c r="B25" t="n">
-        <v>42.5571970869608</v>
+        <v>41.8130136582201</v>
       </c>
       <c r="C25" t="n">
-        <v>23.8113805969587</v>
+        <v>28.4595506549474</v>
       </c>
       <c r="D25" t="s">
         <v>27</v>
       </c>
       <c r="E25" t="n">
-        <v>0.01</v>
+        <v>0.488742918949694</v>
       </c>
       <c r="F25" t="n">
         <v>0.01</v>
       </c>
       <c r="G25" t="n">
-        <v>103.126758820758</v>
+        <v>96.2077096166592</v>
       </c>
       <c r="H25" t="n">
-        <v>209.561261070927</v>
+        <v>197.016188908362</v>
       </c>
       <c r="I25" t="n">
         <v>44</v>
       </c>
       <c r="J25" t="n">
-        <v>-20.1886194030413</v>
+        <v>-15.5404493450526</v>
       </c>
       <c r="K25" t="s">
         <v>54</v>
@@ -20833,31 +20833,31 @@
         <v>44562</v>
       </c>
       <c r="B26" t="n">
-        <v>84.6889188243886</v>
+        <v>87.7811243992726</v>
       </c>
       <c r="C26" t="n">
-        <v>64.4278126841453</v>
+        <v>70.0625473633586</v>
       </c>
       <c r="D26" t="s">
         <v>27</v>
       </c>
       <c r="E26" t="n">
-        <v>5.7088288053982</v>
+        <v>13.1914396725432</v>
       </c>
       <c r="F26" t="n">
-        <v>0.01</v>
+        <v>0.364108191083623</v>
       </c>
       <c r="G26" t="n">
-        <v>195.785830205788</v>
+        <v>177.32594931263</v>
       </c>
       <c r="H26" t="n">
-        <v>283.725801547071</v>
+        <v>280.974727813173</v>
       </c>
       <c r="I26" t="n">
         <v>43</v>
       </c>
       <c r="J26" t="n">
-        <v>21.4278126841453</v>
+        <v>27.0625473633586</v>
       </c>
       <c r="K26" t="s">
         <v>55</v>
@@ -20868,31 +20868,31 @@
         <v>44593</v>
       </c>
       <c r="B27" t="n">
-        <v>78.1756209211953</v>
+        <v>82.2804842216928</v>
       </c>
       <c r="C27" t="n">
-        <v>55.2086479941161</v>
+        <v>63.6668702876464</v>
       </c>
       <c r="D27" t="s">
         <v>27</v>
       </c>
       <c r="E27" t="n">
-        <v>2.75836018681891</v>
+        <v>10.8047902925213</v>
       </c>
       <c r="F27" t="n">
         <v>0.01</v>
       </c>
       <c r="G27" t="n">
-        <v>186.901950945627</v>
+        <v>170.566937608227</v>
       </c>
       <c r="H27" t="n">
-        <v>273.123951520598</v>
+        <v>276.405942719504</v>
       </c>
       <c r="I27" t="n">
         <v>33</v>
       </c>
       <c r="J27" t="n">
-        <v>22.2086479941161</v>
+        <v>30.6668702876464</v>
       </c>
       <c r="K27" t="s">
         <v>55</v>
@@ -20903,31 +20903,31 @@
         <v>44621</v>
       </c>
       <c r="B28" t="n">
-        <v>73.6507958959591</v>
+        <v>75.2669296337228</v>
       </c>
       <c r="C28" t="n">
-        <v>52.5837557617939</v>
+        <v>53.8236667331547</v>
       </c>
       <c r="D28" t="s">
         <v>27</v>
       </c>
       <c r="E28" t="n">
-        <v>0.98041556721328</v>
+        <v>7.86531630237946</v>
       </c>
       <c r="F28" t="n">
         <v>0.01</v>
       </c>
       <c r="G28" t="n">
-        <v>192.816336621353</v>
+        <v>172.272007373865</v>
       </c>
       <c r="H28" t="n">
-        <v>264.445947723355</v>
+        <v>291.291887831</v>
       </c>
       <c r="I28" t="n">
         <v>22</v>
       </c>
       <c r="J28" t="n">
-        <v>30.5837557617939</v>
+        <v>31.8236667331547</v>
       </c>
       <c r="K28" t="s">
         <v>55</v>
@@ -20938,31 +20938,31 @@
         <v>44652</v>
       </c>
       <c r="B29" t="n">
-        <v>57.4123237583535</v>
+        <v>61.2745048721686</v>
       </c>
       <c r="C29" t="n">
-        <v>36.1020053441902</v>
+        <v>37.0189056960663</v>
       </c>
       <c r="D29" t="s">
         <v>27</v>
       </c>
       <c r="E29" t="n">
-        <v>0.01</v>
+        <v>1.08400593878128</v>
       </c>
       <c r="F29" t="n">
         <v>0.01</v>
       </c>
       <c r="G29" t="n">
-        <v>149.952329994698</v>
+        <v>155.034554472374</v>
       </c>
       <c r="H29" t="n">
-        <v>215.031778809861</v>
+        <v>262.780507206639</v>
       </c>
       <c r="I29" t="n">
         <v>23</v>
       </c>
       <c r="J29" t="n">
-        <v>13.1020053441902</v>
+        <v>14.0189056960663</v>
       </c>
       <c r="K29" t="s">
         <v>55</v>
@@ -20973,31 +20973,31 @@
         <v>44682</v>
       </c>
       <c r="B30" t="n">
-        <v>76.669221651119</v>
+        <v>80.7718489614587</v>
       </c>
       <c r="C30" t="n">
-        <v>55.2916964912359</v>
+        <v>57.3388657140311</v>
       </c>
       <c r="D30" t="s">
         <v>27</v>
       </c>
       <c r="E30" t="n">
-        <v>2.54075410008753</v>
+        <v>6.89663887561188</v>
       </c>
       <c r="F30" t="n">
         <v>0.01</v>
       </c>
       <c r="G30" t="n">
-        <v>183.704483706119</v>
+        <v>188.232022949671</v>
       </c>
       <c r="H30" t="n">
-        <v>281.093383722566</v>
+        <v>270.567614153684</v>
       </c>
       <c r="I30" t="n">
         <v>28</v>
       </c>
       <c r="J30" t="n">
-        <v>27.2916964912359</v>
+        <v>29.3388657140311</v>
       </c>
       <c r="K30" t="s">
         <v>55</v>
@@ -21008,31 +21008,31 @@
         <v>44713</v>
       </c>
       <c r="B31" t="n">
-        <v>81.7865411921188</v>
+        <v>88.8990243696895</v>
       </c>
       <c r="C31" t="n">
-        <v>59.3144731747386</v>
+        <v>67.6669895899955</v>
       </c>
       <c r="D31" t="s">
         <v>27</v>
       </c>
       <c r="E31" t="n">
-        <v>3.46780058248574</v>
+        <v>8.42033674078291</v>
       </c>
       <c r="F31" t="n">
         <v>0.01</v>
       </c>
       <c r="G31" t="n">
-        <v>194.093943018879</v>
+        <v>202.668127573672</v>
       </c>
       <c r="H31" t="n">
-        <v>261.977775927729</v>
+        <v>293.611754859096</v>
       </c>
       <c r="I31" t="n">
         <v>36</v>
       </c>
       <c r="J31" t="n">
-        <v>23.3144731747386</v>
+        <v>31.6669895899955</v>
       </c>
       <c r="K31" t="s">
         <v>55</v>
@@ -21043,31 +21043,31 @@
         <v>44743</v>
       </c>
       <c r="B32" t="n">
-        <v>64.3579538422962</v>
+        <v>70.5161549974918</v>
       </c>
       <c r="C32" t="n">
-        <v>40.5559046323125</v>
+        <v>47.3590958952213</v>
       </c>
       <c r="D32" t="s">
         <v>27</v>
       </c>
       <c r="E32" t="n">
-        <v>0.512011607052573</v>
+        <v>2.45556400376434</v>
       </c>
       <c r="F32" t="n">
         <v>0.01</v>
       </c>
       <c r="G32" t="n">
-        <v>157.910875950563</v>
+        <v>171.361820928439</v>
       </c>
       <c r="H32" t="n">
-        <v>255.94437423685</v>
+        <v>247.193202764166</v>
       </c>
       <c r="I32" t="n">
         <v>30</v>
       </c>
       <c r="J32" t="n">
-        <v>10.5559046323125</v>
+        <v>17.3590958952213</v>
       </c>
       <c r="K32" t="s">
         <v>55</v>
@@ -21078,31 +21078,31 @@
         <v>44774</v>
       </c>
       <c r="B33" t="n">
-        <v>53.3823299374726</v>
+        <v>60.084656175415</v>
       </c>
       <c r="C33" t="n">
-        <v>30.5747533534102</v>
+        <v>37.4384227526743</v>
       </c>
       <c r="D33" t="s">
         <v>27</v>
       </c>
       <c r="E33" t="n">
-        <v>0.01</v>
+        <v>0.249003029306044</v>
       </c>
       <c r="F33" t="n">
         <v>0.01</v>
       </c>
       <c r="G33" t="n">
-        <v>146.83523051435</v>
+        <v>156.769989311916</v>
       </c>
       <c r="H33" t="n">
-        <v>226.7885490164</v>
+        <v>232.13043661235</v>
       </c>
       <c r="I33" t="n">
         <v>47</v>
       </c>
       <c r="J33" t="n">
-        <v>-16.4252466465898</v>
+        <v>-9.5615772473257</v>
       </c>
       <c r="K33" t="s">
         <v>54</v>
@@ -21113,10 +21113,10 @@
         <v>44805</v>
       </c>
       <c r="B34" t="n">
-        <v>46.9030591926332</v>
+        <v>50.8069390950979</v>
       </c>
       <c r="C34" t="n">
-        <v>20.3682942417419</v>
+        <v>26.7363792476766</v>
       </c>
       <c r="D34" t="s">
         <v>27</v>
@@ -21128,16 +21128,16 @@
         <v>0.01</v>
       </c>
       <c r="G34" t="n">
-        <v>123.223686491321</v>
+        <v>136.096571937879</v>
       </c>
       <c r="H34" t="n">
-        <v>221.277811051911</v>
+        <v>221.985774339562</v>
       </c>
       <c r="I34" t="n">
         <v>42</v>
       </c>
       <c r="J34" t="n">
-        <v>-21.6317057582581</v>
+        <v>-15.2636207523234</v>
       </c>
       <c r="K34" t="s">
         <v>54</v>
@@ -21148,10 +21148,10 @@
         <v>44835</v>
       </c>
       <c r="B35" t="n">
-        <v>38.5390430745255</v>
+        <v>45.0584094692563</v>
       </c>
       <c r="C35" t="n">
-        <v>14.9614245413198</v>
+        <v>22.3543302818159</v>
       </c>
       <c r="D35" t="s">
         <v>27</v>
@@ -21163,16 +21163,16 @@
         <v>0.01</v>
       </c>
       <c r="G35" t="n">
-        <v>110.318245562532</v>
+        <v>132.964814844239</v>
       </c>
       <c r="H35" t="n">
-        <v>168.317718832482</v>
+        <v>195.974116399089</v>
       </c>
       <c r="I35" t="n">
         <v>34</v>
       </c>
       <c r="J35" t="n">
-        <v>-19.0385754586802</v>
+        <v>-11.6456697181841</v>
       </c>
       <c r="K35" t="s">
         <v>54</v>
@@ -21183,10 +21183,10 @@
         <v>44866</v>
       </c>
       <c r="B36" t="n">
-        <v>39.1202247442964</v>
+        <v>45.8317119817955</v>
       </c>
       <c r="C36" t="n">
-        <v>13.7229651841595</v>
+        <v>20.434201053898</v>
       </c>
       <c r="D36" t="s">
         <v>27</v>
@@ -21198,19 +21198,19 @@
         <v>0.01</v>
       </c>
       <c r="G36" t="n">
-        <v>114.528603312547</v>
+        <v>133.032674138258</v>
       </c>
       <c r="H36" t="n">
-        <v>194.401391417762</v>
+        <v>213.097832523002</v>
       </c>
       <c r="I36" t="n">
         <v>18</v>
       </c>
       <c r="J36" t="n">
-        <v>-4.27703481584048</v>
+        <v>2.43420105389804</v>
       </c>
       <c r="K36" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="37">
@@ -21218,10 +21218,10 @@
         <v>44896</v>
       </c>
       <c r="B37" t="n">
-        <v>38.2579711737945</v>
+        <v>45.193960015961</v>
       </c>
       <c r="C37" t="n">
-        <v>11.4625244578861</v>
+        <v>20.3429166742347</v>
       </c>
       <c r="D37" t="s">
         <v>27</v>
@@ -21233,16 +21233,16 @@
         <v>0.01</v>
       </c>
       <c r="G37" t="n">
-        <v>106.387674456638</v>
+        <v>128.809316395474</v>
       </c>
       <c r="H37" t="n">
-        <v>200.979077916595</v>
+        <v>198.380772294478</v>
       </c>
       <c r="I37" t="n">
         <v>21</v>
       </c>
       <c r="J37" t="n">
-        <v>-9.53747554211395</v>
+        <v>-0.657083325765253</v>
       </c>
       <c r="K37" t="s">
         <v>54</v>
@@ -21253,31 +21253,31 @@
         <v>44927</v>
       </c>
       <c r="B38" t="n">
-        <v>74.4945243103639</v>
+        <v>88.0329963280195</v>
       </c>
       <c r="C38" t="n">
-        <v>40.1854597986874</v>
+        <v>55.3646340372317</v>
       </c>
       <c r="D38" t="s">
         <v>27</v>
       </c>
       <c r="E38" t="n">
-        <v>0.418743638287346</v>
+        <v>0.321744230277498</v>
       </c>
       <c r="F38" t="n">
         <v>0.01</v>
       </c>
       <c r="G38" t="n">
-        <v>198.649106670676</v>
+        <v>209.001328904019</v>
       </c>
       <c r="H38" t="n">
-        <v>294.944771824597</v>
+        <v>311.870393015987</v>
       </c>
       <c r="I38" t="n">
         <v>30</v>
       </c>
       <c r="J38" t="n">
-        <v>10.1854597986874</v>
+        <v>25.3646340372317</v>
       </c>
       <c r="K38" t="s">
         <v>55</v>
@@ -21288,31 +21288,31 @@
         <v>44958</v>
       </c>
       <c r="B39" t="n">
-        <v>67.788243109008</v>
+        <v>84.6369618076756</v>
       </c>
       <c r="C39" t="n">
-        <v>38.9907980058372</v>
+        <v>51.8559019650029</v>
       </c>
       <c r="D39" t="s">
         <v>27</v>
       </c>
       <c r="E39" t="n">
-        <v>0.01</v>
+        <v>0.03272648535418</v>
       </c>
       <c r="F39" t="n">
         <v>0.01</v>
       </c>
       <c r="G39" t="n">
-        <v>178.867881223583</v>
+        <v>208.888947539077</v>
       </c>
       <c r="H39" t="n">
-        <v>285.006086196899</v>
+        <v>325.359854541751</v>
       </c>
       <c r="I39" t="n">
         <v>14</v>
       </c>
       <c r="J39" t="n">
-        <v>24.9907980058372</v>
+        <v>37.8559019650029</v>
       </c>
       <c r="K39" t="s">
         <v>55</v>
@@ -21323,10 +21323,10 @@
         <v>44986</v>
       </c>
       <c r="B40" t="n">
-        <v>63.2493669754588</v>
+        <v>77.6475784401502</v>
       </c>
       <c r="C40" t="n">
-        <v>27.4022355646622</v>
+        <v>43.7060874155232</v>
       </c>
       <c r="D40" t="s">
         <v>27</v>
@@ -21338,16 +21338,16 @@
         <v>0.01</v>
       </c>
       <c r="G40" t="n">
-        <v>173.671929935888</v>
+        <v>189.913219982523</v>
       </c>
       <c r="H40" t="n">
-        <v>274.999330645438</v>
+        <v>300.58238365484</v>
       </c>
       <c r="I40" t="n">
         <v>20</v>
       </c>
       <c r="J40" t="n">
-        <v>7.40223556466217</v>
+        <v>23.7060874155232</v>
       </c>
       <c r="K40" t="s">
         <v>55</v>
@@ -21358,10 +21358,10 @@
         <v>45017</v>
       </c>
       <c r="B41" t="n">
-        <v>51.7031895985752</v>
+        <v>64.0110462147869</v>
       </c>
       <c r="C41" t="n">
-        <v>21.026365975</v>
+        <v>28.7149235139815</v>
       </c>
       <c r="D41" t="s">
         <v>27</v>
@@ -21373,16 +21373,16 @@
         <v>0.01</v>
       </c>
       <c r="G41" t="n">
-        <v>143.267838869884</v>
+        <v>167.180941269807</v>
       </c>
       <c r="H41" t="n">
-        <v>250.527870317272</v>
+        <v>295.258981225053</v>
       </c>
       <c r="I41" t="n">
         <v>17</v>
       </c>
       <c r="J41" t="n">
-        <v>4.02636597499999</v>
+        <v>11.7149235139815</v>
       </c>
       <c r="K41" t="s">
         <v>55</v>
@@ -21393,10 +21393,10 @@
         <v>45047</v>
       </c>
       <c r="B42" t="n">
-        <v>67.1558955882816</v>
+        <v>82.0711229786771</v>
       </c>
       <c r="C42" t="n">
-        <v>35.7744956039816</v>
+        <v>47.336586691389</v>
       </c>
       <c r="D42" t="s">
         <v>27</v>
@@ -21408,16 +21408,16 @@
         <v>0.01</v>
       </c>
       <c r="G42" t="n">
-        <v>183.506824052962</v>
+        <v>208.733769586835</v>
       </c>
       <c r="H42" t="n">
-        <v>278.928158168128</v>
+        <v>352.253552732659</v>
       </c>
       <c r="I42" t="n">
         <v>28</v>
       </c>
       <c r="J42" t="n">
-        <v>7.7744956039816</v>
+        <v>19.336586691389</v>
       </c>
       <c r="K42" t="s">
         <v>55</v>
@@ -21428,10 +21428,10 @@
         <v>45078</v>
       </c>
       <c r="B43" t="n">
-        <v>75.6563967075844</v>
+        <v>92.5003723935378</v>
       </c>
       <c r="C43" t="n">
-        <v>40.2472228335174</v>
+        <v>54.1491909398007</v>
       </c>
       <c r="D43" t="s">
         <v>27</v>
@@ -21443,16 +21443,16 @@
         <v>0.01</v>
       </c>
       <c r="G43" t="n">
-        <v>203.711751316506</v>
+        <v>226.913652377636</v>
       </c>
       <c r="H43" t="n">
-        <v>328.822319509523</v>
+        <v>366.471365390053</v>
       </c>
       <c r="I43" t="n">
         <v>26</v>
       </c>
       <c r="J43" t="n">
-        <v>14.2472228335174</v>
+        <v>28.1491909398007</v>
       </c>
       <c r="K43" t="s">
         <v>55</v>
@@ -21463,10 +21463,10 @@
         <v>45108</v>
       </c>
       <c r="B44" t="n">
-        <v>59.4036649837495</v>
+        <v>73.6304926610687</v>
       </c>
       <c r="C44" t="n">
-        <v>25.7186882032734</v>
+        <v>39.6159448269631</v>
       </c>
       <c r="D44" t="s">
         <v>27</v>
@@ -21478,16 +21478,16 @@
         <v>0.01</v>
       </c>
       <c r="G44" t="n">
-        <v>163.744970514928</v>
+        <v>191.28095587572</v>
       </c>
       <c r="H44" t="n">
-        <v>280.796457061763</v>
+        <v>311.297717449996</v>
       </c>
       <c r="I44" t="n">
         <v>21</v>
       </c>
       <c r="J44" t="n">
-        <v>4.71868820327338</v>
+        <v>18.6159448269631</v>
       </c>
       <c r="K44" t="s">
         <v>55</v>
@@ -21498,10 +21498,10 @@
         <v>45139</v>
       </c>
       <c r="B45" t="n">
-        <v>52.6724642425315</v>
+        <v>65.443307080516</v>
       </c>
       <c r="C45" t="n">
-        <v>17.3114279785071</v>
+        <v>29.9076163123029</v>
       </c>
       <c r="D45" t="s">
         <v>27</v>
@@ -21513,19 +21513,19 @@
         <v>0.01</v>
       </c>
       <c r="G45" t="n">
-        <v>162.180294214438</v>
+        <v>184.621329731235</v>
       </c>
       <c r="H45" t="n">
-        <v>258.620997621002</v>
+        <v>308.150676186692</v>
       </c>
       <c r="I45" t="n">
         <v>18</v>
       </c>
       <c r="J45" t="n">
-        <v>-0.688572021492853</v>
+        <v>11.9076163123029</v>
       </c>
       <c r="K45" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="46">
@@ -21533,10 +21533,10 @@
         <v>45170</v>
       </c>
       <c r="B46" t="n">
-        <v>45.2576245534111</v>
+        <v>55.3082339417801</v>
       </c>
       <c r="C46" t="n">
-        <v>12.9676450280826</v>
+        <v>21.5783397087253</v>
       </c>
       <c r="D46" t="s">
         <v>27</v>
@@ -21548,19 +21548,19 @@
         <v>0.01</v>
       </c>
       <c r="G46" t="n">
-        <v>128.619084164863</v>
+        <v>146.007231187422</v>
       </c>
       <c r="H46" t="n">
-        <v>242.605966094603</v>
+        <v>320.786629111939</v>
       </c>
       <c r="I46" t="n">
         <v>20</v>
       </c>
       <c r="J46" t="n">
-        <v>-7.0323549719174</v>
+        <v>1.57833970872531</v>
       </c>
       <c r="K46" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="47">
@@ -21568,10 +21568,10 @@
         <v>45200</v>
       </c>
       <c r="B47" t="n">
-        <v>40.3952300455098</v>
+        <v>50.1935356441596</v>
       </c>
       <c r="C47" t="n">
-        <v>6.81516348065544</v>
+        <v>15.4097423518313</v>
       </c>
       <c r="D47" t="s">
         <v>27</v>
@@ -21583,19 +21583,19 @@
         <v>0.01</v>
       </c>
       <c r="G47" t="n">
-        <v>120.808598084268</v>
+        <v>148.271097669097</v>
       </c>
       <c r="H47" t="n">
-        <v>247.032783380299</v>
+        <v>280.015830905594</v>
       </c>
       <c r="I47" t="n">
         <v>14</v>
       </c>
       <c r="J47" t="n">
-        <v>-7.18483651934456</v>
+        <v>1.40974235183127</v>
       </c>
       <c r="K47" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="48">
@@ -21603,10 +21603,10 @@
         <v>45231</v>
       </c>
       <c r="B48" t="n">
-        <v>40.1467990412416</v>
+        <v>47.9235630336752</v>
       </c>
       <c r="C48" t="n">
-        <v>6.25618648594353</v>
+        <v>14.7481599037968</v>
       </c>
       <c r="D48" t="s">
         <v>27</v>
@@ -21618,19 +21618,19 @@
         <v>0.01</v>
       </c>
       <c r="G48" t="n">
-        <v>126.944540616743</v>
+        <v>133.199562977667</v>
       </c>
       <c r="H48" t="n">
-        <v>238.12297713733</v>
+        <v>264.866615177048</v>
       </c>
       <c r="I48" t="n">
         <v>9</v>
       </c>
       <c r="J48" t="n">
-        <v>-2.74381351405647</v>
+        <v>5.74815990379675</v>
       </c>
       <c r="K48" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="49">
@@ -21638,10 +21638,10 @@
         <v>45261</v>
       </c>
       <c r="B49" t="n">
-        <v>41.0951333152301</v>
+        <v>48.2527378626844</v>
       </c>
       <c r="C49" t="n">
-        <v>6.58376370468039</v>
+        <v>13.754479345646</v>
       </c>
       <c r="D49" t="s">
         <v>27</v>
@@ -21653,19 +21653,19 @@
         <v>0.01</v>
       </c>
       <c r="G49" t="n">
-        <v>123.754505573807</v>
+        <v>135.720885941179</v>
       </c>
       <c r="H49" t="n">
-        <v>254.202117527919</v>
+        <v>255.871486806572</v>
       </c>
       <c r="I49" t="n">
         <v>8</v>
       </c>
       <c r="J49" t="n">
-        <v>-1.41623629531961</v>
+        <v>5.75447934564596</v>
       </c>
       <c r="K49" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="50">
@@ -21673,10 +21673,10 @@
         <v>45292</v>
       </c>
       <c r="B50" t="n">
-        <v>78.6639576462681</v>
+        <v>87.4195413023612</v>
       </c>
       <c r="C50" t="n">
-        <v>36.3265351484778</v>
+        <v>45.9994158647448</v>
       </c>
       <c r="D50" t="s">
         <v>27</v>
@@ -21688,16 +21688,16 @@
         <v>0.01</v>
       </c>
       <c r="G50" t="n">
-        <v>211.110909858961</v>
+        <v>246.262989141759</v>
       </c>
       <c r="H50" t="n">
-        <v>356.967801791339</v>
+        <v>409.86923338045</v>
       </c>
       <c r="I50" t="n">
         <v>35</v>
       </c>
       <c r="J50" t="n">
-        <v>1.32653514847777</v>
+        <v>10.9994158647448</v>
       </c>
       <c r="K50" t="s">
         <v>55</v>
@@ -21708,10 +21708,10 @@
         <v>45323</v>
       </c>
       <c r="B51" t="n">
-        <v>71.1678047658435</v>
+        <v>84.0870620147396</v>
       </c>
       <c r="C51" t="n">
-        <v>30.3229253413982</v>
+        <v>45.2022022683935</v>
       </c>
       <c r="D51" t="s">
         <v>27</v>
@@ -21723,16 +21723,16 @@
         <v>0.01</v>
       </c>
       <c r="G51" t="n">
-        <v>197.594365050086</v>
+        <v>226.016991259769</v>
       </c>
       <c r="H51" t="n">
-        <v>368.247302249783</v>
+        <v>432.262908761606</v>
       </c>
       <c r="I51" t="n">
         <v>11</v>
       </c>
       <c r="J51" t="n">
-        <v>19.3229253413982</v>
+        <v>34.2022022683935</v>
       </c>
       <c r="K51" t="s">
         <v>55</v>
@@ -21743,10 +21743,10 @@
         <v>45352</v>
       </c>
       <c r="B52" t="n">
-        <v>67.4551634892655</v>
+        <v>77.8642989203978</v>
       </c>
       <c r="C52" t="n">
-        <v>26.5753106720603</v>
+        <v>36.1780719317757</v>
       </c>
       <c r="D52" t="s">
         <v>27</v>
@@ -21758,16 +21758,16 @@
         <v>0.01</v>
       </c>
       <c r="G52" t="n">
-        <v>198.042428125933</v>
+        <v>202.423180091131</v>
       </c>
       <c r="H52" t="n">
-        <v>355.491839776936</v>
+        <v>376.384038170248</v>
       </c>
       <c r="I52" t="n">
         <v>21</v>
       </c>
       <c r="J52" t="n">
-        <v>5.57531067206029</v>
+        <v>15.1780719317757</v>
       </c>
       <c r="K52" t="s">
         <v>55</v>
@@ -21778,10 +21778,10 @@
         <v>45383</v>
       </c>
       <c r="B53" t="n">
-        <v>53.617586637107</v>
+        <v>64.8031023639777</v>
       </c>
       <c r="C53" t="n">
-        <v>15.096106708282</v>
+        <v>23.4088086474296</v>
       </c>
       <c r="D53" t="s">
         <v>27</v>
@@ -21793,16 +21793,16 @@
         <v>0.01</v>
       </c>
       <c r="G53" t="n">
-        <v>150.611731845786</v>
+        <v>186.458070516439</v>
       </c>
       <c r="H53" t="n">
-        <v>316.434373326492</v>
+        <v>330.427654711707</v>
       </c>
       <c r="I53" t="n">
         <v>26</v>
       </c>
       <c r="J53" t="n">
-        <v>-10.903893291718</v>
+        <v>-2.59119135257039</v>
       </c>
       <c r="K53" t="s">
         <v>54</v>
@@ -21813,10 +21813,10 @@
         <v>45413</v>
       </c>
       <c r="B54" t="n">
-        <v>69.523434502279</v>
+        <v>83.5548475778439</v>
       </c>
       <c r="C54" t="n">
-        <v>24.4298392168261</v>
+        <v>42.420778311675</v>
       </c>
       <c r="D54" t="s">
         <v>27</v>
@@ -21828,19 +21828,19 @@
         <v>0.01</v>
       </c>
       <c r="G54" t="n">
-        <v>180.449930496253</v>
+        <v>239.894689509155</v>
       </c>
       <c r="H54" t="n">
-        <v>391.592284867105</v>
+        <v>421.454263338846</v>
       </c>
       <c r="I54" t="n">
         <v>29</v>
       </c>
       <c r="J54" t="n">
-        <v>-4.57016078317388</v>
+        <v>13.420778311675</v>
       </c>
       <c r="K54" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="55">
@@ -21848,10 +21848,10 @@
         <v>45444</v>
       </c>
       <c r="B55" t="n">
-        <v>76.4492736292564</v>
+        <v>90.2988959379091</v>
       </c>
       <c r="C55" t="n">
-        <v>28.6630056482252</v>
+        <v>47.3124524838988</v>
       </c>
       <c r="D55" t="s">
         <v>27</v>
@@ -21863,16 +21863,16 @@
         <v>0.01</v>
       </c>
       <c r="G55" t="n">
-        <v>201.838568119755</v>
+        <v>252.794707888147</v>
       </c>
       <c r="H55" t="n">
-        <v>413.226937108552</v>
+        <v>380.281067468915</v>
       </c>
       <c r="I55" t="n">
         <v>22</v>
       </c>
       <c r="J55" t="n">
-        <v>6.66300564822524</v>
+        <v>25.3124524838988</v>
       </c>
       <c r="K55" t="s">
         <v>55</v>
@@ -21883,10 +21883,10 @@
         <v>45474</v>
       </c>
       <c r="B56" t="n">
-        <v>61.8906050141308</v>
+        <v>74.8404474841727</v>
       </c>
       <c r="C56" t="n">
-        <v>16.4978547298059</v>
+        <v>33.8149110040712</v>
       </c>
       <c r="D56" t="s">
         <v>27</v>
@@ -21898,16 +21898,16 @@
         <v>0.01</v>
       </c>
       <c r="G56" t="n">
-        <v>177.063204564482</v>
+        <v>232.872027704664</v>
       </c>
       <c r="H56" t="n">
-        <v>355.855268021243</v>
+        <v>375.298592136702</v>
       </c>
       <c r="I56" t="n">
         <v>40</v>
       </c>
       <c r="J56" t="n">
-        <v>-23.5021452701941</v>
+        <v>-6.18508899592877</v>
       </c>
       <c r="K56" t="s">
         <v>54</v>
@@ -21918,10 +21918,10 @@
         <v>45505</v>
       </c>
       <c r="B57" t="n">
-        <v>54.697361679784</v>
+        <v>65.1233809360276</v>
       </c>
       <c r="C57" t="n">
-        <v>8.59925724032679</v>
+        <v>22.2145912107367</v>
       </c>
       <c r="D57" t="s">
         <v>27</v>
@@ -21933,16 +21933,16 @@
         <v>0.01</v>
       </c>
       <c r="G57" t="n">
-        <v>164.752633229962</v>
+        <v>195.21024107852</v>
       </c>
       <c r="H57" t="n">
-        <v>339.34871721312</v>
+        <v>314.764821026753</v>
       </c>
       <c r="I57" t="n">
         <v>31</v>
       </c>
       <c r="J57" t="n">
-        <v>-22.4007427596732</v>
+        <v>-8.78540878926334</v>
       </c>
       <c r="K57" t="s">
         <v>54</v>
@@ -21953,10 +21953,10 @@
         <v>45536</v>
       </c>
       <c r="B58" t="n">
-        <v>47.6564898788086</v>
+        <v>55.8528337505865</v>
       </c>
       <c r="C58" t="n">
-        <v>4.79770959361959</v>
+        <v>15.2805746261208</v>
       </c>
       <c r="D58" t="s">
         <v>27</v>
@@ -21968,19 +21968,19 @@
         <v>0.01</v>
       </c>
       <c r="G58" t="n">
-        <v>149.336899575571</v>
+        <v>173.705892155305</v>
       </c>
       <c r="H58" t="n">
-        <v>339.397990084769</v>
+        <v>332.22977800052</v>
       </c>
       <c r="I58" t="n">
         <v>10</v>
       </c>
       <c r="J58" t="n">
-        <v>-5.20229040638041</v>
+        <v>5.28057462612075</v>
       </c>
       <c r="K58" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="59">
@@ -21988,10 +21988,10 @@
         <v>45566</v>
       </c>
       <c r="B59" t="n">
-        <v>41.5478396009483</v>
+        <v>48.2297257727133</v>
       </c>
       <c r="C59" t="n">
-        <v>2.98272914883452</v>
+        <v>12.2495738278548</v>
       </c>
       <c r="D59" t="s">
         <v>27</v>
@@ -22003,16 +22003,16 @@
         <v>0.01</v>
       </c>
       <c r="G59" t="n">
-        <v>131.901924212827</v>
+        <v>145.885576304892</v>
       </c>
       <c r="H59" t="n">
-        <v>330.722957890609</v>
+        <v>280.710709169999</v>
       </c>
       <c r="I59" t="n">
         <v>14</v>
       </c>
       <c r="J59" t="n">
-        <v>-11.0172708511655</v>
+        <v>-1.75042617214515</v>
       </c>
       <c r="K59" t="s">
         <v>54</v>
@@ -22023,10 +22023,10 @@
         <v>45597</v>
       </c>
       <c r="B60" t="n">
-        <v>42.8466138434441</v>
+        <v>49.1619713481242</v>
       </c>
       <c r="C60" t="n">
-        <v>2.82682024598992</v>
+        <v>13.3080416003162</v>
       </c>
       <c r="D60" t="s">
         <v>27</v>
@@ -22038,16 +22038,16 @@
         <v>0.01</v>
       </c>
       <c r="G60" t="n">
-        <v>142.062882180099</v>
+        <v>150.663321932917</v>
       </c>
       <c r="H60" t="n">
-        <v>350.884757869725</v>
+        <v>300.461753769548</v>
       </c>
       <c r="I60" t="n">
         <v>17</v>
       </c>
       <c r="J60" t="n">
-        <v>-14.1731797540101</v>
+        <v>-3.69195839968384</v>
       </c>
       <c r="K60" t="s">
         <v>54</v>
@@ -22058,10 +22058,10 @@
         <v>45627</v>
       </c>
       <c r="B61" t="n">
-        <v>43.67449552814</v>
+        <v>48.3670176497679</v>
       </c>
       <c r="C61" t="n">
-        <v>2.17882853148483</v>
+        <v>10.5681039168878</v>
       </c>
       <c r="D61" t="s">
         <v>27</v>
@@ -22073,16 +22073,16 @@
         <v>0.01</v>
       </c>
       <c r="G61" t="n">
-        <v>145.908550518896</v>
+        <v>142.895031172547</v>
       </c>
       <c r="H61" t="n">
-        <v>296.513477970647</v>
+        <v>333.77459028471</v>
       </c>
       <c r="I61" t="n">
         <v>11</v>
       </c>
       <c r="J61" t="n">
-        <v>-8.82117146851517</v>
+        <v>-0.431896083112179</v>
       </c>
       <c r="K61" t="s">
         <v>54</v>
@@ -22093,10 +22093,10 @@
         <v>45658</v>
       </c>
       <c r="B62" t="n">
-        <v>75.9222552057361</v>
+        <v>88.1698461629027</v>
       </c>
       <c r="C62" t="n">
-        <v>20.0281707629913</v>
+        <v>42.1353793123589</v>
       </c>
       <c r="D62" t="s">
         <v>27</v>
@@ -22108,19 +22108,19 @@
         <v>0.01</v>
       </c>
       <c r="G62" t="n">
-        <v>230.191483404548</v>
+        <v>232.147615940301</v>
       </c>
       <c r="H62" t="n">
-        <v>429.814195812693</v>
+        <v>468.900002905697</v>
       </c>
       <c r="I62" t="n">
         <v>22</v>
       </c>
       <c r="J62" t="n">
-        <v>-1.97182923700871</v>
+        <v>20.1353793123589</v>
       </c>
       <c r="K62" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="63">
@@ -22128,10 +22128,10 @@
         <v>45689</v>
       </c>
       <c r="B63" t="n">
-        <v>70.448310898745</v>
+        <v>82.7952550555744</v>
       </c>
       <c r="C63" t="n">
-        <v>19.56710370677</v>
+        <v>33.9061909082197</v>
       </c>
       <c r="D63" t="s">
         <v>27</v>
@@ -22143,16 +22143,16 @@
         <v>0.01</v>
       </c>
       <c r="G63" t="n">
-        <v>218.676332200768</v>
+        <v>224.818260950978</v>
       </c>
       <c r="H63" t="n">
-        <v>401.957436468084</v>
+        <v>431.012038000452</v>
       </c>
       <c r="I63" t="n">
         <v>34</v>
       </c>
       <c r="J63" t="n">
-        <v>-14.43289629323</v>
+        <v>-0.0938090917803365</v>
       </c>
       <c r="K63" t="s">
         <v>54</v>
@@ -22163,10 +22163,10 @@
         <v>45717</v>
       </c>
       <c r="B64" t="n">
-        <v>66.6479284756743</v>
+        <v>78.8156177508014</v>
       </c>
       <c r="C64" t="n">
-        <v>15.3165701504695</v>
+        <v>27.6356006678369</v>
       </c>
       <c r="D64" t="s">
         <v>27</v>
@@ -22178,16 +22178,16 @@
         <v>0.01</v>
       </c>
       <c r="G64" t="n">
-        <v>204.225233354015</v>
+        <v>207.357191821892</v>
       </c>
       <c r="H64" t="n">
-        <v>415.753068163134</v>
+        <v>401.420867372961</v>
       </c>
       <c r="I64" t="n">
         <v>31</v>
       </c>
       <c r="J64" t="n">
-        <v>-15.6834298495305</v>
+        <v>-3.36439933216308</v>
       </c>
       <c r="K64" t="s">
         <v>54</v>
@@ -22198,10 +22198,10 @@
         <v>45748</v>
       </c>
       <c r="B65" t="n">
-        <v>56.2652949477619</v>
+        <v>66.5312910664891</v>
       </c>
       <c r="C65" t="n">
-        <v>6.70035246744374</v>
+        <v>16.8399178448519</v>
       </c>
       <c r="D65" t="s">
         <v>27</v>
@@ -22213,16 +22213,16 @@
         <v>0.01</v>
       </c>
       <c r="G65" t="n">
-        <v>179.608606321851</v>
+        <v>198.523032176471</v>
       </c>
       <c r="H65" t="n">
-        <v>343.687580501526</v>
+        <v>385.258621090267</v>
       </c>
       <c r="I65" t="n">
         <v>29</v>
       </c>
       <c r="J65" t="n">
-        <v>-22.2996475325563</v>
+        <v>-12.1600821551481</v>
       </c>
       <c r="K65" t="s">
         <v>54</v>
@@ -22233,10 +22233,10 @@
         <v>45778</v>
       </c>
       <c r="B66" t="n">
-        <v>72.8370334656308</v>
+        <v>83.0408522591917</v>
       </c>
       <c r="C66" t="n">
-        <v>16.0565271269733</v>
+        <v>29.9281822507795</v>
       </c>
       <c r="D66" t="s">
         <v>27</v>
@@ -22248,19 +22248,19 @@
         <v>0.01</v>
       </c>
       <c r="G66" t="n">
-        <v>228.350143726228</v>
+        <v>244.467231562419</v>
       </c>
       <c r="H66" t="n">
-        <v>428.692430129174</v>
+        <v>397.911152963732</v>
       </c>
       <c r="I66" t="n">
         <v>22</v>
       </c>
       <c r="J66" t="n">
-        <v>-5.94347287302673</v>
+        <v>7.92818225077952</v>
       </c>
       <c r="K66" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="67">
@@ -22268,10 +22268,10 @@
         <v>45809</v>
       </c>
       <c r="B67" t="n">
-        <v>75.586090407653</v>
+        <v>91.8347872156971</v>
       </c>
       <c r="C67" t="n">
-        <v>21.0914009015687</v>
+        <v>37.103214618812</v>
       </c>
       <c r="D67" t="s">
         <v>27</v>
@@ -22283,19 +22283,19 @@
         <v>0.01</v>
       </c>
       <c r="G67" t="n">
-        <v>208.316793423186</v>
+        <v>264.224794508955</v>
       </c>
       <c r="H67" t="n">
-        <v>472.857859194063</v>
+        <v>489.449839733146</v>
       </c>
       <c r="I67" t="n">
         <v>25</v>
       </c>
       <c r="J67" t="n">
-        <v>-3.90859909843133</v>
+        <v>12.103214618812</v>
       </c>
       <c r="K67" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="68">
@@ -22303,10 +22303,10 @@
         <v>45839</v>
       </c>
       <c r="B68" t="n">
-        <v>60.9310360560885</v>
+        <v>75.933228401731</v>
       </c>
       <c r="C68" t="n">
-        <v>11.7070850756089</v>
+        <v>18.8327641258115</v>
       </c>
       <c r="D68" t="s">
         <v>27</v>
@@ -22318,16 +22318,16 @@
         <v>0.01</v>
       </c>
       <c r="G68" t="n">
-        <v>192.005323348012</v>
+        <v>235.217416353643</v>
       </c>
       <c r="H68" t="n">
-        <v>361.199301710263</v>
+        <v>433.477438527327</v>
       </c>
       <c r="I68" t="n">
         <v>30</v>
       </c>
       <c r="J68" t="n">
-        <v>-18.2929149243911</v>
+        <v>-11.1672358741885</v>
       </c>
       <c r="K68" t="s">
         <v>54</v>
@@ -22338,10 +22338,10 @@
         <v>45870</v>
       </c>
       <c r="B69" t="n">
-        <v>55.2722830396491</v>
+        <v>68.1781274895813</v>
       </c>
       <c r="C69" t="n">
-        <v>7.83904571339251</v>
+        <v>13.1478429715563</v>
       </c>
       <c r="D69" t="s">
         <v>27</v>
@@ -22353,16 +22353,16 @@
         <v>0.01</v>
       </c>
       <c r="G69" t="n">
-        <v>162.646280313171</v>
+        <v>221.471666796391</v>
       </c>
       <c r="H69" t="n">
-        <v>403.975073937525</v>
+        <v>401.716586731334</v>
       </c>
       <c r="I69" t="n">
         <v>26</v>
       </c>
       <c r="J69" t="n">
-        <v>-18.1609542866075</v>
+        <v>-12.8521570284437</v>
       </c>
       <c r="K69" t="s">
         <v>54</v>
@@ -22373,10 +22373,10 @@
         <v>45901</v>
       </c>
       <c r="B70" t="n">
-        <v>49.3140989577107</v>
+        <v>59.1208958325532</v>
       </c>
       <c r="C70" t="n">
-        <v>3.35029012088559</v>
+        <v>9.31775696672869</v>
       </c>
       <c r="D70" t="s">
         <v>27</v>
@@ -22388,16 +22388,16 @@
         <v>0.01</v>
       </c>
       <c r="G70" t="n">
-        <v>148.200536634102</v>
+        <v>184.907927144587</v>
       </c>
       <c r="H70" t="n">
-        <v>397.865316893413</v>
+        <v>332.615974887436</v>
       </c>
       <c r="I70" t="n">
         <v>22</v>
       </c>
       <c r="J70" t="n">
-        <v>-18.6497098791144</v>
+        <v>-12.6822430332713</v>
       </c>
       <c r="K70" t="s">
         <v>54</v>
@@ -22408,10 +22408,10 @@
         <v>45931</v>
       </c>
       <c r="B71" t="n">
-        <v>44.7091288068846</v>
+        <v>53.9916485331323</v>
       </c>
       <c r="C71" t="n">
-        <v>1.62273529458453</v>
+        <v>3.64308201628634</v>
       </c>
       <c r="D71" t="s">
         <v>27</v>
@@ -22423,16 +22423,16 @@
         <v>0.01</v>
       </c>
       <c r="G71" t="n">
-        <v>132.058574268503</v>
+        <v>180.451558141936</v>
       </c>
       <c r="H71" t="n">
-        <v>350.929008126579</v>
+        <v>339.006895739599</v>
       </c>
       <c r="I71" t="n">
         <v>21</v>
       </c>
       <c r="J71" t="n">
-        <v>-19.3772647054155</v>
+        <v>-17.3569179837137</v>
       </c>
       <c r="K71" t="s">
         <v>54</v>
@@ -22443,10 +22443,10 @@
         <v>45962</v>
       </c>
       <c r="B72" t="n">
-        <v>43.9564938709598</v>
+        <v>54.3701620957664</v>
       </c>
       <c r="C72" t="n">
-        <v>0.919654633765553</v>
+        <v>2.85526321100815</v>
       </c>
       <c r="D72" t="s">
         <v>27</v>
@@ -22458,16 +22458,16 @@
         <v>0.01</v>
       </c>
       <c r="G72" t="n">
-        <v>136.044247159077</v>
+        <v>160.558037481661</v>
       </c>
       <c r="H72" t="n">
-        <v>324.45855162525</v>
+        <v>356.469811046365</v>
       </c>
       <c r="I72" t="n">
         <v>28</v>
       </c>
       <c r="J72" t="n">
-        <v>-27.0803453662344</v>
+        <v>-25.1447367889918</v>
       </c>
       <c r="K72" t="s">
         <v>54</v>
@@ -22478,10 +22478,10 @@
         <v>45992</v>
       </c>
       <c r="B73" t="n">
-        <v>45.6480234505281</v>
+        <v>54.1486145968342</v>
       </c>
       <c r="C73" t="n">
-        <v>0.545283696837193</v>
+        <v>4.55372635507665</v>
       </c>
       <c r="D73" t="s">
         <v>27</v>
@@ -22493,16 +22493,16 @@
         <v>0.01</v>
       </c>
       <c r="G73" t="n">
-        <v>134.047000889089</v>
+        <v>165.952907274777</v>
       </c>
       <c r="H73" t="n">
-        <v>345.360567212058</v>
+        <v>403.623406058087</v>
       </c>
       <c r="I73" t="n">
         <v>21</v>
       </c>
       <c r="J73" t="n">
-        <v>-20.4547163031628</v>
+        <v>-16.4462736449234</v>
       </c>
       <c r="K73" t="s">
         <v>54</v>
@@ -54342,31 +54342,31 @@
         <v>43831</v>
       </c>
       <c r="B2" t="n">
-        <v>175.515559712954</v>
+        <v>201.972416418421</v>
       </c>
       <c r="C2" t="n">
-        <v>178.142423174524</v>
+        <v>201.931204627775</v>
       </c>
       <c r="D2" t="s">
         <v>40</v>
       </c>
       <c r="E2" t="n">
-        <v>122.887625190924</v>
+        <v>199.693277938551</v>
       </c>
       <c r="F2" t="n">
-        <v>89.7689416006188</v>
+        <v>198.96120224631</v>
       </c>
       <c r="G2" t="n">
-        <v>220.853778771476</v>
+        <v>204.279660488705</v>
       </c>
       <c r="H2" t="n">
-        <v>266.097541501315</v>
+        <v>205.252239967691</v>
       </c>
       <c r="I2" t="n">
         <v>164</v>
       </c>
       <c r="J2" t="n">
-        <v>14.1424231745235</v>
+        <v>37.9312046277751</v>
       </c>
       <c r="K2" t="s">
         <v>55</v>
@@ -54377,31 +54377,31 @@
         <v>43862</v>
       </c>
       <c r="B3" t="n">
-        <v>189.662988792238</v>
+        <v>213.56746958666</v>
       </c>
       <c r="C3" t="n">
-        <v>184.940512000127</v>
+        <v>213.576625790401</v>
       </c>
       <c r="D3" t="s">
         <v>40</v>
       </c>
       <c r="E3" t="n">
-        <v>112.059765335503</v>
+        <v>211.193893545793</v>
       </c>
       <c r="F3" t="n">
-        <v>81.3461729403192</v>
+        <v>210.441013214554</v>
       </c>
       <c r="G3" t="n">
-        <v>263.332672699114</v>
+        <v>215.909756330184</v>
       </c>
       <c r="H3" t="n">
-        <v>356.943044852696</v>
+        <v>216.909605730101</v>
       </c>
       <c r="I3" t="n">
         <v>138</v>
       </c>
       <c r="J3" t="n">
-        <v>46.9405120001269</v>
+        <v>75.5766257904012</v>
       </c>
       <c r="K3" t="s">
         <v>55</v>
@@ -54412,31 +54412,31 @@
         <v>43891</v>
       </c>
       <c r="B4" t="n">
-        <v>232.98205647765</v>
+        <v>241.158156499152</v>
       </c>
       <c r="C4" t="n">
-        <v>222.361286887249</v>
+        <v>241.077288583851</v>
       </c>
       <c r="D4" t="s">
         <v>40</v>
       </c>
       <c r="E4" t="n">
-        <v>131.502199528069</v>
+        <v>238.631466495058</v>
       </c>
       <c r="F4" t="n">
-        <v>91.418714213929</v>
+        <v>237.831130961758</v>
       </c>
       <c r="G4" t="n">
-        <v>336.148484013974</v>
+        <v>243.835734448246</v>
       </c>
       <c r="H4" t="n">
-        <v>463.80316009543</v>
+        <v>244.70472443093</v>
       </c>
       <c r="I4" t="n">
         <v>108</v>
       </c>
       <c r="J4" t="n">
-        <v>114.361286887249</v>
+        <v>133.077288583851</v>
       </c>
       <c r="K4" t="s">
         <v>55</v>
@@ -54447,31 +54447,31 @@
         <v>43922</v>
       </c>
       <c r="B5" t="n">
-        <v>195.231928826765</v>
+        <v>184.607744138848</v>
       </c>
       <c r="C5" t="n">
-        <v>182.527717476957</v>
+        <v>184.61643366616</v>
       </c>
       <c r="D5" t="s">
         <v>40</v>
       </c>
       <c r="E5" t="n">
-        <v>94.7143185780729</v>
+        <v>182.40159809214</v>
       </c>
       <c r="F5" t="n">
-        <v>54.3965289882304</v>
+        <v>181.701965376239</v>
       </c>
       <c r="G5" t="n">
-        <v>311.974423862925</v>
+        <v>186.955113546478</v>
       </c>
       <c r="H5" t="n">
-        <v>421.923526444322</v>
+        <v>187.716122254515</v>
       </c>
       <c r="I5" t="n">
         <v>60</v>
       </c>
       <c r="J5" t="n">
-        <v>122.527717476957</v>
+        <v>124.61643366616</v>
       </c>
       <c r="K5" t="s">
         <v>55</v>
@@ -54482,31 +54482,31 @@
         <v>43952</v>
       </c>
       <c r="B6" t="n">
-        <v>228.108915204268</v>
+        <v>179.838390680687</v>
       </c>
       <c r="C6" t="n">
-        <v>213.923190824817</v>
+        <v>179.848642381572</v>
       </c>
       <c r="D6" t="s">
         <v>40</v>
       </c>
       <c r="E6" t="n">
-        <v>109.947495849864</v>
+        <v>177.661978233528</v>
       </c>
       <c r="F6" t="n">
-        <v>66.0689578714225</v>
+        <v>176.971503950517</v>
       </c>
       <c r="G6" t="n">
-        <v>363.697619891238</v>
+        <v>181.989449287442</v>
       </c>
       <c r="H6" t="n">
-        <v>490.9986613995</v>
+        <v>182.907499238642</v>
       </c>
       <c r="I6" t="n">
         <v>85</v>
       </c>
       <c r="J6" t="n">
-        <v>128.923190824817</v>
+        <v>94.8486423815719</v>
       </c>
       <c r="K6" t="s">
         <v>55</v>
@@ -54517,31 +54517,31 @@
         <v>43983</v>
       </c>
       <c r="B7" t="n">
-        <v>244.972765822556</v>
+        <v>197.821943514916</v>
       </c>
       <c r="C7" t="n">
-        <v>228.534957657236</v>
+        <v>197.788428070281</v>
       </c>
       <c r="D7" t="s">
         <v>40</v>
       </c>
       <c r="E7" t="n">
-        <v>113.786269958716</v>
+        <v>195.637418479585</v>
       </c>
       <c r="F7" t="n">
-        <v>68.4649957347182</v>
+        <v>194.849162970965</v>
       </c>
       <c r="G7" t="n">
-        <v>394.581407364344</v>
+        <v>200.095209821785</v>
       </c>
       <c r="H7" t="n">
-        <v>530.30122487218</v>
+        <v>200.999680262975</v>
       </c>
       <c r="I7" t="n">
         <v>56</v>
       </c>
       <c r="J7" t="n">
-        <v>172.534957657236</v>
+        <v>141.788428070281</v>
       </c>
       <c r="K7" t="s">
         <v>55</v>
@@ -54552,31 +54552,31 @@
         <v>44013</v>
       </c>
       <c r="B8" t="n">
-        <v>262.434307946797</v>
+        <v>211.903372433254</v>
       </c>
       <c r="C8" t="n">
-        <v>245.701522658317</v>
+        <v>211.830021095461</v>
       </c>
       <c r="D8" t="s">
         <v>40</v>
       </c>
       <c r="E8" t="n">
-        <v>118.094373658773</v>
+        <v>209.579058802734</v>
       </c>
       <c r="F8" t="n">
-        <v>67.3940608624889</v>
+        <v>208.829064913406</v>
       </c>
       <c r="G8" t="n">
-        <v>429.29088787333</v>
+        <v>214.276957460236</v>
       </c>
       <c r="H8" t="n">
-        <v>571.47304566873</v>
+        <v>215.273023423069</v>
       </c>
       <c r="I8" t="n">
         <v>76</v>
       </c>
       <c r="J8" t="n">
-        <v>169.701522658317</v>
+        <v>135.830021095461</v>
       </c>
       <c r="K8" t="s">
         <v>55</v>
@@ -54587,31 +54587,31 @@
         <v>44044</v>
       </c>
       <c r="B9" t="n">
-        <v>242.219135475954</v>
+        <v>207.137758014576</v>
       </c>
       <c r="C9" t="n">
-        <v>221.507410435362</v>
+        <v>207.179409522248</v>
       </c>
       <c r="D9" t="s">
         <v>40</v>
       </c>
       <c r="E9" t="n">
-        <v>97.418376962681</v>
+        <v>204.832734159975</v>
       </c>
       <c r="F9" t="n">
-        <v>54.0179470749322</v>
+        <v>204.091289094212</v>
       </c>
       <c r="G9" t="n">
-        <v>410.337831902568</v>
+        <v>209.47742816068</v>
       </c>
       <c r="H9" t="n">
-        <v>539.098923211644</v>
+        <v>210.462288654257</v>
       </c>
       <c r="I9" t="n">
         <v>79</v>
       </c>
       <c r="J9" t="n">
-        <v>142.507410435362</v>
+        <v>128.179409522248</v>
       </c>
       <c r="K9" t="s">
         <v>55</v>
@@ -54622,31 +54622,31 @@
         <v>44075</v>
       </c>
       <c r="B10" t="n">
-        <v>223.253469797281</v>
+        <v>197.641464075488</v>
       </c>
       <c r="C10" t="n">
-        <v>202.420828856058</v>
+        <v>197.640987964386</v>
       </c>
       <c r="D10" t="s">
         <v>40</v>
       </c>
       <c r="E10" t="n">
-        <v>81.6363561038616</v>
+        <v>195.412865368085</v>
       </c>
       <c r="F10" t="n">
-        <v>40.4663422622041</v>
+        <v>194.625062826889</v>
       </c>
       <c r="G10" t="n">
-        <v>389.538106682501</v>
+        <v>199.885631170536</v>
       </c>
       <c r="H10" t="n">
-        <v>521.09943440238</v>
+        <v>200.772069668404</v>
       </c>
       <c r="I10" t="n">
         <v>60</v>
       </c>
       <c r="J10" t="n">
-        <v>142.420828856058</v>
+        <v>137.640987964386</v>
       </c>
       <c r="K10" t="s">
         <v>55</v>
@@ -54657,31 +54657,31 @@
         <v>44105</v>
       </c>
       <c r="B11" t="n">
-        <v>200.265092054064</v>
+        <v>174.452435457787</v>
       </c>
       <c r="C11" t="n">
-        <v>178.578375000745</v>
+        <v>174.469378031359</v>
       </c>
       <c r="D11" t="s">
         <v>40</v>
       </c>
       <c r="E11" t="n">
-        <v>62.9137204685567</v>
+        <v>172.375975663645</v>
       </c>
       <c r="F11" t="n">
-        <v>27.4128873006767</v>
+        <v>171.636113565603</v>
       </c>
       <c r="G11" t="n">
-        <v>361.460836682649</v>
+        <v>176.578371532811</v>
       </c>
       <c r="H11" t="n">
-        <v>507.987357722325</v>
+        <v>177.482687642784</v>
       </c>
       <c r="I11" t="n">
         <v>94</v>
       </c>
       <c r="J11" t="n">
-        <v>84.5783750007447</v>
+        <v>80.4693780313593</v>
       </c>
       <c r="K11" t="s">
         <v>55</v>
@@ -54692,31 +54692,31 @@
         <v>44136</v>
       </c>
       <c r="B12" t="n">
-        <v>167.989899361901</v>
+        <v>155.169607925836</v>
       </c>
       <c r="C12" t="n">
-        <v>144.458430406336</v>
+        <v>155.172042055323</v>
       </c>
       <c r="D12" t="s">
         <v>40</v>
       </c>
       <c r="E12" t="n">
-        <v>42.1719763161769</v>
+        <v>153.142051106473</v>
       </c>
       <c r="F12" t="n">
-        <v>11.3467478002574</v>
+        <v>152.501040967566</v>
       </c>
       <c r="G12" t="n">
-        <v>322.540556964531</v>
+        <v>157.161675964861</v>
       </c>
       <c r="H12" t="n">
-        <v>455.709525304724</v>
+        <v>158.014890217698</v>
       </c>
       <c r="I12" t="n">
         <v>48</v>
       </c>
       <c r="J12" t="n">
-        <v>96.4584304063356</v>
+        <v>107.172042055323</v>
       </c>
       <c r="K12" t="s">
         <v>55</v>
@@ -54727,31 +54727,31 @@
         <v>44166</v>
       </c>
       <c r="B13" t="n">
-        <v>157.510085383233</v>
+        <v>134.897455437412</v>
       </c>
       <c r="C13" t="n">
-        <v>133.913083032992</v>
+        <v>134.909974467866</v>
       </c>
       <c r="D13" t="s">
         <v>40</v>
       </c>
       <c r="E13" t="n">
-        <v>34.075686490048</v>
+        <v>133.01699828421</v>
       </c>
       <c r="F13" t="n">
-        <v>8.23017331873823</v>
+        <v>132.419635722026</v>
       </c>
       <c r="G13" t="n">
-        <v>307.230529407837</v>
+        <v>136.76497707084</v>
       </c>
       <c r="H13" t="n">
-        <v>439.326474098501</v>
+        <v>137.560979758207</v>
       </c>
       <c r="I13" t="n">
         <v>48</v>
       </c>
       <c r="J13" t="n">
-        <v>85.9130830329923</v>
+        <v>86.9099744678656</v>
       </c>
       <c r="K13" t="s">
         <v>55</v>
@@ -54762,31 +54762,31 @@
         <v>44197</v>
       </c>
       <c r="B14" t="n">
-        <v>199.554171110678</v>
+        <v>202.007925631586</v>
       </c>
       <c r="C14" t="n">
-        <v>171.136110040986</v>
+        <v>202.010592158625</v>
       </c>
       <c r="D14" t="s">
         <v>40</v>
       </c>
       <c r="E14" t="n">
-        <v>48.2279310770613</v>
+        <v>199.69345860695</v>
       </c>
       <c r="F14" t="n">
-        <v>12.3255009517126</v>
+        <v>198.961382583239</v>
       </c>
       <c r="G14" t="n">
-        <v>384.212355539582</v>
+        <v>204.456626225679</v>
       </c>
       <c r="H14" t="n">
-        <v>545.546323297871</v>
+        <v>205.929314464754</v>
       </c>
       <c r="I14" t="n">
         <v>62</v>
       </c>
       <c r="J14" t="n">
-        <v>109.136110040986</v>
+        <v>140.010592158625</v>
       </c>
       <c r="K14" t="s">
         <v>55</v>
@@ -54797,31 +54797,31 @@
         <v>44228</v>
       </c>
       <c r="B15" t="n">
-        <v>215.075172013307</v>
+        <v>213.531263941109</v>
       </c>
       <c r="C15" t="n">
-        <v>183.048383233649</v>
+        <v>213.495375906918</v>
       </c>
       <c r="D15" t="s">
         <v>40</v>
       </c>
       <c r="E15" t="n">
-        <v>48.5064787089231</v>
+        <v>211.194084587393</v>
       </c>
       <c r="F15" t="n">
-        <v>12.2177945169785</v>
+        <v>210.44120391533</v>
       </c>
       <c r="G15" t="n">
-        <v>421.017511224212</v>
+        <v>215.891741670555</v>
       </c>
       <c r="H15" t="n">
-        <v>590.480783412777</v>
+        <v>216.909799339599</v>
       </c>
       <c r="I15" t="n">
         <v>67</v>
       </c>
       <c r="J15" t="n">
-        <v>116.048383233649</v>
+        <v>146.495375906918</v>
       </c>
       <c r="K15" t="s">
         <v>55</v>
@@ -54832,31 +54832,31 @@
         <v>44256</v>
       </c>
       <c r="B16" t="n">
-        <v>257.972146917551</v>
+        <v>241.099156307571</v>
       </c>
       <c r="C16" t="n">
-        <v>224.55768531555</v>
+        <v>241.033197949569</v>
       </c>
       <c r="D16" t="s">
         <v>40</v>
       </c>
       <c r="E16" t="n">
-        <v>63.380093552217</v>
+        <v>238.631682281271</v>
       </c>
       <c r="F16" t="n">
-        <v>20.5715474333738</v>
+        <v>237.831346385809</v>
       </c>
       <c r="G16" t="n">
-        <v>495.017847539459</v>
+        <v>243.623548718802</v>
       </c>
       <c r="H16" t="n">
-        <v>692.319957275139</v>
+        <v>244.621455024584</v>
       </c>
       <c r="I16" t="n">
         <v>82</v>
       </c>
       <c r="J16" t="n">
-        <v>142.55768531555</v>
+        <v>159.033197949569</v>
       </c>
       <c r="K16" t="s">
         <v>55</v>
@@ -54867,31 +54867,31 @@
         <v>44287</v>
       </c>
       <c r="B17" t="n">
-        <v>220.937601225894</v>
+        <v>184.577586297597</v>
       </c>
       <c r="C17" t="n">
-        <v>187.001357136517</v>
+        <v>184.616599735439</v>
       </c>
       <c r="D17" t="s">
         <v>40</v>
       </c>
       <c r="E17" t="n">
-        <v>39.7640103886001</v>
+        <v>182.386384187953</v>
       </c>
       <c r="F17" t="n">
-        <v>5.75792040646054</v>
+        <v>181.702130129468</v>
       </c>
       <c r="G17" t="n">
-        <v>443.631863399632</v>
+        <v>186.786234823856</v>
       </c>
       <c r="H17" t="n">
-        <v>652.72372551787</v>
+        <v>187.716289712133</v>
       </c>
       <c r="I17" t="n">
         <v>45</v>
       </c>
       <c r="J17" t="n">
-        <v>142.001357136517</v>
+        <v>139.616599735439</v>
       </c>
       <c r="K17" t="s">
         <v>55</v>
@@ -54902,31 +54902,31 @@
         <v>44317</v>
       </c>
       <c r="B18" t="n">
-        <v>254.109430949008</v>
+        <v>179.805043741077</v>
       </c>
       <c r="C18" t="n">
-        <v>214.759300601918</v>
+        <v>179.735102244902</v>
       </c>
       <c r="D18" t="s">
         <v>40</v>
       </c>
       <c r="E18" t="n">
-        <v>49.3246513603561</v>
+        <v>177.66213902778</v>
       </c>
       <c r="F18" t="n">
-        <v>11.5466446802226</v>
+        <v>176.971664432006</v>
       </c>
       <c r="G18" t="n">
-        <v>501.776855627304</v>
+        <v>181.989612028216</v>
       </c>
       <c r="H18" t="n">
-        <v>730.972808563099</v>
+        <v>182.835483129885</v>
       </c>
       <c r="I18" t="n">
         <v>59</v>
       </c>
       <c r="J18" t="n">
-        <v>155.759300601918</v>
+        <v>120.735102244902</v>
       </c>
       <c r="K18" t="s">
         <v>55</v>
@@ -54937,31 +54937,31 @@
         <v>44348</v>
       </c>
       <c r="B19" t="n">
-        <v>272.877921570479</v>
+        <v>197.850800275235</v>
       </c>
       <c r="C19" t="n">
-        <v>232.327674574404</v>
+        <v>197.788606021812</v>
       </c>
       <c r="D19" t="s">
         <v>40</v>
       </c>
       <c r="E19" t="n">
-        <v>52.192227992357</v>
+        <v>195.572225537747</v>
       </c>
       <c r="F19" t="n">
-        <v>12.2305264476152</v>
+        <v>194.849339595309</v>
       </c>
       <c r="G19" t="n">
-        <v>536.302159682897</v>
+        <v>200.112917878538</v>
       </c>
       <c r="H19" t="n">
-        <v>797.669548253391</v>
+        <v>201.075539122108</v>
       </c>
       <c r="I19" t="n">
         <v>51</v>
       </c>
       <c r="J19" t="n">
-        <v>181.327674574404</v>
+        <v>146.788606021812</v>
       </c>
       <c r="K19" t="s">
         <v>55</v>
@@ -54972,31 +54972,31 @@
         <v>44378</v>
       </c>
       <c r="B20" t="n">
-        <v>290.777209016828</v>
+        <v>211.966544935326</v>
       </c>
       <c r="C20" t="n">
-        <v>247.510712898572</v>
+        <v>211.952880375513</v>
       </c>
       <c r="D20" t="s">
         <v>40</v>
       </c>
       <c r="E20" t="n">
-        <v>57.0262166317119</v>
+        <v>209.579248387854</v>
       </c>
       <c r="F20" t="n">
-        <v>14.4642694651125</v>
+        <v>208.829254159001</v>
       </c>
       <c r="G20" t="n">
-        <v>577.06185240533</v>
+        <v>214.458205386394</v>
       </c>
       <c r="H20" t="n">
-        <v>834.893598540705</v>
+        <v>215.273215566309</v>
       </c>
       <c r="I20" t="n">
         <v>37</v>
       </c>
       <c r="J20" t="n">
-        <v>210.510712898572</v>
+        <v>174.952880375513</v>
       </c>
       <c r="K20" t="s">
         <v>55</v>
@@ -55007,31 +55007,31 @@
         <v>44409</v>
       </c>
       <c r="B21" t="n">
-        <v>270.082763901264</v>
+        <v>207.06276078295</v>
       </c>
       <c r="C21" t="n">
-        <v>227.992041390374</v>
+        <v>207.058316551841</v>
       </c>
       <c r="D21" t="s">
         <v>40</v>
       </c>
       <c r="E21" t="n">
-        <v>44.3519648793245</v>
+        <v>204.748246048917</v>
       </c>
       <c r="F21" t="n">
-        <v>7.02922225884446</v>
+        <v>203.768258558603</v>
       </c>
       <c r="G21" t="n">
-        <v>545.206144526144</v>
+        <v>209.477615553976</v>
       </c>
       <c r="H21" t="n">
-        <v>793.324490849971</v>
+        <v>210.386986156472</v>
       </c>
       <c r="I21" t="n">
         <v>47</v>
       </c>
       <c r="J21" t="n">
-        <v>180.992041390374</v>
+        <v>160.058316551841</v>
       </c>
       <c r="K21" t="s">
         <v>55</v>
@@ -55042,31 +55042,31 @@
         <v>44440</v>
       </c>
       <c r="B22" t="n">
-        <v>251.599522404843</v>
+        <v>197.594289821415</v>
       </c>
       <c r="C22" t="n">
-        <v>204.211252586522</v>
+        <v>197.562821261374</v>
       </c>
       <c r="D22" t="s">
         <v>40</v>
       </c>
       <c r="E22" t="n">
-        <v>35.9092206333153</v>
+        <v>195.349301299142</v>
       </c>
       <c r="F22" t="n">
-        <v>2.91868878603564</v>
+        <v>194.625239248899</v>
       </c>
       <c r="G22" t="n">
-        <v>531.193667737449</v>
+        <v>199.885809960925</v>
       </c>
       <c r="H22" t="n">
-        <v>767.966063479711</v>
+        <v>200.847885466077</v>
       </c>
       <c r="I22" t="n">
         <v>37</v>
       </c>
       <c r="J22" t="n">
-        <v>167.211252586522</v>
+        <v>160.562821261374</v>
       </c>
       <c r="K22" t="s">
         <v>55</v>
@@ -55077,31 +55077,31 @@
         <v>44470</v>
       </c>
       <c r="B23" t="n">
-        <v>228.267616679432</v>
+        <v>174.428670924702</v>
       </c>
       <c r="C23" t="n">
-        <v>177.365251634965</v>
+        <v>174.395578918519</v>
       </c>
       <c r="D23" t="s">
         <v>40</v>
       </c>
       <c r="E23" t="n">
-        <v>23.3333480979935</v>
+        <v>172.30131831606</v>
       </c>
       <c r="F23" t="n">
-        <v>0.318358442876387</v>
+        <v>171.636269228797</v>
       </c>
       <c r="G23" t="n">
-        <v>495.101266267783</v>
+        <v>176.578529421258</v>
       </c>
       <c r="H23" t="n">
-        <v>744.288847063535</v>
+        <v>177.482845935014</v>
       </c>
       <c r="I23" t="n">
         <v>37</v>
       </c>
       <c r="J23" t="n">
-        <v>140.365251634965</v>
+        <v>137.395578918519</v>
       </c>
       <c r="K23" t="s">
         <v>55</v>
@@ -55112,31 +55112,31 @@
         <v>44501</v>
       </c>
       <c r="B24" t="n">
-        <v>197.323820290332</v>
+        <v>155.156838867827</v>
       </c>
       <c r="C24" t="n">
-        <v>147.337868303222</v>
+        <v>155.172181641832</v>
       </c>
       <c r="D24" t="s">
         <v>40</v>
       </c>
       <c r="E24" t="n">
-        <v>11.6790283844367</v>
+        <v>153.142189776927</v>
       </c>
       <c r="F24" t="n">
-        <v>0.01</v>
+        <v>152.501179347498</v>
       </c>
       <c r="G24" t="n">
-        <v>443.889713926705</v>
+        <v>157.31688167504</v>
       </c>
       <c r="H24" t="n">
-        <v>688.125773311493</v>
+        <v>158.015031077059</v>
       </c>
       <c r="I24" t="n">
         <v>21</v>
       </c>
       <c r="J24" t="n">
-        <v>126.337868303222</v>
+        <v>134.172181641832</v>
       </c>
       <c r="K24" t="s">
         <v>55</v>
@@ -55147,31 +55147,31 @@
         <v>44531</v>
       </c>
       <c r="B25" t="n">
-        <v>186.430483543763</v>
+        <v>134.874839538719</v>
       </c>
       <c r="C25" t="n">
-        <v>136.656275924511</v>
+        <v>134.811620913338</v>
       </c>
       <c r="D25" t="s">
         <v>40</v>
       </c>
       <c r="E25" t="n">
-        <v>8.17620724893952</v>
+        <v>133.003985758066</v>
       </c>
       <c r="F25" t="n">
-        <v>0.01</v>
+        <v>132.419755958662</v>
       </c>
       <c r="G25" t="n">
-        <v>428.514802059246</v>
+        <v>136.909755200969</v>
       </c>
       <c r="H25" t="n">
-        <v>663.882904997853</v>
+        <v>137.561102306777</v>
       </c>
       <c r="I25" t="n">
         <v>15</v>
       </c>
       <c r="J25" t="n">
-        <v>121.656275924511</v>
+        <v>119.811620913338</v>
       </c>
       <c r="K25" t="s">
         <v>55</v>
@@ -55182,31 +55182,31 @@
         <v>44562</v>
       </c>
       <c r="B26" t="n">
-        <v>229.006685064614</v>
+        <v>201.997933427499</v>
       </c>
       <c r="C26" t="n">
-        <v>172.651164968418</v>
+        <v>202.011522434233</v>
       </c>
       <c r="D26" t="s">
         <v>40</v>
       </c>
       <c r="E26" t="n">
-        <v>15.2198521605913</v>
+        <v>199.693639275511</v>
       </c>
       <c r="F26" t="n">
-        <v>0.01</v>
+        <v>198.961562920331</v>
       </c>
       <c r="G26" t="n">
-        <v>508.494171978567</v>
+        <v>204.456809036232</v>
       </c>
       <c r="H26" t="n">
-        <v>778.590271524537</v>
+        <v>205.252606299486</v>
       </c>
       <c r="I26" t="n">
         <v>47</v>
       </c>
       <c r="J26" t="n">
-        <v>125.651164968418</v>
+        <v>155.011522434233</v>
       </c>
       <c r="K26" t="s">
         <v>55</v>
@@ -55217,31 +55217,31 @@
         <v>44593</v>
       </c>
       <c r="B27" t="n">
-        <v>243.597398710588</v>
+        <v>213.528128641444</v>
       </c>
       <c r="C27" t="n">
-        <v>183.543789566497</v>
+        <v>213.577010023098</v>
       </c>
       <c r="D27" t="s">
         <v>40</v>
       </c>
       <c r="E27" t="n">
-        <v>16.054156347091</v>
+        <v>211.177727283907</v>
       </c>
       <c r="F27" t="n">
-        <v>0.01</v>
+        <v>210.441394616278</v>
       </c>
       <c r="G27" t="n">
-        <v>544.375327845144</v>
+        <v>215.910142655876</v>
       </c>
       <c r="H27" t="n">
-        <v>843.40768495023</v>
+        <v>216.90999294927</v>
       </c>
       <c r="I27" t="n">
         <v>30</v>
       </c>
       <c r="J27" t="n">
-        <v>153.543789566497</v>
+        <v>183.577010023098</v>
       </c>
       <c r="K27" t="s">
         <v>55</v>
@@ -55252,31 +55252,31 @@
         <v>44621</v>
       </c>
       <c r="B28" t="n">
-        <v>287.288748620757</v>
+        <v>241.15204758671</v>
       </c>
       <c r="C28" t="n">
-        <v>220.711779316135</v>
+        <v>241.164265032809</v>
       </c>
       <c r="D28" t="s">
         <v>40</v>
       </c>
       <c r="E28" t="n">
-        <v>26.0397771734183</v>
+        <v>238.631898067679</v>
       </c>
       <c r="F28" t="n">
-        <v>0.01</v>
+        <v>237.831561810055</v>
       </c>
       <c r="G28" t="n">
-        <v>630.521762282804</v>
+        <v>243.662414861615</v>
       </c>
       <c r="H28" t="n">
-        <v>935.730626893159</v>
+        <v>244.705161460884</v>
       </c>
       <c r="I28" t="n">
         <v>34</v>
       </c>
       <c r="J28" t="n">
-        <v>186.711779316135</v>
+        <v>207.164265032809</v>
       </c>
       <c r="K28" t="s">
         <v>55</v>
@@ -55287,31 +55287,31 @@
         <v>44652</v>
       </c>
       <c r="B29" t="n">
-        <v>250.858489394741</v>
+        <v>184.589680943996</v>
       </c>
       <c r="C29" t="n">
-        <v>182.374740204016</v>
+        <v>184.502281723082</v>
       </c>
       <c r="D29" t="s">
         <v>40</v>
       </c>
       <c r="E29" t="n">
-        <v>11.4207186731178</v>
+        <v>182.40192823251</v>
       </c>
       <c r="F29" t="n">
-        <v>0.01</v>
+        <v>181.702294882847</v>
       </c>
       <c r="G29" t="n">
-        <v>583.752214737601</v>
+        <v>186.786401866268</v>
       </c>
       <c r="H29" t="n">
-        <v>889.502008356859</v>
+        <v>187.716457169901</v>
       </c>
       <c r="I29" t="n">
         <v>35</v>
       </c>
       <c r="J29" t="n">
-        <v>147.374740204016</v>
+        <v>149.502281723082</v>
       </c>
       <c r="K29" t="s">
         <v>55</v>
@@ -55322,31 +55322,31 @@
         <v>44682</v>
       </c>
       <c r="B30" t="n">
-        <v>283.840687282077</v>
+        <v>179.846329303248</v>
       </c>
       <c r="C30" t="n">
-        <v>213.667338407194</v>
+        <v>179.848965943225</v>
       </c>
       <c r="D30" t="s">
         <v>40</v>
       </c>
       <c r="E30" t="n">
-        <v>18.0525845700396</v>
+        <v>177.723086899766</v>
       </c>
       <c r="F30" t="n">
-        <v>0.01</v>
+        <v>176.971824913639</v>
       </c>
       <c r="G30" t="n">
-        <v>630.054971028412</v>
+        <v>182.156636534757</v>
       </c>
       <c r="H30" t="n">
-        <v>1004.60585789235</v>
+        <v>182.907825540253</v>
       </c>
       <c r="I30" t="n">
         <v>41</v>
       </c>
       <c r="J30" t="n">
-        <v>172.667338407194</v>
+        <v>138.848965943225</v>
       </c>
       <c r="K30" t="s">
         <v>55</v>
@@ -55357,31 +55357,31 @@
         <v>44713</v>
       </c>
       <c r="B31" t="n">
-        <v>300.71293995839</v>
+        <v>197.837075114379</v>
       </c>
       <c r="C31" t="n">
-        <v>228.775814501407</v>
+        <v>197.86717324625</v>
       </c>
       <c r="D31" t="s">
         <v>40</v>
       </c>
       <c r="E31" t="n">
-        <v>21.6989073022419</v>
+        <v>195.573994950279</v>
       </c>
       <c r="F31" t="n">
-        <v>0.01</v>
+        <v>194.849516219813</v>
       </c>
       <c r="G31" t="n">
-        <v>663.121602720136</v>
+        <v>200.288068038285</v>
       </c>
       <c r="H31" t="n">
-        <v>1039.82466440206</v>
+        <v>201.075718546344</v>
       </c>
       <c r="I31" t="n">
         <v>52</v>
       </c>
       <c r="J31" t="n">
-        <v>176.775814501407</v>
+        <v>145.86717324625</v>
       </c>
       <c r="K31" t="s">
         <v>55</v>
@@ -55392,31 +55392,31 @@
         <v>44743</v>
       </c>
       <c r="B32" t="n">
-        <v>319.658656465883</v>
+        <v>211.904871776116</v>
       </c>
       <c r="C32" t="n">
-        <v>243.039849431235</v>
+        <v>211.953071031374</v>
       </c>
       <c r="D32" t="s">
         <v>40</v>
       </c>
       <c r="E32" t="n">
-        <v>23.5079397971423</v>
+        <v>209.579437973146</v>
       </c>
       <c r="F32" t="n">
-        <v>0.01</v>
+        <v>208.829443404766</v>
       </c>
       <c r="G32" t="n">
-        <v>707.428377929531</v>
+        <v>214.259202005964</v>
       </c>
       <c r="H32" t="n">
-        <v>1102.47841858203</v>
+        <v>215.195101713714</v>
       </c>
       <c r="I32" t="n">
         <v>56</v>
       </c>
       <c r="J32" t="n">
-        <v>187.039849431235</v>
+        <v>155.953071031374</v>
       </c>
       <c r="K32" t="s">
         <v>55</v>
@@ -55427,31 +55427,31 @@
         <v>44774</v>
       </c>
       <c r="B33" t="n">
-        <v>299.35516858679</v>
+        <v>207.153908879032</v>
       </c>
       <c r="C33" t="n">
-        <v>224.814870572758</v>
+        <v>207.179782247588</v>
       </c>
       <c r="D33" t="s">
         <v>40</v>
       </c>
       <c r="E33" t="n">
-        <v>15.1753281372873</v>
+        <v>204.816807551545</v>
       </c>
       <c r="F33" t="n">
-        <v>0.01</v>
+        <v>204.091659031289</v>
       </c>
       <c r="G33" t="n">
-        <v>685.277427885948</v>
+        <v>209.47780294744</v>
       </c>
       <c r="H33" t="n">
-        <v>1047.17879833794</v>
+        <v>210.462664321015</v>
       </c>
       <c r="I33" t="n">
         <v>61</v>
       </c>
       <c r="J33" t="n">
-        <v>163.814870572758</v>
+        <v>146.179782247588</v>
       </c>
       <c r="K33" t="s">
         <v>55</v>
@@ -55462,31 +55462,31 @@
         <v>44805</v>
       </c>
       <c r="B34" t="n">
-        <v>280.843098868837</v>
+        <v>197.630124155136</v>
       </c>
       <c r="C34" t="n">
-        <v>203.644951041569</v>
+        <v>197.641713742929</v>
       </c>
       <c r="D34" t="s">
         <v>40</v>
       </c>
       <c r="E34" t="n">
-        <v>10.9756501773462</v>
+        <v>195.349478049177</v>
       </c>
       <c r="F34" t="n">
-        <v>0.01</v>
+        <v>194.625415671067</v>
       </c>
       <c r="G34" t="n">
-        <v>656.036253079503</v>
+        <v>199.885988751473</v>
       </c>
       <c r="H34" t="n">
-        <v>1018.52879848442</v>
+        <v>200.84806468638</v>
       </c>
       <c r="I34" t="n">
         <v>65</v>
       </c>
       <c r="J34" t="n">
-        <v>138.644951041569</v>
+        <v>132.641713742929</v>
       </c>
       <c r="K34" t="s">
         <v>55</v>
@@ -55497,31 +55497,31 @@
         <v>44835</v>
       </c>
       <c r="B35" t="n">
-        <v>257.265750688646</v>
+        <v>174.452072043887</v>
       </c>
       <c r="C35" t="n">
-        <v>176.463440747857</v>
+        <v>174.469344084558</v>
       </c>
       <c r="D35" t="s">
         <v>40</v>
       </c>
       <c r="E35" t="n">
-        <v>4.23028666468575</v>
+        <v>172.301474280682</v>
       </c>
       <c r="F35" t="n">
-        <v>0.01</v>
+        <v>171.636424892132</v>
       </c>
       <c r="G35" t="n">
-        <v>620.688051697364</v>
+        <v>176.578687309847</v>
       </c>
       <c r="H35" t="n">
-        <v>975.723576518832</v>
+        <v>177.483004227386</v>
       </c>
       <c r="I35" t="n">
         <v>47</v>
       </c>
       <c r="J35" t="n">
-        <v>129.463440747857</v>
+        <v>127.469344084558</v>
       </c>
       <c r="K35" t="s">
         <v>55</v>
@@ -55532,31 +55532,31 @@
         <v>44866</v>
       </c>
       <c r="B36" t="n">
-        <v>224.90432463097</v>
+        <v>155.144442463669</v>
       </c>
       <c r="C36" t="n">
-        <v>142.152267439018</v>
+        <v>155.102903351155</v>
       </c>
       <c r="D36" t="s">
         <v>40</v>
       </c>
       <c r="E36" t="n">
-        <v>0.440369790964005</v>
+        <v>153.142328447507</v>
       </c>
       <c r="F36" t="n">
-        <v>0.01</v>
+        <v>152.501317727555</v>
       </c>
       <c r="G36" t="n">
-        <v>558.425615422246</v>
+        <v>157.317022223006</v>
       </c>
       <c r="H36" t="n">
-        <v>894.430142203958</v>
+        <v>158.015171936546</v>
       </c>
       <c r="I36" t="n">
         <v>45</v>
       </c>
       <c r="J36" t="n">
-        <v>97.1522674390177</v>
+        <v>110.102903351155</v>
       </c>
       <c r="K36" t="s">
         <v>55</v>
@@ -55567,31 +55567,31 @@
         <v>44896</v>
       </c>
       <c r="B37" t="n">
-        <v>214.194271136395</v>
+        <v>134.878205630036</v>
       </c>
       <c r="C37" t="n">
-        <v>132.543556500772</v>
+        <v>134.909605458851</v>
       </c>
       <c r="D37" t="s">
         <v>40</v>
       </c>
       <c r="E37" t="n">
-        <v>0.01</v>
+        <v>133.017239299382</v>
       </c>
       <c r="F37" t="n">
-        <v>0.01</v>
+        <v>132.419876195405</v>
       </c>
       <c r="G37" t="n">
-        <v>540.067796426657</v>
+        <v>136.765221457929</v>
       </c>
       <c r="H37" t="n">
-        <v>881.520179738333</v>
+        <v>137.561224855457</v>
       </c>
       <c r="I37" t="n">
         <v>36</v>
       </c>
       <c r="J37" t="n">
-        <v>96.5435565007718</v>
+        <v>98.9096054588505</v>
       </c>
       <c r="K37" t="s">
         <v>55</v>
@@ -55602,31 +55602,31 @@
         <v>44927</v>
       </c>
       <c r="B38" t="n">
-        <v>257.43714646739</v>
+        <v>201.979646896471</v>
       </c>
       <c r="C38" t="n">
-        <v>170.418569867081</v>
+        <v>202.010955586244</v>
       </c>
       <c r="D38" t="s">
         <v>40</v>
       </c>
       <c r="E38" t="n">
-        <v>1.88338931168551</v>
+        <v>199.693819944236</v>
       </c>
       <c r="F38" t="n">
-        <v>0.01</v>
+        <v>198.961743257586</v>
       </c>
       <c r="G38" t="n">
-        <v>638.825785783873</v>
+        <v>204.280208683211</v>
       </c>
       <c r="H38" t="n">
-        <v>992.675102003998</v>
+        <v>205.252789465629</v>
       </c>
       <c r="I38" t="n">
         <v>55</v>
       </c>
       <c r="J38" t="n">
-        <v>115.418569867081</v>
+        <v>147.010955586244</v>
       </c>
       <c r="K38" t="s">
         <v>55</v>
@@ -55637,31 +55637,31 @@
         <v>44958</v>
       </c>
       <c r="B39" t="n">
-        <v>271.50202430972</v>
+        <v>213.587260794218</v>
       </c>
       <c r="C39" t="n">
-        <v>182.14137646567</v>
+        <v>213.577202139706</v>
       </c>
       <c r="D39" t="s">
         <v>40</v>
       </c>
       <c r="E39" t="n">
-        <v>2.72328403459646</v>
+        <v>211.268019857844</v>
       </c>
       <c r="F39" t="n">
-        <v>0.01</v>
+        <v>210.548016133856</v>
       </c>
       <c r="G39" t="n">
-        <v>667.986073702294</v>
+        <v>216.092080582774</v>
       </c>
       <c r="H39" t="n">
-        <v>1039.50592096143</v>
+        <v>216.910186559115</v>
       </c>
       <c r="I39" t="n">
         <v>52</v>
       </c>
       <c r="J39" t="n">
-        <v>130.14137646567</v>
+        <v>161.577202139706</v>
       </c>
       <c r="K39" t="s">
         <v>55</v>
@@ -55672,31 +55672,31 @@
         <v>44986</v>
       </c>
       <c r="B40" t="n">
-        <v>316.585357103246</v>
+        <v>241.163585513052</v>
       </c>
       <c r="C40" t="n">
-        <v>219.049470628247</v>
+        <v>241.164481961355</v>
       </c>
       <c r="D40" t="s">
         <v>40</v>
       </c>
       <c r="E40" t="n">
-        <v>8.63185833574447</v>
+        <v>238.632113854281</v>
       </c>
       <c r="F40" t="n">
-        <v>0.01</v>
+        <v>237.831777234495</v>
       </c>
       <c r="G40" t="n">
-        <v>754.951217921937</v>
+        <v>243.836388828457</v>
       </c>
       <c r="H40" t="n">
-        <v>1172.998728107</v>
+        <v>244.705379976154</v>
       </c>
       <c r="I40" t="n">
         <v>51</v>
       </c>
       <c r="J40" t="n">
-        <v>168.049470628247</v>
+        <v>190.164481961355</v>
       </c>
       <c r="K40" t="s">
         <v>55</v>
@@ -55707,31 +55707,31 @@
         <v>45017</v>
       </c>
       <c r="B41" t="n">
-        <v>279.87624030052</v>
+        <v>184.560490492092</v>
       </c>
       <c r="C41" t="n">
-        <v>177.393825844407</v>
+        <v>184.502447741161</v>
       </c>
       <c r="D41" t="s">
         <v>40</v>
       </c>
       <c r="E41" t="n">
-        <v>1.15966970630049</v>
+        <v>182.386714314703</v>
       </c>
       <c r="F41" t="n">
-        <v>0.01</v>
+        <v>181.702459636373</v>
       </c>
       <c r="G41" t="n">
-        <v>698.07378265771</v>
+        <v>186.955614900427</v>
       </c>
       <c r="H41" t="n">
-        <v>1103.01547449631</v>
+        <v>187.716624627818</v>
       </c>
       <c r="I41" t="n">
         <v>56</v>
       </c>
       <c r="J41" t="n">
-        <v>121.393825844407</v>
+        <v>128.502447741161</v>
       </c>
       <c r="K41" t="s">
         <v>55</v>
@@ -55742,31 +55742,31 @@
         <v>45047</v>
       </c>
       <c r="B42" t="n">
-        <v>314.221950513929</v>
+        <v>179.819964223494</v>
       </c>
       <c r="C42" t="n">
-        <v>210.050287853905</v>
+        <v>179.848421416831</v>
       </c>
       <c r="D42" t="s">
         <v>40</v>
       </c>
       <c r="E42" t="n">
-        <v>4.62035566367554</v>
+        <v>177.66246061672</v>
       </c>
       <c r="F42" t="n">
-        <v>0.01</v>
+        <v>176.971985395418</v>
       </c>
       <c r="G42" t="n">
-        <v>751.973939678658</v>
+        <v>181.989937510203</v>
       </c>
       <c r="H42" t="n">
-        <v>1199.08427641912</v>
+        <v>182.907988691278</v>
       </c>
       <c r="I42" t="n">
         <v>53</v>
       </c>
       <c r="J42" t="n">
-        <v>157.050287853905</v>
+        <v>126.848421416831</v>
       </c>
       <c r="K42" t="s">
         <v>55</v>
@@ -55777,31 +55777,31 @@
         <v>45078</v>
       </c>
       <c r="B43" t="n">
-        <v>330.214218308607</v>
+        <v>197.818967403252</v>
       </c>
       <c r="C43" t="n">
-        <v>229.118835358097</v>
+        <v>197.867351233362</v>
       </c>
       <c r="D43" t="s">
         <v>40</v>
       </c>
       <c r="E43" t="n">
-        <v>5.04491058297535</v>
+        <v>195.574171902996</v>
       </c>
       <c r="F43" t="n">
-        <v>0.01</v>
+        <v>194.849692844476</v>
       </c>
       <c r="G43" t="n">
-        <v>776.662317607009</v>
+        <v>200.113275867171</v>
       </c>
       <c r="H43" t="n">
-        <v>1245.92572556804</v>
+        <v>201.07589797074</v>
       </c>
       <c r="I43" t="n">
         <v>59</v>
       </c>
       <c r="J43" t="n">
-        <v>170.118835358097</v>
+        <v>138.867351233362</v>
       </c>
       <c r="K43" t="s">
         <v>55</v>
@@ -55812,31 +55812,31 @@
         <v>45108</v>
       </c>
       <c r="B44" t="n">
-        <v>351.102467635119</v>
+        <v>211.992918564298</v>
       </c>
       <c r="C44" t="n">
-        <v>248.824529010317</v>
+        <v>211.954028449235</v>
       </c>
       <c r="D44" t="s">
         <v>40</v>
       </c>
       <c r="E44" t="n">
-        <v>7.26230912166398</v>
+        <v>209.645649031961</v>
       </c>
       <c r="F44" t="n">
-        <v>0.01</v>
+        <v>208.829632650702</v>
       </c>
       <c r="G44" t="n">
-        <v>826.129940690758</v>
+        <v>214.458588945258</v>
       </c>
       <c r="H44" t="n">
-        <v>1324.80772741892</v>
+        <v>215.966804991102</v>
       </c>
       <c r="I44" t="n">
         <v>50</v>
       </c>
       <c r="J44" t="n">
-        <v>198.824529010317</v>
+        <v>161.954028449235</v>
       </c>
       <c r="K44" t="s">
         <v>55</v>
@@ -55847,31 +55847,31 @@
         <v>45139</v>
       </c>
       <c r="B45" t="n">
-        <v>331.622298669885</v>
+        <v>207.156917974389</v>
       </c>
       <c r="C45" t="n">
-        <v>226.342096808342</v>
+        <v>207.17996861051</v>
       </c>
       <c r="D45" t="s">
         <v>40</v>
       </c>
       <c r="E45" t="n">
-        <v>2.8873337821149</v>
+        <v>204.898559731947</v>
       </c>
       <c r="F45" t="n">
-        <v>0.01</v>
+        <v>204.091844000077</v>
       </c>
       <c r="G45" t="n">
-        <v>803.5104644494</v>
+        <v>209.460055780495</v>
       </c>
       <c r="H45" t="n">
-        <v>1277.03586254665</v>
+        <v>210.385426104945</v>
       </c>
       <c r="I45" t="n">
         <v>64</v>
       </c>
       <c r="J45" t="n">
-        <v>162.342096808342</v>
+        <v>143.17996861051</v>
       </c>
       <c r="K45" t="s">
         <v>55</v>
@@ -55882,31 +55882,31 @@
         <v>45170</v>
       </c>
       <c r="B46" t="n">
-        <v>313.978812570262</v>
+        <v>197.627297474479</v>
       </c>
       <c r="C46" t="n">
-        <v>203.433923597203</v>
+        <v>197.563176758732</v>
       </c>
       <c r="D46" t="s">
         <v>40</v>
       </c>
       <c r="E46" t="n">
-        <v>0.706923831204573</v>
+        <v>195.333739328658</v>
       </c>
       <c r="F46" t="n">
-        <v>0.01</v>
+        <v>194.625592093395</v>
       </c>
       <c r="G46" t="n">
-        <v>787.515463648642</v>
+        <v>200.061039492112</v>
       </c>
       <c r="H46" t="n">
-        <v>1262.38762424454</v>
+        <v>200.848243906843</v>
       </c>
       <c r="I46" t="n">
         <v>49</v>
       </c>
       <c r="J46" t="n">
-        <v>154.433923597203</v>
+        <v>148.563176758732</v>
       </c>
       <c r="K46" t="s">
         <v>55</v>
@@ -55917,31 +55917,31 @@
         <v>45200</v>
       </c>
       <c r="B47" t="n">
-        <v>291.033265403014</v>
+        <v>174.468211820105</v>
       </c>
       <c r="C47" t="n">
-        <v>179.214109578255</v>
+        <v>174.469501027415</v>
       </c>
       <c r="D47" t="s">
         <v>40</v>
       </c>
       <c r="E47" t="n">
-        <v>0.01</v>
+        <v>172.316578005634</v>
       </c>
       <c r="F47" t="n">
-        <v>0.01</v>
+        <v>171.636580555607</v>
       </c>
       <c r="G47" t="n">
-        <v>737.866455100772</v>
+        <v>176.743208247993</v>
       </c>
       <c r="H47" t="n">
-        <v>1174.5082738959</v>
+        <v>177.4831625199</v>
       </c>
       <c r="I47" t="n">
         <v>59</v>
       </c>
       <c r="J47" t="n">
-        <v>120.214109578255</v>
+        <v>115.469501027415</v>
       </c>
       <c r="K47" t="s">
         <v>55</v>
@@ -55952,31 +55952,31 @@
         <v>45231</v>
       </c>
       <c r="B48" t="n">
-        <v>259.969760038467</v>
+        <v>155.149514081652</v>
       </c>
       <c r="C48" t="n">
-        <v>150.684503151041</v>
+        <v>155.172460815226</v>
       </c>
       <c r="D48" t="s">
         <v>40</v>
       </c>
       <c r="E48" t="n">
-        <v>0.01</v>
+        <v>153.128375533414</v>
       </c>
       <c r="F48" t="n">
-        <v>0.01</v>
+        <v>152.501456107737</v>
       </c>
       <c r="G48" t="n">
-        <v>689.841874121285</v>
+        <v>157.162097400905</v>
       </c>
       <c r="H48" t="n">
-        <v>1125.11451128208</v>
+        <v>158.015312796159</v>
       </c>
       <c r="I48" t="n">
         <v>59</v>
       </c>
       <c r="J48" t="n">
-        <v>91.6845031510405</v>
+        <v>96.1724608152262</v>
       </c>
       <c r="K48" t="s">
         <v>55</v>
@@ -55987,31 +55987,31 @@
         <v>45261</v>
       </c>
       <c r="B49" t="n">
-        <v>249.249667948476</v>
+        <v>134.890612463069</v>
       </c>
       <c r="C49" t="n">
-        <v>137.825564134453</v>
+        <v>134.909726820772</v>
       </c>
       <c r="D49" t="s">
         <v>40</v>
       </c>
       <c r="E49" t="n">
-        <v>0.01</v>
+        <v>133.017359807131</v>
       </c>
       <c r="F49" t="n">
-        <v>0.01</v>
+        <v>132.419996432258</v>
       </c>
       <c r="G49" t="n">
-        <v>665.624883367856</v>
+        <v>136.765343651637</v>
       </c>
       <c r="H49" t="n">
-        <v>1099.32220020849</v>
+        <v>137.561347404247</v>
       </c>
       <c r="I49" t="n">
         <v>38</v>
       </c>
       <c r="J49" t="n">
-        <v>99.8255641344534</v>
+        <v>96.9097268207725</v>
       </c>
       <c r="K49" t="s">
         <v>55</v>
@@ -56022,31 +56022,31 @@
         <v>45292</v>
       </c>
       <c r="B50" t="n">
-        <v>293.479605202428</v>
+        <v>201.989684932707</v>
       </c>
       <c r="C50" t="n">
-        <v>175.145518372431</v>
+        <v>202.011137300298</v>
       </c>
       <c r="D50" t="s">
         <v>40</v>
       </c>
       <c r="E50" t="n">
-        <v>0.01</v>
+        <v>199.694000613123</v>
       </c>
       <c r="F50" t="n">
-        <v>0.01</v>
+        <v>198.961923595004</v>
       </c>
       <c r="G50" t="n">
-        <v>767.136462625305</v>
+        <v>204.280391415041</v>
       </c>
       <c r="H50" t="n">
-        <v>1228.58105423594</v>
+        <v>205.252972631936</v>
       </c>
       <c r="I50" t="n">
         <v>61</v>
       </c>
       <c r="J50" t="n">
-        <v>114.145518372431</v>
+        <v>141.011137300298</v>
       </c>
       <c r="K50" t="s">
         <v>55</v>
@@ -56057,31 +56057,31 @@
         <v>45323</v>
       </c>
       <c r="B51" t="n">
-        <v>307.993131214997</v>
+        <v>213.511132059963</v>
       </c>
       <c r="C51" t="n">
-        <v>182.135126974981</v>
+        <v>213.454256309022</v>
       </c>
       <c r="D51" t="s">
         <v>40</v>
       </c>
       <c r="E51" t="n">
-        <v>0.01</v>
+        <v>211.194657713227</v>
       </c>
       <c r="F51" t="n">
-        <v>0.01</v>
+        <v>210.441776018691</v>
       </c>
       <c r="G51" t="n">
-        <v>809.336938053192</v>
+        <v>215.892321135437</v>
       </c>
       <c r="H51" t="n">
-        <v>1284.93277510003</v>
+        <v>216.910380169134</v>
       </c>
       <c r="I51" t="n">
         <v>61</v>
       </c>
       <c r="J51" t="n">
-        <v>121.135126974981</v>
+        <v>152.454256309022</v>
       </c>
       <c r="K51" t="s">
         <v>55</v>
@@ -56092,31 +56092,31 @@
         <v>45352</v>
       </c>
       <c r="B52" t="n">
-        <v>354.208928318096</v>
+        <v>241.173566500358</v>
       </c>
       <c r="C52" t="n">
-        <v>223.630350619542</v>
+        <v>241.165516784574</v>
       </c>
       <c r="D52" t="s">
         <v>40</v>
       </c>
       <c r="E52" t="n">
-        <v>0.396944619598174</v>
+        <v>238.632329641077</v>
       </c>
       <c r="F52" t="n">
-        <v>0.01</v>
+        <v>237.831992659129</v>
       </c>
       <c r="G52" t="n">
-        <v>895.181925265945</v>
+        <v>243.836606955585</v>
       </c>
       <c r="H52" t="n">
-        <v>1429.12407522532</v>
+        <v>244.705598491621</v>
       </c>
       <c r="I52" t="n">
         <v>80</v>
       </c>
       <c r="J52" t="n">
-        <v>143.630350619542</v>
+        <v>161.165516784574</v>
       </c>
       <c r="K52" t="s">
         <v>55</v>
@@ -56127,31 +56127,31 @@
         <v>45383</v>
       </c>
       <c r="B53" t="n">
-        <v>315.411779332908</v>
+        <v>184.589193254325</v>
       </c>
       <c r="C53" t="n">
-        <v>185.505159097995</v>
+        <v>184.617097944173</v>
       </c>
       <c r="D53" t="s">
         <v>40</v>
       </c>
       <c r="E53" t="n">
-        <v>0.01</v>
+        <v>182.402258373476</v>
       </c>
       <c r="F53" t="n">
-        <v>0.01</v>
+        <v>181.702624390049</v>
       </c>
       <c r="G53" t="n">
-        <v>836.638723190219</v>
+        <v>186.78673595154</v>
       </c>
       <c r="H53" t="n">
-        <v>1351.48775046162</v>
+        <v>187.716792085886</v>
       </c>
       <c r="I53" t="n">
         <v>62</v>
       </c>
       <c r="J53" t="n">
-        <v>123.505159097995</v>
+        <v>122.617097944173</v>
       </c>
       <c r="K53" t="s">
         <v>55</v>
@@ -56162,31 +56162,31 @@
         <v>45413</v>
       </c>
       <c r="B54" t="n">
-        <v>352.342575693239</v>
+        <v>179.86945737545</v>
       </c>
       <c r="C54" t="n">
-        <v>215.783223744133</v>
+        <v>179.849289505461</v>
       </c>
       <c r="D54" t="s">
         <v>40</v>
       </c>
       <c r="E54" t="n">
-        <v>0.01</v>
+        <v>177.662621411407</v>
       </c>
       <c r="F54" t="n">
-        <v>0.01</v>
+        <v>176.972145877342</v>
       </c>
       <c r="G54" t="n">
-        <v>908.33177268347</v>
+        <v>182.156962166215</v>
       </c>
       <c r="H54" t="n">
-        <v>1466.26940433156</v>
+        <v>182.908151842449</v>
       </c>
       <c r="I54" t="n">
         <v>54</v>
       </c>
       <c r="J54" t="n">
-        <v>161.783223744133</v>
+        <v>125.849289505461</v>
       </c>
       <c r="K54" t="s">
         <v>55</v>
@@ -56197,31 +56197,31 @@
         <v>45444</v>
       </c>
       <c r="B55" t="n">
-        <v>368.856066362809</v>
+        <v>197.842368645175</v>
       </c>
       <c r="C55" t="n">
-        <v>233.421217784596</v>
+        <v>197.867529220633</v>
       </c>
       <c r="D55" t="s">
         <v>40</v>
       </c>
       <c r="E55" t="n">
-        <v>0.0544425912058255</v>
+        <v>195.574348855872</v>
       </c>
       <c r="F55" t="n">
-        <v>0.01</v>
+        <v>194.849869469299</v>
       </c>
       <c r="G55" t="n">
-        <v>931.697010708127</v>
+        <v>200.113454861729</v>
       </c>
       <c r="H55" t="n">
-        <v>1508.56341546203</v>
+        <v>201.076077395298</v>
       </c>
       <c r="I55" t="n">
         <v>62</v>
       </c>
       <c r="J55" t="n">
-        <v>171.421217784596</v>
+        <v>135.867529220633</v>
       </c>
       <c r="K55" t="s">
         <v>55</v>
@@ -56232,31 +56232,31 @@
         <v>45474</v>
       </c>
       <c r="B56" t="n">
-        <v>390.380096448577</v>
+        <v>211.964005241854</v>
       </c>
       <c r="C56" t="n">
-        <v>249.203666382141</v>
+        <v>211.953452343612</v>
       </c>
       <c r="D56" t="s">
         <v>40</v>
       </c>
       <c r="E56" t="n">
-        <v>0.162556313287157</v>
+        <v>209.579817144241</v>
       </c>
       <c r="F56" t="n">
-        <v>0.01</v>
+        <v>208.829821896808</v>
       </c>
       <c r="G56" t="n">
-        <v>988.817570045957</v>
+        <v>214.277724254077</v>
       </c>
       <c r="H56" t="n">
-        <v>1562.89759611692</v>
+        <v>215.273791997062</v>
       </c>
       <c r="I56" t="n">
         <v>62</v>
       </c>
       <c r="J56" t="n">
-        <v>187.203666382141</v>
+        <v>149.953452343612</v>
       </c>
       <c r="K56" t="s">
         <v>55</v>
@@ -56267,31 +56267,31 @@
         <v>45505</v>
       </c>
       <c r="B57" t="n">
-        <v>369.953522844935</v>
+        <v>207.173471721288</v>
       </c>
       <c r="C57" t="n">
-        <v>228.620683446819</v>
+        <v>207.180154973599</v>
       </c>
       <c r="D57" t="s">
         <v>40</v>
       </c>
       <c r="E57" t="n">
-        <v>0.01</v>
+        <v>204.898745066107</v>
       </c>
       <c r="F57" t="n">
-        <v>0.01</v>
+        <v>204.092028969033</v>
       </c>
       <c r="G57" t="n">
-        <v>951.770687182088</v>
+        <v>209.657195436286</v>
       </c>
       <c r="H57" t="n">
-        <v>1505.22632980214</v>
+        <v>210.463039988447</v>
       </c>
       <c r="I57" t="n">
         <v>70</v>
       </c>
       <c r="J57" t="n">
-        <v>158.620683446819</v>
+        <v>137.180154973599</v>
       </c>
       <c r="K57" t="s">
         <v>55</v>
@@ -56302,31 +56302,31 @@
         <v>45536</v>
       </c>
       <c r="B58" t="n">
-        <v>351.612026663283</v>
+        <v>197.626828190269</v>
       </c>
       <c r="C58" t="n">
-        <v>208.992517960854</v>
+        <v>197.56335450765</v>
       </c>
       <c r="D58" t="s">
         <v>40</v>
       </c>
       <c r="E58" t="n">
-        <v>0.01</v>
+        <v>195.349831549724</v>
       </c>
       <c r="F58" t="n">
-        <v>0.01</v>
+        <v>194.625768515883</v>
       </c>
       <c r="G58" t="n">
-        <v>917.014489132805</v>
+        <v>200.061218361172</v>
       </c>
       <c r="H58" t="n">
-        <v>1496.53305306468</v>
+        <v>200.848423127467</v>
       </c>
       <c r="I58" t="n">
         <v>88</v>
       </c>
       <c r="J58" t="n">
-        <v>120.992517960854</v>
+        <v>109.56335450765</v>
       </c>
       <c r="K58" t="s">
         <v>55</v>
@@ -56337,31 +56337,31 @@
         <v>45566</v>
       </c>
       <c r="B59" t="n">
-        <v>325.0322923352</v>
+        <v>174.372667764777</v>
       </c>
       <c r="C59" t="n">
-        <v>184.868873180142</v>
+        <v>174.248724888094</v>
       </c>
       <c r="D59" t="s">
         <v>40</v>
       </c>
       <c r="E59" t="n">
-        <v>0.01</v>
+        <v>172.316733977303</v>
       </c>
       <c r="F59" t="n">
-        <v>0.01</v>
+        <v>171.636736219223</v>
       </c>
       <c r="G59" t="n">
-        <v>858.380253759371</v>
+        <v>176.562537006649</v>
       </c>
       <c r="H59" t="n">
-        <v>1417.17190211818</v>
+        <v>177.483320812556</v>
       </c>
       <c r="I59" t="n">
         <v>74</v>
       </c>
       <c r="J59" t="n">
-        <v>110.868873180142</v>
+        <v>100.248724888094</v>
       </c>
       <c r="K59" t="s">
         <v>55</v>
@@ -56372,31 +56372,31 @@
         <v>45597</v>
       </c>
       <c r="B60" t="n">
-        <v>292.488693908869</v>
+        <v>155.184812754749</v>
       </c>
       <c r="C60" t="n">
-        <v>147.781636962836</v>
+        <v>155.173256468845</v>
       </c>
       <c r="D60" t="s">
         <v>40</v>
       </c>
       <c r="E60" t="n">
-        <v>0.01</v>
+        <v>153.199042864939</v>
       </c>
       <c r="F60" t="n">
-        <v>0.01</v>
+        <v>152.501594488044</v>
       </c>
       <c r="G60" t="n">
-        <v>793.807358296917</v>
+        <v>157.162237879839</v>
       </c>
       <c r="H60" t="n">
-        <v>1345.92791782252</v>
+        <v>158.015453655898</v>
       </c>
       <c r="I60" t="n">
         <v>115</v>
       </c>
       <c r="J60" t="n">
-        <v>32.7816369628361</v>
+        <v>40.1732564688453</v>
       </c>
       <c r="K60" t="s">
         <v>55</v>
@@ -56407,31 +56407,31 @@
         <v>45627</v>
       </c>
       <c r="B61" t="n">
-        <v>281.301897719045</v>
+        <v>134.847307294026</v>
       </c>
       <c r="C61" t="n">
-        <v>135.456048624911</v>
+        <v>134.811984867026</v>
       </c>
       <c r="D61" t="s">
         <v>40</v>
       </c>
       <c r="E61" t="n">
-        <v>0.01</v>
+        <v>133.004347263467</v>
       </c>
       <c r="F61" t="n">
-        <v>0.01</v>
+        <v>132.420116669219</v>
       </c>
       <c r="G61" t="n">
-        <v>776.842212615054</v>
+        <v>136.765465845455</v>
       </c>
       <c r="H61" t="n">
-        <v>1334.22068609738</v>
+        <v>137.561469953146</v>
       </c>
       <c r="I61" t="n">
         <v>87</v>
       </c>
       <c r="J61" t="n">
-        <v>48.4560486249106</v>
+        <v>47.8119848670261</v>
       </c>
       <c r="K61" t="s">
         <v>55</v>
@@ -56442,31 +56442,31 @@
         <v>45658</v>
       </c>
       <c r="B62" t="n">
-        <v>326.395155089632</v>
+        <v>202.006122046542</v>
       </c>
       <c r="C62" t="n">
-        <v>169.354265191719</v>
+        <v>202.012067577407</v>
       </c>
       <c r="D62" t="s">
         <v>40</v>
       </c>
       <c r="E62" t="n">
-        <v>0.01</v>
+        <v>199.694181282173</v>
       </c>
       <c r="F62" t="n">
-        <v>0.01</v>
+        <v>198.962103932584</v>
       </c>
       <c r="G62" t="n">
-        <v>885.443499736081</v>
+        <v>204.457357468873</v>
       </c>
       <c r="H62" t="n">
-        <v>1423.5962052164</v>
+        <v>205.253155798408</v>
       </c>
       <c r="I62" t="n">
         <v>152</v>
       </c>
       <c r="J62" t="n">
-        <v>17.354265191719</v>
+        <v>50.0120675774067</v>
       </c>
       <c r="K62" t="s">
         <v>55</v>
@@ -56477,31 +56477,31 @@
         <v>45689</v>
       </c>
       <c r="B63" t="n">
-        <v>340.716262507561</v>
+        <v>213.51325420339</v>
       </c>
       <c r="C63" t="n">
-        <v>178.297000468592</v>
+        <v>213.454448370585</v>
       </c>
       <c r="D63" t="s">
         <v>40</v>
       </c>
       <c r="E63" t="n">
-        <v>0.01</v>
+        <v>211.194848755516</v>
       </c>
       <c r="F63" t="n">
-        <v>0.01</v>
+        <v>210.441966720156</v>
       </c>
       <c r="G63" t="n">
-        <v>910.442269863973</v>
+        <v>215.892514290745</v>
       </c>
       <c r="H63" t="n">
-        <v>1521.00381918817</v>
+        <v>216.910573779326</v>
       </c>
       <c r="I63" t="n">
         <v>133</v>
       </c>
       <c r="J63" t="n">
-        <v>45.2970004685922</v>
+        <v>80.4544483705852</v>
       </c>
       <c r="K63" t="s">
         <v>55</v>
@@ -56512,31 +56512,31 @@
         <v>45717</v>
       </c>
       <c r="B64" t="n">
-        <v>388.616298458326</v>
+        <v>241.134560564748</v>
       </c>
       <c r="C64" t="n">
-        <v>217.897046146865</v>
+        <v>241.078373031952</v>
       </c>
       <c r="D64" t="s">
         <v>40</v>
       </c>
       <c r="E64" t="n">
-        <v>0.01</v>
+        <v>238.632545428069</v>
       </c>
       <c r="F64" t="n">
-        <v>0.01</v>
+        <v>237.832208083958</v>
       </c>
       <c r="G64" t="n">
-        <v>1018.97234437957</v>
+        <v>243.643762779455</v>
       </c>
       <c r="H64" t="n">
-        <v>1696.46359137388</v>
+        <v>244.705817007283</v>
       </c>
       <c r="I64" t="n">
         <v>158</v>
       </c>
       <c r="J64" t="n">
-        <v>59.8970461468651</v>
+        <v>83.0783730319516</v>
       </c>
       <c r="K64" t="s">
         <v>55</v>
@@ -56547,31 +56547,31 @@
         <v>45748</v>
       </c>
       <c r="B65" t="n">
-        <v>350.074220810691</v>
+        <v>184.588704718108</v>
       </c>
       <c r="C65" t="n">
-        <v>186.785283703132</v>
+        <v>184.61726401405</v>
       </c>
       <c r="D65" t="s">
         <v>40</v>
       </c>
       <c r="E65" t="n">
-        <v>0.01</v>
+        <v>182.402423444183</v>
       </c>
       <c r="F65" t="n">
-        <v>0.01</v>
+        <v>181.702789143873</v>
       </c>
       <c r="G65" t="n">
-        <v>942.594301760611</v>
+        <v>186.786902994401</v>
       </c>
       <c r="H65" t="n">
-        <v>1600.30198159203</v>
+        <v>187.716959544104</v>
       </c>
       <c r="I65" t="n">
         <v>133</v>
       </c>
       <c r="J65" t="n">
-        <v>53.7852837031317</v>
+        <v>51.6172640140501</v>
       </c>
       <c r="K65" t="s">
         <v>55</v>
@@ -56582,31 +56582,31 @@
         <v>45778</v>
       </c>
       <c r="B66" t="n">
-        <v>384.545064692878</v>
+        <v>179.76416870872</v>
       </c>
       <c r="C66" t="n">
-        <v>215.812926428558</v>
+        <v>179.735749164782</v>
       </c>
       <c r="D66" t="s">
         <v>40</v>
       </c>
       <c r="E66" t="n">
-        <v>0.01</v>
+        <v>177.647604331539</v>
       </c>
       <c r="F66" t="n">
-        <v>0.01</v>
+        <v>176.97230635941</v>
       </c>
       <c r="G66" t="n">
-        <v>1011.87255104774</v>
+        <v>181.973546508663</v>
       </c>
       <c r="H66" t="n">
-        <v>1718.66641572465</v>
+        <v>182.836135605498</v>
       </c>
       <c r="I66" t="n">
         <v>179</v>
       </c>
       <c r="J66" t="n">
-        <v>36.8129264285583</v>
+        <v>0.735749164781765</v>
       </c>
       <c r="K66" t="s">
         <v>55</v>
@@ -56617,31 +56617,31 @@
         <v>45809</v>
       </c>
       <c r="B67" t="n">
-        <v>401.857674082218</v>
+        <v>197.822020259471</v>
       </c>
       <c r="C67" t="n">
-        <v>232.244990237319</v>
+        <v>197.789317829538</v>
       </c>
       <c r="D67" t="s">
         <v>40</v>
       </c>
       <c r="E67" t="n">
-        <v>0.01</v>
+        <v>195.574525808908</v>
       </c>
       <c r="F67" t="n">
-        <v>0.01</v>
+        <v>194.850046094281</v>
       </c>
       <c r="G67" t="n">
-        <v>1065.05420200961</v>
+        <v>200.096104754571</v>
       </c>
       <c r="H67" t="n">
-        <v>1728.07536024039</v>
+        <v>201.000577216115</v>
       </c>
       <c r="I67" t="n">
         <v>160</v>
       </c>
       <c r="J67" t="n">
-        <v>72.2449902373191</v>
+        <v>37.7893178295375</v>
       </c>
       <c r="K67" t="s">
         <v>55</v>
@@ -56652,31 +56652,31 @@
         <v>45839</v>
       </c>
       <c r="B68" t="n">
-        <v>423.020019233326</v>
+        <v>211.905888305048</v>
       </c>
       <c r="C68" t="n">
-        <v>248.24829782261</v>
+        <v>211.953642999988</v>
       </c>
       <c r="D68" t="s">
         <v>40</v>
       </c>
       <c r="E68" t="n">
-        <v>0.01</v>
+        <v>209.580006730045</v>
       </c>
       <c r="F68" t="n">
-        <v>0.01</v>
+        <v>208.830011143086</v>
       </c>
       <c r="G68" t="n">
-        <v>1091.60380568756</v>
+        <v>214.259777077777</v>
       </c>
       <c r="H68" t="n">
-        <v>1813.38193453102</v>
+        <v>215.195678040134</v>
       </c>
       <c r="I68" t="n">
         <v>200</v>
       </c>
       <c r="J68" t="n">
-        <v>48.2482978226097</v>
+        <v>11.9536429999878</v>
       </c>
       <c r="K68" t="s">
         <v>55</v>
@@ -56687,31 +56687,31 @@
         <v>45870</v>
       </c>
       <c r="B69" t="n">
-        <v>402.554537584166</v>
+        <v>207.139420500372</v>
       </c>
       <c r="C69" t="n">
-        <v>225.758717501619</v>
+        <v>207.059061785643</v>
       </c>
       <c r="D69" t="s">
         <v>40</v>
       </c>
       <c r="E69" t="n">
-        <v>0.01</v>
+        <v>204.898930400433</v>
       </c>
       <c r="F69" t="n">
-        <v>0.01</v>
+        <v>204.092213938156</v>
       </c>
       <c r="G69" t="n">
-        <v>1062.60845419656</v>
+        <v>209.47836512884</v>
       </c>
       <c r="H69" t="n">
-        <v>1752.90090821757</v>
+        <v>210.463227822415</v>
       </c>
       <c r="I69" t="n">
         <v>197</v>
       </c>
       <c r="J69" t="n">
-        <v>28.7587175016187</v>
+        <v>10.0590617856427</v>
       </c>
       <c r="K69" t="s">
         <v>55</v>
@@ -56722,31 +56722,31 @@
         <v>45901</v>
       </c>
       <c r="B70" t="n">
-        <v>383.849095996488</v>
+        <v>197.615041843716</v>
       </c>
       <c r="C70" t="n">
-        <v>206.617128743526</v>
+        <v>197.563532256729</v>
       </c>
       <c r="D70" t="s">
         <v>40</v>
       </c>
       <c r="E70" t="n">
-        <v>0.01</v>
+        <v>195.350008300237</v>
       </c>
       <c r="F70" t="n">
-        <v>0.01</v>
+        <v>194.625944938529</v>
       </c>
       <c r="G70" t="n">
-        <v>1026.55093571547</v>
+        <v>199.886525124082</v>
       </c>
       <c r="H70" t="n">
-        <v>1734.37624986541</v>
+        <v>200.848602348252</v>
       </c>
       <c r="I70" t="n">
         <v>262</v>
       </c>
       <c r="J70" t="n">
-        <v>-55.3828712564744</v>
+        <v>-64.4364677432714</v>
       </c>
       <c r="K70" t="s">
         <v>54</v>
@@ -56757,31 +56757,31 @@
         <v>45931</v>
       </c>
       <c r="B71" t="n">
-        <v>357.014851877188</v>
+        <v>174.45664438471</v>
       </c>
       <c r="C71" t="n">
-        <v>185.027542211268</v>
+        <v>174.396206557789</v>
       </c>
       <c r="D71" t="s">
         <v>40</v>
       </c>
       <c r="E71" t="n">
-        <v>0.01</v>
+        <v>172.301942175392</v>
       </c>
       <c r="F71" t="n">
-        <v>0.01</v>
+        <v>171.636891882979</v>
       </c>
       <c r="G71" t="n">
-        <v>973.205780708415</v>
+        <v>176.74352417281</v>
       </c>
       <c r="H71" t="n">
-        <v>1649.60214416277</v>
+        <v>177.483479105353</v>
       </c>
       <c r="I71" t="n">
         <v>208</v>
       </c>
       <c r="J71" t="n">
-        <v>-22.9724577887317</v>
+        <v>-33.6037934422106</v>
       </c>
       <c r="K71" t="s">
         <v>54</v>
@@ -56792,31 +56792,31 @@
         <v>45962</v>
       </c>
       <c r="B72" t="n">
-        <v>324.003556083228</v>
+        <v>155.135480833604</v>
       </c>
       <c r="C72" t="n">
-        <v>147.659499118101</v>
+        <v>155.067783054557</v>
       </c>
       <c r="D72" t="s">
         <v>40</v>
       </c>
       <c r="E72" t="n">
-        <v>0.01</v>
+        <v>153.128652862438</v>
       </c>
       <c r="F72" t="n">
-        <v>0.01</v>
+        <v>152.501732868476</v>
       </c>
       <c r="G72" t="n">
-        <v>905.897609040585</v>
+        <v>157.162378358898</v>
       </c>
       <c r="H72" t="n">
-        <v>1569.59249325152</v>
+        <v>158.015594515764</v>
       </c>
       <c r="I72" t="n">
         <v>169</v>
       </c>
       <c r="J72" t="n">
-        <v>-21.3405008818991</v>
+        <v>-13.9322169454432</v>
       </c>
       <c r="K72" t="s">
         <v>54</v>
@@ -56827,31 +56827,31 @@
         <v>45992</v>
       </c>
       <c r="B73" t="n">
-        <v>313.223602749473</v>
+        <v>134.917869624658</v>
       </c>
       <c r="C73" t="n">
-        <v>133.242916680287</v>
+        <v>134.910581278851</v>
       </c>
       <c r="D73" t="s">
         <v>40</v>
       </c>
       <c r="E73" t="n">
-        <v>0.01</v>
+        <v>133.017600822956</v>
       </c>
       <c r="F73" t="n">
-        <v>0.01</v>
+        <v>132.420236906289</v>
       </c>
       <c r="G73" t="n">
-        <v>883.778305764362</v>
+        <v>136.910244234441</v>
       </c>
       <c r="H73" t="n">
-        <v>1544.73153781352</v>
+        <v>137.561592502155</v>
       </c>
       <c r="I73" t="n">
         <v>182</v>
       </c>
       <c r="J73" t="n">
-        <v>-48.7570833197125</v>
+        <v>-47.0894187211489</v>
       </c>
       <c r="K73" t="s">
         <v>54</v>
